--- a/output/sample/portfolio_dashboard_sample.xlsx
+++ b/output/sample/portfolio_dashboard_sample.xlsx
@@ -254,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -382,6 +382,12 @@
     </xf>
     <xf numFmtId="2" fontId="23" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -811,7 +817,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>80934.80267948778</v>
+        <v>80948.91581741307</v>
       </c>
       <c r="D5" s="2" t="n"/>
     </row>
@@ -822,7 +828,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>26794.80267948778</v>
+        <v>26808.91581741307</v>
       </c>
       <c r="D6" s="2" t="n"/>
     </row>
@@ -833,7 +839,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>49.49169316492017</v>
+        <v>49.5177610221889</v>
       </c>
       <c r="D7" s="2" t="n"/>
     </row>
@@ -897,7 +903,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>64.77801723311731</v>
+        <v>64.78415805286481</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>65</v>
@@ -909,7 +915,7 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>41.75790478337835</v>
+        <v>41.77116920492907</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>55</v>
@@ -922,7 +928,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>20.58336679884454</v>
+        <v>20.57977816653656</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>25</v>
@@ -934,7 +940,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>24.1498199211525</v>
+        <v>24.14476795526446</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>8</v>
@@ -947,7 +953,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>8.460803908866717</v>
+        <v>8.459328799641117</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>5</v>
@@ -959,7 +965,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>15.53026313713126</v>
+        <v>15.5217931241751</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>11</v>
@@ -972,7 +978,7 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>6.177812059171433</v>
+        <v>6.176734980957511</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>5</v>
@@ -984,7 +990,7 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>10.66366665568281</v>
+        <v>10.66269639765878</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>14</v>
@@ -998,7 +1004,7 @@
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>7.898345502655069</v>
+        <v>7.899573317972592</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>12</v>
@@ -1054,10 +1060,10 @@
         </is>
       </c>
       <c r="B21" s="28" t="n">
-        <v>12433.59985351562</v>
+        <v>12441.60034179688</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>15.3624886227922</v>
+        <v>15.36969361005393</v>
       </c>
       <c r="D21" s="30" t="n"/>
       <c r="E21" s="12" t="inlineStr">
@@ -1076,7 +1082,7 @@
         <v>11547.61339873075</v>
       </c>
       <c r="C22" s="33" t="n">
-        <v>14.26779706186569</v>
+        <v>14.26530952530278</v>
       </c>
       <c r="D22" s="30" t="n"/>
       <c r="E22" s="34" t="inlineStr">
@@ -1095,7 +1101,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>13.23905143133624</v>
+        <v>13.23674325269094</v>
       </c>
       <c r="D23" s="30" t="n"/>
       <c r="E23" s="35" t="inlineStr">
@@ -1111,10 +1117,10 @@
         </is>
       </c>
       <c r="B24" s="32" t="n">
-        <v>9963.177533948419</v>
+        <v>9967.849677611011</v>
       </c>
       <c r="C24" s="33" t="n">
-        <v>12.31012766337849</v>
+        <v>12.31375315772519</v>
       </c>
       <c r="D24" s="30" t="n"/>
       <c r="E24" s="34" t="inlineStr">
@@ -1130,10 +1136,10 @@
         </is>
       </c>
       <c r="B25" s="28" t="n">
-        <v>6883.919906616211</v>
+        <v>6880.860214233398</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>8.505512682692782</v>
+        <v>8.500249996866843</v>
       </c>
       <c r="D25" s="30" t="n"/>
       <c r="E25" s="12" t="inlineStr">
@@ -1148,7 +1154,7 @@
     <row r="27">
       <c r="A27" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 09:47 v2.0</t>
+          <t>Generated 2026-05-04 10:02 v2.0</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1339,7 @@
     <row r="26">
       <c r="A26" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 09:47 v2.0</t>
+          <t>Generated 2026-05-04 10:02 v2.0</t>
         </is>
       </c>
     </row>
@@ -1534,25 +1540,25 @@
         <v>128</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>155.4199981689453</v>
+        <v>155.5200042724609</v>
       </c>
       <c r="J4" s="28" t="n">
         <v>10240</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>12433.59985351562</v>
+        <v>12441.60034179688</v>
       </c>
       <c r="L4" s="29" t="n">
-        <v>15.3624886227922</v>
+        <v>15.36969361005393</v>
       </c>
       <c r="M4" s="29" t="n">
-        <v>23.71558945298844</v>
+        <v>23.72446300453892</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>2193.599853515625</v>
+        <v>2201.600341796875</v>
       </c>
       <c r="O4" s="29" t="n">
-        <v>21.42187356948853</v>
+        <v>21.50000333786011</v>
       </c>
       <c r="P4" s="27" t="inlineStr">
         <is>
@@ -1571,7 +1577,7 @@
       </c>
       <c r="S4" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 09:46</t>
+          <t>2026-05-04 10:01</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1628,10 @@
         <v>11547.61339873075</v>
       </c>
       <c r="L5" s="33" t="n">
-        <v>14.26779706186569</v>
+        <v>14.26530952530278</v>
       </c>
       <c r="M5" s="33" t="n">
-        <v>22.02567733822422</v>
+        <v>22.01974981856225</v>
       </c>
       <c r="N5" s="32" t="n">
         <v>9307.613398730755</v>
@@ -1650,7 +1656,7 @@
       </c>
       <c r="S5" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 09:46</t>
+          <t>2026-05-04 10:01</t>
         </is>
       </c>
     </row>
@@ -1692,25 +1698,25 @@
         <v>570</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>664.2118355965613</v>
+        <v>664.5233118407341</v>
       </c>
       <c r="J6" s="28" t="n">
         <v>8550</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>9963.177533948419</v>
+        <v>9967.849677611011</v>
       </c>
       <c r="L6" s="29" t="n">
-        <v>12.31012766337849</v>
+        <v>12.31375315772519</v>
       </c>
       <c r="M6" s="29" t="n">
-        <v>19.0035573627978</v>
+        <v>19.00735230313095</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>1413.177533948419</v>
+        <v>1417.849677611011</v>
       </c>
       <c r="O6" s="29" t="n">
-        <v>16.52839220992303</v>
+        <v>16.58303716504107</v>
       </c>
       <c r="P6" s="27" t="inlineStr">
         <is>
@@ -1729,7 +1735,7 @@
       </c>
       <c r="S6" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 09:46</t>
+          <t>2026-05-04 10:01</t>
         </is>
       </c>
     </row>
@@ -1771,25 +1777,25 @@
         <v>56</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>76.48799896240234</v>
+        <v>76.45400238037109</v>
       </c>
       <c r="J7" s="32" t="n">
         <v>5040</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>6883.919906616211</v>
+        <v>6880.860214233398</v>
       </c>
       <c r="L7" s="33" t="n">
-        <v>8.505512682692782</v>
+        <v>8.500249996866843</v>
       </c>
       <c r="M7" s="33" t="n">
-        <v>13.13024548448883</v>
+        <v>13.12087746811576</v>
       </c>
       <c r="N7" s="32" t="n">
-        <v>1843.919906616211</v>
+        <v>1840.860214233398</v>
       </c>
       <c r="O7" s="33" t="n">
-        <v>36.58571243286133</v>
+        <v>36.52500425066267</v>
       </c>
       <c r="P7" s="31" t="inlineStr">
         <is>
@@ -1808,7 +1814,7 @@
       </c>
       <c r="S7" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 09:46</t>
+          <t>2026-05-04 10:01</t>
         </is>
       </c>
     </row>
@@ -1850,25 +1856,25 @@
         <v>98</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>118.004997253418</v>
+        <v>118.0950012207031</v>
       </c>
       <c r="J8" s="28" t="n">
         <v>4900</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>5900.249862670898</v>
+        <v>5904.750061035156</v>
       </c>
       <c r="L8" s="29" t="n">
-        <v>7.290126950746573</v>
+        <v>7.294415251161368</v>
       </c>
       <c r="M8" s="29" t="n">
-        <v>11.25401372584703</v>
+        <v>11.25956633596908</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>1000.249862670898</v>
+        <v>1004.750061035156</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>20.41326250348772</v>
+        <v>20.50510328643176</v>
       </c>
       <c r="P8" s="27" t="inlineStr">
         <is>
@@ -1887,7 +1893,7 @@
       </c>
       <c r="S8" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 09:46</t>
+          <t>2026-05-04 10:01</t>
         </is>
       </c>
     </row>
@@ -1938,10 +1944,10 @@
         <v>5699.399871826172</v>
       </c>
       <c r="L9" s="33" t="n">
-        <v>7.041964251641569</v>
+        <v>7.040736511754693</v>
       </c>
       <c r="M9" s="33" t="n">
-        <v>10.8709166356537</v>
+        <v>10.86799106968304</v>
       </c>
       <c r="N9" s="32" t="n">
         <v>1739.399871826172</v>
@@ -1966,7 +1972,7 @@
       </c>
       <c r="S9" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 09:46</t>
+          <t>2026-05-04 10:01</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2023,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>13.23905143133624</v>
+        <v>13.23674325269094</v>
       </c>
       <c r="M10" s="29" t="n">
         <v>64.31917363528412</v>
@@ -2045,7 +2051,7 @@
       </c>
       <c r="S10" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 09:46</t>
+          <t>2026-05-04 10:01</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2102,7 @@
         <v>5944.107150852142</v>
       </c>
       <c r="L11" s="33" t="n">
-        <v>7.344315367508301</v>
+        <v>7.343034913845621</v>
       </c>
       <c r="M11" s="33" t="n">
         <v>35.68082636471589</v>
@@ -2124,7 +2130,7 @@
       </c>
       <c r="S11" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 09:46</t>
+          <t>2026-05-04 10:01</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2181,7 @@
         <v>5000</v>
       </c>
       <c r="L12" s="29" t="n">
-        <v>6.177812059171433</v>
+        <v>6.176734980957511</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>100</v>
@@ -2203,7 +2209,7 @@
       </c>
       <c r="S12" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 09:46</t>
+          <t>2026-05-04 10:02</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2260,7 @@
         <v>6847.734948739668</v>
       </c>
       <c r="L13" s="33" t="n">
-        <v>8.460803908866717</v>
+        <v>8.459328799641117</v>
       </c>
       <c r="M13" s="33" t="n">
         <v>100</v>
@@ -2282,14 +2288,14 @@
       </c>
       <c r="S13" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 09:46</t>
+          <t>2026-05-04 10:02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 09:47 v2.0</t>
+          <t>Generated 2026-05-04 10:02 v2.0</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S39"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2326,7 +2332,9 @@
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2426,15 +2434,25 @@
       </c>
       <c r="Q4" s="11" t="inlineStr">
         <is>
+          <t>VaR 95%</t>
+        </is>
+      </c>
+      <c r="R4" s="11" t="inlineStr">
+        <is>
+          <t>CVaR 95%</t>
+        </is>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
           <t>α (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr">
+      <c r="T4" s="11" t="inlineStr">
         <is>
           <t>β (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="U4" s="11" t="inlineStr">
         <is>
           <t>Period Used</t>
         </is>
@@ -2452,31 +2470,31 @@
         </is>
       </c>
       <c r="C5" s="44" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="D5" s="44" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="E5" s="44" t="n">
-        <v>6.07</v>
+        <v>6.09</v>
       </c>
       <c r="F5" s="44" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
       <c r="G5" s="44" t="n">
-        <v>6.74</v>
+        <v>6.76</v>
       </c>
       <c r="H5" s="44" t="n">
-        <v>7.15</v>
+        <v>7.17</v>
       </c>
       <c r="I5" s="44" t="n">
-        <v>22.18</v>
+        <v>22.21</v>
       </c>
       <c r="J5" s="44" t="n">
-        <v>49.14</v>
+        <v>49.17</v>
       </c>
       <c r="K5" s="44" t="n">
-        <v>45.31</v>
+        <v>45.34</v>
       </c>
       <c r="L5" s="44" t="n">
         <v>7.95</v>
@@ -2493,13 +2511,19 @@
       <c r="P5" s="45" t="n">
         <v>-13.91</v>
       </c>
-      <c r="Q5" s="44" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="R5" s="44" t="n">
+      <c r="Q5" s="45" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="R5" s="45" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="S5" s="44" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T5" s="44" t="n">
         <v>0.15</v>
       </c>
-      <c r="S5" s="43" t="inlineStr">
+      <c r="U5" s="43" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -2558,13 +2582,19 @@
       <c r="P6" s="46" t="n">
         <v>-20.22</v>
       </c>
-      <c r="Q6" s="29" t="n">
+      <c r="Q6" s="46" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="R6" s="46" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="S6" s="29" t="n">
         <v>5.17</v>
       </c>
-      <c r="R6" s="29" t="n">
+      <c r="T6" s="29" t="n">
         <v>0.3</v>
       </c>
-      <c r="S6" s="27" t="inlineStr">
+      <c r="U6" s="27" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -2582,34 +2612,34 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6.6</v>
+        <v>6.61</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>6.35</v>
+        <v>6.36</v>
       </c>
       <c r="H7" s="33" t="n">
-        <v>6.48</v>
+        <v>6.49</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>23.64</v>
+        <v>23.65</v>
       </c>
       <c r="J7" s="33" t="n">
-        <v>56.11</v>
+        <v>56.12</v>
       </c>
       <c r="K7" s="33" t="n">
-        <v>58.68</v>
+        <v>58.7</v>
       </c>
       <c r="L7" s="33" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
       <c r="M7" s="33" t="n">
         <v>15.1</v>
@@ -2624,12 +2654,18 @@
         <v>-20.07</v>
       </c>
       <c r="Q7" s="47" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="R7" s="47" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="S7" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="R7" s="33" t="n">
+      <c r="T7" s="33" t="n">
         <v>0.78</v>
       </c>
-      <c r="S7" s="31" t="inlineStr">
+      <c r="U7" s="31" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -2689,12 +2725,18 @@
         <v>-17.35</v>
       </c>
       <c r="Q8" s="46" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="R8" s="46" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="S8" s="46" t="n">
         <v>-1.39</v>
       </c>
-      <c r="R8" s="29" t="n">
+      <c r="T8" s="29" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="S8" s="27" t="inlineStr">
+      <c r="U8" s="27" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -2754,12 +2796,18 @@
         <v>-24.81</v>
       </c>
       <c r="Q9" s="47" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="R9" s="47" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="S9" s="47" t="n">
         <v>-3.89</v>
       </c>
-      <c r="R9" s="33" t="n">
+      <c r="T9" s="33" t="n">
         <v>0.79</v>
       </c>
-      <c r="S9" s="31" t="inlineStr">
+      <c r="U9" s="31" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -2777,31 +2825,31 @@
         </is>
       </c>
       <c r="C10" s="46" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>5.93</v>
+        <v>5.94</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>5.04</v>
+        <v>5.05</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>5.33</v>
+        <v>5.34</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>21.7</v>
+        <v>21.71</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>55.64</v>
+        <v>55.65</v>
       </c>
       <c r="K10" s="29" t="n">
-        <v>63.24</v>
+        <v>63.25</v>
       </c>
       <c r="L10" s="29" t="n">
         <v>10.46</v>
@@ -2819,12 +2867,18 @@
         <v>-20.63</v>
       </c>
       <c r="Q10" s="46" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="R10" s="46" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="S10" s="46" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="R10" s="29" t="n">
+      <c r="T10" s="29" t="n">
         <v>0.86</v>
       </c>
-      <c r="S10" s="27" t="inlineStr">
+      <c r="U10" s="27" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -2883,13 +2937,19 @@
       <c r="P11" s="47" t="n">
         <v>-25.91</v>
       </c>
-      <c r="Q11" s="33" t="n">
+      <c r="Q11" s="47" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="R11" s="47" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="S11" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="33" t="n">
+      <c r="T11" s="33" t="n">
         <v>1.06</v>
       </c>
-      <c r="S11" s="31" t="inlineStr">
+      <c r="U11" s="31" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -2949,12 +3009,18 @@
         <v>-22.45</v>
       </c>
       <c r="Q12" s="46" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="R12" s="46" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="S12" s="46" t="n">
         <v>-0.13</v>
       </c>
-      <c r="R12" s="29" t="n">
+      <c r="T12" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="S12" s="27" t="inlineStr">
+      <c r="U12" s="27" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3013,13 +3079,19 @@
       <c r="P13" s="47" t="n">
         <v>-31.38</v>
       </c>
-      <c r="Q13" s="33" t="n">
+      <c r="Q13" s="47" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="R13" s="47" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="S13" s="33" t="n">
         <v>1.59</v>
       </c>
-      <c r="R13" s="33" t="n">
+      <c r="T13" s="33" t="n">
         <v>1.23</v>
       </c>
-      <c r="S13" s="31" t="inlineStr">
+      <c r="U13" s="31" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3078,13 +3150,19 @@
       <c r="P14" s="46" t="n">
         <v>-23.17</v>
       </c>
-      <c r="Q14" s="29" t="n">
+      <c r="Q14" s="46" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="R14" s="46" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="S14" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="R14" s="29" t="n">
+      <c r="T14" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="S14" s="27" t="inlineStr">
+      <c r="U14" s="27" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3102,34 +3180,34 @@
         </is>
       </c>
       <c r="C15" s="33" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="D15" s="33" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="E15" s="33" t="n">
-        <v>7.55</v>
+        <v>7.63</v>
       </c>
       <c r="F15" s="33" t="n">
-        <v>4.46</v>
+        <v>4.54</v>
       </c>
       <c r="G15" s="33" t="n">
-        <v>5.61</v>
+        <v>5.69</v>
       </c>
       <c r="H15" s="33" t="n">
-        <v>6.01</v>
+        <v>6.09</v>
       </c>
       <c r="I15" s="33" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="J15" s="33" t="n">
-        <v>62.99</v>
+        <v>63.11</v>
       </c>
       <c r="K15" s="33" t="n">
-        <v>75.48</v>
+        <v>75.62</v>
       </c>
       <c r="L15" s="33" t="n">
-        <v>12.21</v>
+        <v>12.23</v>
       </c>
       <c r="M15" s="33" t="n">
         <v>14.24</v>
@@ -3143,13 +3221,19 @@
       <c r="P15" s="47" t="n">
         <v>-21.73</v>
       </c>
-      <c r="Q15" s="33" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R15" s="33" t="n">
+      <c r="Q15" s="47" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="R15" s="47" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="S15" s="33" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="T15" s="33" t="n">
         <v>0.22</v>
       </c>
-      <c r="S15" s="31" t="inlineStr">
+      <c r="U15" s="31" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3158,7 +3242,7 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
@@ -3167,54 +3251,60 @@
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>0.95</v>
+        <v>0.04</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>1.25</v>
+        <v>0.93</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>7.99</v>
+        <v>9.6</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>4.94</v>
+        <v>10.93</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>6.85</v>
+        <v>10.3</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>7.08</v>
+        <v>17.9</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>24.9</v>
+        <v>44.84</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>63.17</v>
+        <v>73.92</v>
       </c>
       <c r="K16" s="29" t="n">
-        <v>70.66</v>
+        <v>57.6</v>
       </c>
       <c r="L16" s="29" t="n">
-        <v>11.57</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M16" s="29" t="n">
-        <v>13.81</v>
+        <v>18.27</v>
       </c>
       <c r="N16" s="29" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="O16" s="29" t="n">
-        <v>0.7</v>
+        <v>0.46</v>
       </c>
       <c r="P16" s="46" t="n">
-        <v>-21.07</v>
-      </c>
-      <c r="Q16" s="29" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="R16" s="29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S16" s="27" t="inlineStr">
+        <v>-21.24</v>
+      </c>
+      <c r="Q16" s="46" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="R16" s="46" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T16" s="29" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="U16" s="27" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3223,7 +3313,7 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
@@ -3232,54 +3322,60 @@
         </is>
       </c>
       <c r="C17" s="33" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>1.84</v>
+        <v>1.32</v>
       </c>
       <c r="E17" s="33" t="n">
-        <v>13.08</v>
+        <v>8.06</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>9.359999999999999</v>
+        <v>5.01</v>
       </c>
       <c r="G17" s="33" t="n">
-        <v>17.01</v>
+        <v>6.92</v>
       </c>
       <c r="H17" s="33" t="n">
-        <v>16.61</v>
+        <v>7.15</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>41.31</v>
+        <v>24.98</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>69.36</v>
+        <v>63.28</v>
       </c>
       <c r="K17" s="33" t="n">
-        <v>42.72</v>
+        <v>70.77</v>
       </c>
       <c r="L17" s="33" t="n">
-        <v>7.65</v>
+        <v>11.59</v>
       </c>
       <c r="M17" s="33" t="n">
-        <v>18.83</v>
+        <v>13.81</v>
       </c>
       <c r="N17" s="33" t="n">
-        <v>0.19</v>
+        <v>0.55</v>
       </c>
       <c r="O17" s="33" t="n">
-        <v>0.26</v>
+        <v>0.7</v>
       </c>
       <c r="P17" s="47" t="n">
-        <v>-24.38</v>
-      </c>
-      <c r="Q17" s="33" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="R17" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="S17" s="31" t="inlineStr">
+        <v>-21.07</v>
+      </c>
+      <c r="Q17" s="47" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="R17" s="47" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="S17" s="33" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="T17" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U17" s="31" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3288,7 +3384,7 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
@@ -3297,54 +3393,60 @@
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>0.21</v>
+        <v>2.22</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>0.67</v>
+        <v>1.8</v>
       </c>
       <c r="E18" s="29" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="F18" s="46" t="n">
-        <v>-0.42</v>
+        <v>13.03</v>
+      </c>
+      <c r="F18" s="29" t="n">
+        <v>9.31</v>
       </c>
       <c r="G18" s="29" t="n">
-        <v>7.79</v>
+        <v>16.96</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>2.83</v>
+        <v>16.56</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>15.17</v>
+        <v>41.25</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>41.11</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="K18" s="29" t="n">
-        <v>55.53</v>
+        <v>42.65</v>
       </c>
       <c r="L18" s="29" t="n">
-        <v>9.65</v>
+        <v>7.64</v>
       </c>
       <c r="M18" s="29" t="n">
-        <v>14.94</v>
+        <v>18.83</v>
       </c>
       <c r="N18" s="29" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="O18" s="29" t="n">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="P18" s="46" t="n">
-        <v>-22.86</v>
-      </c>
-      <c r="Q18" s="29" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="R18" s="29" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="S18" s="27" t="inlineStr">
+        <v>-24.38</v>
+      </c>
+      <c r="Q18" s="46" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="R18" s="46" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T18" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U18" s="27" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3404,12 +3506,18 @@
         <v>-19.81</v>
       </c>
       <c r="Q19" s="47" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="R19" s="47" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="S19" s="47" t="n">
         <v>-6</v>
       </c>
-      <c r="R19" s="33" t="n">
+      <c r="T19" s="33" t="n">
         <v>0.02</v>
       </c>
-      <c r="S19" s="31" t="inlineStr">
+      <c r="U19" s="31" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3418,7 +3526,7 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
+          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
@@ -3427,54 +3535,60 @@
         </is>
       </c>
       <c r="C20" s="29" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>9.6</v>
+        <v>0.31</v>
+      </c>
+      <c r="D20" s="46" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E20" s="46" t="n">
+        <v>-1.11</v>
       </c>
       <c r="F20" s="29" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>10.3</v>
+        <v>0.9</v>
+      </c>
+      <c r="G20" s="46" t="n">
+        <v>-1.55</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>44.84</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>73.92</v>
-      </c>
-      <c r="K20" s="29" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="L20" s="29" t="n">
-        <v>9.539999999999999</v>
+        <v>0.02</v>
+      </c>
+      <c r="I20" s="46" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="J20" s="46" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="K20" s="46" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="L20" s="46" t="n">
+        <v>-0.33</v>
       </c>
       <c r="M20" s="29" t="n">
-        <v>18.27</v>
-      </c>
-      <c r="N20" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O20" s="29" t="n">
-        <v>0.46</v>
+        <v>10.65</v>
+      </c>
+      <c r="N20" s="46" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="O20" s="46" t="n">
+        <v>-0.61</v>
       </c>
       <c r="P20" s="46" t="n">
-        <v>-21.24</v>
-      </c>
-      <c r="Q20" s="29" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="R20" s="29" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="S20" s="27" t="inlineStr">
+        <v>-15.77</v>
+      </c>
+      <c r="Q20" s="46" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="R20" s="46" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="S20" s="46" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="T20" s="46" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U20" s="27" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3483,7 +3597,7 @@
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
+          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
@@ -3491,55 +3605,61 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C21" s="47" t="n">
-        <v>-0.1</v>
+      <c r="C21" s="33" t="n">
+        <v>0.21</v>
       </c>
       <c r="D21" s="33" t="n">
-        <v>1.15</v>
+        <v>0.67</v>
       </c>
       <c r="E21" s="33" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="F21" s="33" t="n">
-        <v>5.42</v>
+        <v>4.89</v>
+      </c>
+      <c r="F21" s="47" t="n">
+        <v>-0.42</v>
       </c>
       <c r="G21" s="33" t="n">
-        <v>4.8</v>
+        <v>7.79</v>
       </c>
       <c r="H21" s="33" t="n">
-        <v>6.4</v>
+        <v>2.83</v>
       </c>
       <c r="I21" s="33" t="n">
-        <v>25.3</v>
+        <v>15.17</v>
       </c>
       <c r="J21" s="33" t="n">
-        <v>70.90000000000001</v>
+        <v>41.11</v>
       </c>
       <c r="K21" s="33" t="n">
-        <v>88.40000000000001</v>
+        <v>55.53</v>
       </c>
       <c r="L21" s="33" t="n">
-        <v>13.82</v>
+        <v>9.65</v>
       </c>
       <c r="M21" s="33" t="n">
-        <v>17.29</v>
+        <v>14.94</v>
       </c>
       <c r="N21" s="33" t="n">
-        <v>0.57</v>
+        <v>0.38</v>
       </c>
       <c r="O21" s="33" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="P21" s="47" t="n">
-        <v>-22.73</v>
-      </c>
-      <c r="Q21" s="33" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="R21" s="33" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="S21" s="31" t="inlineStr">
+        <v>-22.86</v>
+      </c>
+      <c r="Q21" s="47" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="R21" s="47" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="S21" s="33" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="T21" s="33" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U21" s="31" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3548,7 +3668,7 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
+          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
@@ -3556,55 +3676,61 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="D22" s="46" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="E22" s="46" t="n">
-        <v>-1.11</v>
+      <c r="C22" s="46" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E22" s="29" t="n">
+        <v>8.880000000000001</v>
       </c>
       <c r="F22" s="29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G22" s="46" t="n">
-        <v>-1.55</v>
+        <v>5.47</v>
+      </c>
+      <c r="G22" s="29" t="n">
+        <v>4.85</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I22" s="46" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="J22" s="46" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="K22" s="46" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="L22" s="46" t="n">
-        <v>-0.33</v>
+        <v>6.45</v>
+      </c>
+      <c r="I22" s="29" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="J22" s="29" t="n">
+        <v>70.98</v>
+      </c>
+      <c r="K22" s="29" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="L22" s="29" t="n">
+        <v>13.84</v>
       </c>
       <c r="M22" s="29" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="N22" s="46" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="O22" s="46" t="n">
-        <v>-0.61</v>
+        <v>17.29</v>
+      </c>
+      <c r="N22" s="29" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O22" s="29" t="n">
+        <v>0.79</v>
       </c>
       <c r="P22" s="46" t="n">
-        <v>-15.77</v>
+        <v>-22.73</v>
       </c>
       <c r="Q22" s="46" t="n">
-        <v>-4.14</v>
+        <v>-1.73</v>
       </c>
       <c r="R22" s="46" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="S22" s="27" t="inlineStr">
+        <v>-2.53</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="T22" s="29" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="U22" s="27" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3663,13 +3789,19 @@
       <c r="P23" s="47" t="n">
         <v>-15.94</v>
       </c>
-      <c r="Q23" s="33" t="n">
+      <c r="Q23" s="47" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="R23" s="47" t="n">
+        <v>-2.57</v>
+      </c>
+      <c r="S23" s="33" t="n">
         <v>17.05</v>
       </c>
-      <c r="R23" s="33" t="n">
+      <c r="T23" s="33" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="S23" s="31" t="inlineStr">
+      <c r="U23" s="31" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3690,263 +3822,313 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
           <t>● Strong</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>● Fair</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>● Weak</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="48" customHeight="1">
       <c r="A28" s="27" t="inlineStr">
         <is>
           <t>CAGR</t>
         </is>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Compound Annual Growth Rate. The single yearly return that, if repeated every year, would grow your portfolio from start to end value. Accounts for compounding. ~7% is the long-term global equity average.</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>&gt; 7.0</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>3.0 – 7.0</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>&lt; 3.0</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="F28" s="27" t="inlineStr">
         <is>
           <t>Equity risk premium (Dimson et al.)</t>
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="48" customHeight="1">
       <c r="A29" s="31" t="inlineStr">
         <is>
           <t>α (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B29" s="31" t="inlineStr">
+      <c r="B29" s="49" t="inlineStr">
+        <is>
+          <t>Extra annual return vs the benchmark, after adjusting for how risky the portfolio is (CAPM). Positive = you beat the market beyond what your risk alone justified. Negative = you underperformed after fees and noise.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
         <is>
           <t>&gt; 0.0</t>
         </is>
       </c>
-      <c r="C29" s="31" t="inlineStr">
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>-1.0 – 0.0</t>
         </is>
       </c>
-      <c r="D29" s="31" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>&lt; -1.0</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="F29" s="31" t="inlineStr">
         <is>
           <t>Jensen's Alpha (CAPM)</t>
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="48" customHeight="1">
       <c r="A30" s="27" t="inlineStr">
         <is>
           <t>β (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>How much your portfolio moves when the benchmark moves 1%. β=1 in line, β=0.5 half as reactive, β=1.5 amplifies by 50%, β≈0 uncorrelated. Tells you how much systematic market risk you're running.</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>&lt; 0.7%</t>
         </is>
       </c>
-      <c r="C30" s="27" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>1.0% – 0.7%</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>&gt; 1.0%</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
+      <c r="F30" s="27" t="inlineStr">
         <is>
           <t>CAPM, 1.0 = market</t>
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="48" customHeight="1">
       <c r="A31" s="31" t="inlineStr">
         <is>
           <t>Max DD</t>
         </is>
       </c>
-      <c r="B31" s="31" t="inlineStr">
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>Maximum Drawdown. Worst peak-to-trough loss over the period — the most painful scenario an investor lived through. -20% is typical for diversified equity; deeper drops signal concentration or high volatility.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
         <is>
           <t>&lt; 15.0%</t>
         </is>
       </c>
-      <c r="C31" s="31" t="inlineStr">
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>30.0% – 15.0%</t>
         </is>
       </c>
-      <c r="D31" s="31" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>&gt; 30.0%</t>
         </is>
       </c>
-      <c r="E31" s="31" t="inlineStr">
+      <c r="F31" s="31" t="inlineStr">
         <is>
           <t>Retail drawdown tolerance</t>
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="48" customHeight="1">
       <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
-      <c r="B32" s="27" t="inlineStr">
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>How bumpy the ride is. Annualized standard deviation of daily returns. A 15% vol means ~±15% year-to-year noise around the average return. Equity indexes ~15–20%, bonds ~3–7%.</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>&lt; 10.0%</t>
         </is>
       </c>
-      <c r="C32" s="27" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>18.0% – 10.0%</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>&gt; 18.0%</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
+      <c r="F32" s="27" t="inlineStr">
         <is>
           <t>Hist. equity vol ~15%</t>
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="48" customHeight="1">
       <c r="A33" s="31" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="B33" s="31" t="inlineStr">
+      <c r="B33" s="49" t="inlineStr">
+        <is>
+          <t>Return per unit of risk taken: (CAGR − risk-free rate) / Volatility. Above 1 is good, above 2 is excellent, negative means you were paid less than a safe bond for the risk you ran.</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
         <is>
           <t>&gt; 1.0</t>
         </is>
       </c>
-      <c r="C33" s="31" t="inlineStr">
+      <c r="D33" s="31" t="inlineStr">
         <is>
           <t>0.5 – 1.0</t>
         </is>
       </c>
-      <c r="D33" s="31" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>&lt; 0.5</t>
         </is>
       </c>
-      <c r="E33" s="31" t="inlineStr">
+      <c r="F33" s="31" t="inlineStr">
         <is>
           <t>Sharpe (1994)</t>
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="48" customHeight="1">
       <c r="A34" s="27" t="inlineStr">
         <is>
           <t>Sortino</t>
         </is>
       </c>
-      <c r="B34" s="27" t="inlineStr">
+      <c r="B34" s="48" t="inlineStr">
+        <is>
+          <t>Like Sharpe but only penalizes downside volatility (ignores upside swings). More honest when returns are asymmetric. Usually higher than Sharpe — the gap shows how much of your volatility is actually good volatility.</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>&gt; 1.5</t>
         </is>
       </c>
-      <c r="C34" s="27" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>0.7 – 1.5</t>
         </is>
       </c>
-      <c r="D34" s="27" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>&lt; 0.7</t>
         </is>
       </c>
-      <c r="E34" s="27" t="inlineStr">
+      <c r="F34" s="27" t="inlineStr">
         <is>
           <t>Sortino &amp; Price (1994)</t>
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="48" customHeight="1">
       <c r="A35" s="31" t="inlineStr">
         <is>
           <t>VaR 95%</t>
         </is>
       </c>
-      <c r="B35" s="31" t="inlineStr">
+      <c r="B35" s="49" t="inlineStr">
+        <is>
+          <t>Value at Risk. The daily loss exceeded only 5% of the time (historical simulation). A VaR of -1.2% means on an average month you should expect about one day worse than -1.2%. Non-parametric: no normal-distribution assumption.</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="inlineStr">
         <is>
           <t>&lt; 0.8%</t>
         </is>
       </c>
-      <c r="C35" s="31" t="inlineStr">
+      <c r="D35" s="31" t="inlineStr">
         <is>
           <t>1.5% – 0.8%</t>
         </is>
       </c>
-      <c r="D35" s="31" t="inlineStr">
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>&gt; 1.5%</t>
         </is>
       </c>
-      <c r="E35" s="31" t="inlineStr">
+      <c r="F35" s="31" t="inlineStr">
         <is>
           <t>Basel III (retail adj.)</t>
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="48" customHeight="1">
       <c r="A36" s="27" t="inlineStr">
         <is>
           <t>CVaR 95%</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr">
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>Conditional VaR, a.k.a. Expected Shortfall. The average loss on the worst 5% of days. Always more negative than VaR. Captures tail risk VaR misses — how bad it really gets when it goes bad.</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>&lt; 1.2%</t>
         </is>
       </c>
-      <c r="C36" s="27" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
         <is>
           <t>2.0% – 1.2%</t>
         </is>
       </c>
-      <c r="D36" s="27" t="inlineStr">
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>&gt; 2.0%</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="F36" s="27" t="inlineStr">
         <is>
           <t>Artzner et al. (1999)</t>
         </is>
@@ -3955,13 +4137,13 @@
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 09:47 v2.0</t>
+          <t>Generated 2026-05-04 10:02 v2.0</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4050,13 +4232,13 @@
         </is>
       </c>
       <c r="D5" s="29" t="n">
-        <v>14.26779706186569</v>
+        <v>14.26530952530278</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>415.5184553004801</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>59.28532995687162</v>
+        <v>59.27499378337036</v>
       </c>
     </row>
     <row r="6">
@@ -4076,13 +4258,13 @@
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>13.23905143133624</v>
+        <v>13.23674325269094</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>91.33928843906948</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>12.09245537346497</v>
+        <v>12.09034709951444</v>
       </c>
     </row>
     <row r="7">
@@ -4102,13 +4284,13 @@
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>8.460803908866717</v>
+        <v>8.459328799641117</v>
       </c>
       <c r="E7" s="29" t="n">
         <v>55.27743647935755</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>4.6769155063668</v>
+        <v>4.676100103801618</v>
       </c>
     </row>
     <row r="8">
@@ -4128,13 +4310,13 @@
         </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>15.3624886227922</v>
+        <v>15.36969361005393</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>21.42187356948853</v>
+        <v>21.50000333786011</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.290932889901604</v>
+        <v>3.304484639180467</v>
       </c>
     </row>
     <row r="9">
@@ -4154,13 +4336,13 @@
         </is>
       </c>
       <c r="D9" s="29" t="n">
-        <v>8.505512682692782</v>
+        <v>8.500249996866843</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>36.58571243286133</v>
+        <v>36.52500425066267</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>3.11180241103053</v>
+        <v>3.104716672672568</v>
       </c>
     </row>
     <row r="10">
@@ -4180,13 +4362,13 @@
         </is>
       </c>
       <c r="D10" s="33" t="n">
-        <v>7.041964251641569</v>
+        <v>7.040736511754693</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>43.92423918752959</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>3.093129221391371</v>
+        <v>3.092589945986859</v>
       </c>
     </row>
     <row r="11">
@@ -4206,13 +4388,13 @@
         </is>
       </c>
       <c r="D11" s="29" t="n">
-        <v>7.344315367508301</v>
+        <v>7.343034913845621</v>
       </c>
       <c r="E11" s="29" t="n">
         <v>41.5263607345748</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>3.04982689299631</v>
+        <v>3.049295167189306</v>
       </c>
     </row>
     <row r="12">
@@ -4232,13 +4414,13 @@
         </is>
       </c>
       <c r="D12" s="33" t="n">
-        <v>12.31012766337849</v>
+        <v>12.31375315772519</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.52839220992303</v>
+        <v>16.58303716504107</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>2.03466618174543</v>
+        <v>2.041994262556988</v>
       </c>
     </row>
     <row r="13">
@@ -4258,13 +4440,13 @@
         </is>
       </c>
       <c r="D13" s="29" t="n">
-        <v>7.290126950746573</v>
+        <v>7.294415251161368</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>20.41326250348772</v>
+        <v>20.50510328643176</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>1.488152751293403</v>
+        <v>1.495727381391869</v>
       </c>
     </row>
     <row r="14">
@@ -4284,7 +4466,7 @@
         </is>
       </c>
       <c r="D14" s="33" t="n">
-        <v>6.177812059171433</v>
+        <v>6.176734980957511</v>
       </c>
       <c r="E14" s="33" t="n">
         <v>0</v>
@@ -4329,10 +4511,10 @@
         </is>
       </c>
       <c r="B18" s="28" t="n">
-        <v>52427.96042730808</v>
+        <v>52442.07356523337</v>
       </c>
       <c r="C18" s="29" t="n">
-        <v>92.39865586729506</v>
+        <v>92.42597375466755</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>6</v>
@@ -4417,10 +4599,10 @@
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>41.75790478337835</v>
+        <v>41.77116920492907</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>19.45450942763309</v>
+        <v>19.52938126311098</v>
       </c>
     </row>
     <row r="26">
@@ -4430,10 +4612,10 @@
         </is>
       </c>
       <c r="B26" s="33" t="n">
-        <v>15.53026313713126</v>
+        <v>15.5217931241751</v>
       </c>
       <c r="C26" s="33" t="n">
-        <v>29.00379300117493</v>
+        <v>29.01250379426139</v>
       </c>
     </row>
     <row r="27">
@@ -4443,10 +4625,10 @@
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>10.66366665568281</v>
+        <v>10.66269639765878</v>
       </c>
       <c r="C27" s="29" t="n">
-        <v>28.58645842016861</v>
+        <v>28.64311527060715</v>
       </c>
     </row>
     <row r="28">
@@ -4456,10 +4638,10 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>24.1498199211525</v>
+        <v>24.14476795526446</v>
       </c>
       <c r="C28" s="33" t="n">
-        <v>152.4511971244854</v>
+        <v>152.507853974924</v>
       </c>
     </row>
     <row r="29">
@@ -4469,10 +4651,10 @@
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>7.898345502655069</v>
+        <v>7.899573317972592</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>28.58645842016861</v>
+        <v>28.64311527060715</v>
       </c>
     </row>
   </sheetData>
@@ -4525,12 +4707,12 @@
           <t>Total Value (EUR)</t>
         </is>
       </c>
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>Sum of current market values of all holdings, converted to EUR.</t>
         </is>
       </c>
-      <c r="C4" s="48" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>Point-in-time (today)</t>
         </is>
@@ -4542,12 +4724,12 @@
           <t>YTD Return</t>
         </is>
       </c>
-      <c r="B5" s="49" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Year-to-date return. Formula: (Current Value / Value at Jan 1) - 1.</t>
         </is>
       </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Jan 1 of current year to today</t>
         </is>
@@ -4559,12 +4741,12 @@
           <t>CAGR</t>
         </is>
       </c>
-      <c r="B6" s="48" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>Compound Annual Growth Rate. Formula: (End/Start)^(1/years) - 1. Measures mean annual growth rate assuming constant compounding.</t>
         </is>
       </c>
-      <c r="C6" s="48" t="inlineStr">
+      <c r="C6" s="50" t="inlineStr">
         <is>
           <t>Full history: 2.3 years (853 calendar days)</t>
         </is>
@@ -4576,12 +4758,12 @@
           <t>Sharpe Ratio</t>
         </is>
       </c>
-      <c r="B7" s="49" t="inlineStr">
+      <c r="B7" s="51" t="inlineStr">
         <is>
           <t>Risk-adjusted return. Formula: (Return - Rf) / Volatility. Higher is better.</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="51" t="inlineStr">
         <is>
           <t>Risk-free rate: 4.0%. Period: 2.3 years (853 calendar days)</t>
         </is>
@@ -4593,12 +4775,12 @@
           <t>Sortino Ratio</t>
         </is>
       </c>
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B8" s="50" t="inlineStr">
         <is>
           <t>Downside risk-adjusted return. Uses only negative returns for deviation. Formula: (Return - Rf) / Downside Deviation.</t>
         </is>
       </c>
-      <c r="C8" s="48" t="inlineStr">
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>Risk-free rate: 4.0%. Period: 2.3 years (853 calendar days)</t>
         </is>
@@ -4610,12 +4792,12 @@
           <t>Volatility</t>
         </is>
       </c>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="B9" s="51" t="inlineStr">
         <is>
           <t>Annualized std dev of daily returns. Formula: StdDev(daily) x sqrt(252).</t>
         </is>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="51" t="inlineStr">
         <is>
           <t>Period: 2.3 years (853 calendar days). Trading days/year: 252</t>
         </is>
@@ -4627,12 +4809,12 @@
           <t>Max Drawdown</t>
         </is>
       </c>
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
         <is>
           <t>Largest peak-to-trough decline. Formula: min((V - CumMax) / CumMax).</t>
         </is>
       </c>
-      <c r="C10" s="48" t="inlineStr">
+      <c r="C10" s="50" t="inlineStr">
         <is>
           <t>Period: 2.3 years (853 calendar days)</t>
         </is>
@@ -4644,12 +4826,12 @@
           <t>VaR (95%)</t>
         </is>
       </c>
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="51" t="inlineStr">
         <is>
           <t>Value at Risk via historical simulation. The 5th percentile of daily returns. Non-parametric: no distributional assumptions, robust for fat tails.</t>
         </is>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="51" t="inlineStr">
         <is>
           <t>Period: 2.3 years (853 calendar days). Confidence: 95%</t>
         </is>
@@ -4661,12 +4843,12 @@
           <t>CVaR (95%)</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr">
+      <c r="B12" s="50" t="inlineStr">
         <is>
           <t>Conditional VaR (Expected Shortfall). Average loss beyond VaR threshold. A coherent risk measure per Artzner et al. (1999), preferred for tail risk.</t>
         </is>
       </c>
-      <c r="C12" s="48" t="inlineStr">
+      <c r="C12" s="50" t="inlineStr">
         <is>
           <t>Period: 2.3 years (853 calendar days). Confidence: 95%</t>
         </is>
@@ -4678,12 +4860,12 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="B13" s="49" t="inlineStr">
+      <c r="B13" s="51" t="inlineStr">
         <is>
           <t>CAPM sensitivity to market. Formula: Cov(Rp, Rb) / Var(Rb). Beta=1 means same as market.</t>
         </is>
       </c>
-      <c r="C13" s="49" t="inlineStr">
+      <c r="C13" s="51" t="inlineStr">
         <is>
           <t>Benchmark: S&amp;P 500. Period: 2.3 years (853 calendar days)</t>
         </is>
@@ -4695,12 +4877,12 @@
           <t>Alpha</t>
         </is>
       </c>
-      <c r="B14" s="48" t="inlineStr">
+      <c r="B14" s="50" t="inlineStr">
         <is>
           <t>Jensen's Alpha. Excess return vs CAPM expected. Formula: Rp - [Rf + Beta x (Rb - Rf)].</t>
         </is>
       </c>
-      <c r="C14" s="48" t="inlineStr">
+      <c r="C14" s="50" t="inlineStr">
         <is>
           <t>Benchmark: S&amp;P 500. Risk-free rate: 4.0%</t>
         </is>
@@ -4712,12 +4894,12 @@
           <t>Weighted Yield</t>
         </is>
       </c>
-      <c r="B15" s="49" t="inlineStr">
+      <c r="B15" s="51" t="inlineStr">
         <is>
           <t>Portfolio-weighted average dividend/coupon yield.</t>
         </is>
       </c>
-      <c r="C15" s="49" t="inlineStr">
+      <c r="C15" s="51" t="inlineStr">
         <is>
           <t>Based on latest yield data from yfinance</t>
         </is>
@@ -4729,12 +4911,12 @@
           <t>Geography Allocation</t>
         </is>
       </c>
-      <c r="B16" s="48" t="inlineStr">
+      <c r="B16" s="50" t="inlineStr">
         <is>
           <t>Geographic exposure of equity holdings only. Multi-geo ETFs split proportionally.</t>
         </is>
       </c>
-      <c r="C16" s="48" t="inlineStr">
+      <c r="C16" s="50" t="inlineStr">
         <is>
           <t>Equity only. Sources: justETF, index_geo_allocation.csv, yfinance</t>
         </is>
@@ -4746,12 +4928,12 @@
           <t>Rebalancing Amount</t>
         </is>
       </c>
-      <c r="B17" s="49" t="inlineStr">
+      <c r="B17" s="51" t="inlineStr">
         <is>
           <t>Suggested trade amount to reach target. Asset class: total value. Geography: equity value.</t>
         </is>
       </c>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="C17" s="51" t="inlineStr">
         <is>
           <t>Threshold from config (rebalancing_threshold)</t>
         </is>
@@ -4760,7 +4942,7 @@
     <row r="20">
       <c r="A20" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 09:47 v2.0</t>
+          <t>Generated 2026-05-04 10:02 v2.0</t>
         </is>
       </c>
     </row>

--- a/output/sample/portfolio_dashboard_sample.xlsx
+++ b/output/sample/portfolio_dashboard_sample.xlsx
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>80948.91581741307</v>
+        <v>80950.0840273767</v>
       </c>
       <c r="D5" s="2" t="n"/>
     </row>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>26808.91581741307</v>
+        <v>26810.0840273767</v>
       </c>
       <c r="D6" s="2" t="n"/>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>49.5177610221889</v>
+        <v>49.51991877978703</v>
       </c>
       <c r="D7" s="2" t="n"/>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>64.78415805286481</v>
+        <v>64.7846662610765</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>65</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>41.77116920492907</v>
+        <v>41.77246629294275</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>55</v>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>20.57977816653656</v>
+        <v>20.57948117485098</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>25</v>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>24.14476795526446</v>
+        <v>24.14423011363721</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>8</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>8.459328799641117</v>
+        <v>8.459206721050242</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>5</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>15.5217931241751</v>
+        <v>15.52144736535534</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>11</v>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>6.176734980957511</v>
+        <v>6.176645843022274</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>5</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>10.66269639765878</v>
+        <v>10.66245887862393</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>14</v>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>7.899573317972592</v>
+        <v>7.899397349440786</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>12</v>
@@ -1063,7 +1063,7 @@
         <v>12441.60034179688</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>15.36969361005393</v>
+        <v>15.36947180634083</v>
       </c>
       <c r="D21" s="30" t="n"/>
       <c r="E21" s="12" t="inlineStr">
@@ -1082,7 +1082,7 @@
         <v>11547.61339873075</v>
       </c>
       <c r="C22" s="33" t="n">
-        <v>14.26530952530278</v>
+        <v>14.26510365921972</v>
       </c>
       <c r="D22" s="30" t="n"/>
       <c r="E22" s="34" t="inlineStr">
@@ -1101,7 +1101,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>13.23674325269094</v>
+        <v>13.236552230093</v>
       </c>
       <c r="D23" s="30" t="n"/>
       <c r="E23" s="35" t="inlineStr">
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="B24" s="32" t="n">
-        <v>9967.849677611011</v>
+        <v>9969.017887574628</v>
       </c>
       <c r="C24" s="33" t="n">
-        <v>12.31375315772519</v>
+        <v>12.3150185788605</v>
       </c>
       <c r="D24" s="30" t="n"/>
       <c r="E24" s="34" t="inlineStr">
@@ -1139,7 +1139,7 @@
         <v>6880.860214233398</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>8.500249996866843</v>
+        <v>8.500127327732415</v>
       </c>
       <c r="D25" s="30" t="n"/>
       <c r="E25" s="12" t="inlineStr">
@@ -1154,7 +1154,7 @@
     <row r="27">
       <c r="A27" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 10:02 v2.0</t>
+          <t>Generated 2026-05-04 10:06 v2.0</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
     <row r="26">
       <c r="A26" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 10:02 v2.0</t>
+          <t>Generated 2026-05-04 10:06 v2.0</t>
         </is>
       </c>
     </row>
@@ -1549,10 +1549,10 @@
         <v>12441.60034179688</v>
       </c>
       <c r="L4" s="29" t="n">
-        <v>15.36969361005393</v>
+        <v>15.36947180634083</v>
       </c>
       <c r="M4" s="29" t="n">
-        <v>23.72446300453892</v>
+        <v>23.723934525499</v>
       </c>
       <c r="N4" s="28" t="n">
         <v>2201.600341796875</v>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="S4" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 10:01</t>
+          <t>2026-05-04 10:06</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>11547.61339873075</v>
       </c>
       <c r="L5" s="33" t="n">
-        <v>14.26530952530278</v>
+        <v>14.26510365921972</v>
       </c>
       <c r="M5" s="33" t="n">
-        <v>22.01974981856225</v>
+        <v>22.01925931320324</v>
       </c>
       <c r="N5" s="32" t="n">
         <v>9307.613398730755</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="S5" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 10:01</t>
+          <t>2026-05-04 10:06</t>
         </is>
       </c>
     </row>
@@ -1698,25 +1698,25 @@
         <v>570</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>664.5233118407341</v>
+        <v>664.6011925049752</v>
       </c>
       <c r="J6" s="28" t="n">
         <v>8550</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>9967.849677611011</v>
+        <v>9969.017887574628</v>
       </c>
       <c r="L6" s="29" t="n">
-        <v>12.31375315772519</v>
+        <v>12.3150185788605</v>
       </c>
       <c r="M6" s="29" t="n">
-        <v>19.00735230313095</v>
+        <v>19.00915647111936</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>1417.849677611011</v>
+        <v>1419.017887574628</v>
       </c>
       <c r="O6" s="29" t="n">
-        <v>16.58303716504107</v>
+        <v>16.59670043946933</v>
       </c>
       <c r="P6" s="27" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="S6" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 10:01</t>
+          <t>2026-05-04 10:06</t>
         </is>
       </c>
     </row>
@@ -1786,10 +1786,10 @@
         <v>6880.860214233398</v>
       </c>
       <c r="L7" s="33" t="n">
-        <v>8.500249996866843</v>
+        <v>8.500127327732415</v>
       </c>
       <c r="M7" s="33" t="n">
-        <v>13.12087746811576</v>
+        <v>13.12058519137484</v>
       </c>
       <c r="N7" s="32" t="n">
         <v>1840.860214233398</v>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="S7" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 10:01</t>
+          <t>2026-05-04 10:06</t>
         </is>
       </c>
     </row>
@@ -1865,10 +1865,10 @@
         <v>5904.750061035156</v>
       </c>
       <c r="L8" s="29" t="n">
-        <v>7.294415251161368</v>
+        <v>7.294309983715664</v>
       </c>
       <c r="M8" s="29" t="n">
-        <v>11.25956633596908</v>
+        <v>11.25931552123806</v>
       </c>
       <c r="N8" s="28" t="n">
         <v>1004.750061035156</v>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="S8" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 10:01</t>
+          <t>2026-05-04 10:06</t>
         </is>
       </c>
     </row>
@@ -1944,10 +1944,10 @@
         <v>5699.399871826172</v>
       </c>
       <c r="L9" s="33" t="n">
-        <v>7.040736511754693</v>
+        <v>7.04063490520736</v>
       </c>
       <c r="M9" s="33" t="n">
-        <v>10.86799106968304</v>
+        <v>10.8677489775655</v>
       </c>
       <c r="N9" s="32" t="n">
         <v>1739.399871826172</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="S9" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 10:01</t>
+          <t>2026-05-04 10:06</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>13.23674325269094</v>
+        <v>13.236552230093</v>
       </c>
       <c r="M10" s="29" t="n">
         <v>64.31917363528412</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="S10" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 10:01</t>
+          <t>2026-05-04 10:06</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         <v>5944.107150852142</v>
       </c>
       <c r="L11" s="33" t="n">
-        <v>7.343034913845621</v>
+        <v>7.34292894475797</v>
       </c>
       <c r="M11" s="33" t="n">
         <v>35.68082636471589</v>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="S11" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 10:01</t>
+          <t>2026-05-04 10:06</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
         <v>5000</v>
       </c>
       <c r="L12" s="29" t="n">
-        <v>6.176734980957511</v>
+        <v>6.176645843022274</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>100</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="S12" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 10:02</t>
+          <t>2026-05-04 10:06</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
         <v>6847.734948739668</v>
       </c>
       <c r="L13" s="33" t="n">
-        <v>8.459328799641117</v>
+        <v>8.459206721050242</v>
       </c>
       <c r="M13" s="33" t="n">
         <v>100</v>
@@ -2288,14 +2288,14 @@
       </c>
       <c r="S13" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 10:02</t>
+          <t>2026-05-04 10:06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 10:02 v2.0</t>
+          <t>Generated 2026-05-04 10:06 v2.0</t>
         </is>
       </c>
     </row>
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6.61</v>
+        <v>6.63</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>6.36</v>
+        <v>6.37</v>
       </c>
       <c r="H7" s="33" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>23.65</v>
+        <v>23.67</v>
       </c>
       <c r="J7" s="33" t="n">
-        <v>56.12</v>
+        <v>56.14</v>
       </c>
       <c r="K7" s="33" t="n">
-        <v>58.7</v>
+        <v>58.72</v>
       </c>
       <c r="L7" s="33" t="n">
         <v>9.83</v>
@@ -2660,7 +2660,7 @@
         <v>-2.13</v>
       </c>
       <c r="S7" s="47" t="n">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="T7" s="33" t="n">
         <v>0.78</v>
@@ -2824,35 +2824,35 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C10" s="46" t="n">
-        <v>-0.01</v>
+      <c r="C10" s="29" t="n">
+        <v>0</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>5.94</v>
+        <v>5.95</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>5.05</v>
+        <v>5.07</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>5.34</v>
+        <v>5.35</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>21.71</v>
+        <v>21.72</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>55.65</v>
+        <v>55.67</v>
       </c>
       <c r="K10" s="29" t="n">
-        <v>63.25</v>
+        <v>63.27</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>10.46</v>
+        <v>10.47</v>
       </c>
       <c r="M10" s="29" t="n">
         <v>16.47</v>
@@ -3242,7 +3242,7 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
@@ -3251,58 +3251,58 @@
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>0.04</v>
+        <v>1.01</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>0.93</v>
+        <v>1.32</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>9.6</v>
+        <v>8.06</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>10.93</v>
+        <v>5.01</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>10.3</v>
+        <v>6.92</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>17.9</v>
+        <v>7.15</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>44.84</v>
+        <v>24.98</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>73.92</v>
+        <v>63.28</v>
       </c>
       <c r="K16" s="29" t="n">
-        <v>57.6</v>
+        <v>70.77</v>
       </c>
       <c r="L16" s="29" t="n">
-        <v>9.539999999999999</v>
+        <v>11.59</v>
       </c>
       <c r="M16" s="29" t="n">
-        <v>18.27</v>
+        <v>13.81</v>
       </c>
       <c r="N16" s="29" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="O16" s="29" t="n">
-        <v>0.46</v>
+        <v>0.7</v>
       </c>
       <c r="P16" s="46" t="n">
-        <v>-21.24</v>
+        <v>-21.07</v>
       </c>
       <c r="Q16" s="46" t="n">
-        <v>-1.78</v>
+        <v>-1.39</v>
       </c>
       <c r="R16" s="46" t="n">
-        <v>-2.5</v>
+        <v>-2.13</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>3.42</v>
+        <v>5.98</v>
       </c>
       <c r="T16" s="29" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="U16" s="27" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
@@ -3322,58 +3322,58 @@
         </is>
       </c>
       <c r="C17" s="33" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="E17" s="33" t="n">
-        <v>8.06</v>
+        <v>13.03</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>5.01</v>
+        <v>9.31</v>
       </c>
       <c r="G17" s="33" t="n">
-        <v>6.92</v>
+        <v>16.96</v>
       </c>
       <c r="H17" s="33" t="n">
-        <v>7.15</v>
+        <v>16.56</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>24.98</v>
+        <v>41.25</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>63.28</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="K17" s="33" t="n">
-        <v>70.77</v>
+        <v>42.65</v>
       </c>
       <c r="L17" s="33" t="n">
-        <v>11.59</v>
+        <v>7.64</v>
       </c>
       <c r="M17" s="33" t="n">
-        <v>13.81</v>
+        <v>18.83</v>
       </c>
       <c r="N17" s="33" t="n">
-        <v>0.55</v>
+        <v>0.19</v>
       </c>
       <c r="O17" s="33" t="n">
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="P17" s="47" t="n">
-        <v>-21.07</v>
+        <v>-24.38</v>
       </c>
       <c r="Q17" s="47" t="n">
-        <v>-1.39</v>
+        <v>-1.59</v>
       </c>
       <c r="R17" s="47" t="n">
-        <v>-2.13</v>
+        <v>-2.59</v>
       </c>
       <c r="S17" s="33" t="n">
-        <v>5.98</v>
+        <v>2.82</v>
       </c>
       <c r="T17" s="33" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="U17" s="31" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
@@ -3393,58 +3393,58 @@
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>2.22</v>
+        <v>0.21</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>1.8</v>
+        <v>0.67</v>
       </c>
       <c r="E18" s="29" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>9.31</v>
+        <v>4.89</v>
+      </c>
+      <c r="F18" s="46" t="n">
+        <v>-0.42</v>
       </c>
       <c r="G18" s="29" t="n">
-        <v>16.96</v>
+        <v>7.79</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>16.56</v>
+        <v>2.83</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>41.25</v>
+        <v>15.17</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>69.29000000000001</v>
+        <v>41.11</v>
       </c>
       <c r="K18" s="29" t="n">
-        <v>42.65</v>
+        <v>55.53</v>
       </c>
       <c r="L18" s="29" t="n">
-        <v>7.64</v>
+        <v>9.65</v>
       </c>
       <c r="M18" s="29" t="n">
-        <v>18.83</v>
+        <v>14.94</v>
       </c>
       <c r="N18" s="29" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="O18" s="29" t="n">
-        <v>0.26</v>
+        <v>0.51</v>
       </c>
       <c r="P18" s="46" t="n">
-        <v>-24.38</v>
+        <v>-22.86</v>
       </c>
       <c r="Q18" s="46" t="n">
-        <v>-1.59</v>
+        <v>-1.53</v>
       </c>
       <c r="R18" s="46" t="n">
-        <v>-2.59</v>
+        <v>-2.22</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>2.82</v>
+        <v>4.23</v>
       </c>
       <c r="T18" s="29" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="U18" s="27" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
+          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
@@ -3535,58 +3535,58 @@
         </is>
       </c>
       <c r="C20" s="29" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="D20" s="46" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="E20" s="46" t="n">
-        <v>-1.11</v>
+        <v>0.04</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>9.6</v>
       </c>
       <c r="F20" s="29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G20" s="46" t="n">
-        <v>-1.55</v>
+        <v>10.93</v>
+      </c>
+      <c r="G20" s="29" t="n">
+        <v>10.3</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I20" s="46" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="J20" s="46" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="K20" s="46" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="L20" s="46" t="n">
-        <v>-0.33</v>
+        <v>17.9</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="J20" s="29" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="K20" s="29" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="L20" s="29" t="n">
+        <v>9.539999999999999</v>
       </c>
       <c r="M20" s="29" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="N20" s="46" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="O20" s="46" t="n">
-        <v>-0.61</v>
+        <v>18.27</v>
+      </c>
+      <c r="N20" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O20" s="29" t="n">
+        <v>0.46</v>
       </c>
       <c r="P20" s="46" t="n">
-        <v>-15.77</v>
+        <v>-21.24</v>
       </c>
       <c r="Q20" s="46" t="n">
-        <v>-1.1</v>
+        <v>-1.78</v>
       </c>
       <c r="R20" s="46" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="S20" s="46" t="n">
-        <v>-4.14</v>
-      </c>
-      <c r="T20" s="46" t="n">
-        <v>-0.02</v>
+        <v>-2.5</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T20" s="29" t="n">
+        <v>0.26</v>
       </c>
       <c r="U20" s="27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
+          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
@@ -3606,58 +3606,58 @@
         </is>
       </c>
       <c r="C21" s="33" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D21" s="33" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E21" s="33" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="F21" s="47" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="G21" s="33" t="n">
-        <v>7.79</v>
+        <v>0.31</v>
+      </c>
+      <c r="D21" s="47" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E21" s="47" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="F21" s="33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G21" s="47" t="n">
+        <v>-1.55</v>
       </c>
       <c r="H21" s="33" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="I21" s="33" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="J21" s="33" t="n">
-        <v>41.11</v>
-      </c>
-      <c r="K21" s="33" t="n">
-        <v>55.53</v>
-      </c>
-      <c r="L21" s="33" t="n">
-        <v>9.65</v>
+        <v>0.02</v>
+      </c>
+      <c r="I21" s="47" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="J21" s="47" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="K21" s="47" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="L21" s="47" t="n">
+        <v>-0.33</v>
       </c>
       <c r="M21" s="33" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="N21" s="33" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O21" s="33" t="n">
-        <v>0.51</v>
+        <v>10.65</v>
+      </c>
+      <c r="N21" s="47" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="O21" s="47" t="n">
+        <v>-0.61</v>
       </c>
       <c r="P21" s="47" t="n">
-        <v>-22.86</v>
+        <v>-15.77</v>
       </c>
       <c r="Q21" s="47" t="n">
-        <v>-1.53</v>
+        <v>-1.1</v>
       </c>
       <c r="R21" s="47" t="n">
-        <v>-2.22</v>
-      </c>
-      <c r="S21" s="33" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="T21" s="33" t="n">
-        <v>0.17</v>
+        <v>-1.48</v>
+      </c>
+      <c r="S21" s="47" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="T21" s="47" t="n">
+        <v>-0.02</v>
       </c>
       <c r="U21" s="31" t="inlineStr">
         <is>
@@ -3677,31 +3677,31 @@
         </is>
       </c>
       <c r="C22" s="46" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="D22" s="29" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="E22" s="29" t="n">
-        <v>8.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F22" s="29" t="n">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
       <c r="G22" s="29" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>6.45</v>
+        <v>6.46</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>25.36</v>
+        <v>25.37</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>70.98</v>
+        <v>71</v>
       </c>
       <c r="K22" s="29" t="n">
-        <v>88.48999999999999</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="L22" s="29" t="n">
         <v>13.84</v>
@@ -3859,17 +3859,17 @@
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>&gt; 7.0</t>
+          <t>&gt; 7.0%</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
-          <t>3.0 – 7.0</t>
+          <t>3.0% – 7.0%</t>
         </is>
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
-          <t>&lt; 3.0</t>
+          <t>&lt; 3.0%</t>
         </is>
       </c>
       <c r="F28" s="27" t="inlineStr">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="C29" s="31" t="inlineStr">
         <is>
-          <t>&gt; 0.0</t>
+          <t>&gt; 0.0%</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>-1.0 – 0.0</t>
+          <t>-1.0% – 0.0%</t>
         </is>
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
-          <t>&lt; -1.0</t>
+          <t>&lt; -1.0%</t>
         </is>
       </c>
       <c r="F29" s="31" t="inlineStr">
@@ -3923,17 +3923,17 @@
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>&lt; 0.7%</t>
+          <t>&lt; 0.7</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
         <is>
-          <t>1.0% – 0.7%</t>
+          <t>1.0 – 0.7</t>
         </is>
       </c>
       <c r="E30" s="27" t="inlineStr">
         <is>
-          <t>&gt; 1.0%</t>
+          <t>&gt; 1.0</t>
         </is>
       </c>
       <c r="F30" s="27" t="inlineStr">
@@ -4137,7 +4137,7 @@
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 10:02 v2.0</t>
+          <t>Generated 2026-05-04 10:06 v2.0</t>
         </is>
       </c>
     </row>
@@ -4232,13 +4232,13 @@
         </is>
       </c>
       <c r="D5" s="29" t="n">
-        <v>14.26530952530278</v>
+        <v>14.26510365921972</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>415.5184553004801</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>59.27499378337036</v>
+        <v>59.27413837180207</v>
       </c>
     </row>
     <row r="6">
@@ -4258,13 +4258,13 @@
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>13.23674325269094</v>
+        <v>13.236552230093</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>91.33928843906948</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>12.09034709951444</v>
+        <v>12.09017262083273</v>
       </c>
     </row>
     <row r="7">
@@ -4284,13 +4284,13 @@
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>8.459328799641117</v>
+        <v>8.459206721050242</v>
       </c>
       <c r="E7" s="29" t="n">
         <v>55.27743647935755</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>4.676100103801618</v>
+        <v>4.676032621886091</v>
       </c>
     </row>
     <row r="8">
@@ -4310,13 +4310,13 @@
         </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>15.36969361005393</v>
+        <v>15.36947180634083</v>
       </c>
       <c r="E8" s="33" t="n">
         <v>21.50000333786011</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.304484639180467</v>
+        <v>3.304436951374748</v>
       </c>
     </row>
     <row r="9">
@@ -4336,13 +4336,13 @@
         </is>
       </c>
       <c r="D9" s="29" t="n">
-        <v>8.500249996866843</v>
+        <v>8.500127327732415</v>
       </c>
       <c r="E9" s="29" t="n">
         <v>36.52500425066267</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>3.104716672672568</v>
+        <v>3.104671867766003</v>
       </c>
     </row>
     <row r="10">
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="D10" s="33" t="n">
-        <v>7.040736511754693</v>
+        <v>7.04063490520736</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>43.92423918752959</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>3.092589945986859</v>
+        <v>3.092545316083978</v>
       </c>
     </row>
     <row r="11">
@@ -4388,13 +4388,13 @@
         </is>
       </c>
       <c r="D11" s="29" t="n">
-        <v>7.343034913845621</v>
+        <v>7.34292894475797</v>
       </c>
       <c r="E11" s="29" t="n">
         <v>41.5263607345748</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>3.049295167189306</v>
+        <v>3.049251162083701</v>
       </c>
     </row>
     <row r="12">
@@ -4414,13 +4414,13 @@
         </is>
       </c>
       <c r="D12" s="33" t="n">
-        <v>12.31375315772519</v>
+        <v>12.3150185788605</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.58303716504107</v>
+        <v>16.59670043946933</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>2.041994262556988</v>
+        <v>2.043886742598471</v>
       </c>
     </row>
     <row r="13">
@@ -4440,13 +4440,13 @@
         </is>
       </c>
       <c r="D13" s="29" t="n">
-        <v>7.294415251161368</v>
+        <v>7.294309983715664</v>
       </c>
       <c r="E13" s="29" t="n">
         <v>20.50510328643176</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>1.495727381391869</v>
+        <v>1.495705796193401</v>
       </c>
     </row>
     <row r="14">
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="D14" s="33" t="n">
-        <v>6.176734980957511</v>
+        <v>6.176645843022274</v>
       </c>
       <c r="E14" s="33" t="n">
         <v>0</v>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="B18" s="28" t="n">
-        <v>52442.07356523337</v>
+        <v>52443.24177519698</v>
       </c>
       <c r="C18" s="29" t="n">
-        <v>92.42597375466755</v>
+        <v>92.42825096707226</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>6</v>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>41.77116920492907</v>
+        <v>41.77246629294275</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>19.52938126311098</v>
+        <v>19.5339356879204</v>
       </c>
     </row>
     <row r="26">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="B26" s="33" t="n">
-        <v>15.5217931241751</v>
+        <v>15.52144736535534</v>
       </c>
       <c r="C26" s="33" t="n">
         <v>29.01250379426139</v>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>10.66269639765878</v>
+        <v>10.66245887862393</v>
       </c>
       <c r="C27" s="29" t="n">
         <v>28.64311527060715</v>
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>24.14476795526446</v>
+        <v>24.14423011363721</v>
       </c>
       <c r="C28" s="33" t="n">
         <v>152.507853974924</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>7.899573317972592</v>
+        <v>7.899397349440786</v>
       </c>
       <c r="C29" s="29" t="n">
         <v>28.64311527060715</v>
@@ -4942,7 +4942,7 @@
     <row r="20">
       <c r="A20" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 10:02 v2.0</t>
+          <t>Generated 2026-05-04 10:06 v2.0</t>
         </is>
       </c>
     </row>

--- a/output/sample/portfolio_dashboard_sample.xlsx
+++ b/output/sample/portfolio_dashboard_sample.xlsx
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>80950.0840273767</v>
+        <v>80725.24431148739</v>
       </c>
       <c r="D5" s="2" t="n"/>
     </row>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>26810.0840273767</v>
+        <v>26585.24431148739</v>
       </c>
       <c r="D6" s="2" t="n"/>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>49.51991877978703</v>
+        <v>49.10462562151346</v>
       </c>
       <c r="D7" s="2" t="n"/>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>64.7846662610765</v>
+        <v>64.6865828709259</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>65</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>41.77246629294275</v>
+        <v>41.77736996416787</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>55</v>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>20.57948117485098</v>
+        <v>20.63680010575007</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>25</v>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>24.14423011363721</v>
+        <v>24.23467868773753</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>8</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>8.459206721050242</v>
+        <v>8.482767698189821</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>5</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>15.52144736535534</v>
+        <v>15.45140327227481</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>11</v>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>6.176645843022274</v>
+        <v>6.193849325134205</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>5</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>10.66245887862393</v>
+        <v>9.79204943317003</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>14</v>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>7.899397349440786</v>
+        <v>8.744498642649752</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>12</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="B21" s="28" t="n">
-        <v>12441.60034179688</v>
+        <v>12363.19946289062</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>15.36947180634083</v>
+        <v>15.31515892994493</v>
       </c>
       <c r="D21" s="30" t="n"/>
       <c r="E21" s="12" t="inlineStr">
@@ -1082,7 +1082,7 @@
         <v>11547.61339873075</v>
       </c>
       <c r="C22" s="33" t="n">
-        <v>14.26510365921972</v>
+        <v>14.30483549132784</v>
       </c>
       <c r="D22" s="30" t="n"/>
       <c r="E22" s="34" t="inlineStr">
@@ -1101,7 +1101,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>13.236552230093</v>
+        <v>13.27341929278388</v>
       </c>
       <c r="D23" s="30" t="n"/>
       <c r="E23" s="35" t="inlineStr">
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="B24" s="32" t="n">
-        <v>9969.017887574628</v>
+        <v>9953.269281914818</v>
       </c>
       <c r="C24" s="33" t="n">
-        <v>12.3150185788605</v>
+        <v>12.32981004493342</v>
       </c>
       <c r="D24" s="30" t="n"/>
       <c r="E24" s="34" t="inlineStr">
@@ -1132,19 +1132,19 @@
     <row r="25">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+          <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
       <c r="B25" s="28" t="n">
-        <v>6880.860214233398</v>
+        <v>6847.734948739668</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>8.500127327732415</v>
+        <v>8.482767698189821</v>
       </c>
       <c r="D25" s="30" t="n"/>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>Equities</t>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>Commodities</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
     <row r="27">
       <c r="A27" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 10:06 v2.0</t>
+          <t>Generated 2026-05-04 12:40 v2.0</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
     <row r="9">
       <c r="A9" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Equities 64.8% (tgt. 65.0%)</t>
+          <t xml:space="preserve">    Equities 64.7% (tgt. 65.0%)</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
     <row r="15">
       <c r="A15" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Dev ex-USA ex-EMU ex-JP 7.9% (tgt. 12.0%)</t>
+          <t xml:space="preserve">    Dev ex-USA ex-EMU ex-JP 8.7% (tgt. 12.0%)</t>
         </is>
       </c>
     </row>
@@ -1283,14 +1283,14 @@
     <row r="17">
       <c r="A17" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Eurozone EMU 10.7% (tgt. 14.0%)</t>
+          <t xml:space="preserve">    Eurozone EMU 9.8% (tgt. 14.0%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Japan 24.1% (tgt. 8.0%)</t>
+          <t xml:space="preserve">    Japan 24.2% (tgt. 8.0%)</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
     <row r="26">
       <c r="A26" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 10:06 v2.0</t>
+          <t>Generated 2026-05-04 12:40 v2.0</t>
         </is>
       </c>
     </row>
@@ -1540,25 +1540,25 @@
         <v>128</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>155.5200042724609</v>
+        <v>154.5399932861328</v>
       </c>
       <c r="J4" s="28" t="n">
         <v>10240</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>12441.60034179688</v>
+        <v>12363.19946289062</v>
       </c>
       <c r="L4" s="29" t="n">
-        <v>15.36947180634083</v>
+        <v>15.31515892994493</v>
       </c>
       <c r="M4" s="29" t="n">
-        <v>23.723934525499</v>
+        <v>23.67594368140368</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>2201.600341796875</v>
+        <v>2123.199462890625</v>
       </c>
       <c r="O4" s="29" t="n">
-        <v>21.50000333786011</v>
+        <v>20.73436975479126</v>
       </c>
       <c r="P4" s="27" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="Q4" s="27" t="inlineStr">
         <is>
-          <t>input_csv</t>
+          <t>index_geo_allocation (index: FTSE All-World)</t>
         </is>
       </c>
       <c r="R4" s="27" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="S4" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 10:06</t>
+          <t>2026-05-04 12:40</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>11547.61339873075</v>
       </c>
       <c r="L5" s="33" t="n">
-        <v>14.26510365921972</v>
+        <v>14.30483549132784</v>
       </c>
       <c r="M5" s="33" t="n">
-        <v>22.01925931320324</v>
+        <v>22.11406887865969</v>
       </c>
       <c r="N5" s="32" t="n">
         <v>9307.613398730755</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Q5" s="31" t="inlineStr">
         <is>
-          <t>input_csv</t>
+          <t>yfinance_top_holdings</t>
         </is>
       </c>
       <c r="R5" s="31" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="S5" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 10:06</t>
+          <t>2026-05-04 12:40</t>
         </is>
       </c>
     </row>
@@ -1698,25 +1698,25 @@
         <v>570</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>664.6011925049752</v>
+        <v>663.5512854609879</v>
       </c>
       <c r="J6" s="28" t="n">
         <v>8550</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>9969.017887574628</v>
+        <v>9953.269281914818</v>
       </c>
       <c r="L6" s="29" t="n">
-        <v>12.3150185788605</v>
+        <v>12.32981004493342</v>
       </c>
       <c r="M6" s="29" t="n">
-        <v>19.00915647111936</v>
+        <v>19.06084615651446</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>1419.017887574628</v>
+        <v>1403.269281914818</v>
       </c>
       <c r="O6" s="29" t="n">
-        <v>16.59670043946933</v>
+        <v>16.41250622122594</v>
       </c>
       <c r="P6" s="27" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="Q6" s="27" t="inlineStr">
         <is>
-          <t>input_csv</t>
+          <t>index_geo_allocation (index: S&amp;P 500)</t>
         </is>
       </c>
       <c r="R6" s="27" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="S6" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 10:06</t>
+          <t>2026-05-04 12:40</t>
         </is>
       </c>
     </row>
@@ -1777,25 +1777,25 @@
         <v>56</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>76.45400238037109</v>
+        <v>75.74800109863281</v>
       </c>
       <c r="J7" s="32" t="n">
         <v>5040</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>6880.860214233398</v>
+        <v>6817.320098876953</v>
       </c>
       <c r="L7" s="33" t="n">
-        <v>8.500127327732415</v>
+        <v>8.445090698730574</v>
       </c>
       <c r="M7" s="33" t="n">
-        <v>13.12058519137484</v>
+        <v>13.05539777171676</v>
       </c>
       <c r="N7" s="32" t="n">
-        <v>1840.860214233398</v>
+        <v>1777.320098876953</v>
       </c>
       <c r="O7" s="33" t="n">
-        <v>36.52500425066267</v>
+        <v>35.26428767613002</v>
       </c>
       <c r="P7" s="31" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Q7" s="31" t="inlineStr">
         <is>
-          <t>input_csv</t>
+          <t>index_geo_allocation (index: MSCI Emerging Markets)</t>
         </is>
       </c>
       <c r="R7" s="31" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="S7" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 10:06</t>
+          <t>2026-05-04 12:40</t>
         </is>
       </c>
     </row>
@@ -1856,25 +1856,25 @@
         <v>98</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>118.0950012207031</v>
+        <v>117.3399963378906</v>
       </c>
       <c r="J8" s="28" t="n">
         <v>4900</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>5904.750061035156</v>
+        <v>5866.999816894531</v>
       </c>
       <c r="L8" s="29" t="n">
-        <v>7.294309983715664</v>
+        <v>7.26786257128694</v>
       </c>
       <c r="M8" s="29" t="n">
-        <v>11.25931552123806</v>
+        <v>11.235502400535</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>1004.750061035156</v>
+        <v>966.9998168945312</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>20.50510328643176</v>
+        <v>19.73469014070472</v>
       </c>
       <c r="P8" s="27" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Q8" s="27" t="inlineStr">
         <is>
-          <t>input_csv</t>
+          <t>index_geo_allocation (index: MSCI World)</t>
         </is>
       </c>
       <c r="R8" s="27" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="S8" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 10:06</t>
+          <t>2026-05-04 12:40</t>
         </is>
       </c>
     </row>
@@ -1935,34 +1935,34 @@
         <v>33</v>
       </c>
       <c r="I9" s="32" t="n">
-        <v>47.49499893188477</v>
+        <v>47.25</v>
       </c>
       <c r="J9" s="32" t="n">
         <v>3960</v>
       </c>
       <c r="K9" s="32" t="n">
-        <v>5699.399871826172</v>
+        <v>5670</v>
       </c>
       <c r="L9" s="33" t="n">
-        <v>7.04063490520736</v>
+        <v>7.023825134702188</v>
       </c>
       <c r="M9" s="33" t="n">
-        <v>10.8677489775655</v>
+        <v>10.8582411111704</v>
       </c>
       <c r="N9" s="32" t="n">
-        <v>1739.399871826172</v>
+        <v>1710</v>
       </c>
       <c r="O9" s="33" t="n">
-        <v>43.92423918752959</v>
+        <v>43.18181818181818</v>
       </c>
       <c r="P9" s="31" t="inlineStr">
         <is>
-          <t>Eurozone EMU: 72, Dev ex-USA ex-EMU ex-JP: 27</t>
+          <t>Eurozone EMU: 64, Dev ex-USA ex-EMU ex-JP: 35</t>
         </is>
       </c>
       <c r="Q9" s="31" t="inlineStr">
         <is>
-          <t>input_csv</t>
+          <t>yfinance_top_holdings</t>
         </is>
       </c>
       <c r="R9" s="31" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="S9" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 10:06</t>
+          <t>2026-05-04 12:40</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>13.236552230093</v>
+        <v>13.27341929278388</v>
       </c>
       <c r="M10" s="29" t="n">
         <v>64.31917363528412</v>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="P10" s="27" t="inlineStr">
         <is>
-          <t>USA: 44, Dev ex-USA ex-EMU ex-JP: 24, Japan: 13, Eurozone EMU: 12, Emerging Markets: 5</t>
+          <t>Eurozone EMU</t>
         </is>
       </c>
       <c r="Q10" s="27" t="inlineStr">
         <is>
-          <t>input_csv</t>
+          <t>index_geo_allocation (ticker)</t>
         </is>
       </c>
       <c r="R10" s="27" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="S10" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 10:06</t>
+          <t>2026-05-04 12:40</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         <v>5944.107150852142</v>
       </c>
       <c r="L11" s="33" t="n">
-        <v>7.34292894475797</v>
+        <v>7.363380812966189</v>
       </c>
       <c r="M11" s="33" t="n">
         <v>35.68082636471589</v>
@@ -2115,12 +2115,12 @@
       </c>
       <c r="P11" s="31" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="Q11" s="31" t="inlineStr">
         <is>
-          <t>input_csv</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="R11" s="31" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="S11" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 10:06</t>
+          <t>2026-05-04 12:40</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
         <v>5000</v>
       </c>
       <c r="L12" s="29" t="n">
-        <v>6.176645843022274</v>
+        <v>6.193849325134205</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>100</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="S12" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 10:06</t>
+          <t>2026-05-04 12:40</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
         <v>6847.734948739668</v>
       </c>
       <c r="L13" s="33" t="n">
-        <v>8.459206721050242</v>
+        <v>8.482767698189821</v>
       </c>
       <c r="M13" s="33" t="n">
         <v>100</v>
@@ -2288,14 +2288,14 @@
       </c>
       <c r="S13" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 10:06</t>
+          <t>2026-05-04 12:40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 10:06 v2.0</t>
+          <t>Generated 2026-05-04 12:40 v2.0</t>
         </is>
       </c>
     </row>
@@ -2470,43 +2470,43 @@
         </is>
       </c>
       <c r="C5" s="44" t="n">
-        <v>0.44</v>
+        <v>0.15</v>
       </c>
       <c r="D5" s="44" t="n">
-        <v>0.64</v>
+        <v>0.34</v>
       </c>
       <c r="E5" s="44" t="n">
-        <v>6.09</v>
+        <v>5.78</v>
       </c>
       <c r="F5" s="44" t="n">
-        <v>4.19</v>
+        <v>3.88</v>
       </c>
       <c r="G5" s="44" t="n">
-        <v>6.76</v>
+        <v>6.45</v>
       </c>
       <c r="H5" s="44" t="n">
-        <v>7.17</v>
+        <v>6.85</v>
       </c>
       <c r="I5" s="44" t="n">
-        <v>22.21</v>
+        <v>21.85</v>
       </c>
       <c r="J5" s="44" t="n">
-        <v>49.17</v>
+        <v>48.73</v>
       </c>
       <c r="K5" s="44" t="n">
-        <v>45.34</v>
+        <v>44.91</v>
       </c>
       <c r="L5" s="44" t="n">
-        <v>7.95</v>
+        <v>7.89</v>
       </c>
       <c r="M5" s="44" t="n">
         <v>8.109999999999999</v>
       </c>
       <c r="N5" s="44" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="O5" s="44" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="P5" s="45" t="n">
         <v>-13.91</v>
@@ -2518,7 +2518,7 @@
         <v>-1.22</v>
       </c>
       <c r="S5" s="44" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="T5" s="44" t="n">
         <v>0.15</v>
@@ -2612,34 +2612,34 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6.63</v>
+        <v>6.56</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>4.45</v>
+        <v>4.39</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>6.37</v>
+        <v>6.31</v>
       </c>
       <c r="H7" s="33" t="n">
-        <v>6.51</v>
+        <v>6.44</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>23.67</v>
+        <v>23.59</v>
       </c>
       <c r="J7" s="33" t="n">
-        <v>56.14</v>
+        <v>56.05</v>
       </c>
       <c r="K7" s="33" t="n">
-        <v>58.72</v>
+        <v>58.62</v>
       </c>
       <c r="L7" s="33" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
       <c r="M7" s="33" t="n">
         <v>15.1</v>
@@ -2660,7 +2660,7 @@
         <v>-2.13</v>
       </c>
       <c r="S7" s="47" t="n">
-        <v>-0.49</v>
+        <v>-0.51</v>
       </c>
       <c r="T7" s="33" t="n">
         <v>0.78</v>
@@ -2824,35 +2824,35 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
-        <v>0</v>
+      <c r="C10" s="46" t="n">
+        <v>-0.06</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>5.95</v>
+        <v>5.88</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>3.96</v>
+        <v>3.89</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>5.35</v>
+        <v>5.28</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>21.72</v>
+        <v>21.64</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>55.67</v>
+        <v>55.57</v>
       </c>
       <c r="K10" s="29" t="n">
-        <v>63.27</v>
+        <v>63.17</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>10.47</v>
+        <v>10.45</v>
       </c>
       <c r="M10" s="29" t="n">
         <v>16.47</v>
@@ -2873,7 +2873,7 @@
         <v>-2.29</v>
       </c>
       <c r="S10" s="46" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="T10" s="29" t="n">
         <v>0.86</v>
@@ -3171,7 +3171,7 @@
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
         </is>
       </c>
       <c r="B15" s="31" t="inlineStr">
@@ -3180,58 +3180,58 @@
         </is>
       </c>
       <c r="C15" s="33" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="D15" s="33" t="n">
-        <v>1.26</v>
+        <v>0</v>
+      </c>
+      <c r="D15" s="47" t="n">
+        <v>-0.11</v>
       </c>
       <c r="E15" s="33" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="F15" s="33" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="G15" s="33" t="n">
-        <v>5.69</v>
+        <v>0.38</v>
+      </c>
+      <c r="F15" s="47" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G15" s="47" t="n">
+        <v>-0.64</v>
       </c>
       <c r="H15" s="33" t="n">
-        <v>6.09</v>
+        <v>0.09</v>
       </c>
       <c r="I15" s="33" t="n">
-        <v>23.3</v>
+        <v>0.12</v>
       </c>
       <c r="J15" s="33" t="n">
-        <v>63.11</v>
-      </c>
-      <c r="K15" s="33" t="n">
-        <v>75.62</v>
-      </c>
-      <c r="L15" s="33" t="n">
-        <v>12.23</v>
+        <v>7.86</v>
+      </c>
+      <c r="K15" s="47" t="n">
+        <v>-8.98</v>
+      </c>
+      <c r="L15" s="47" t="n">
+        <v>-1.87</v>
       </c>
       <c r="M15" s="33" t="n">
-        <v>14.24</v>
-      </c>
-      <c r="N15" s="33" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="O15" s="33" t="n">
-        <v>0.74</v>
+        <v>5.55</v>
+      </c>
+      <c r="N15" s="47" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="O15" s="47" t="n">
+        <v>-1.63</v>
       </c>
       <c r="P15" s="47" t="n">
-        <v>-21.73</v>
+        <v>-19.81</v>
       </c>
       <c r="Q15" s="47" t="n">
-        <v>-1.45</v>
+        <v>-0.55</v>
       </c>
       <c r="R15" s="47" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="S15" s="33" t="n">
-        <v>6.42</v>
+        <v>-0.77</v>
+      </c>
+      <c r="S15" s="47" t="n">
+        <v>-6</v>
       </c>
       <c r="T15" s="33" t="n">
-        <v>0.22</v>
+        <v>0.02</v>
       </c>
       <c r="U15" s="31" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
@@ -3251,58 +3251,58 @@
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>1.01</v>
+        <v>0.26</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>1.32</v>
+        <v>0.61</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>8.06</v>
+        <v>6.94</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>5.01</v>
+        <v>3.87</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>6.92</v>
+        <v>5.02</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>7.15</v>
+        <v>5.41</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>24.98</v>
+        <v>22.51</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>63.28</v>
+        <v>62.07</v>
       </c>
       <c r="K16" s="29" t="n">
-        <v>70.77</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="L16" s="29" t="n">
-        <v>11.59</v>
+        <v>12.08</v>
       </c>
       <c r="M16" s="29" t="n">
-        <v>13.81</v>
+        <v>14.24</v>
       </c>
       <c r="N16" s="29" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="O16" s="29" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="P16" s="46" t="n">
-        <v>-21.07</v>
+        <v>-21.73</v>
       </c>
       <c r="Q16" s="46" t="n">
-        <v>-1.39</v>
+        <v>-1.45</v>
       </c>
       <c r="R16" s="46" t="n">
-        <v>-2.13</v>
+        <v>-2.19</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>5.98</v>
+        <v>6.27</v>
       </c>
       <c r="T16" s="29" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="U16" s="27" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
@@ -3322,58 +3322,58 @@
         </is>
       </c>
       <c r="C17" s="33" t="n">
-        <v>2.22</v>
+        <v>0.38</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>1.8</v>
+        <v>0.68</v>
       </c>
       <c r="E17" s="33" t="n">
-        <v>13.03</v>
+        <v>7.38</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>9.31</v>
+        <v>4.35</v>
       </c>
       <c r="G17" s="33" t="n">
-        <v>16.96</v>
+        <v>6.24</v>
       </c>
       <c r="H17" s="33" t="n">
-        <v>16.56</v>
+        <v>6.48</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>41.25</v>
+        <v>24.19</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>69.29000000000001</v>
+        <v>62.25</v>
       </c>
       <c r="K17" s="33" t="n">
-        <v>42.65</v>
+        <v>69.69</v>
       </c>
       <c r="L17" s="33" t="n">
-        <v>7.64</v>
+        <v>11.45</v>
       </c>
       <c r="M17" s="33" t="n">
-        <v>18.83</v>
+        <v>13.8</v>
       </c>
       <c r="N17" s="33" t="n">
-        <v>0.19</v>
+        <v>0.54</v>
       </c>
       <c r="O17" s="33" t="n">
-        <v>0.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P17" s="47" t="n">
-        <v>-24.38</v>
+        <v>-21.07</v>
       </c>
       <c r="Q17" s="47" t="n">
-        <v>-1.59</v>
+        <v>-1.39</v>
       </c>
       <c r="R17" s="47" t="n">
-        <v>-2.59</v>
+        <v>-2.13</v>
       </c>
       <c r="S17" s="33" t="n">
-        <v>2.82</v>
+        <v>5.84</v>
       </c>
       <c r="T17" s="33" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="U17" s="31" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
@@ -3393,58 +3393,58 @@
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>0.21</v>
+        <v>1.27</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="E18" s="29" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="F18" s="46" t="n">
-        <v>-0.42</v>
+        <v>11.98</v>
+      </c>
+      <c r="F18" s="29" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="G18" s="29" t="n">
-        <v>7.79</v>
+        <v>15.88</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>2.83</v>
+        <v>15.48</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>15.17</v>
+        <v>39.95</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>41.11</v>
+        <v>67.73</v>
       </c>
       <c r="K18" s="29" t="n">
-        <v>55.53</v>
+        <v>41.34</v>
       </c>
       <c r="L18" s="29" t="n">
-        <v>9.65</v>
+        <v>7.44</v>
       </c>
       <c r="M18" s="29" t="n">
-        <v>14.94</v>
+        <v>18.82</v>
       </c>
       <c r="N18" s="29" t="n">
-        <v>0.38</v>
+        <v>0.18</v>
       </c>
       <c r="O18" s="29" t="n">
-        <v>0.51</v>
+        <v>0.25</v>
       </c>
       <c r="P18" s="46" t="n">
-        <v>-22.86</v>
+        <v>-24.38</v>
       </c>
       <c r="Q18" s="46" t="n">
-        <v>-1.53</v>
+        <v>-1.59</v>
       </c>
       <c r="R18" s="46" t="n">
-        <v>-2.22</v>
+        <v>-2.59</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>4.23</v>
+        <v>2.62</v>
       </c>
       <c r="T18" s="29" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="U18" s="27" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
+          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
@@ -3464,58 +3464,58 @@
         </is>
       </c>
       <c r="C19" s="33" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="D19" s="47" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="E19" s="33" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F19" s="47" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
+      </c>
+      <c r="E19" s="47" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="F19" s="33" t="n">
+        <v>0.9</v>
       </c>
       <c r="G19" s="47" t="n">
-        <v>-0.64</v>
+        <v>-1.55</v>
       </c>
       <c r="H19" s="33" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I19" s="33" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J19" s="33" t="n">
-        <v>7.86</v>
+        <v>0.02</v>
+      </c>
+      <c r="I19" s="47" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="J19" s="47" t="n">
+        <v>-0.82</v>
       </c>
       <c r="K19" s="47" t="n">
-        <v>-8.98</v>
+        <v>-1.61</v>
       </c>
       <c r="L19" s="47" t="n">
-        <v>-1.87</v>
+        <v>-0.33</v>
       </c>
       <c r="M19" s="33" t="n">
-        <v>5.55</v>
+        <v>10.65</v>
       </c>
       <c r="N19" s="47" t="n">
-        <v>-1.06</v>
+        <v>-0.41</v>
       </c>
       <c r="O19" s="47" t="n">
-        <v>-1.63</v>
+        <v>-0.61</v>
       </c>
       <c r="P19" s="47" t="n">
-        <v>-19.81</v>
+        <v>-15.77</v>
       </c>
       <c r="Q19" s="47" t="n">
-        <v>-0.55</v>
+        <v>-1.1</v>
       </c>
       <c r="R19" s="47" t="n">
-        <v>-0.77</v>
+        <v>-1.48</v>
       </c>
       <c r="S19" s="47" t="n">
-        <v>-6</v>
-      </c>
-      <c r="T19" s="33" t="n">
-        <v>0.02</v>
+        <v>-4.14</v>
+      </c>
+      <c r="T19" s="47" t="n">
+        <v>-0.02</v>
       </c>
       <c r="U19" s="31" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
+          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
@@ -3534,59 +3534,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
-        <v>0.04</v>
+      <c r="C20" s="46" t="n">
+        <v>-0.2</v>
       </c>
       <c r="D20" s="29" t="n">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="E20" s="29" t="n">
-        <v>9.6</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="F20" s="29" t="n">
-        <v>10.93</v>
+        <v>5.32</v>
       </c>
       <c r="G20" s="29" t="n">
-        <v>10.3</v>
+        <v>4.7</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>17.9</v>
+        <v>6.3</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>44.84</v>
+        <v>25.17</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>73.92</v>
+        <v>70.73</v>
       </c>
       <c r="K20" s="29" t="n">
-        <v>57.6</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="L20" s="29" t="n">
-        <v>9.539999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="M20" s="29" t="n">
-        <v>18.27</v>
+        <v>17.29</v>
       </c>
       <c r="N20" s="29" t="n">
-        <v>0.3</v>
+        <v>0.57</v>
       </c>
       <c r="O20" s="29" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="P20" s="46" t="n">
-        <v>-21.24</v>
+        <v>-22.73</v>
       </c>
       <c r="Q20" s="46" t="n">
-        <v>-1.78</v>
+        <v>-1.73</v>
       </c>
       <c r="R20" s="46" t="n">
-        <v>-2.5</v>
+        <v>-2.53</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>3.42</v>
+        <v>6.35</v>
       </c>
       <c r="T20" s="29" t="n">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="U20" s="27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
+          <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
@@ -3605,59 +3605,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C21" s="33" t="n">
-        <v>0.31</v>
+      <c r="C21" s="47" t="n">
+        <v>-0.1</v>
       </c>
       <c r="D21" s="47" t="n">
-        <v>-0.7</v>
+        <v>-2.09</v>
       </c>
       <c r="E21" s="47" t="n">
-        <v>-1.11</v>
+        <v>-4.21</v>
       </c>
       <c r="F21" s="33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G21" s="47" t="n">
-        <v>-1.55</v>
+        <v>0.51</v>
+      </c>
+      <c r="G21" s="33" t="n">
+        <v>13.93</v>
       </c>
       <c r="H21" s="33" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I21" s="47" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="J21" s="47" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="K21" s="47" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="L21" s="47" t="n">
-        <v>-0.33</v>
+        <v>7.54</v>
+      </c>
+      <c r="I21" s="33" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="J21" s="33" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="K21" s="33" t="n">
+        <v>165.56</v>
+      </c>
+      <c r="L21" s="33" t="n">
+        <v>21.61</v>
       </c>
       <c r="M21" s="33" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="N21" s="47" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="O21" s="47" t="n">
-        <v>-0.61</v>
+        <v>17.9</v>
+      </c>
+      <c r="N21" s="33" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="O21" s="33" t="n">
+        <v>1.36</v>
       </c>
       <c r="P21" s="47" t="n">
-        <v>-15.77</v>
+        <v>-15.94</v>
       </c>
       <c r="Q21" s="47" t="n">
-        <v>-1.1</v>
+        <v>-1.75</v>
       </c>
       <c r="R21" s="47" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="S21" s="47" t="n">
-        <v>-4.14</v>
-      </c>
-      <c r="T21" s="47" t="n">
-        <v>-0.02</v>
+        <v>-2.57</v>
+      </c>
+      <c r="S21" s="33" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="T21" s="33" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="U21" s="31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
+          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
@@ -3676,59 +3676,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C22" s="46" t="n">
-        <v>-0.04</v>
+      <c r="C22" s="29" t="n">
+        <v>0.04</v>
       </c>
       <c r="D22" s="29" t="n">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="E22" s="29" t="n">
-        <v>8.890000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="F22" s="29" t="n">
-        <v>5.49</v>
+        <v>10.93</v>
       </c>
       <c r="G22" s="29" t="n">
-        <v>4.86</v>
+        <v>10.3</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>6.46</v>
+        <v>17.9</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>25.37</v>
+        <v>44.84</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>71</v>
+        <v>73.92</v>
       </c>
       <c r="K22" s="29" t="n">
-        <v>88.51000000000001</v>
+        <v>57.6</v>
       </c>
       <c r="L22" s="29" t="n">
-        <v>13.84</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M22" s="29" t="n">
-        <v>17.29</v>
+        <v>18.27</v>
       </c>
       <c r="N22" s="29" t="n">
-        <v>0.57</v>
+        <v>0.3</v>
       </c>
       <c r="O22" s="29" t="n">
-        <v>0.79</v>
+        <v>0.46</v>
       </c>
       <c r="P22" s="46" t="n">
-        <v>-22.73</v>
+        <v>-21.24</v>
       </c>
       <c r="Q22" s="46" t="n">
-        <v>-1.73</v>
+        <v>-1.78</v>
       </c>
       <c r="R22" s="46" t="n">
-        <v>-2.53</v>
+        <v>-2.5</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>6.38</v>
+        <v>3.42</v>
       </c>
       <c r="T22" s="29" t="n">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="U22" s="27" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>Invesco Physical Gold ETC</t>
+          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
       <c r="B23" s="31" t="inlineStr">
@@ -3748,58 +3748,58 @@
         </is>
       </c>
       <c r="C23" s="47" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="D23" s="47" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="E23" s="47" t="n">
-        <v>-4.21</v>
-      </c>
-      <c r="F23" s="33" t="n">
-        <v>0.51</v>
+        <v>-0.31</v>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E23" s="33" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="F23" s="47" t="n">
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G23" s="33" t="n">
-        <v>13.93</v>
+        <v>7.24</v>
       </c>
       <c r="H23" s="33" t="n">
-        <v>7.54</v>
+        <v>2.3</v>
       </c>
       <c r="I23" s="33" t="n">
-        <v>39.11</v>
+        <v>14.57</v>
       </c>
       <c r="J23" s="33" t="n">
-        <v>114.75</v>
+        <v>40.38</v>
       </c>
       <c r="K23" s="33" t="n">
-        <v>165.56</v>
+        <v>54.73</v>
       </c>
       <c r="L23" s="33" t="n">
-        <v>21.61</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M23" s="33" t="n">
-        <v>17.9</v>
+        <v>14.94</v>
       </c>
       <c r="N23" s="33" t="n">
-        <v>0.98</v>
+        <v>0.37</v>
       </c>
       <c r="O23" s="33" t="n">
-        <v>1.36</v>
+        <v>0.5</v>
       </c>
       <c r="P23" s="47" t="n">
-        <v>-15.94</v>
+        <v>-22.86</v>
       </c>
       <c r="Q23" s="47" t="n">
-        <v>-1.75</v>
+        <v>-1.53</v>
       </c>
       <c r="R23" s="47" t="n">
-        <v>-2.57</v>
+        <v>-2.22</v>
       </c>
       <c r="S23" s="33" t="n">
-        <v>17.05</v>
+        <v>4.11</v>
       </c>
       <c r="T23" s="33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="U23" s="31" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 10:06 v2.0</t>
+          <t>Generated 2026-05-04 12:40 v2.0</t>
         </is>
       </c>
     </row>
@@ -4232,13 +4232,13 @@
         </is>
       </c>
       <c r="D5" s="29" t="n">
-        <v>14.26510365921972</v>
+        <v>14.30483549132784</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>415.5184553004801</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>59.27413837180207</v>
+        <v>59.43923146684028</v>
       </c>
     </row>
     <row r="6">
@@ -4258,13 +4258,13 @@
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>13.236552230093</v>
+        <v>13.27341929278388</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>91.33928843906948</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>12.09017262083273</v>
+        <v>12.12384673356297</v>
       </c>
     </row>
     <row r="7">
@@ -4284,13 +4284,13 @@
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>8.459206721050242</v>
+        <v>8.482767698189821</v>
       </c>
       <c r="E7" s="29" t="n">
         <v>55.27743647935755</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>4.676032621886091</v>
+        <v>4.689056526058339</v>
       </c>
     </row>
     <row r="8">
@@ -4310,39 +4310,39 @@
         </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>15.36947180634083</v>
+        <v>15.31515892994493</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>21.50000333786011</v>
+        <v>20.73436975479126</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.304436951374748</v>
+        <v>3.175501681068715</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>LU0292107645</t>
+          <t>IE00B1FZS798</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>XMME.DE</t>
+          <t>IBTM.L</t>
         </is>
       </c>
       <c r="D9" s="29" t="n">
-        <v>8.500127327732415</v>
+        <v>7.363380812966189</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>36.52500425066267</v>
+        <v>41.5263607345748</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>3.104671867766003</v>
+        <v>3.057744078652807</v>
       </c>
     </row>
     <row r="10">
@@ -4362,39 +4362,39 @@
         </is>
       </c>
       <c r="D10" s="33" t="n">
-        <v>7.04063490520736</v>
+        <v>7.023825134702188</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>43.92423918752959</v>
+        <v>43.18181818181818</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>3.092545316083978</v>
+        <v>3.033015399075945</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>IE00B1FZS798</t>
+          <t>LU0292107645</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>IBTM.L</t>
+          <t>XMME.DE</t>
         </is>
       </c>
       <c r="D11" s="29" t="n">
-        <v>7.34292894475797</v>
+        <v>8.445090698730574</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>41.5263607345748</v>
+        <v>35.26428767613002</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>3.049251162083701</v>
+        <v>2.978101078510449</v>
       </c>
     </row>
     <row r="12">
@@ -4414,13 +4414,13 @@
         </is>
       </c>
       <c r="D12" s="33" t="n">
-        <v>12.3150185788605</v>
+        <v>12.32981004493342</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.59670043946933</v>
+        <v>16.41250622122594</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>2.043886742598471</v>
+        <v>2.023630840690039</v>
       </c>
     </row>
     <row r="13">
@@ -4440,13 +4440,13 @@
         </is>
       </c>
       <c r="D13" s="29" t="n">
-        <v>7.294309983715664</v>
+        <v>7.26786257128694</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>20.50510328643176</v>
+        <v>19.73469014070472</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>1.495705796193401</v>
+        <v>1.434290158295732</v>
       </c>
     </row>
     <row r="14">
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="D14" s="33" t="n">
-        <v>6.176645843022274</v>
+        <v>6.193849325134205</v>
       </c>
       <c r="E14" s="33" t="n">
         <v>0</v>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="B18" s="28" t="n">
-        <v>52443.24177519698</v>
+        <v>52218.40205930769</v>
       </c>
       <c r="C18" s="29" t="n">
-        <v>92.42825096707226</v>
+        <v>91.8076878791917</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>6</v>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>41.77246629294275</v>
+        <v>41.77736996416787</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>19.5339356879204</v>
+        <v>18.9605220389073</v>
       </c>
     </row>
     <row r="26">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="B26" s="33" t="n">
-        <v>15.52144736535534</v>
+        <v>15.45140327227481</v>
       </c>
       <c r="C26" s="33" t="n">
-        <v>29.01250379426139</v>
+        <v>27.99932871546064</v>
       </c>
     </row>
     <row r="27">
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>10.66245887862393</v>
+        <v>9.79204943317003</v>
       </c>
       <c r="C27" s="29" t="n">
-        <v>28.64311527060715</v>
+        <v>27.88362602577139</v>
       </c>
     </row>
     <row r="28">
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>24.14423011363721</v>
+        <v>24.23467868773753</v>
       </c>
       <c r="C28" s="33" t="n">
-        <v>152.507853974924</v>
+        <v>151.9958383986587</v>
       </c>
     </row>
     <row r="29">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>7.899397349440786</v>
+        <v>8.744498642649752</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>28.64311527060715</v>
+        <v>27.88362602577139</v>
       </c>
     </row>
   </sheetData>
@@ -4942,7 +4942,7 @@
     <row r="20">
       <c r="A20" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 10:06 v2.0</t>
+          <t>Generated 2026-05-04 12:40 v2.0</t>
         </is>
       </c>
     </row>

--- a/output/sample/portfolio_dashboard_sample.xlsx
+++ b/output/sample/portfolio_dashboard_sample.xlsx
@@ -12,7 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Return Contribution" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentation" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;€&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;€&quot;+#,##0.00;&quot;€&quot;-#,##0.00;&quot;€&quot;0.00"/>
     <numFmt numFmtId="166" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;;0.00&quot;%&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -148,8 +148,8 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0064748B"/>
-      <sz val="9"/>
+      <color rgb="00DC2626"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -254,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -356,11 +356,58 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -383,17 +430,14 @@
     <xf numFmtId="2" fontId="23" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -817,7 +861,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>80725.24431148739</v>
+        <v>80819.52608965823</v>
       </c>
       <c r="D5" s="2" t="n"/>
     </row>
@@ -828,7 +872,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>26585.24431148739</v>
+        <v>26679.52608965823</v>
       </c>
       <c r="D6" s="2" t="n"/>
     </row>
@@ -839,7 +883,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>49.10462562151346</v>
+        <v>49.27877002153349</v>
       </c>
       <c r="D7" s="2" t="n"/>
     </row>
@@ -903,7 +947,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>64.6865828709259</v>
+        <v>64.72777850669991</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>65</v>
@@ -915,7 +959,7 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>41.77736996416787</v>
+        <v>41.78590318582933</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>55</v>
@@ -928,7 +972,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>20.63680010575007</v>
+        <v>20.61272579717805</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>25</v>
@@ -940,7 +984,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>24.23467868773753</v>
+        <v>24.19736373853591</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>8</v>
@@ -953,7 +997,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>8.482767698189821</v>
+        <v>8.472871940801831</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>5</v>
@@ -965,7 +1009,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>15.45140327227481</v>
+        <v>15.49054543942014</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>11</v>
@@ -978,7 +1022,7 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>6.193849325134205</v>
+        <v>6.186623755320196</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>5</v>
@@ -990,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>9.79204943317003</v>
+        <v>9.782738357331008</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>14</v>
@@ -1004,7 +1048,7 @@
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>8.744498642649752</v>
+        <v>8.743449278883624</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>12</v>
@@ -1060,10 +1104,10 @@
         </is>
       </c>
       <c r="B21" s="28" t="n">
-        <v>12363.19946289062</v>
+        <v>12400</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>15.31515892994493</v>
+        <v>15.34282691319409</v>
       </c>
       <c r="D21" s="30" t="n"/>
       <c r="E21" s="12" t="inlineStr">
@@ -1082,7 +1126,7 @@
         <v>11547.61339873075</v>
       </c>
       <c r="C22" s="33" t="n">
-        <v>14.30483549132784</v>
+        <v>14.2881478739683</v>
       </c>
       <c r="D22" s="30" t="n"/>
       <c r="E22" s="34" t="inlineStr">
@@ -1101,7 +1145,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>13.27341929278388</v>
+        <v>13.25793489645195</v>
       </c>
       <c r="D23" s="30" t="n"/>
       <c r="E23" s="35" t="inlineStr">
@@ -1117,10 +1161,10 @@
         </is>
       </c>
       <c r="B24" s="32" t="n">
-        <v>9953.269281914818</v>
+        <v>9961.430530910857</v>
       </c>
       <c r="C24" s="33" t="n">
-        <v>12.32981004493342</v>
+        <v>12.325524551901</v>
       </c>
       <c r="D24" s="30" t="n"/>
       <c r="E24" s="34" t="inlineStr">
@@ -1132,19 +1176,19 @@
     <row r="25">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>Invesco Physical Gold ETC</t>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
       <c r="B25" s="28" t="n">
-        <v>6847.734948739668</v>
+        <v>6848.640060424805</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>8.482767698189821</v>
+        <v>8.473991857892328</v>
       </c>
       <c r="D25" s="30" t="n"/>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>Commodities</t>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Equities</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1198,7 @@
     <row r="27">
       <c r="A27" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 12:40 v2.0</t>
+          <t>Generated 2026-05-04 13:06 v2.0</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1183,6 +1227,8 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1192,177 +1238,492 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>REBALANCING + LUMP SUM ALLOCATION (1000.0 EUR) — NO SELL</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="27" t="inlineStr">
-        <is>
-          <t>No rebalancing needed — portfolio is aligned with targets</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="37" t="inlineStr">
-        <is>
-          <t>Post-Rebalancing Verification</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="38" t="inlineStr">
-        <is>
-          <t>✗  Asset Allocation</t>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="37" t="inlineStr">
+        <is>
+          <t>●  Action needed — largest deviation 16.2% (&gt;5.0%). Rebalancing recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>REBALANCING ACTIONS · lump sum 1000.0 EUR · no-sell mode</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>No actions within the current tolerance and no-sell / min-transaction constraints.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Equities 64.7% (tgt. 65.0%)</t>
-        </is>
-      </c>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ALLOCATION DEVIATIONS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Fixed Income 20.6% (tgt. 25.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Cash &amp; Cash Equivalents 6.2% (tgt. 5.0%)</t>
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>Ordered by |delta|. Threshold ±2.5% (green), ±5.0% (amber), beyond (red).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Commodities 8.5% (tgt. 5.0%)</t>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Current %</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Target %</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Delta (pp)</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Alternative 0.0% (tgt. 0.0%)</t>
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="n">
+        <v>24.19736373853591</v>
+      </c>
+      <c r="D13" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="40" t="n">
+        <v>16.19736373853591</v>
+      </c>
+      <c r="F13" s="41" t="inlineStr">
+        <is>
+          <t>● Action</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
-        <is>
-          <t>✗  Geo Allocation</t>
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="C14" s="42" t="n">
+        <v>41.78590318582933</v>
+      </c>
+      <c r="D14" s="42" t="n">
+        <v>55</v>
+      </c>
+      <c r="E14" s="43" t="n">
+        <v>-13.21409681417067</v>
+      </c>
+      <c r="F14" s="44" t="inlineStr">
+        <is>
+          <t>● Action</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Dev ex-USA ex-EMU ex-JP 8.7% (tgt. 12.0%)</t>
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>Emerging Markets</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="C15" s="39" t="n">
+        <v>15.49054543942014</v>
+      </c>
+      <c r="D15" s="39" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" s="45" t="n">
+        <v>4.490545439420137</v>
+      </c>
+      <c r="F15" s="46" t="inlineStr">
+        <is>
+          <t>● Drift</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Emerging Markets 15.5% (tgt. 11.0%)</t>
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C16" s="42" t="n">
+        <v>20.61272579717805</v>
+      </c>
+      <c r="D16" s="42" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="47" t="n">
+        <v>-4.387274202821946</v>
+      </c>
+      <c r="F16" s="48" t="inlineStr">
+        <is>
+          <t>● Drift</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Eurozone EMU 9.8% (tgt. 14.0%)</t>
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>Eurozone EMU</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="n">
+        <v>9.782738357331008</v>
+      </c>
+      <c r="D17" s="39" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" s="45" t="n">
+        <v>-4.217261642668992</v>
+      </c>
+      <c r="F17" s="46" t="inlineStr">
+        <is>
+          <t>● Drift</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Japan 24.2% (tgt. 8.0%)</t>
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C18" s="42" t="n">
+        <v>8.472871940801831</v>
+      </c>
+      <c r="D18" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="47" t="n">
+        <v>3.472871940801831</v>
+      </c>
+      <c r="F18" s="48" t="inlineStr">
+        <is>
+          <t>● Drift</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    USA 41.8% (tgt. 55.0%)</t>
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Dev ex-USA ex-EMU ex-JP</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="n">
+        <v>8.743449278883624</v>
+      </c>
+      <c r="D19" s="39" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="45" t="n">
+        <v>-3.256550721116376</v>
+      </c>
+      <c r="F19" s="46" t="inlineStr">
+        <is>
+          <t>● Drift</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t>✗  Per-Holding Equity Targets</t>
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>Cash &amp; Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C20" s="42" t="n">
+        <v>6.186623755320196</v>
+      </c>
+      <c r="D20" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="49" t="n">
+        <v>1.186623755320196</v>
+      </c>
+      <c r="F20" s="50" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    No targets set</t>
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Equities</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="n">
+        <v>64.72777850669991</v>
+      </c>
+      <c r="D21" s="39" t="n">
+        <v>65</v>
+      </c>
+      <c r="E21" s="51" t="n">
+        <v>-0.2722214933000942</v>
+      </c>
+      <c r="F21" s="52" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t>✗  Per-Holding FI Targets</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    IEAG.L 64.3% (tgt. 1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    IBTM.L 35.7% (tgt. 1%)</t>
-        </is>
-      </c>
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>Alternative</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="50" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SOLVER PARAMETERS</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-04 12:40 v2.0</t>
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="53" t="inlineStr">
+        <is>
+          <t>Alert threshold</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>±2.5%</t>
+        </is>
+      </c>
+      <c r="G27" s="27" t="inlineStr">
+        <is>
+          <t>Deviation at which a category turns amber (green below, red beyond 2×)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="54" t="inlineStr">
+        <is>
+          <t>Solver tolerance</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G28" s="31" t="inlineStr">
+        <is>
+          <t>Actual tolerance the optimizer converged at (progressive up to max)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="53" t="inlineStr">
+        <is>
+          <t>Max tolerance</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>±2.0%</t>
+        </is>
+      </c>
+      <c r="G29" s="27" t="inlineStr">
+        <is>
+          <t>Cap on solver tolerance (from config.rebalancing_max_tolerance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="54" t="inlineStr">
+        <is>
+          <t>Min transaction</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>0.0 EUR</t>
+        </is>
+      </c>
+      <c r="G30" s="31" t="inlineStr">
+        <is>
+          <t>Trades below this amount are skipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="53" t="inlineStr">
+        <is>
+          <t>Lump sum</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>1000.0 EUR</t>
+        </is>
+      </c>
+      <c r="G31" s="27" t="inlineStr">
+        <is>
+          <t>Additional cash to deploy in the rebalance</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="54" t="inlineStr">
+        <is>
+          <t>No-sell mode</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="G32" s="31" t="inlineStr">
+        <is>
+          <t>If enabled, the solver can only buy, never sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="36" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-04 13:06 v2.0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A3:E3"/>
+  <mergeCells count="6">
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1540,25 +1901,25 @@
         <v>128</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>154.5399932861328</v>
+        <v>155</v>
       </c>
       <c r="J4" s="28" t="n">
         <v>10240</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>12363.19946289062</v>
+        <v>12400</v>
       </c>
       <c r="L4" s="29" t="n">
-        <v>15.31515892994493</v>
+        <v>15.34282691319409</v>
       </c>
       <c r="M4" s="29" t="n">
-        <v>23.67594368140368</v>
+        <v>23.70362040403714</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>2123.199462890625</v>
+        <v>2160</v>
       </c>
       <c r="O4" s="29" t="n">
-        <v>20.73436975479126</v>
+        <v>21.09375</v>
       </c>
       <c r="P4" s="27" t="inlineStr">
         <is>
@@ -1577,7 +1938,7 @@
       </c>
       <c r="S4" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40</t>
+          <t>2026-05-04 13:06</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1989,10 @@
         <v>11547.61339873075</v>
       </c>
       <c r="L5" s="33" t="n">
-        <v>14.30483549132784</v>
+        <v>14.2881478739683</v>
       </c>
       <c r="M5" s="33" t="n">
-        <v>22.11406887865969</v>
+        <v>22.07421327226508</v>
       </c>
       <c r="N5" s="32" t="n">
         <v>9307.613398730755</v>
@@ -1656,7 +2017,7 @@
       </c>
       <c r="S5" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40</t>
+          <t>2026-05-04 13:06</t>
         </is>
       </c>
     </row>
@@ -1698,25 +2059,25 @@
         <v>570</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>663.5512854609879</v>
+        <v>664.0953687273905</v>
       </c>
       <c r="J6" s="28" t="n">
         <v>8550</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>9953.269281914818</v>
+        <v>9961.430530910857</v>
       </c>
       <c r="L6" s="29" t="n">
-        <v>12.32981004493342</v>
+        <v>12.325524551901</v>
       </c>
       <c r="M6" s="29" t="n">
-        <v>19.06084615651446</v>
+        <v>19.04209419241106</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>1403.269281914818</v>
+        <v>1411.430530910857</v>
       </c>
       <c r="O6" s="29" t="n">
-        <v>16.41250622122594</v>
+        <v>16.50795942585797</v>
       </c>
       <c r="P6" s="27" t="inlineStr">
         <is>
@@ -1735,7 +2096,7 @@
       </c>
       <c r="S6" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40</t>
+          <t>2026-05-04 13:06</t>
         </is>
       </c>
     </row>
@@ -1777,25 +2138,25 @@
         <v>56</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>75.74800109863281</v>
+        <v>76.09600067138672</v>
       </c>
       <c r="J7" s="32" t="n">
         <v>5040</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>6817.320098876953</v>
+        <v>6848.640060424805</v>
       </c>
       <c r="L7" s="33" t="n">
-        <v>8.445090698730574</v>
+        <v>8.473991857892328</v>
       </c>
       <c r="M7" s="33" t="n">
-        <v>13.05539777171676</v>
+        <v>13.09173905453158</v>
       </c>
       <c r="N7" s="32" t="n">
-        <v>1777.320098876953</v>
+        <v>1808.640060424805</v>
       </c>
       <c r="O7" s="33" t="n">
-        <v>35.26428767613002</v>
+        <v>35.88571548461914</v>
       </c>
       <c r="P7" s="31" t="inlineStr">
         <is>
@@ -1814,7 +2175,7 @@
       </c>
       <c r="S7" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40</t>
+          <t>2026-05-04 13:06</t>
         </is>
       </c>
     </row>
@@ -1856,25 +2217,25 @@
         <v>98</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>117.3399963378906</v>
+        <v>117.6999969482422</v>
       </c>
       <c r="J8" s="28" t="n">
         <v>4900</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>5866.999816894531</v>
+        <v>5884.999847412109</v>
       </c>
       <c r="L8" s="29" t="n">
-        <v>7.26786257128694</v>
+        <v>7.281655971211097</v>
       </c>
       <c r="M8" s="29" t="n">
-        <v>11.235502400535</v>
+        <v>11.24966148878009</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>966.9998168945312</v>
+        <v>984.9998474121094</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>19.73469014070472</v>
+        <v>20.10203770228795</v>
       </c>
       <c r="P8" s="27" t="inlineStr">
         <is>
@@ -1893,7 +2254,7 @@
       </c>
       <c r="S8" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40</t>
+          <t>2026-05-04 13:06</t>
         </is>
       </c>
     </row>
@@ -1944,10 +2305,10 @@
         <v>5670</v>
       </c>
       <c r="L9" s="33" t="n">
-        <v>7.023825134702188</v>
+        <v>7.015631338533103</v>
       </c>
       <c r="M9" s="33" t="n">
-        <v>10.8582411111704</v>
+        <v>10.83867158797505</v>
       </c>
       <c r="N9" s="32" t="n">
         <v>1710</v>
@@ -1972,7 +2333,7 @@
       </c>
       <c r="S9" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40</t>
+          <t>2026-05-04 13:06</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2384,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>13.27341929278388</v>
+        <v>13.25793489645195</v>
       </c>
       <c r="M10" s="29" t="n">
         <v>64.31917363528412</v>
@@ -2051,7 +2412,7 @@
       </c>
       <c r="S10" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40</t>
+          <t>2026-05-04 13:06</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2463,7 @@
         <v>5944.107150852142</v>
       </c>
       <c r="L11" s="33" t="n">
-        <v>7.363380812966189</v>
+        <v>7.354790900726102</v>
       </c>
       <c r="M11" s="33" t="n">
         <v>35.68082636471589</v>
@@ -2130,7 +2491,7 @@
       </c>
       <c r="S11" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40</t>
+          <t>2026-05-04 13:06</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2542,7 @@
         <v>5000</v>
       </c>
       <c r="L12" s="29" t="n">
-        <v>6.193849325134205</v>
+        <v>6.186623755320196</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>100</v>
@@ -2209,7 +2570,7 @@
       </c>
       <c r="S12" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40</t>
+          <t>2026-05-04 13:06</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2590,7 @@
           <t>IE00B579F325</t>
         </is>
       </c>
-      <c r="D13" s="40" t="inlineStr">
+      <c r="D13" s="55" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
@@ -2260,7 +2621,7 @@
         <v>6847.734948739668</v>
       </c>
       <c r="L13" s="33" t="n">
-        <v>8.482767698189821</v>
+        <v>8.472871940801831</v>
       </c>
       <c r="M13" s="33" t="n">
         <v>100</v>
@@ -2288,14 +2649,14 @@
       </c>
       <c r="S13" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40</t>
+          <t>2026-05-04 13:06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 12:40 v2.0</t>
+          <t>Generated 2026-05-04 13:06 v2.0</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2706,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="41" t="inlineStr">
+      <c r="A2" s="56" t="inlineStr">
         <is>
           <t>Period returns (1D–5Y) and risk metrics calculated on available history per instrument (max 5 years). α/β computed vs S&amp;P 500.</t>
         </is>
@@ -2459,71 +2820,71 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>** TOTAL PORTFOLIO **</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr">
         <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="C5" s="44" t="n">
+      <c r="C5" s="59" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D5" s="59" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E5" s="59" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="F5" s="59" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="G5" s="59" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="H5" s="59" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="I5" s="59" t="n">
+        <v>22</v>
+      </c>
+      <c r="J5" s="59" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="K5" s="59" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="L5" s="59" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="M5" s="59" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="N5" s="59" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="O5" s="59" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="P5" s="60" t="n">
+        <v>-13.91</v>
+      </c>
+      <c r="Q5" s="60" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="R5" s="60" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="S5" s="59" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T5" s="59" t="n">
         <v>0.15</v>
       </c>
-      <c r="D5" s="44" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E5" s="44" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="F5" s="44" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="G5" s="44" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="H5" s="44" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="I5" s="44" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="J5" s="44" t="n">
-        <v>48.73</v>
-      </c>
-      <c r="K5" s="44" t="n">
-        <v>44.91</v>
-      </c>
-      <c r="L5" s="44" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="M5" s="44" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="N5" s="44" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="O5" s="44" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="P5" s="45" t="n">
-        <v>-13.91</v>
-      </c>
-      <c r="Q5" s="45" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="R5" s="45" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="S5" s="44" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T5" s="44" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="U5" s="43" t="inlineStr">
+      <c r="U5" s="58" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -2579,13 +2940,13 @@
       <c r="O6" s="29" t="n">
         <v>0.73</v>
       </c>
-      <c r="P6" s="46" t="n">
+      <c r="P6" s="61" t="n">
         <v>-20.22</v>
       </c>
-      <c r="Q6" s="46" t="n">
+      <c r="Q6" s="61" t="n">
         <v>-1.4</v>
       </c>
-      <c r="R6" s="46" t="n">
+      <c r="R6" s="61" t="n">
         <v>-2.13</v>
       </c>
       <c r="S6" s="29" t="n">
@@ -2612,34 +2973,34 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6.56</v>
+        <v>6.62</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>4.39</v>
+        <v>4.45</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>6.31</v>
+        <v>6.37</v>
       </c>
       <c r="H7" s="33" t="n">
-        <v>6.44</v>
+        <v>6.5</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>23.59</v>
+        <v>23.66</v>
       </c>
       <c r="J7" s="33" t="n">
-        <v>56.05</v>
+        <v>56.14</v>
       </c>
       <c r="K7" s="33" t="n">
-        <v>58.62</v>
+        <v>58.71</v>
       </c>
       <c r="L7" s="33" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
       <c r="M7" s="33" t="n">
         <v>15.1</v>
@@ -2650,17 +3011,17 @@
       <c r="O7" s="33" t="n">
         <v>0.55</v>
       </c>
-      <c r="P7" s="47" t="n">
+      <c r="P7" s="62" t="n">
         <v>-20.07</v>
       </c>
-      <c r="Q7" s="47" t="n">
+      <c r="Q7" s="62" t="n">
         <v>-1.44</v>
       </c>
-      <c r="R7" s="47" t="n">
+      <c r="R7" s="62" t="n">
         <v>-2.13</v>
       </c>
-      <c r="S7" s="47" t="n">
-        <v>-0.51</v>
+      <c r="S7" s="62" t="n">
+        <v>-0.49</v>
       </c>
       <c r="T7" s="33" t="n">
         <v>0.78</v>
@@ -2682,10 +3043,10 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C8" s="46" t="n">
+      <c r="C8" s="61" t="n">
         <v>-0.59</v>
       </c>
-      <c r="D8" s="46" t="n">
+      <c r="D8" s="61" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" s="29" t="n">
@@ -2721,16 +3082,16 @@
       <c r="O8" s="29" t="n">
         <v>0.44</v>
       </c>
-      <c r="P8" s="46" t="n">
+      <c r="P8" s="61" t="n">
         <v>-17.35</v>
       </c>
-      <c r="Q8" s="46" t="n">
+      <c r="Q8" s="61" t="n">
         <v>-1.63</v>
       </c>
-      <c r="R8" s="46" t="n">
+      <c r="R8" s="61" t="n">
         <v>-2.43</v>
       </c>
-      <c r="S8" s="46" t="n">
+      <c r="S8" s="61" t="n">
         <v>-1.39</v>
       </c>
       <c r="T8" s="29" t="n">
@@ -2753,7 +3114,7 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="62" t="n">
         <v>-0.16</v>
       </c>
       <c r="D9" s="33" t="n">
@@ -2792,16 +3153,16 @@
       <c r="O9" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="P9" s="47" t="n">
+      <c r="P9" s="62" t="n">
         <v>-24.81</v>
       </c>
-      <c r="Q9" s="47" t="n">
+      <c r="Q9" s="62" t="n">
         <v>-1.93</v>
       </c>
-      <c r="R9" s="47" t="n">
+      <c r="R9" s="62" t="n">
         <v>-2.72</v>
       </c>
-      <c r="S9" s="47" t="n">
+      <c r="S9" s="62" t="n">
         <v>-3.89</v>
       </c>
       <c r="T9" s="33" t="n">
@@ -2824,35 +3185,35 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C10" s="46" t="n">
-        <v>-0.06</v>
+      <c r="C10" s="29" t="n">
+        <v>-0</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>5.88</v>
+        <v>5.95</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>5.28</v>
+        <v>5.34</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>21.64</v>
+        <v>21.72</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>55.57</v>
+        <v>55.66</v>
       </c>
       <c r="K10" s="29" t="n">
-        <v>63.17</v>
+        <v>63.26</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>10.45</v>
+        <v>10.46</v>
       </c>
       <c r="M10" s="29" t="n">
         <v>16.47</v>
@@ -2863,17 +3224,17 @@
       <c r="O10" s="29" t="n">
         <v>0.52</v>
       </c>
-      <c r="P10" s="46" t="n">
+      <c r="P10" s="61" t="n">
         <v>-20.63</v>
       </c>
-      <c r="Q10" s="46" t="n">
+      <c r="Q10" s="61" t="n">
         <v>-1.56</v>
       </c>
-      <c r="R10" s="46" t="n">
+      <c r="R10" s="61" t="n">
         <v>-2.29</v>
       </c>
-      <c r="S10" s="46" t="n">
-        <v>-0.57</v>
+      <c r="S10" s="61" t="n">
+        <v>-0.5600000000000001</v>
       </c>
       <c r="T10" s="29" t="n">
         <v>0.86</v>
@@ -2934,13 +3295,13 @@
       <c r="O11" s="33" t="n">
         <v>0.55</v>
       </c>
-      <c r="P11" s="47" t="n">
+      <c r="P11" s="62" t="n">
         <v>-25.91</v>
       </c>
-      <c r="Q11" s="47" t="n">
+      <c r="Q11" s="62" t="n">
         <v>-2.26</v>
       </c>
-      <c r="R11" s="47" t="n">
+      <c r="R11" s="62" t="n">
         <v>-3.15</v>
       </c>
       <c r="S11" s="33" t="n">
@@ -2966,10 +3327,10 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n">
+      <c r="C12" s="61" t="n">
         <v>-0.42</v>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="61" t="n">
         <v>-0.5</v>
       </c>
       <c r="E12" s="29" t="n">
@@ -3005,16 +3366,16 @@
       <c r="O12" s="29" t="n">
         <v>0.61</v>
       </c>
-      <c r="P12" s="46" t="n">
+      <c r="P12" s="61" t="n">
         <v>-22.45</v>
       </c>
-      <c r="Q12" s="46" t="n">
+      <c r="Q12" s="61" t="n">
         <v>-1.79</v>
       </c>
-      <c r="R12" s="46" t="n">
+      <c r="R12" s="61" t="n">
         <v>-2.66</v>
       </c>
-      <c r="S12" s="46" t="n">
+      <c r="S12" s="61" t="n">
         <v>-0.13</v>
       </c>
       <c r="T12" s="29" t="n">
@@ -3076,13 +3437,13 @@
       <c r="O13" s="33" t="n">
         <v>0.7</v>
       </c>
-      <c r="P13" s="47" t="n">
+      <c r="P13" s="62" t="n">
         <v>-31.38</v>
       </c>
-      <c r="Q13" s="47" t="n">
+      <c r="Q13" s="62" t="n">
         <v>-2.45</v>
       </c>
-      <c r="R13" s="47" t="n">
+      <c r="R13" s="62" t="n">
         <v>-3.4</v>
       </c>
       <c r="S13" s="33" t="n">
@@ -3108,7 +3469,7 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C14" s="46" t="n">
+      <c r="C14" s="61" t="n">
         <v>-0.09</v>
       </c>
       <c r="D14" s="29" t="n">
@@ -3147,13 +3508,13 @@
       <c r="O14" s="29" t="n">
         <v>0.62</v>
       </c>
-      <c r="P14" s="46" t="n">
+      <c r="P14" s="61" t="n">
         <v>-23.17</v>
       </c>
-      <c r="Q14" s="46" t="n">
+      <c r="Q14" s="61" t="n">
         <v>-1.87</v>
       </c>
-      <c r="R14" s="46" t="n">
+      <c r="R14" s="61" t="n">
         <v>-2.64</v>
       </c>
       <c r="S14" s="29" t="n">
@@ -3182,16 +3543,16 @@
       <c r="C15" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="62" t="n">
         <v>-0.11</v>
       </c>
       <c r="E15" s="33" t="n">
         <v>0.38</v>
       </c>
-      <c r="F15" s="47" t="n">
+      <c r="F15" s="62" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G15" s="47" t="n">
+      <c r="G15" s="62" t="n">
         <v>-0.64</v>
       </c>
       <c r="H15" s="33" t="n">
@@ -3203,31 +3564,31 @@
       <c r="J15" s="33" t="n">
         <v>7.86</v>
       </c>
-      <c r="K15" s="47" t="n">
+      <c r="K15" s="62" t="n">
         <v>-8.98</v>
       </c>
-      <c r="L15" s="47" t="n">
+      <c r="L15" s="62" t="n">
         <v>-1.87</v>
       </c>
       <c r="M15" s="33" t="n">
         <v>5.55</v>
       </c>
-      <c r="N15" s="47" t="n">
+      <c r="N15" s="62" t="n">
         <v>-1.06</v>
       </c>
-      <c r="O15" s="47" t="n">
+      <c r="O15" s="62" t="n">
         <v>-1.63</v>
       </c>
-      <c r="P15" s="47" t="n">
+      <c r="P15" s="62" t="n">
         <v>-19.81</v>
       </c>
-      <c r="Q15" s="47" t="n">
+      <c r="Q15" s="62" t="n">
         <v>-0.55</v>
       </c>
-      <c r="R15" s="47" t="n">
+      <c r="R15" s="62" t="n">
         <v>-0.77</v>
       </c>
-      <c r="S15" s="47" t="n">
+      <c r="S15" s="62" t="n">
         <v>-6</v>
       </c>
       <c r="T15" s="33" t="n">
@@ -3242,7 +3603,7 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
@@ -3251,58 +3612,58 @@
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>0.26</v>
+        <v>0.68</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>0.61</v>
+        <v>0.98</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>6.94</v>
+        <v>7.7</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>3.87</v>
+        <v>4.66</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>5.02</v>
+        <v>6.56</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>5.41</v>
+        <v>6.79</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>22.51</v>
+        <v>24.56</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>62.07</v>
+        <v>62.73</v>
       </c>
       <c r="K16" s="29" t="n">
-        <v>74.48999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="L16" s="29" t="n">
-        <v>12.08</v>
+        <v>11.51</v>
       </c>
       <c r="M16" s="29" t="n">
-        <v>14.24</v>
+        <v>13.8</v>
       </c>
       <c r="N16" s="29" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="O16" s="29" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="P16" s="46" t="n">
-        <v>-21.73</v>
-      </c>
-      <c r="Q16" s="46" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="R16" s="46" t="n">
-        <v>-2.19</v>
+        <v>0.7</v>
+      </c>
+      <c r="P16" s="61" t="n">
+        <v>-21.07</v>
+      </c>
+      <c r="Q16" s="61" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="R16" s="61" t="n">
+        <v>-2.13</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>6.27</v>
+        <v>5.91</v>
       </c>
       <c r="T16" s="29" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="U16" s="27" t="inlineStr">
         <is>
@@ -3313,7 +3674,7 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
@@ -3322,58 +3683,58 @@
         </is>
       </c>
       <c r="C17" s="33" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="E17" s="33" t="n">
-        <v>7.38</v>
+        <v>7.27</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>4.35</v>
+        <v>4.19</v>
       </c>
       <c r="G17" s="33" t="n">
-        <v>6.24</v>
+        <v>5.34</v>
       </c>
       <c r="H17" s="33" t="n">
-        <v>6.48</v>
+        <v>5.73</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>24.19</v>
+        <v>22.88</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>62.25</v>
+        <v>62.57</v>
       </c>
       <c r="K17" s="33" t="n">
-        <v>69.69</v>
+        <v>75.03</v>
       </c>
       <c r="L17" s="33" t="n">
-        <v>11.45</v>
+        <v>12.15</v>
       </c>
       <c r="M17" s="33" t="n">
-        <v>13.8</v>
+        <v>14.24</v>
       </c>
       <c r="N17" s="33" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="O17" s="33" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="P17" s="47" t="n">
-        <v>-21.07</v>
-      </c>
-      <c r="Q17" s="47" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="R17" s="47" t="n">
-        <v>-2.13</v>
+        <v>0.73</v>
+      </c>
+      <c r="P17" s="62" t="n">
+        <v>-21.73</v>
+      </c>
+      <c r="Q17" s="62" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="R17" s="62" t="n">
+        <v>-2.19</v>
       </c>
       <c r="S17" s="33" t="n">
-        <v>5.84</v>
+        <v>6.34</v>
       </c>
       <c r="T17" s="33" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="U17" s="31" t="inlineStr">
         <is>
@@ -3393,55 +3754,55 @@
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>1.27</v>
+        <v>1.74</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>0.86</v>
+        <v>1.32</v>
       </c>
       <c r="E18" s="29" t="n">
-        <v>11.98</v>
+        <v>12.5</v>
       </c>
       <c r="F18" s="29" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G18" s="29" t="n">
-        <v>15.88</v>
+        <v>16.41</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>15.48</v>
+        <v>16.01</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>39.95</v>
+        <v>40.59</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>67.73</v>
+        <v>68.5</v>
       </c>
       <c r="K18" s="29" t="n">
-        <v>41.34</v>
+        <v>41.99</v>
       </c>
       <c r="L18" s="29" t="n">
-        <v>7.44</v>
+        <v>7.54</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>18.82</v>
       </c>
       <c r="N18" s="29" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="O18" s="29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P18" s="46" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P18" s="61" t="n">
         <v>-24.38</v>
       </c>
-      <c r="Q18" s="46" t="n">
+      <c r="Q18" s="61" t="n">
         <v>-1.59</v>
       </c>
-      <c r="R18" s="46" t="n">
+      <c r="R18" s="61" t="n">
         <v>-2.59</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="T18" s="29" t="n">
         <v>0.1</v>
@@ -3455,7 +3816,7 @@
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
+          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
@@ -3463,59 +3824,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C19" s="33" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="D19" s="47" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="E19" s="47" t="n">
-        <v>-1.11</v>
+      <c r="C19" s="62" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E19" s="33" t="n">
+        <v>8.81</v>
       </c>
       <c r="F19" s="33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G19" s="47" t="n">
-        <v>-1.55</v>
+        <v>5.4</v>
+      </c>
+      <c r="G19" s="33" t="n">
+        <v>4.78</v>
       </c>
       <c r="H19" s="33" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I19" s="47" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="J19" s="47" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="K19" s="47" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="L19" s="47" t="n">
-        <v>-0.33</v>
+        <v>6.38</v>
+      </c>
+      <c r="I19" s="33" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="J19" s="33" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="K19" s="33" t="n">
+        <v>88.36</v>
+      </c>
+      <c r="L19" s="33" t="n">
+        <v>13.82</v>
       </c>
       <c r="M19" s="33" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="N19" s="47" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="O19" s="47" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="P19" s="47" t="n">
-        <v>-15.77</v>
-      </c>
-      <c r="Q19" s="47" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="R19" s="47" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="S19" s="47" t="n">
-        <v>-4.14</v>
-      </c>
-      <c r="T19" s="47" t="n">
-        <v>-0.02</v>
+        <v>17.29</v>
+      </c>
+      <c r="N19" s="33" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O19" s="33" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P19" s="62" t="n">
+        <v>-22.73</v>
+      </c>
+      <c r="Q19" s="62" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="R19" s="62" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="S19" s="33" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="T19" s="33" t="n">
+        <v>0.42</v>
       </c>
       <c r="U19" s="31" t="inlineStr">
         <is>
@@ -3526,7 +3887,7 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
+          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
@@ -3534,59 +3895,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C20" s="46" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>8.720000000000001</v>
+      <c r="C20" s="29" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D20" s="61" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E20" s="61" t="n">
+        <v>-1.11</v>
       </c>
       <c r="F20" s="29" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
+      </c>
+      <c r="G20" s="61" t="n">
+        <v>-1.55</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>25.17</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>70.73</v>
-      </c>
-      <c r="K20" s="29" t="n">
-        <v>88.20999999999999</v>
-      </c>
-      <c r="L20" s="29" t="n">
-        <v>13.8</v>
+        <v>0.02</v>
+      </c>
+      <c r="I20" s="61" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="J20" s="61" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="K20" s="61" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="L20" s="61" t="n">
+        <v>-0.33</v>
       </c>
       <c r="M20" s="29" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="N20" s="29" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="O20" s="29" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="P20" s="46" t="n">
-        <v>-22.73</v>
-      </c>
-      <c r="Q20" s="46" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="R20" s="46" t="n">
-        <v>-2.53</v>
-      </c>
-      <c r="S20" s="29" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="T20" s="29" t="n">
-        <v>0.42</v>
+        <v>10.65</v>
+      </c>
+      <c r="N20" s="61" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="O20" s="61" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="P20" s="61" t="n">
+        <v>-15.77</v>
+      </c>
+      <c r="Q20" s="61" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="R20" s="61" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="S20" s="61" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="T20" s="61" t="n">
+        <v>-0.02</v>
       </c>
       <c r="U20" s="27" t="inlineStr">
         <is>
@@ -3605,13 +3966,13 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C21" s="47" t="n">
+      <c r="C21" s="62" t="n">
         <v>-0.1</v>
       </c>
-      <c r="D21" s="47" t="n">
+      <c r="D21" s="62" t="n">
         <v>-2.09</v>
       </c>
-      <c r="E21" s="47" t="n">
+      <c r="E21" s="62" t="n">
         <v>-4.21</v>
       </c>
       <c r="F21" s="33" t="n">
@@ -3644,13 +4005,13 @@
       <c r="O21" s="33" t="n">
         <v>1.36</v>
       </c>
-      <c r="P21" s="47" t="n">
+      <c r="P21" s="62" t="n">
         <v>-15.94</v>
       </c>
-      <c r="Q21" s="47" t="n">
+      <c r="Q21" s="62" t="n">
         <v>-1.75</v>
       </c>
-      <c r="R21" s="47" t="n">
+      <c r="R21" s="62" t="n">
         <v>-2.57</v>
       </c>
       <c r="S21" s="33" t="n">
@@ -3668,7 +4029,7 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
+          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
@@ -3676,59 +4037,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
-        <v>0.04</v>
+      <c r="C22" s="61" t="n">
+        <v>-0.31</v>
       </c>
       <c r="D22" s="29" t="n">
-        <v>0.93</v>
+        <v>0.15</v>
       </c>
       <c r="E22" s="29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F22" s="29" t="n">
-        <v>10.93</v>
+        <v>4.35</v>
+      </c>
+      <c r="F22" s="61" t="n">
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G22" s="29" t="n">
-        <v>10.3</v>
+        <v>7.24</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>17.9</v>
+        <v>2.3</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>44.84</v>
+        <v>14.57</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>73.92</v>
+        <v>40.38</v>
       </c>
       <c r="K22" s="29" t="n">
-        <v>57.6</v>
+        <v>54.73</v>
       </c>
       <c r="L22" s="29" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="M22" s="29" t="n">
-        <v>18.27</v>
+        <v>14.94</v>
       </c>
       <c r="N22" s="29" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="O22" s="29" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P22" s="46" t="n">
-        <v>-21.24</v>
-      </c>
-      <c r="Q22" s="46" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="R22" s="46" t="n">
-        <v>-2.5</v>
+        <v>0.5</v>
+      </c>
+      <c r="P22" s="61" t="n">
+        <v>-22.86</v>
+      </c>
+      <c r="Q22" s="61" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="R22" s="61" t="n">
+        <v>-2.22</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>3.42</v>
+        <v>4.11</v>
       </c>
       <c r="T22" s="29" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="U22" s="27" t="inlineStr">
         <is>
@@ -3739,7 +4100,7 @@
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
+          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
       <c r="B23" s="31" t="inlineStr">
@@ -3747,59 +4108,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C23" s="47" t="n">
-        <v>-0.31</v>
+      <c r="C23" s="33" t="n">
+        <v>0.04</v>
       </c>
       <c r="D23" s="33" t="n">
-        <v>0.15</v>
+        <v>0.93</v>
       </c>
       <c r="E23" s="33" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="F23" s="47" t="n">
-        <v>-0.9399999999999999</v>
+        <v>9.6</v>
+      </c>
+      <c r="F23" s="33" t="n">
+        <v>10.93</v>
       </c>
       <c r="G23" s="33" t="n">
-        <v>7.24</v>
+        <v>10.3</v>
       </c>
       <c r="H23" s="33" t="n">
-        <v>2.3</v>
+        <v>17.9</v>
       </c>
       <c r="I23" s="33" t="n">
-        <v>14.57</v>
+        <v>44.84</v>
       </c>
       <c r="J23" s="33" t="n">
-        <v>40.38</v>
+        <v>73.92</v>
       </c>
       <c r="K23" s="33" t="n">
-        <v>54.73</v>
+        <v>57.6</v>
       </c>
       <c r="L23" s="33" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="M23" s="33" t="n">
-        <v>14.94</v>
+        <v>18.27</v>
       </c>
       <c r="N23" s="33" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="O23" s="33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P23" s="47" t="n">
-        <v>-22.86</v>
-      </c>
-      <c r="Q23" s="47" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="R23" s="47" t="n">
-        <v>-2.22</v>
+        <v>0.46</v>
+      </c>
+      <c r="P23" s="62" t="n">
+        <v>-21.24</v>
+      </c>
+      <c r="Q23" s="62" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="R23" s="62" t="n">
+        <v>-2.5</v>
       </c>
       <c r="S23" s="33" t="n">
-        <v>4.11</v>
+        <v>3.42</v>
       </c>
       <c r="T23" s="33" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="U23" s="31" t="inlineStr">
         <is>
@@ -3808,7 +4169,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>Legend — Rating Thresholds</t>
         </is>
@@ -3852,7 +4213,7 @@
           <t>CAGR</t>
         </is>
       </c>
-      <c r="B28" s="48" t="inlineStr">
+      <c r="B28" s="64" t="inlineStr">
         <is>
           <t>Compound Annual Growth Rate. The single yearly return that, if repeated every year, would grow your portfolio from start to end value. Accounts for compounding. ~7% is the long-term global equity average.</t>
         </is>
@@ -3884,7 +4245,7 @@
           <t>α (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B29" s="49" t="inlineStr">
+      <c r="B29" s="65" t="inlineStr">
         <is>
           <t>Extra annual return vs the benchmark, after adjusting for how risky the portfolio is (CAPM). Positive = you beat the market beyond what your risk alone justified. Negative = you underperformed after fees and noise.</t>
         </is>
@@ -3916,7 +4277,7 @@
           <t>β (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B30" s="48" t="inlineStr">
+      <c r="B30" s="64" t="inlineStr">
         <is>
           <t>How much your portfolio moves when the benchmark moves 1%. β=1 in line, β=0.5 half as reactive, β=1.5 amplifies by 50%, β≈0 uncorrelated. Tells you how much systematic market risk you're running.</t>
         </is>
@@ -3948,7 +4309,7 @@
           <t>Max DD</t>
         </is>
       </c>
-      <c r="B31" s="49" t="inlineStr">
+      <c r="B31" s="65" t="inlineStr">
         <is>
           <t>Maximum Drawdown. Worst peak-to-trough loss over the period — the most painful scenario an investor lived through. -20% is typical for diversified equity; deeper drops signal concentration or high volatility.</t>
         </is>
@@ -3980,7 +4341,7 @@
           <t>Volatility</t>
         </is>
       </c>
-      <c r="B32" s="48" t="inlineStr">
+      <c r="B32" s="64" t="inlineStr">
         <is>
           <t>How bumpy the ride is. Annualized standard deviation of daily returns. A 15% vol means ~±15% year-to-year noise around the average return. Equity indexes ~15–20%, bonds ~3–7%.</t>
         </is>
@@ -4012,7 +4373,7 @@
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="B33" s="49" t="inlineStr">
+      <c r="B33" s="65" t="inlineStr">
         <is>
           <t>Return per unit of risk taken: (CAGR − risk-free rate) / Volatility. Above 1 is good, above 2 is excellent, negative means you were paid less than a safe bond for the risk you ran.</t>
         </is>
@@ -4044,7 +4405,7 @@
           <t>Sortino</t>
         </is>
       </c>
-      <c r="B34" s="48" t="inlineStr">
+      <c r="B34" s="64" t="inlineStr">
         <is>
           <t>Like Sharpe but only penalizes downside volatility (ignores upside swings). More honest when returns are asymmetric. Usually higher than Sharpe — the gap shows how much of your volatility is actually good volatility.</t>
         </is>
@@ -4076,7 +4437,7 @@
           <t>VaR 95%</t>
         </is>
       </c>
-      <c r="B35" s="49" t="inlineStr">
+      <c r="B35" s="65" t="inlineStr">
         <is>
           <t>Value at Risk. The daily loss exceeded only 5% of the time (historical simulation). A VaR of -1.2% means on an average month you should expect about one day worse than -1.2%. Non-parametric: no normal-distribution assumption.</t>
         </is>
@@ -4108,7 +4469,7 @@
           <t>CVaR 95%</t>
         </is>
       </c>
-      <c r="B36" s="48" t="inlineStr">
+      <c r="B36" s="64" t="inlineStr">
         <is>
           <t>Conditional VaR, a.k.a. Expected Shortfall. The average loss on the worst 5% of days. Always more negative than VaR. Captures tail risk VaR misses — how bad it really gets when it goes bad.</t>
         </is>
@@ -4137,7 +4498,7 @@
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 12:40 v2.0</t>
+          <t>Generated 2026-05-04 13:06 v2.0</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4538,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="63" t="inlineStr">
         <is>
           <t>Return Contribution by Holding</t>
         </is>
@@ -4232,13 +4593,13 @@
         </is>
       </c>
       <c r="D5" s="29" t="n">
-        <v>14.30483549132784</v>
+        <v>14.2881478739683</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>415.5184553004801</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>59.43923146684028</v>
+        <v>59.36989133696145</v>
       </c>
     </row>
     <row r="6">
@@ -4258,13 +4619,13 @@
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>13.27341929278388</v>
+        <v>13.25793489645195</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>91.33928843906948</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>12.12384673356297</v>
+        <v>12.1097033961343</v>
       </c>
     </row>
     <row r="7">
@@ -4284,13 +4645,13 @@
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>8.482767698189821</v>
+        <v>8.472871940801831</v>
       </c>
       <c r="E7" s="29" t="n">
         <v>55.27743647935755</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>4.689056526058339</v>
+        <v>4.683586405054041</v>
       </c>
     </row>
     <row r="8">
@@ -4310,13 +4671,13 @@
         </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>15.31515892994493</v>
+        <v>15.34282691319409</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>20.73436975479126</v>
+        <v>21.09375</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.175501681068715</v>
+        <v>3.236377552001878</v>
       </c>
     </row>
     <row r="9">
@@ -4336,65 +4697,65 @@
         </is>
       </c>
       <c r="D9" s="29" t="n">
-        <v>7.363380812966189</v>
+        <v>7.354790900726102</v>
       </c>
       <c r="E9" s="29" t="n">
         <v>41.5263607345748</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>3.057744078652807</v>
+        <v>3.054177000709204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>IE00B945VV12</t>
+          <t>LU0292107645</t>
         </is>
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>VERX.DE</t>
+          <t>XMME.DE</t>
         </is>
       </c>
       <c r="D10" s="33" t="n">
-        <v>7.023825134702188</v>
+        <v>8.473991857892328</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>43.18181818181818</v>
+        <v>35.88571548461914</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>3.033015399075945</v>
+        <v>3.040952608313032</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>LU0292107645</t>
+          <t>IE00B945VV12</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>XMME.DE</t>
+          <t>VERX.DE</t>
         </is>
       </c>
       <c r="D11" s="29" t="n">
-        <v>8.445090698730574</v>
+        <v>7.015631338533103</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>35.26428767613002</v>
+        <v>43.18181818181818</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>2.978101078510449</v>
+        <v>3.029477168912022</v>
       </c>
     </row>
     <row r="12">
@@ -4414,13 +4775,13 @@
         </is>
       </c>
       <c r="D12" s="33" t="n">
-        <v>12.32981004493342</v>
+        <v>12.325524551901</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.41250622122594</v>
+        <v>16.50795942585797</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>2.023630840690039</v>
+        <v>2.034692592051979</v>
       </c>
     </row>
     <row r="13">
@@ -4440,13 +4801,13 @@
         </is>
       </c>
       <c r="D13" s="29" t="n">
-        <v>7.26786257128694</v>
+        <v>7.281655971211097</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>19.73469014070472</v>
+        <v>20.10203770228795</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>1.434290158295732</v>
+        <v>1.463761228683756</v>
       </c>
     </row>
     <row r="14">
@@ -4466,7 +4827,7 @@
         </is>
       </c>
       <c r="D14" s="33" t="n">
-        <v>6.193849325134205</v>
+        <v>6.186623755320196</v>
       </c>
       <c r="E14" s="33" t="n">
         <v>0</v>
@@ -4476,7 +4837,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="63" t="inlineStr">
         <is>
           <t>Breakdown by Asset Class</t>
         </is>
@@ -4511,10 +4872,10 @@
         </is>
       </c>
       <c r="B18" s="28" t="n">
-        <v>52218.40205930769</v>
+        <v>52312.68383747853</v>
       </c>
       <c r="C18" s="29" t="n">
-        <v>91.8076878791917</v>
+        <v>92.04828934917724</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>6</v>
@@ -4569,7 +4930,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="63" t="inlineStr">
         <is>
           <t>Breakdown by Geography (Equity Only)</t>
         </is>
@@ -4599,23 +4960,23 @@
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>41.77736996416787</v>
+        <v>41.78590318582933</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>18.9605220389073</v>
+        <v>19.23458237604864</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="40" t="inlineStr">
+      <c r="A26" s="55" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
       <c r="B26" s="33" t="n">
-        <v>15.45140327227481</v>
+        <v>15.49054543942014</v>
       </c>
       <c r="C26" s="33" t="n">
-        <v>27.99932871546064</v>
+        <v>28.48973274230957</v>
       </c>
     </row>
     <row r="27">
@@ -4625,10 +4986,10 @@
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>9.79204943317003</v>
+        <v>9.782738357331008</v>
       </c>
       <c r="C27" s="29" t="n">
-        <v>27.88362602577139</v>
+        <v>28.12586862803538</v>
       </c>
     </row>
     <row r="28">
@@ -4638,10 +4999,10 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>24.23467868773753</v>
+        <v>24.19736373853591</v>
       </c>
       <c r="C28" s="33" t="n">
-        <v>151.9958383986587</v>
+        <v>152.2380810009227</v>
       </c>
     </row>
     <row r="29">
@@ -4651,299 +5012,10 @@
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>8.744498642649752</v>
+        <v>8.743449278883624</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>27.88362602577139</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0064748B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metrics Documentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Description &amp; Calculation</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Timeframe / Parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="27" t="inlineStr">
-        <is>
-          <t>Total Value (EUR)</t>
-        </is>
-      </c>
-      <c r="B4" s="50" t="inlineStr">
-        <is>
-          <t>Sum of current market values of all holdings, converted to EUR.</t>
-        </is>
-      </c>
-      <c r="C4" s="50" t="inlineStr">
-        <is>
-          <t>Point-in-time (today)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>YTD Return</t>
-        </is>
-      </c>
-      <c r="B5" s="51" t="inlineStr">
-        <is>
-          <t>Year-to-date return. Formula: (Current Value / Value at Jan 1) - 1.</t>
-        </is>
-      </c>
-      <c r="C5" s="51" t="inlineStr">
-        <is>
-          <t>Jan 1 of current year to today</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>CAGR</t>
-        </is>
-      </c>
-      <c r="B6" s="50" t="inlineStr">
-        <is>
-          <t>Compound Annual Growth Rate. Formula: (End/Start)^(1/years) - 1. Measures mean annual growth rate assuming constant compounding.</t>
-        </is>
-      </c>
-      <c r="C6" s="50" t="inlineStr">
-        <is>
-          <t>Full history: 2.3 years (853 calendar days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio</t>
-        </is>
-      </c>
-      <c r="B7" s="51" t="inlineStr">
-        <is>
-          <t>Risk-adjusted return. Formula: (Return - Rf) / Volatility. Higher is better.</t>
-        </is>
-      </c>
-      <c r="C7" s="51" t="inlineStr">
-        <is>
-          <t>Risk-free rate: 4.0%. Period: 2.3 years (853 calendar days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Sortino Ratio</t>
-        </is>
-      </c>
-      <c r="B8" s="50" t="inlineStr">
-        <is>
-          <t>Downside risk-adjusted return. Uses only negative returns for deviation. Formula: (Return - Rf) / Downside Deviation.</t>
-        </is>
-      </c>
-      <c r="C8" s="50" t="inlineStr">
-        <is>
-          <t>Risk-free rate: 4.0%. Period: 2.3 years (853 calendar days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>Volatility</t>
-        </is>
-      </c>
-      <c r="B9" s="51" t="inlineStr">
-        <is>
-          <t>Annualized std dev of daily returns. Formula: StdDev(daily) x sqrt(252).</t>
-        </is>
-      </c>
-      <c r="C9" s="51" t="inlineStr">
-        <is>
-          <t>Period: 2.3 years (853 calendar days). Trading days/year: 252</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>Max Drawdown</t>
-        </is>
-      </c>
-      <c r="B10" s="50" t="inlineStr">
-        <is>
-          <t>Largest peak-to-trough decline. Formula: min((V - CumMax) / CumMax).</t>
-        </is>
-      </c>
-      <c r="C10" s="50" t="inlineStr">
-        <is>
-          <t>Period: 2.3 years (853 calendar days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>VaR (95%)</t>
-        </is>
-      </c>
-      <c r="B11" s="51" t="inlineStr">
-        <is>
-          <t>Value at Risk via historical simulation. The 5th percentile of daily returns. Non-parametric: no distributional assumptions, robust for fat tails.</t>
-        </is>
-      </c>
-      <c r="C11" s="51" t="inlineStr">
-        <is>
-          <t>Period: 2.3 years (853 calendar days). Confidence: 95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>CVaR (95%)</t>
-        </is>
-      </c>
-      <c r="B12" s="50" t="inlineStr">
-        <is>
-          <t>Conditional VaR (Expected Shortfall). Average loss beyond VaR threshold. A coherent risk measure per Artzner et al. (1999), preferred for tail risk.</t>
-        </is>
-      </c>
-      <c r="C12" s="50" t="inlineStr">
-        <is>
-          <t>Period: 2.3 years (853 calendar days). Confidence: 95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="B13" s="51" t="inlineStr">
-        <is>
-          <t>CAPM sensitivity to market. Formula: Cov(Rp, Rb) / Var(Rb). Beta=1 means same as market.</t>
-        </is>
-      </c>
-      <c r="C13" s="51" t="inlineStr">
-        <is>
-          <t>Benchmark: S&amp;P 500. Period: 2.3 years (853 calendar days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>Alpha</t>
-        </is>
-      </c>
-      <c r="B14" s="50" t="inlineStr">
-        <is>
-          <t>Jensen's Alpha. Excess return vs CAPM expected. Formula: Rp - [Rf + Beta x (Rb - Rf)].</t>
-        </is>
-      </c>
-      <c r="C14" s="50" t="inlineStr">
-        <is>
-          <t>Benchmark: S&amp;P 500. Risk-free rate: 4.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>Weighted Yield</t>
-        </is>
-      </c>
-      <c r="B15" s="51" t="inlineStr">
-        <is>
-          <t>Portfolio-weighted average dividend/coupon yield.</t>
-        </is>
-      </c>
-      <c r="C15" s="51" t="inlineStr">
-        <is>
-          <t>Based on latest yield data from yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>Geography Allocation</t>
-        </is>
-      </c>
-      <c r="B16" s="50" t="inlineStr">
-        <is>
-          <t>Geographic exposure of equity holdings only. Multi-geo ETFs split proportionally.</t>
-        </is>
-      </c>
-      <c r="C16" s="50" t="inlineStr">
-        <is>
-          <t>Equity only. Sources: justETF, index_geo_allocation.csv, yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>Rebalancing Amount</t>
-        </is>
-      </c>
-      <c r="B17" s="51" t="inlineStr">
-        <is>
-          <t>Suggested trade amount to reach target. Asset class: total value. Geography: equity value.</t>
-        </is>
-      </c>
-      <c r="C17" s="51" t="inlineStr">
-        <is>
-          <t>Threshold from config (rebalancing_threshold)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="36" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-04 12:40 v2.0</t>
-        </is>
+        <v>28.12586862803538</v>
       </c>
     </row>
   </sheetData>

--- a/output/sample/portfolio_dashboard_sample.xlsx
+++ b/output/sample/portfolio_dashboard_sample.xlsx
@@ -254,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -360,46 +360,49 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -861,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>80819.52608965823</v>
+        <v>80818.52679156253</v>
       </c>
       <c r="D5" s="2" t="n"/>
     </row>
@@ -872,7 +875,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>26679.52608965823</v>
+        <v>26678.52679156253</v>
       </c>
       <c r="D6" s="2" t="n"/>
     </row>
@@ -883,7 +886,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>49.27877002153349</v>
+        <v>49.27692425482551</v>
       </c>
       <c r="D7" s="2" t="n"/>
     </row>
@@ -947,7 +950,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>64.72777850669991</v>
+        <v>64.72734237571399</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>65</v>
@@ -959,7 +962,7 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>41.78590318582933</v>
+        <v>41.78221986945917</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>55</v>
@@ -972,7 +975,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>20.61272579717805</v>
+        <v>20.61298066766944</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>25</v>
@@ -984,7 +987,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>24.19736373853591</v>
+        <v>24.19739538174008</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>8</v>
@@ -997,7 +1000,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>8.472871940801831</v>
+        <v>8.47297670545335</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>5</v>
@@ -1009,7 +1012,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>15.49054543942014</v>
+        <v>15.49538355778712</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>11</v>
@@ -1022,7 +1025,7 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>6.186623755320196</v>
+        <v>6.186700251163203</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>5</v>
@@ -1034,7 +1037,7 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>9.782738357331008</v>
+        <v>9.78236697442971</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>14</v>
@@ -1048,7 +1051,7 @@
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>8.743449278883624</v>
+        <v>8.742634216583923</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>12</v>
@@ -1104,10 +1107,10 @@
         </is>
       </c>
       <c r="B21" s="28" t="n">
-        <v>12400</v>
+        <v>12396.80053710938</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>15.34282691319409</v>
+        <v>15.33905779931094</v>
       </c>
       <c r="D21" s="30" t="n"/>
       <c r="E21" s="12" t="inlineStr">
@@ -1126,7 +1129,7 @@
         <v>11547.61339873075</v>
       </c>
       <c r="C22" s="33" t="n">
-        <v>14.2881478739683</v>
+        <v>14.28832454285263</v>
       </c>
       <c r="D22" s="30" t="n"/>
       <c r="E22" s="34" t="inlineStr">
@@ -1145,7 +1148,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>13.25793489645195</v>
+        <v>13.25809882704585</v>
       </c>
       <c r="D23" s="30" t="n"/>
       <c r="E23" s="35" t="inlineStr">
@@ -1164,7 +1167,7 @@
         <v>9961.430530910857</v>
       </c>
       <c r="C24" s="33" t="n">
-        <v>12.325524551901</v>
+        <v>12.3256769535062</v>
       </c>
       <c r="D24" s="30" t="n"/>
       <c r="E24" s="34" t="inlineStr">
@@ -1180,10 +1183,10 @@
         </is>
       </c>
       <c r="B25" s="28" t="n">
-        <v>6848.640060424805</v>
+        <v>6851.339950561523</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>8.473991857892328</v>
+        <v>8.477437318588693</v>
       </c>
       <c r="D25" s="30" t="n"/>
       <c r="E25" s="12" t="inlineStr">
@@ -1198,7 +1201,7 @@
     <row r="27">
       <c r="A27" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:06 v2.0</t>
+          <t>Generated 2026-05-04 13:21 v2.0</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1227,7 +1230,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1281,449 +1284,749 @@
     <row r="10">
       <c r="A10" s="38" t="inlineStr">
         <is>
-          <t>Ordered by |delta|. Threshold ±2.5% (green), ±5.0% (amber), beyond (red).</t>
+          <t>Status color based on delta after rebalancing vs target. Threshold ±2.5% (green), ±5.0% (amber), beyond (red).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>Asset Allocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Current %</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Target %</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Delta (pp)</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Post-rebal %</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Delta after rebal (pp)</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="n">
+        <v>20.61298066766944</v>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" s="40" t="n">
+        <v>20.61298066766944</v>
+      </c>
+      <c r="E14" s="41" t="n">
+        <v>-4.38701933233056</v>
+      </c>
+      <c r="F14" s="42" t="inlineStr">
+        <is>
+          <t>● Drift</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="n">
+        <v>8.47297670545335</v>
+      </c>
+      <c r="C15" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="43" t="n">
+        <v>8.47297670545335</v>
+      </c>
+      <c r="E15" s="44" t="n">
+        <v>3.47297670545335</v>
+      </c>
+      <c r="F15" s="45" t="inlineStr">
+        <is>
+          <t>● Drift</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Cash &amp; Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="n">
+        <v>6.186700251163203</v>
+      </c>
+      <c r="C16" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="40" t="n">
+        <v>6.186700251163203</v>
+      </c>
+      <c r="E16" s="46" t="n">
+        <v>1.186700251163203</v>
+      </c>
+      <c r="F16" s="47" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Equities</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="n">
+        <v>64.72734237571399</v>
+      </c>
+      <c r="C17" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="D17" s="43" t="n">
+        <v>64.727342375714</v>
+      </c>
+      <c r="E17" s="48" t="n">
+        <v>-0.2726576242859977</v>
+      </c>
+      <c r="F17" s="49" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Alternative</t>
+        </is>
+      </c>
+      <c r="B18" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="47" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>Geography (equity only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Current %</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Target %</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Post-rebal %</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Delta after rebal (pp)</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="C13" s="39" t="n">
-        <v>24.19736373853591</v>
-      </c>
-      <c r="D13" s="39" t="n">
+      <c r="B22" s="40" t="n">
+        <v>24.19739538174008</v>
+      </c>
+      <c r="C22" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="E13" s="40" t="n">
-        <v>16.19736373853591</v>
-      </c>
-      <c r="F13" s="41" t="inlineStr">
+      <c r="D22" s="40" t="n">
+        <v>24.19739538174008</v>
+      </c>
+      <c r="E22" s="50" t="n">
+        <v>16.19739538174008</v>
+      </c>
+      <c r="F22" s="51" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="C14" s="42" t="n">
-        <v>41.78590318582933</v>
-      </c>
-      <c r="D14" s="42" t="n">
+      <c r="B23" s="43" t="n">
+        <v>41.78221986945917</v>
+      </c>
+      <c r="C23" s="43" t="n">
         <v>55</v>
       </c>
-      <c r="E14" s="43" t="n">
-        <v>-13.21409681417067</v>
-      </c>
-      <c r="F14" s="44" t="inlineStr">
+      <c r="D23" s="43" t="n">
+        <v>41.78221986945916</v>
+      </c>
+      <c r="E23" s="52" t="n">
+        <v>-13.21778013054084</v>
+      </c>
+      <c r="F23" s="53" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="C15" s="39" t="n">
-        <v>15.49054543942014</v>
-      </c>
-      <c r="D15" s="39" t="n">
+      <c r="B24" s="40" t="n">
+        <v>15.49538355778712</v>
+      </c>
+      <c r="C24" s="40" t="n">
         <v>11</v>
       </c>
-      <c r="E15" s="45" t="n">
-        <v>4.490545439420137</v>
-      </c>
-      <c r="F15" s="46" t="inlineStr">
+      <c r="D24" s="40" t="n">
+        <v>15.49538355778712</v>
+      </c>
+      <c r="E24" s="41" t="n">
+        <v>4.495383557787118</v>
+      </c>
+      <c r="F24" s="42" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="C16" s="42" t="n">
-        <v>20.61272579717805</v>
-      </c>
-      <c r="D16" s="42" t="n">
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>Eurozone EMU</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="n">
+        <v>9.78236697442971</v>
+      </c>
+      <c r="C25" s="43" t="n">
+        <v>14</v>
+      </c>
+      <c r="D25" s="43" t="n">
+        <v>9.782366974429706</v>
+      </c>
+      <c r="E25" s="44" t="n">
+        <v>-4.217633025570294</v>
+      </c>
+      <c r="F25" s="45" t="inlineStr">
+        <is>
+          <t>● Drift</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>Dev ex-USA ex-EMU ex-JP</t>
+        </is>
+      </c>
+      <c r="B26" s="40" t="n">
+        <v>8.742634216583923</v>
+      </c>
+      <c r="C26" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" s="40" t="n">
+        <v>8.742634216583921</v>
+      </c>
+      <c r="E26" s="41" t="n">
+        <v>-3.257365783416079</v>
+      </c>
+      <c r="F26" s="42" t="inlineStr">
+        <is>
+          <t>● Drift</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>Per-Holding Equity Targets</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Current %</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Target %</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Post-rebal %</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Delta after rebal (pp)</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>CNKY.L</t>
+        </is>
+      </c>
+      <c r="B30" s="40" t="n">
+        <v>22.07463495089159</v>
+      </c>
+      <c r="C30" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" s="40" t="n">
+        <v>22.07463495089159</v>
+      </c>
+      <c r="E30" s="50" t="n">
+        <v>12.07463495089159</v>
+      </c>
+      <c r="F30" s="51" t="inlineStr">
+        <is>
+          <t>● Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>VERX.DE</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="n">
+        <v>10.83887863662915</v>
+      </c>
+      <c r="C31" s="43" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" s="43" t="n">
+        <v>10.83887863662915</v>
+      </c>
+      <c r="E31" s="44" t="n">
+        <v>-4.161121363370849</v>
+      </c>
+      <c r="F31" s="45" t="inlineStr">
+        <is>
+          <t>● Drift</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>EUNL.DE</t>
+        </is>
+      </c>
+      <c r="B32" s="40" t="n">
+        <v>11.24892110411809</v>
+      </c>
+      <c r="C32" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="D32" s="40" t="n">
+        <v>11.24892110411809</v>
+      </c>
+      <c r="E32" s="41" t="n">
+        <v>-3.751078895881914</v>
+      </c>
+      <c r="F32" s="42" t="inlineStr">
+        <is>
+          <t>● Drift</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>XMME.DE</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="n">
+        <v>13.09715030377868</v>
+      </c>
+      <c r="C33" s="43" t="n">
+        <v>15</v>
+      </c>
+      <c r="D33" s="43" t="n">
+        <v>13.09715030377868</v>
+      </c>
+      <c r="E33" s="48" t="n">
+        <v>-1.902849696221319</v>
+      </c>
+      <c r="F33" s="49" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>VWCE.DE</t>
+        </is>
+      </c>
+      <c r="B34" s="40" t="n">
+        <v>23.69795705541933</v>
+      </c>
+      <c r="C34" s="40" t="n">
         <v>25</v>
       </c>
-      <c r="E16" s="47" t="n">
-        <v>-4.387274202821946</v>
-      </c>
-      <c r="F16" s="48" t="inlineStr">
-        <is>
-          <t>● Drift</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="inlineStr">
-        <is>
-          <t>Eurozone EMU</t>
-        </is>
-      </c>
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="n">
-        <v>9.782738357331008</v>
-      </c>
-      <c r="D17" s="39" t="n">
-        <v>14</v>
-      </c>
-      <c r="E17" s="45" t="n">
-        <v>-4.217261642668992</v>
-      </c>
-      <c r="F17" s="46" t="inlineStr">
-        <is>
-          <t>● Drift</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="C18" s="42" t="n">
-        <v>8.472871940801831</v>
-      </c>
-      <c r="D18" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="E18" s="47" t="n">
-        <v>3.472871940801831</v>
-      </c>
-      <c r="F18" s="48" t="inlineStr">
-        <is>
-          <t>● Drift</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>Dev ex-USA ex-EMU ex-JP</t>
-        </is>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="C19" s="39" t="n">
-        <v>8.743449278883624</v>
-      </c>
-      <c r="D19" s="39" t="n">
-        <v>12</v>
-      </c>
-      <c r="E19" s="45" t="n">
-        <v>-3.256550721116376</v>
-      </c>
-      <c r="F19" s="46" t="inlineStr">
-        <is>
-          <t>● Drift</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="31" t="inlineStr">
-        <is>
-          <t>Cash &amp; Cash Equivalents</t>
-        </is>
-      </c>
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="C20" s="42" t="n">
-        <v>6.186623755320196</v>
-      </c>
-      <c r="D20" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" s="49" t="n">
-        <v>1.186623755320196</v>
-      </c>
-      <c r="F20" s="50" t="inlineStr">
+      <c r="D34" s="40" t="n">
+        <v>23.69795705541933</v>
+      </c>
+      <c r="E34" s="46" t="n">
+        <v>-1.30204294458067</v>
+      </c>
+      <c r="F34" s="47" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>Equities</t>
-        </is>
-      </c>
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="C21" s="39" t="n">
-        <v>64.72777850669991</v>
-      </c>
-      <c r="D21" s="39" t="n">
-        <v>65</v>
-      </c>
-      <c r="E21" s="51" t="n">
-        <v>-0.2722214933000942</v>
-      </c>
-      <c r="F21" s="52" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>CSPX.L</t>
+        </is>
+      </c>
+      <c r="B35" s="43" t="n">
+        <v>19.04245794916315</v>
+      </c>
+      <c r="C35" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="D35" s="43" t="n">
+        <v>19.04245794916315</v>
+      </c>
+      <c r="E35" s="48" t="n">
+        <v>-0.957542050836846</v>
+      </c>
+      <c r="F35" s="49" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="31" t="inlineStr">
-        <is>
-          <t>Alternative</t>
-        </is>
-      </c>
-      <c r="B22" s="31" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="C22" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="50" t="inlineStr">
-        <is>
-          <t>● Aligned</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>Per-Holding Fixed Income Targets</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Current %</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Target %</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Post-rebal %</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>Delta after rebal (pp)</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>IBTM.L</t>
+        </is>
+      </c>
+      <c r="B39" s="40" t="n">
+        <v>35.68082636471589</v>
+      </c>
+      <c r="C39" s="40" t="n">
+        <v>30</v>
+      </c>
+      <c r="D39" s="40" t="n">
+        <v>35.68082636471589</v>
+      </c>
+      <c r="E39" s="50" t="n">
+        <v>5.680826364715891</v>
+      </c>
+      <c r="F39" s="51" t="inlineStr">
+        <is>
+          <t>● Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>IEAG.L</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="n">
+        <v>64.31917363528412</v>
+      </c>
+      <c r="C40" s="43" t="n">
+        <v>70</v>
+      </c>
+      <c r="D40" s="43" t="n">
+        <v>64.31917363528412</v>
+      </c>
+      <c r="E40" s="52" t="n">
+        <v>-5.680826364715884</v>
+      </c>
+      <c r="F40" s="53" t="inlineStr">
+        <is>
+          <t>● Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>SOLVER PARAMETERS</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="53" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="54" t="inlineStr">
         <is>
           <t>Alert threshold</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B46" s="27" t="inlineStr">
         <is>
           <t>±2.5%</t>
         </is>
       </c>
-      <c r="G27" s="27" t="inlineStr">
+      <c r="G46" s="27" t="inlineStr">
         <is>
           <t>Deviation at which a category turns amber (green below, red beyond 2×)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="54" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="55" t="inlineStr">
         <is>
           <t>Solver tolerance</t>
         </is>
       </c>
-      <c r="B28" s="31" t="inlineStr">
+      <c r="B47" s="31" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G28" s="31" t="inlineStr">
+      <c r="G47" s="31" t="inlineStr">
         <is>
           <t>Actual tolerance the optimizer converged at (progressive up to max)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="53" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="54" t="inlineStr">
         <is>
           <t>Max tolerance</t>
         </is>
       </c>
-      <c r="B29" s="27" t="inlineStr">
+      <c r="B48" s="27" t="inlineStr">
         <is>
           <t>±2.0%</t>
         </is>
       </c>
-      <c r="G29" s="27" t="inlineStr">
+      <c r="G48" s="27" t="inlineStr">
         <is>
           <t>Cap on solver tolerance (from config.rebalancing_max_tolerance)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="54" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="55" t="inlineStr">
         <is>
           <t>Min transaction</t>
         </is>
       </c>
-      <c r="B30" s="31" t="inlineStr">
+      <c r="B49" s="31" t="inlineStr">
         <is>
           <t>0.0 EUR</t>
         </is>
       </c>
-      <c r="G30" s="31" t="inlineStr">
+      <c r="G49" s="31" t="inlineStr">
         <is>
           <t>Trades below this amount are skipped</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="53" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="54" t="inlineStr">
         <is>
           <t>Lump sum</t>
         </is>
       </c>
-      <c r="B31" s="27" t="inlineStr">
+      <c r="B50" s="27" t="inlineStr">
         <is>
           <t>1000.0 EUR</t>
         </is>
       </c>
-      <c r="G31" s="27" t="inlineStr">
+      <c r="G50" s="27" t="inlineStr">
         <is>
           <t>Additional cash to deploy in the rebalance</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="54" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="55" t="inlineStr">
         <is>
           <t>No-sell mode</t>
         </is>
       </c>
-      <c r="B32" s="31" t="inlineStr">
+      <c r="B51" s="31" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="G32" s="31" t="inlineStr">
+      <c r="G51" s="31" t="inlineStr">
         <is>
           <t>If enabled, the solver can only buy, never sell</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="36" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-04 13:06 v2.0</t>
+    <row r="53">
+      <c r="A53" s="36" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-04 13:21 v2.0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="10">
+    <mergeCell ref="A44:G44"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1901,25 +2204,25 @@
         <v>128</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>155</v>
+        <v>154.9600067138672</v>
       </c>
       <c r="J4" s="28" t="n">
         <v>10240</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>12400</v>
+        <v>12396.80053710938</v>
       </c>
       <c r="L4" s="29" t="n">
-        <v>15.34282691319409</v>
+        <v>15.33905779931094</v>
       </c>
       <c r="M4" s="29" t="n">
-        <v>23.70362040403714</v>
+        <v>23.69795705541933</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>2160</v>
+        <v>2156.800537109375</v>
       </c>
       <c r="O4" s="29" t="n">
-        <v>21.09375</v>
+        <v>21.06250524520874</v>
       </c>
       <c r="P4" s="27" t="inlineStr">
         <is>
@@ -1938,7 +2241,7 @@
       </c>
       <c r="S4" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:06</t>
+          <t>2026-05-04 13:21</t>
         </is>
       </c>
     </row>
@@ -1989,10 +2292,10 @@
         <v>11547.61339873075</v>
       </c>
       <c r="L5" s="33" t="n">
-        <v>14.2881478739683</v>
+        <v>14.28832454285263</v>
       </c>
       <c r="M5" s="33" t="n">
-        <v>22.07421327226508</v>
+        <v>22.07463495089159</v>
       </c>
       <c r="N5" s="32" t="n">
         <v>9307.613398730755</v>
@@ -2017,7 +2320,7 @@
       </c>
       <c r="S5" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:06</t>
+          <t>2026-05-04 13:21</t>
         </is>
       </c>
     </row>
@@ -2068,10 +2371,10 @@
         <v>9961.430530910857</v>
       </c>
       <c r="L6" s="29" t="n">
-        <v>12.325524551901</v>
+        <v>12.3256769535062</v>
       </c>
       <c r="M6" s="29" t="n">
-        <v>19.04209419241106</v>
+        <v>19.04245794916315</v>
       </c>
       <c r="N6" s="28" t="n">
         <v>1411.430530910857</v>
@@ -2096,7 +2399,7 @@
       </c>
       <c r="S6" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:06</t>
+          <t>2026-05-04 13:21</t>
         </is>
       </c>
     </row>
@@ -2138,25 +2441,25 @@
         <v>56</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>76.09600067138672</v>
+        <v>76.12599945068359</v>
       </c>
       <c r="J7" s="32" t="n">
         <v>5040</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>6848.640060424805</v>
+        <v>6851.339950561523</v>
       </c>
       <c r="L7" s="33" t="n">
-        <v>8.473991857892328</v>
+        <v>8.477437318588693</v>
       </c>
       <c r="M7" s="33" t="n">
-        <v>13.09173905453158</v>
+        <v>13.09715030377868</v>
       </c>
       <c r="N7" s="32" t="n">
-        <v>1808.640060424805</v>
+        <v>1811.339950561523</v>
       </c>
       <c r="O7" s="33" t="n">
-        <v>35.88571548461914</v>
+        <v>35.93928473336356</v>
       </c>
       <c r="P7" s="31" t="inlineStr">
         <is>
@@ -2175,7 +2478,7 @@
       </c>
       <c r="S7" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:06</t>
+          <t>2026-05-04 13:21</t>
         </is>
       </c>
     </row>
@@ -2217,25 +2520,25 @@
         <v>98</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>117.6999969482422</v>
+        <v>117.6900024414062</v>
       </c>
       <c r="J8" s="28" t="n">
         <v>4900</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>5884.999847412109</v>
+        <v>5884.500122070312</v>
       </c>
       <c r="L8" s="29" t="n">
-        <v>7.281655971211097</v>
+        <v>7.28112767663646</v>
       </c>
       <c r="M8" s="29" t="n">
-        <v>11.24966148878009</v>
+        <v>11.24892110411809</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>984.9998474121094</v>
+        <v>984.5001220703125</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>20.10203770228795</v>
+        <v>20.09183922592474</v>
       </c>
       <c r="P8" s="27" t="inlineStr">
         <is>
@@ -2254,7 +2557,7 @@
       </c>
       <c r="S8" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:06</t>
+          <t>2026-05-04 13:21</t>
         </is>
       </c>
     </row>
@@ -2305,10 +2608,10 @@
         <v>5670</v>
       </c>
       <c r="L9" s="33" t="n">
-        <v>7.015631338533103</v>
+        <v>7.015718084819072</v>
       </c>
       <c r="M9" s="33" t="n">
-        <v>10.83867158797505</v>
+        <v>10.83887863662915</v>
       </c>
       <c r="N9" s="32" t="n">
         <v>1710</v>
@@ -2333,7 +2636,7 @@
       </c>
       <c r="S9" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:06</t>
+          <t>2026-05-04 13:21</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2687,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>13.25793489645195</v>
+        <v>13.25809882704585</v>
       </c>
       <c r="M10" s="29" t="n">
         <v>64.31917363528412</v>
@@ -2412,7 +2715,7 @@
       </c>
       <c r="S10" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:06</t>
+          <t>2026-05-04 13:21</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2766,7 @@
         <v>5944.107150852142</v>
       </c>
       <c r="L11" s="33" t="n">
-        <v>7.354790900726102</v>
+        <v>7.354881840623588</v>
       </c>
       <c r="M11" s="33" t="n">
         <v>35.68082636471589</v>
@@ -2491,7 +2794,7 @@
       </c>
       <c r="S11" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:06</t>
+          <t>2026-05-04 13:21</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2845,7 @@
         <v>5000</v>
       </c>
       <c r="L12" s="29" t="n">
-        <v>6.186623755320196</v>
+        <v>6.186700251163203</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>100</v>
@@ -2570,7 +2873,7 @@
       </c>
       <c r="S12" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:06</t>
+          <t>2026-05-04 13:21</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2893,7 @@
           <t>IE00B579F325</t>
         </is>
       </c>
-      <c r="D13" s="55" t="inlineStr">
+      <c r="D13" s="56" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
@@ -2621,7 +2924,7 @@
         <v>6847.734948739668</v>
       </c>
       <c r="L13" s="33" t="n">
-        <v>8.472871940801831</v>
+        <v>8.47297670545335</v>
       </c>
       <c r="M13" s="33" t="n">
         <v>100</v>
@@ -2649,14 +2952,14 @@
       </c>
       <c r="S13" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:06</t>
+          <t>2026-05-04 13:21</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:06 v2.0</t>
+          <t>Generated 2026-05-04 13:21 v2.0</t>
         </is>
       </c>
     </row>
@@ -2706,7 +3009,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="56" t="inlineStr">
+      <c r="A2" s="57" t="inlineStr">
         <is>
           <t>Period returns (1D–5Y) and risk metrics calculated on available history per instrument (max 5 years). α/β computed vs S&amp;P 500.</t>
         </is>
@@ -2820,71 +3123,71 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="57" t="inlineStr">
+      <c r="A5" s="58" t="inlineStr">
         <is>
           <t>** TOTAL PORTFOLIO **</t>
         </is>
       </c>
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="C5" s="59" t="n">
+      <c r="C5" s="60" t="n">
         <v>0.27</v>
       </c>
-      <c r="D5" s="59" t="n">
+      <c r="D5" s="60" t="n">
         <v>0.47</v>
       </c>
-      <c r="E5" s="59" t="n">
+      <c r="E5" s="60" t="n">
         <v>5.91</v>
       </c>
-      <c r="F5" s="59" t="n">
+      <c r="F5" s="60" t="n">
         <v>4.01</v>
       </c>
-      <c r="G5" s="59" t="n">
+      <c r="G5" s="60" t="n">
         <v>6.58</v>
       </c>
-      <c r="H5" s="59" t="n">
+      <c r="H5" s="60" t="n">
         <v>6.98</v>
       </c>
-      <c r="I5" s="59" t="n">
+      <c r="I5" s="60" t="n">
         <v>22</v>
       </c>
-      <c r="J5" s="59" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="K5" s="59" t="n">
+      <c r="J5" s="60" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="K5" s="60" t="n">
         <v>45.09</v>
       </c>
-      <c r="L5" s="59" t="n">
+      <c r="L5" s="60" t="n">
         <v>7.92</v>
       </c>
-      <c r="M5" s="59" t="n">
+      <c r="M5" s="60" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="N5" s="59" t="n">
+      <c r="N5" s="60" t="n">
         <v>0.48</v>
       </c>
-      <c r="O5" s="59" t="n">
+      <c r="O5" s="60" t="n">
         <v>0.63</v>
       </c>
-      <c r="P5" s="60" t="n">
+      <c r="P5" s="61" t="n">
         <v>-13.91</v>
       </c>
-      <c r="Q5" s="60" t="n">
+      <c r="Q5" s="61" t="n">
         <v>-0.77</v>
       </c>
-      <c r="R5" s="60" t="n">
+      <c r="R5" s="61" t="n">
         <v>-1.22</v>
       </c>
-      <c r="S5" s="59" t="n">
+      <c r="S5" s="60" t="n">
         <v>2.68</v>
       </c>
-      <c r="T5" s="59" t="n">
+      <c r="T5" s="60" t="n">
         <v>0.15</v>
       </c>
-      <c r="U5" s="58" t="inlineStr">
+      <c r="U5" s="59" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -2940,13 +3243,13 @@
       <c r="O6" s="29" t="n">
         <v>0.73</v>
       </c>
-      <c r="P6" s="61" t="n">
+      <c r="P6" s="62" t="n">
         <v>-20.22</v>
       </c>
-      <c r="Q6" s="61" t="n">
+      <c r="Q6" s="62" t="n">
         <v>-1.4</v>
       </c>
-      <c r="R6" s="61" t="n">
+      <c r="R6" s="62" t="n">
         <v>-2.13</v>
       </c>
       <c r="S6" s="29" t="n">
@@ -2973,31 +3276,31 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6.62</v>
+        <v>6.64</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>6.37</v>
+        <v>6.39</v>
       </c>
       <c r="H7" s="33" t="n">
-        <v>6.5</v>
+        <v>6.52</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>23.66</v>
+        <v>23.69</v>
       </c>
       <c r="J7" s="33" t="n">
-        <v>56.14</v>
+        <v>56.16</v>
       </c>
       <c r="K7" s="33" t="n">
-        <v>58.71</v>
+        <v>58.74</v>
       </c>
       <c r="L7" s="33" t="n">
         <v>9.83</v>
@@ -3011,16 +3314,16 @@
       <c r="O7" s="33" t="n">
         <v>0.55</v>
       </c>
-      <c r="P7" s="62" t="n">
+      <c r="P7" s="63" t="n">
         <v>-20.07</v>
       </c>
-      <c r="Q7" s="62" t="n">
+      <c r="Q7" s="63" t="n">
         <v>-1.44</v>
       </c>
-      <c r="R7" s="62" t="n">
+      <c r="R7" s="63" t="n">
         <v>-2.13</v>
       </c>
-      <c r="S7" s="62" t="n">
+      <c r="S7" s="63" t="n">
         <v>-0.49</v>
       </c>
       <c r="T7" s="33" t="n">
@@ -3043,10 +3346,10 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C8" s="61" t="n">
+      <c r="C8" s="62" t="n">
         <v>-0.59</v>
       </c>
-      <c r="D8" s="61" t="n">
+      <c r="D8" s="62" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" s="29" t="n">
@@ -3082,16 +3385,16 @@
       <c r="O8" s="29" t="n">
         <v>0.44</v>
       </c>
-      <c r="P8" s="61" t="n">
+      <c r="P8" s="62" t="n">
         <v>-17.35</v>
       </c>
-      <c r="Q8" s="61" t="n">
+      <c r="Q8" s="62" t="n">
         <v>-1.63</v>
       </c>
-      <c r="R8" s="61" t="n">
+      <c r="R8" s="62" t="n">
         <v>-2.43</v>
       </c>
-      <c r="S8" s="61" t="n">
+      <c r="S8" s="62" t="n">
         <v>-1.39</v>
       </c>
       <c r="T8" s="29" t="n">
@@ -3114,7 +3417,7 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C9" s="62" t="n">
+      <c r="C9" s="63" t="n">
         <v>-0.16</v>
       </c>
       <c r="D9" s="33" t="n">
@@ -3153,16 +3456,16 @@
       <c r="O9" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="P9" s="62" t="n">
+      <c r="P9" s="63" t="n">
         <v>-24.81</v>
       </c>
-      <c r="Q9" s="62" t="n">
+      <c r="Q9" s="63" t="n">
         <v>-1.93</v>
       </c>
-      <c r="R9" s="62" t="n">
+      <c r="R9" s="63" t="n">
         <v>-2.72</v>
       </c>
-      <c r="S9" s="62" t="n">
+      <c r="S9" s="63" t="n">
         <v>-3.89</v>
       </c>
       <c r="T9" s="33" t="n">
@@ -3186,34 +3489,34 @@
         </is>
       </c>
       <c r="C10" s="29" t="n">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>5.95</v>
+        <v>5.97</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>5.06</v>
+        <v>5.08</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>5.34</v>
+        <v>5.37</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>21.72</v>
+        <v>21.74</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>55.66</v>
+        <v>55.7</v>
       </c>
       <c r="K10" s="29" t="n">
-        <v>63.26</v>
+        <v>63.3</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>10.46</v>
+        <v>10.47</v>
       </c>
       <c r="M10" s="29" t="n">
         <v>16.47</v>
@@ -3224,16 +3527,16 @@
       <c r="O10" s="29" t="n">
         <v>0.52</v>
       </c>
-      <c r="P10" s="61" t="n">
+      <c r="P10" s="62" t="n">
         <v>-20.63</v>
       </c>
-      <c r="Q10" s="61" t="n">
+      <c r="Q10" s="62" t="n">
         <v>-1.56</v>
       </c>
-      <c r="R10" s="61" t="n">
+      <c r="R10" s="62" t="n">
         <v>-2.29</v>
       </c>
-      <c r="S10" s="61" t="n">
+      <c r="S10" s="62" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="T10" s="29" t="n">
@@ -3295,13 +3598,13 @@
       <c r="O11" s="33" t="n">
         <v>0.55</v>
       </c>
-      <c r="P11" s="62" t="n">
+      <c r="P11" s="63" t="n">
         <v>-25.91</v>
       </c>
-      <c r="Q11" s="62" t="n">
+      <c r="Q11" s="63" t="n">
         <v>-2.26</v>
       </c>
-      <c r="R11" s="62" t="n">
+      <c r="R11" s="63" t="n">
         <v>-3.15</v>
       </c>
       <c r="S11" s="33" t="n">
@@ -3327,10 +3630,10 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C12" s="61" t="n">
+      <c r="C12" s="62" t="n">
         <v>-0.42</v>
       </c>
-      <c r="D12" s="61" t="n">
+      <c r="D12" s="62" t="n">
         <v>-0.5</v>
       </c>
       <c r="E12" s="29" t="n">
@@ -3366,16 +3669,16 @@
       <c r="O12" s="29" t="n">
         <v>0.61</v>
       </c>
-      <c r="P12" s="61" t="n">
+      <c r="P12" s="62" t="n">
         <v>-22.45</v>
       </c>
-      <c r="Q12" s="61" t="n">
+      <c r="Q12" s="62" t="n">
         <v>-1.79</v>
       </c>
-      <c r="R12" s="61" t="n">
+      <c r="R12" s="62" t="n">
         <v>-2.66</v>
       </c>
-      <c r="S12" s="61" t="n">
+      <c r="S12" s="62" t="n">
         <v>-0.13</v>
       </c>
       <c r="T12" s="29" t="n">
@@ -3437,13 +3740,13 @@
       <c r="O13" s="33" t="n">
         <v>0.7</v>
       </c>
-      <c r="P13" s="62" t="n">
+      <c r="P13" s="63" t="n">
         <v>-31.38</v>
       </c>
-      <c r="Q13" s="62" t="n">
+      <c r="Q13" s="63" t="n">
         <v>-2.45</v>
       </c>
-      <c r="R13" s="62" t="n">
+      <c r="R13" s="63" t="n">
         <v>-3.4</v>
       </c>
       <c r="S13" s="33" t="n">
@@ -3469,7 +3772,7 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C14" s="61" t="n">
+      <c r="C14" s="62" t="n">
         <v>-0.09</v>
       </c>
       <c r="D14" s="29" t="n">
@@ -3508,13 +3811,13 @@
       <c r="O14" s="29" t="n">
         <v>0.62</v>
       </c>
-      <c r="P14" s="61" t="n">
+      <c r="P14" s="62" t="n">
         <v>-23.17</v>
       </c>
-      <c r="Q14" s="61" t="n">
+      <c r="Q14" s="62" t="n">
         <v>-1.87</v>
       </c>
-      <c r="R14" s="61" t="n">
+      <c r="R14" s="62" t="n">
         <v>-2.64</v>
       </c>
       <c r="S14" s="29" t="n">
@@ -3543,16 +3846,16 @@
       <c r="C15" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="62" t="n">
+      <c r="D15" s="63" t="n">
         <v>-0.11</v>
       </c>
       <c r="E15" s="33" t="n">
         <v>0.38</v>
       </c>
-      <c r="F15" s="62" t="n">
+      <c r="F15" s="63" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G15" s="62" t="n">
+      <c r="G15" s="63" t="n">
         <v>-0.64</v>
       </c>
       <c r="H15" s="33" t="n">
@@ -3564,31 +3867,31 @@
       <c r="J15" s="33" t="n">
         <v>7.86</v>
       </c>
-      <c r="K15" s="62" t="n">
+      <c r="K15" s="63" t="n">
         <v>-8.98</v>
       </c>
-      <c r="L15" s="62" t="n">
+      <c r="L15" s="63" t="n">
         <v>-1.87</v>
       </c>
       <c r="M15" s="33" t="n">
         <v>5.55</v>
       </c>
-      <c r="N15" s="62" t="n">
+      <c r="N15" s="63" t="n">
         <v>-1.06</v>
       </c>
-      <c r="O15" s="62" t="n">
+      <c r="O15" s="63" t="n">
         <v>-1.63</v>
       </c>
-      <c r="P15" s="62" t="n">
+      <c r="P15" s="63" t="n">
         <v>-19.81</v>
       </c>
-      <c r="Q15" s="62" t="n">
+      <c r="Q15" s="63" t="n">
         <v>-0.55</v>
       </c>
-      <c r="R15" s="62" t="n">
+      <c r="R15" s="63" t="n">
         <v>-0.77</v>
       </c>
-      <c r="S15" s="62" t="n">
+      <c r="S15" s="63" t="n">
         <v>-6</v>
       </c>
       <c r="T15" s="33" t="n">
@@ -3603,7 +3906,7 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
@@ -3612,58 +3915,58 @@
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>7.7</v>
+        <v>7.26</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>4.66</v>
+        <v>4.18</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>6.56</v>
+        <v>5.33</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>6.79</v>
+        <v>5.72</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>24.56</v>
+        <v>22.87</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>62.73</v>
+        <v>62.56</v>
       </c>
       <c r="K16" s="29" t="n">
-        <v>70.2</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="L16" s="29" t="n">
-        <v>11.51</v>
+        <v>12.15</v>
       </c>
       <c r="M16" s="29" t="n">
-        <v>13.8</v>
+        <v>14.24</v>
       </c>
       <c r="N16" s="29" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="O16" s="29" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P16" s="61" t="n">
-        <v>-21.07</v>
-      </c>
-      <c r="Q16" s="61" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="R16" s="61" t="n">
-        <v>-2.13</v>
+        <v>0.73</v>
+      </c>
+      <c r="P16" s="62" t="n">
+        <v>-21.73</v>
+      </c>
+      <c r="Q16" s="62" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="R16" s="62" t="n">
+        <v>-2.19</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>5.91</v>
+        <v>6.34</v>
       </c>
       <c r="T16" s="29" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="U16" s="27" t="inlineStr">
         <is>
@@ -3674,7 +3977,7 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
@@ -3683,58 +3986,58 @@
         </is>
       </c>
       <c r="C17" s="33" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="E17" s="33" t="n">
-        <v>7.27</v>
+        <v>7.67</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>4.19</v>
+        <v>4.63</v>
       </c>
       <c r="G17" s="33" t="n">
-        <v>5.34</v>
+        <v>6.53</v>
       </c>
       <c r="H17" s="33" t="n">
-        <v>5.73</v>
+        <v>6.77</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>22.88</v>
+        <v>24.53</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>62.57</v>
+        <v>62.69</v>
       </c>
       <c r="K17" s="33" t="n">
-        <v>75.03</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="L17" s="33" t="n">
-        <v>12.15</v>
+        <v>11.51</v>
       </c>
       <c r="M17" s="33" t="n">
-        <v>14.24</v>
+        <v>13.8</v>
       </c>
       <c r="N17" s="33" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="O17" s="33" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="P17" s="62" t="n">
-        <v>-21.73</v>
-      </c>
-      <c r="Q17" s="62" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="R17" s="62" t="n">
-        <v>-2.19</v>
+        <v>0.7</v>
+      </c>
+      <c r="P17" s="63" t="n">
+        <v>-21.07</v>
+      </c>
+      <c r="Q17" s="63" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="R17" s="63" t="n">
+        <v>-2.13</v>
       </c>
       <c r="S17" s="33" t="n">
-        <v>6.34</v>
+        <v>5.9</v>
       </c>
       <c r="T17" s="33" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="U17" s="31" t="inlineStr">
         <is>
@@ -3754,34 +4057,34 @@
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="E18" s="29" t="n">
-        <v>12.5</v>
+        <v>12.54</v>
       </c>
       <c r="F18" s="29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="G18" s="29" t="n">
-        <v>16.41</v>
+        <v>16.45</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>16.01</v>
+        <v>16.06</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>40.59</v>
+        <v>40.65</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>68.5</v>
+        <v>68.56</v>
       </c>
       <c r="K18" s="29" t="n">
-        <v>41.99</v>
+        <v>42.04</v>
       </c>
       <c r="L18" s="29" t="n">
-        <v>7.54</v>
+        <v>7.55</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>18.82</v>
@@ -3792,17 +4095,17 @@
       <c r="O18" s="29" t="n">
         <v>0.26</v>
       </c>
-      <c r="P18" s="61" t="n">
+      <c r="P18" s="62" t="n">
         <v>-24.38</v>
       </c>
-      <c r="Q18" s="61" t="n">
+      <c r="Q18" s="62" t="n">
         <v>-1.59</v>
       </c>
-      <c r="R18" s="61" t="n">
+      <c r="R18" s="62" t="n">
         <v>-2.59</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="T18" s="29" t="n">
         <v>0.1</v>
@@ -3824,7 +4127,7 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C19" s="62" t="n">
+      <c r="C19" s="63" t="n">
         <v>-0.11</v>
       </c>
       <c r="D19" s="33" t="n">
@@ -3863,13 +4166,13 @@
       <c r="O19" s="33" t="n">
         <v>0.79</v>
       </c>
-      <c r="P19" s="62" t="n">
+      <c r="P19" s="63" t="n">
         <v>-22.73</v>
       </c>
-      <c r="Q19" s="62" t="n">
+      <c r="Q19" s="63" t="n">
         <v>-1.73</v>
       </c>
-      <c r="R19" s="62" t="n">
+      <c r="R19" s="63" t="n">
         <v>-2.53</v>
       </c>
       <c r="S19" s="33" t="n">
@@ -3898,55 +4201,55 @@
       <c r="C20" s="29" t="n">
         <v>0.31</v>
       </c>
-      <c r="D20" s="61" t="n">
+      <c r="D20" s="62" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E20" s="61" t="n">
+      <c r="E20" s="62" t="n">
         <v>-1.11</v>
       </c>
       <c r="F20" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="G20" s="61" t="n">
+      <c r="G20" s="62" t="n">
         <v>-1.55</v>
       </c>
       <c r="H20" s="29" t="n">
         <v>0.02</v>
       </c>
-      <c r="I20" s="61" t="n">
+      <c r="I20" s="62" t="n">
         <v>-0.52</v>
       </c>
-      <c r="J20" s="61" t="n">
+      <c r="J20" s="62" t="n">
         <v>-0.82</v>
       </c>
-      <c r="K20" s="61" t="n">
+      <c r="K20" s="62" t="n">
         <v>-1.61</v>
       </c>
-      <c r="L20" s="61" t="n">
+      <c r="L20" s="62" t="n">
         <v>-0.33</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>10.65</v>
       </c>
-      <c r="N20" s="61" t="n">
+      <c r="N20" s="62" t="n">
         <v>-0.41</v>
       </c>
-      <c r="O20" s="61" t="n">
+      <c r="O20" s="62" t="n">
         <v>-0.61</v>
       </c>
-      <c r="P20" s="61" t="n">
+      <c r="P20" s="62" t="n">
         <v>-15.77</v>
       </c>
-      <c r="Q20" s="61" t="n">
+      <c r="Q20" s="62" t="n">
         <v>-1.1</v>
       </c>
-      <c r="R20" s="61" t="n">
+      <c r="R20" s="62" t="n">
         <v>-1.48</v>
       </c>
-      <c r="S20" s="61" t="n">
+      <c r="S20" s="62" t="n">
         <v>-4.14</v>
       </c>
-      <c r="T20" s="61" t="n">
+      <c r="T20" s="62" t="n">
         <v>-0.02</v>
       </c>
       <c r="U20" s="27" t="inlineStr">
@@ -3966,13 +4269,13 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C21" s="62" t="n">
+      <c r="C21" s="63" t="n">
         <v>-0.1</v>
       </c>
-      <c r="D21" s="62" t="n">
+      <c r="D21" s="63" t="n">
         <v>-2.09</v>
       </c>
-      <c r="E21" s="62" t="n">
+      <c r="E21" s="63" t="n">
         <v>-4.21</v>
       </c>
       <c r="F21" s="33" t="n">
@@ -4005,13 +4308,13 @@
       <c r="O21" s="33" t="n">
         <v>1.36</v>
       </c>
-      <c r="P21" s="62" t="n">
+      <c r="P21" s="63" t="n">
         <v>-15.94</v>
       </c>
-      <c r="Q21" s="62" t="n">
+      <c r="Q21" s="63" t="n">
         <v>-1.75</v>
       </c>
-      <c r="R21" s="62" t="n">
+      <c r="R21" s="63" t="n">
         <v>-2.57</v>
       </c>
       <c r="S21" s="33" t="n">
@@ -4029,7 +4332,7 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
+          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
@@ -4037,59 +4340,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C22" s="61" t="n">
-        <v>-0.31</v>
+      <c r="C22" s="29" t="n">
+        <v>0.04</v>
       </c>
       <c r="D22" s="29" t="n">
-        <v>0.15</v>
+        <v>0.93</v>
       </c>
       <c r="E22" s="29" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="F22" s="61" t="n">
-        <v>-0.9399999999999999</v>
+        <v>9.6</v>
+      </c>
+      <c r="F22" s="29" t="n">
+        <v>10.93</v>
       </c>
       <c r="G22" s="29" t="n">
-        <v>7.24</v>
+        <v>10.3</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>2.3</v>
+        <v>17.9</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>14.57</v>
+        <v>44.84</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>40.38</v>
+        <v>73.92</v>
       </c>
       <c r="K22" s="29" t="n">
-        <v>54.73</v>
+        <v>57.6</v>
       </c>
       <c r="L22" s="29" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="M22" s="29" t="n">
-        <v>14.94</v>
+        <v>18.27</v>
       </c>
       <c r="N22" s="29" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="O22" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P22" s="61" t="n">
-        <v>-22.86</v>
-      </c>
-      <c r="Q22" s="61" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="R22" s="61" t="n">
-        <v>-2.22</v>
+        <v>0.46</v>
+      </c>
+      <c r="P22" s="62" t="n">
+        <v>-21.24</v>
+      </c>
+      <c r="Q22" s="62" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="R22" s="62" t="n">
+        <v>-2.5</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>4.11</v>
+        <v>3.42</v>
       </c>
       <c r="T22" s="29" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="U22" s="27" t="inlineStr">
         <is>
@@ -4100,7 +4403,7 @@
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
+          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
       <c r="B23" s="31" t="inlineStr">
@@ -4108,59 +4411,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C23" s="33" t="n">
-        <v>0.04</v>
+      <c r="C23" s="63" t="n">
+        <v>-0.31</v>
       </c>
       <c r="D23" s="33" t="n">
-        <v>0.93</v>
+        <v>0.15</v>
       </c>
       <c r="E23" s="33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F23" s="33" t="n">
-        <v>10.93</v>
+        <v>4.35</v>
+      </c>
+      <c r="F23" s="63" t="n">
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G23" s="33" t="n">
-        <v>10.3</v>
+        <v>7.24</v>
       </c>
       <c r="H23" s="33" t="n">
-        <v>17.9</v>
+        <v>2.3</v>
       </c>
       <c r="I23" s="33" t="n">
-        <v>44.84</v>
+        <v>14.57</v>
       </c>
       <c r="J23" s="33" t="n">
-        <v>73.92</v>
+        <v>40.38</v>
       </c>
       <c r="K23" s="33" t="n">
-        <v>57.6</v>
+        <v>54.73</v>
       </c>
       <c r="L23" s="33" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="M23" s="33" t="n">
-        <v>18.27</v>
+        <v>14.94</v>
       </c>
       <c r="N23" s="33" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="O23" s="33" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P23" s="62" t="n">
-        <v>-21.24</v>
-      </c>
-      <c r="Q23" s="62" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="R23" s="62" t="n">
-        <v>-2.5</v>
+        <v>0.5</v>
+      </c>
+      <c r="P23" s="63" t="n">
+        <v>-22.86</v>
+      </c>
+      <c r="Q23" s="63" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="R23" s="63" t="n">
+        <v>-2.22</v>
       </c>
       <c r="S23" s="33" t="n">
-        <v>3.42</v>
+        <v>4.11</v>
       </c>
       <c r="T23" s="33" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="U23" s="31" t="inlineStr">
         <is>
@@ -4169,7 +4472,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="63" t="inlineStr">
+      <c r="A26" s="64" t="inlineStr">
         <is>
           <t>Legend — Rating Thresholds</t>
         </is>
@@ -4213,7 +4516,7 @@
           <t>CAGR</t>
         </is>
       </c>
-      <c r="B28" s="64" t="inlineStr">
+      <c r="B28" s="65" t="inlineStr">
         <is>
           <t>Compound Annual Growth Rate. The single yearly return that, if repeated every year, would grow your portfolio from start to end value. Accounts for compounding. ~7% is the long-term global equity average.</t>
         </is>
@@ -4245,7 +4548,7 @@
           <t>α (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B29" s="65" t="inlineStr">
+      <c r="B29" s="66" t="inlineStr">
         <is>
           <t>Extra annual return vs the benchmark, after adjusting for how risky the portfolio is (CAPM). Positive = you beat the market beyond what your risk alone justified. Negative = you underperformed after fees and noise.</t>
         </is>
@@ -4277,7 +4580,7 @@
           <t>β (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B30" s="64" t="inlineStr">
+      <c r="B30" s="65" t="inlineStr">
         <is>
           <t>How much your portfolio moves when the benchmark moves 1%. β=1 in line, β=0.5 half as reactive, β=1.5 amplifies by 50%, β≈0 uncorrelated. Tells you how much systematic market risk you're running.</t>
         </is>
@@ -4309,7 +4612,7 @@
           <t>Max DD</t>
         </is>
       </c>
-      <c r="B31" s="65" t="inlineStr">
+      <c r="B31" s="66" t="inlineStr">
         <is>
           <t>Maximum Drawdown. Worst peak-to-trough loss over the period — the most painful scenario an investor lived through. -20% is typical for diversified equity; deeper drops signal concentration or high volatility.</t>
         </is>
@@ -4341,7 +4644,7 @@
           <t>Volatility</t>
         </is>
       </c>
-      <c r="B32" s="64" t="inlineStr">
+      <c r="B32" s="65" t="inlineStr">
         <is>
           <t>How bumpy the ride is. Annualized standard deviation of daily returns. A 15% vol means ~±15% year-to-year noise around the average return. Equity indexes ~15–20%, bonds ~3–7%.</t>
         </is>
@@ -4373,7 +4676,7 @@
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="B33" s="65" t="inlineStr">
+      <c r="B33" s="66" t="inlineStr">
         <is>
           <t>Return per unit of risk taken: (CAGR − risk-free rate) / Volatility. Above 1 is good, above 2 is excellent, negative means you were paid less than a safe bond for the risk you ran.</t>
         </is>
@@ -4405,7 +4708,7 @@
           <t>Sortino</t>
         </is>
       </c>
-      <c r="B34" s="64" t="inlineStr">
+      <c r="B34" s="65" t="inlineStr">
         <is>
           <t>Like Sharpe but only penalizes downside volatility (ignores upside swings). More honest when returns are asymmetric. Usually higher than Sharpe — the gap shows how much of your volatility is actually good volatility.</t>
         </is>
@@ -4437,7 +4740,7 @@
           <t>VaR 95%</t>
         </is>
       </c>
-      <c r="B35" s="65" t="inlineStr">
+      <c r="B35" s="66" t="inlineStr">
         <is>
           <t>Value at Risk. The daily loss exceeded only 5% of the time (historical simulation). A VaR of -1.2% means on an average month you should expect about one day worse than -1.2%. Non-parametric: no normal-distribution assumption.</t>
         </is>
@@ -4469,7 +4772,7 @@
           <t>CVaR 95%</t>
         </is>
       </c>
-      <c r="B36" s="64" t="inlineStr">
+      <c r="B36" s="65" t="inlineStr">
         <is>
           <t>Conditional VaR, a.k.a. Expected Shortfall. The average loss on the worst 5% of days. Always more negative than VaR. Captures tail risk VaR misses — how bad it really gets when it goes bad.</t>
         </is>
@@ -4498,7 +4801,7 @@
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:06 v2.0</t>
+          <t>Generated 2026-05-04 13:21 v2.0</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4841,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="63" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>Return Contribution by Holding</t>
         </is>
@@ -4593,13 +4896,13 @@
         </is>
       </c>
       <c r="D5" s="29" t="n">
-        <v>14.2881478739683</v>
+        <v>14.28832454285263</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>415.5184553004801</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>59.36989133696145</v>
+        <v>59.37062542878062</v>
       </c>
     </row>
     <row r="6">
@@ -4619,13 +4922,13 @@
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>13.25793489645195</v>
+        <v>13.25809882704585</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>91.33928843906948</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>12.1097033961343</v>
+        <v>12.1098531291723</v>
       </c>
     </row>
     <row r="7">
@@ -4645,13 +4948,13 @@
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>8.472871940801831</v>
+        <v>8.47297670545335</v>
       </c>
       <c r="E7" s="29" t="n">
         <v>55.27743647935755</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>4.683586405054041</v>
+        <v>4.683644316267737</v>
       </c>
     </row>
     <row r="8">
@@ -4671,13 +4974,13 @@
         </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>15.34282691319409</v>
+        <v>15.33905779931094</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>21.09375</v>
+        <v>21.06250524520874</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.236377552001878</v>
+        <v>3.230789853545467</v>
       </c>
     </row>
     <row r="9">
@@ -4697,13 +5000,13 @@
         </is>
       </c>
       <c r="D9" s="29" t="n">
-        <v>7.354790900726102</v>
+        <v>7.354881840623588</v>
       </c>
       <c r="E9" s="29" t="n">
         <v>41.5263607345748</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>3.054177000709204</v>
+        <v>3.054214764739086</v>
       </c>
     </row>
     <row r="10">
@@ -4723,13 +5026,13 @@
         </is>
       </c>
       <c r="D10" s="33" t="n">
-        <v>8.473991857892328</v>
+        <v>8.477437318588693</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>35.88571548461914</v>
+        <v>35.93928473336356</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>3.040952608313032</v>
+        <v>3.046730336020011</v>
       </c>
     </row>
     <row r="11">
@@ -4749,13 +5052,13 @@
         </is>
       </c>
       <c r="D11" s="29" t="n">
-        <v>7.015631338533103</v>
+        <v>7.015718084819072</v>
       </c>
       <c r="E11" s="29" t="n">
         <v>43.18181818181818</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>3.029477168912022</v>
+        <v>3.029514627535509</v>
       </c>
     </row>
     <row r="12">
@@ -4775,13 +5078,13 @@
         </is>
       </c>
       <c r="D12" s="33" t="n">
-        <v>12.325524551901</v>
+        <v>12.3256769535062</v>
       </c>
       <c r="E12" s="33" t="n">
         <v>16.50795942585797</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>2.034692592051979</v>
+        <v>2.03471775044713</v>
       </c>
     </row>
     <row r="13">
@@ -4801,13 +5104,13 @@
         </is>
       </c>
       <c r="D13" s="29" t="n">
-        <v>7.281655971211097</v>
+        <v>7.28112767663646</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>20.10203770228795</v>
+        <v>20.09183922592474</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>1.463761228683756</v>
+        <v>1.462912466624107</v>
       </c>
     </row>
     <row r="14">
@@ -4827,7 +5130,7 @@
         </is>
       </c>
       <c r="D14" s="33" t="n">
-        <v>6.186623755320196</v>
+        <v>6.186700251163203</v>
       </c>
       <c r="E14" s="33" t="n">
         <v>0</v>
@@ -4837,7 +5140,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="63" t="inlineStr">
+      <c r="A16" s="64" t="inlineStr">
         <is>
           <t>Breakdown by Asset Class</t>
         </is>
@@ -4872,10 +5175,10 @@
         </is>
       </c>
       <c r="B18" s="28" t="n">
-        <v>52312.68383747853</v>
+        <v>52311.68453938283</v>
       </c>
       <c r="C18" s="29" t="n">
-        <v>92.04828934917724</v>
+        <v>92.05031035210889</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>6</v>
@@ -4930,7 +5233,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="63" t="inlineStr">
+      <c r="A23" s="64" t="inlineStr">
         <is>
           <t>Breakdown by Geography (Equity Only)</t>
         </is>
@@ -4960,23 +5263,23 @@
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>41.78590318582933</v>
+        <v>41.78221986945917</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>19.23458237604864</v>
+        <v>19.22076796566382</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="55" t="inlineStr">
+      <c r="A26" s="56" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
       <c r="B26" s="33" t="n">
-        <v>15.49054543942014</v>
+        <v>15.49538355778712</v>
       </c>
       <c r="C26" s="33" t="n">
-        <v>28.48973274230957</v>
+        <v>28.50089498928615</v>
       </c>
     </row>
     <row r="27">
@@ -4986,10 +5289,10 @@
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>9.782738357331008</v>
+        <v>9.78236697442971</v>
       </c>
       <c r="C27" s="29" t="n">
-        <v>28.12586862803538</v>
+        <v>28.11205421765055</v>
       </c>
     </row>
     <row r="28">
@@ -4999,10 +5302,10 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>24.19736373853591</v>
+        <v>24.19739538174008</v>
       </c>
       <c r="C28" s="33" t="n">
-        <v>152.2380810009227</v>
+        <v>152.2242665905379</v>
       </c>
     </row>
     <row r="29">
@@ -5012,10 +5315,10 @@
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>8.743449278883624</v>
+        <v>8.742634216583923</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>28.12586862803538</v>
+        <v>28.11205421765055</v>
       </c>
     </row>
   </sheetData>

--- a/output/sample/portfolio_dashboard_sample.xlsx
+++ b/output/sample/portfolio_dashboard_sample.xlsx
@@ -363,7 +363,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -372,7 +372,7 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>80818.52679156253</v>
+        <v>80820.75625323245</v>
       </c>
       <c r="D5" s="2" t="n"/>
     </row>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>26678.52679156253</v>
+        <v>26680.75625323245</v>
       </c>
       <c r="D6" s="2" t="n"/>
     </row>
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>49.27692425482551</v>
+        <v>49.28104221136397</v>
       </c>
       <c r="D7" s="2" t="n"/>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>64.72734237571399</v>
+        <v>64.72831538118703</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>65</v>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>41.78221986945917</v>
+        <v>41.79626795598796</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>55</v>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>20.61298066766944</v>
+        <v>20.61241205321405</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>25</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>24.19739538174008</v>
+        <v>24.19785747467557</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>8</v>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>8.47297670545335</v>
+        <v>8.472742976177967</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>5</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>15.49538355778712</v>
+        <v>15.50380579197923</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>11</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>6.186700251163203</v>
+        <v>6.18652958942094</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>5</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>9.78236697442971</v>
+        <v>9.766116970263369</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>14</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>8.742634216583923</v>
+        <v>8.735951807093869</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>12</v>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="B21" s="28" t="n">
-        <v>12396.80053710938</v>
+        <v>12406.40014648438</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>15.33905779931094</v>
+        <v>15.35051232088437</v>
       </c>
       <c r="D21" s="30" t="n"/>
       <c r="E21" s="12" t="inlineStr">
@@ -1129,7 +1129,7 @@
         <v>11547.61339873075</v>
       </c>
       <c r="C22" s="33" t="n">
-        <v>14.28832454285263</v>
+        <v>14.2879303956883</v>
       </c>
       <c r="D22" s="30" t="n"/>
       <c r="E22" s="34" t="inlineStr">
@@ -1148,7 +1148,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>13.25809882704585</v>
+        <v>13.25773309892698</v>
       </c>
       <c r="D23" s="30" t="n"/>
       <c r="E23" s="35" t="inlineStr">
@@ -1167,7 +1167,7 @@
         <v>9961.430530910857</v>
       </c>
       <c r="C24" s="33" t="n">
-        <v>12.3256769535062</v>
+        <v>12.32533694648823</v>
       </c>
       <c r="D24" s="30" t="n"/>
       <c r="E24" s="34" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="B25" s="28" t="n">
-        <v>6851.339950561523</v>
+        <v>6855.119934082031</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>8.477437318588693</v>
+        <v>8.481880462245561</v>
       </c>
       <c r="D25" s="30" t="n"/>
       <c r="E25" s="12" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="27">
       <c r="A27" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:21 v2.0</t>
+          <t>Generated 2026-05-04 13:28 v2.0</t>
         </is>
       </c>
     </row>
@@ -1334,16 +1334,16 @@
         </is>
       </c>
       <c r="B14" s="40" t="n">
-        <v>20.61298066766944</v>
+        <v>20.61241205321405</v>
       </c>
       <c r="C14" s="40" t="n">
         <v>25</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>20.61298066766944</v>
+        <v>20.61241205321405</v>
       </c>
       <c r="E14" s="41" t="n">
-        <v>-4.38701933233056</v>
+        <v>-4.387587946785949</v>
       </c>
       <c r="F14" s="42" t="inlineStr">
         <is>
@@ -1358,16 +1358,16 @@
         </is>
       </c>
       <c r="B15" s="43" t="n">
-        <v>8.47297670545335</v>
+        <v>8.472742976177967</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>5</v>
       </c>
       <c r="D15" s="43" t="n">
-        <v>8.47297670545335</v>
+        <v>8.472742976177967</v>
       </c>
       <c r="E15" s="44" t="n">
-        <v>3.47297670545335</v>
+        <v>3.472742976177967</v>
       </c>
       <c r="F15" s="45" t="inlineStr">
         <is>
@@ -1382,16 +1382,16 @@
         </is>
       </c>
       <c r="B16" s="40" t="n">
-        <v>6.186700251163203</v>
+        <v>6.18652958942094</v>
       </c>
       <c r="C16" s="40" t="n">
         <v>5</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>6.186700251163203</v>
+        <v>6.18652958942094</v>
       </c>
       <c r="E16" s="46" t="n">
-        <v>1.186700251163203</v>
+        <v>1.18652958942094</v>
       </c>
       <c r="F16" s="47" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="B17" s="43" t="n">
-        <v>64.72734237571399</v>
+        <v>64.72831538118703</v>
       </c>
       <c r="C17" s="43" t="n">
         <v>65</v>
       </c>
       <c r="D17" s="43" t="n">
-        <v>64.727342375714</v>
+        <v>64.72831538118703</v>
       </c>
       <c r="E17" s="48" t="n">
-        <v>-0.2726576242859977</v>
+        <v>-0.2716846188129693</v>
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
@@ -1493,16 +1493,16 @@
         </is>
       </c>
       <c r="B22" s="40" t="n">
-        <v>24.19739538174008</v>
+        <v>24.19785747467557</v>
       </c>
       <c r="C22" s="40" t="n">
         <v>8</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>24.19739538174008</v>
+        <v>24.19785747467557</v>
       </c>
       <c r="E22" s="50" t="n">
-        <v>16.19739538174008</v>
+        <v>16.19785747467557</v>
       </c>
       <c r="F22" s="51" t="inlineStr">
         <is>
@@ -1517,16 +1517,16 @@
         </is>
       </c>
       <c r="B23" s="43" t="n">
-        <v>41.78221986945917</v>
+        <v>41.79626795598796</v>
       </c>
       <c r="C23" s="43" t="n">
         <v>55</v>
       </c>
       <c r="D23" s="43" t="n">
-        <v>41.78221986945916</v>
+        <v>41.79626795598796</v>
       </c>
       <c r="E23" s="52" t="n">
-        <v>-13.21778013054084</v>
+        <v>-13.20373204401204</v>
       </c>
       <c r="F23" s="53" t="inlineStr">
         <is>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="B24" s="40" t="n">
-        <v>15.49538355778712</v>
+        <v>15.50380579197923</v>
       </c>
       <c r="C24" s="40" t="n">
         <v>11</v>
       </c>
       <c r="D24" s="40" t="n">
-        <v>15.49538355778712</v>
+        <v>15.50380579197923</v>
       </c>
       <c r="E24" s="41" t="n">
-        <v>4.495383557787118</v>
+        <v>4.50380579197923</v>
       </c>
       <c r="F24" s="42" t="inlineStr">
         <is>
@@ -1565,16 +1565,16 @@
         </is>
       </c>
       <c r="B25" s="43" t="n">
-        <v>9.78236697442971</v>
+        <v>9.766116970263369</v>
       </c>
       <c r="C25" s="43" t="n">
         <v>14</v>
       </c>
       <c r="D25" s="43" t="n">
-        <v>9.782366974429706</v>
+        <v>9.766116970263365</v>
       </c>
       <c r="E25" s="44" t="n">
-        <v>-4.217633025570294</v>
+        <v>-4.233883029736635</v>
       </c>
       <c r="F25" s="45" t="inlineStr">
         <is>
@@ -1589,16 +1589,16 @@
         </is>
       </c>
       <c r="B26" s="40" t="n">
-        <v>8.742634216583923</v>
+        <v>8.735951807093869</v>
       </c>
       <c r="C26" s="40" t="n">
         <v>12</v>
       </c>
       <c r="D26" s="40" t="n">
-        <v>8.742634216583921</v>
+        <v>8.735951807093867</v>
       </c>
       <c r="E26" s="41" t="n">
-        <v>-3.257365783416079</v>
+        <v>-3.264048192906133</v>
       </c>
       <c r="F26" s="42" t="inlineStr">
         <is>
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="B30" s="40" t="n">
-        <v>22.07463495089159</v>
+        <v>22.07369419634397</v>
       </c>
       <c r="C30" s="40" t="n">
         <v>10</v>
       </c>
       <c r="D30" s="40" t="n">
-        <v>22.07463495089159</v>
+        <v>22.07369419634397</v>
       </c>
       <c r="E30" s="50" t="n">
-        <v>12.07463495089159</v>
+        <v>12.07369419634397</v>
       </c>
       <c r="F30" s="51" t="inlineStr">
         <is>
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="B31" s="43" t="n">
-        <v>10.83887863662915</v>
+        <v>10.81089082353887</v>
       </c>
       <c r="C31" s="43" t="n">
         <v>15</v>
       </c>
       <c r="D31" s="43" t="n">
-        <v>10.83887863662915</v>
+        <v>10.81089082353887</v>
       </c>
       <c r="E31" s="44" t="n">
-        <v>-4.161121363370849</v>
+        <v>-4.189109176461129</v>
       </c>
       <c r="F31" s="45" t="inlineStr">
         <is>
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="B32" s="40" t="n">
-        <v>11.24892110411809</v>
+        <v>11.25465370943649</v>
       </c>
       <c r="C32" s="40" t="n">
         <v>15</v>
       </c>
       <c r="D32" s="40" t="n">
-        <v>11.24892110411809</v>
+        <v>11.25465370943649</v>
       </c>
       <c r="E32" s="41" t="n">
-        <v>-3.751078895881914</v>
+        <v>-3.745346290563509</v>
       </c>
       <c r="F32" s="42" t="inlineStr">
         <is>
@@ -1724,16 +1724,16 @@
         </is>
       </c>
       <c r="B33" s="43" t="n">
-        <v>13.09715030377868</v>
+        <v>13.10381772226808</v>
       </c>
       <c r="C33" s="43" t="n">
         <v>15</v>
       </c>
       <c r="D33" s="43" t="n">
-        <v>13.09715030377868</v>
+        <v>13.10381772226808</v>
       </c>
       <c r="E33" s="48" t="n">
-        <v>-1.902849696221319</v>
+        <v>-1.896182277731922</v>
       </c>
       <c r="F33" s="49" t="inlineStr">
         <is>
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="B34" s="40" t="n">
-        <v>23.69795705541933</v>
+        <v>23.71529713153314</v>
       </c>
       <c r="C34" s="40" t="n">
         <v>25</v>
       </c>
       <c r="D34" s="40" t="n">
-        <v>23.69795705541933</v>
+        <v>23.71529713153314</v>
       </c>
       <c r="E34" s="46" t="n">
-        <v>-1.30204294458067</v>
+        <v>-1.284702868466862</v>
       </c>
       <c r="F34" s="47" t="inlineStr">
         <is>
@@ -1772,16 +1772,16 @@
         </is>
       </c>
       <c r="B35" s="43" t="n">
-        <v>19.04245794916315</v>
+        <v>19.04164641687945</v>
       </c>
       <c r="C35" s="43" t="n">
         <v>20</v>
       </c>
       <c r="D35" s="43" t="n">
-        <v>19.04245794916315</v>
+        <v>19.04164641687945</v>
       </c>
       <c r="E35" s="48" t="n">
-        <v>-0.957542050836846</v>
+        <v>-0.9583535831205516</v>
       </c>
       <c r="F35" s="49" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
     <row r="53">
       <c r="A53" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:21 v2.0</t>
+          <t>Generated 2026-05-04 13:28 v2.0</t>
         </is>
       </c>
     </row>
@@ -2204,25 +2204,25 @@
         <v>128</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>154.9600067138672</v>
+        <v>155.0800018310547</v>
       </c>
       <c r="J4" s="28" t="n">
         <v>10240</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>12396.80053710938</v>
+        <v>12406.40014648438</v>
       </c>
       <c r="L4" s="29" t="n">
-        <v>15.33905779931094</v>
+        <v>15.35051232088437</v>
       </c>
       <c r="M4" s="29" t="n">
-        <v>23.69795705541933</v>
+        <v>23.71529713153314</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>2156.800537109375</v>
+        <v>2166.400146484375</v>
       </c>
       <c r="O4" s="29" t="n">
-        <v>21.06250524520874</v>
+        <v>21.15625143051147</v>
       </c>
       <c r="P4" s="27" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="S4" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:21</t>
+          <t>2026-05-04 13:28</t>
         </is>
       </c>
     </row>
@@ -2292,10 +2292,10 @@
         <v>11547.61339873075</v>
       </c>
       <c r="L5" s="33" t="n">
-        <v>14.28832454285263</v>
+        <v>14.2879303956883</v>
       </c>
       <c r="M5" s="33" t="n">
-        <v>22.07463495089159</v>
+        <v>22.07369419634397</v>
       </c>
       <c r="N5" s="32" t="n">
         <v>9307.613398730755</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="S5" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:21</t>
+          <t>2026-05-04 13:28</t>
         </is>
       </c>
     </row>
@@ -2371,10 +2371,10 @@
         <v>9961.430530910857</v>
       </c>
       <c r="L6" s="29" t="n">
-        <v>12.3256769535062</v>
+        <v>12.32533694648823</v>
       </c>
       <c r="M6" s="29" t="n">
-        <v>19.04245794916315</v>
+        <v>19.04164641687945</v>
       </c>
       <c r="N6" s="28" t="n">
         <v>1411.430530910857</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="S6" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:21</t>
+          <t>2026-05-04 13:28</t>
         </is>
       </c>
     </row>
@@ -2441,25 +2441,25 @@
         <v>56</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>76.12599945068359</v>
+        <v>76.16799926757812</v>
       </c>
       <c r="J7" s="32" t="n">
         <v>5040</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>6851.339950561523</v>
+        <v>6855.119934082031</v>
       </c>
       <c r="L7" s="33" t="n">
-        <v>8.477437318588693</v>
+        <v>8.481880462245561</v>
       </c>
       <c r="M7" s="33" t="n">
-        <v>13.09715030377868</v>
+        <v>13.10381772226808</v>
       </c>
       <c r="N7" s="32" t="n">
-        <v>1811.339950561523</v>
+        <v>1815.119934082031</v>
       </c>
       <c r="O7" s="33" t="n">
-        <v>35.93928473336356</v>
+        <v>36.01428440638951</v>
       </c>
       <c r="P7" s="31" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="S7" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:21</t>
+          <t>2026-05-04 13:28</t>
         </is>
       </c>
     </row>
@@ -2520,25 +2520,25 @@
         <v>98</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>117.6900024414062</v>
+        <v>117.754997253418</v>
       </c>
       <c r="J8" s="28" t="n">
         <v>4900</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>5884.500122070312</v>
+        <v>5887.749862670898</v>
       </c>
       <c r="L8" s="29" t="n">
-        <v>7.28112767663646</v>
+        <v>7.284947748104517</v>
       </c>
       <c r="M8" s="29" t="n">
-        <v>11.24892110411809</v>
+        <v>11.25465370943649</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>984.5001220703125</v>
+        <v>987.7498626708984</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>20.09183922592474</v>
+        <v>20.1581604626714</v>
       </c>
       <c r="P8" s="27" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="S8" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:21</t>
+          <t>2026-05-04 13:28</t>
         </is>
       </c>
     </row>
@@ -2599,25 +2599,25 @@
         <v>33</v>
       </c>
       <c r="I9" s="32" t="n">
-        <v>47.25</v>
+        <v>47.13000106811523</v>
       </c>
       <c r="J9" s="32" t="n">
         <v>3960</v>
       </c>
       <c r="K9" s="32" t="n">
-        <v>5670</v>
+        <v>5655.600128173828</v>
       </c>
       <c r="L9" s="33" t="n">
-        <v>7.015718084819072</v>
+        <v>6.997707507776049</v>
       </c>
       <c r="M9" s="33" t="n">
-        <v>10.83887863662915</v>
+        <v>10.81089082353887</v>
       </c>
       <c r="N9" s="32" t="n">
-        <v>1710</v>
+        <v>1695.600128173828</v>
       </c>
       <c r="O9" s="33" t="n">
-        <v>43.18181818181818</v>
+        <v>42.81818505489465</v>
       </c>
       <c r="P9" s="31" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="S9" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:21</t>
+          <t>2026-05-04 13:28</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>13.25809882704585</v>
+        <v>13.25773309892698</v>
       </c>
       <c r="M10" s="29" t="n">
         <v>64.31917363528412</v>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="S10" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:21</t>
+          <t>2026-05-04 13:28</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
         <v>5944.107150852142</v>
       </c>
       <c r="L11" s="33" t="n">
-        <v>7.354881840623588</v>
+        <v>7.354678954287075</v>
       </c>
       <c r="M11" s="33" t="n">
         <v>35.68082636471589</v>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="S11" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:21</t>
+          <t>2026-05-04 13:28</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
         <v>5000</v>
       </c>
       <c r="L12" s="29" t="n">
-        <v>6.186700251163203</v>
+        <v>6.18652958942094</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>100</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="S12" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:21</t>
+          <t>2026-05-04 13:28</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <v>6847.734948739668</v>
       </c>
       <c r="L13" s="33" t="n">
-        <v>8.47297670545335</v>
+        <v>8.472742976177967</v>
       </c>
       <c r="M13" s="33" t="n">
         <v>100</v>
@@ -2952,14 +2952,14 @@
       </c>
       <c r="S13" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:21</t>
+          <t>2026-05-04 13:28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:21 v2.0</t>
+          <t>Generated 2026-05-04 13:28 v2.0</t>
         </is>
       </c>
     </row>
@@ -3149,13 +3149,13 @@
         <v>6.58</v>
       </c>
       <c r="H5" s="60" t="n">
-        <v>6.98</v>
+        <v>6.99</v>
       </c>
       <c r="I5" s="60" t="n">
         <v>22</v>
       </c>
       <c r="J5" s="60" t="n">
-        <v>48.91</v>
+        <v>48.92</v>
       </c>
       <c r="K5" s="60" t="n">
         <v>45.09</v>
@@ -3276,31 +3276,31 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>6.64</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>6.39</v>
+        <v>6.38</v>
       </c>
       <c r="H7" s="33" t="n">
         <v>6.52</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>23.69</v>
+        <v>23.68</v>
       </c>
       <c r="J7" s="33" t="n">
         <v>56.16</v>
       </c>
       <c r="K7" s="33" t="n">
-        <v>58.74</v>
+        <v>58.73</v>
       </c>
       <c r="L7" s="33" t="n">
         <v>9.83</v>
@@ -3495,25 +3495,25 @@
         <v>0.59</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>5.97</v>
+        <v>5.96</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="G10" s="29" t="n">
         <v>5.08</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
       <c r="I10" s="29" t="n">
         <v>21.74</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>55.7</v>
+        <v>55.69</v>
       </c>
       <c r="K10" s="29" t="n">
-        <v>63.3</v>
+        <v>63.29</v>
       </c>
       <c r="L10" s="29" t="n">
         <v>10.47</v>
@@ -3906,7 +3906,7 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
@@ -3915,58 +3915,58 @@
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>0.91</v>
+        <v>1.03</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>7.26</v>
+        <v>7.75</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>4.18</v>
+        <v>4.71</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>5.33</v>
+        <v>6.61</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>5.72</v>
+        <v>6.85</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>22.87</v>
+        <v>24.62</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>62.56</v>
+        <v>62.81</v>
       </c>
       <c r="K16" s="29" t="n">
-        <v>75.01000000000001</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="L16" s="29" t="n">
-        <v>12.15</v>
+        <v>11.52</v>
       </c>
       <c r="M16" s="29" t="n">
-        <v>14.24</v>
+        <v>13.8</v>
       </c>
       <c r="N16" s="29" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="O16" s="29" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="P16" s="62" t="n">
-        <v>-21.73</v>
+        <v>-21.07</v>
       </c>
       <c r="Q16" s="62" t="n">
-        <v>-1.45</v>
+        <v>-1.39</v>
       </c>
       <c r="R16" s="62" t="n">
-        <v>-2.19</v>
+        <v>-2.13</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>6.34</v>
+        <v>5.92</v>
       </c>
       <c r="T16" s="29" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="U16" s="27" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
@@ -3986,58 +3986,58 @@
         </is>
       </c>
       <c r="C17" s="33" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="E17" s="33" t="n">
-        <v>7.67</v>
+        <v>7.32</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>4.63</v>
+        <v>4.24</v>
       </c>
       <c r="G17" s="33" t="n">
-        <v>6.53</v>
+        <v>5.39</v>
       </c>
       <c r="H17" s="33" t="n">
-        <v>6.77</v>
+        <v>5.78</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>24.53</v>
+        <v>22.94</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>62.69</v>
+        <v>62.65</v>
       </c>
       <c r="K17" s="33" t="n">
-        <v>70.15000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="L17" s="33" t="n">
-        <v>11.51</v>
+        <v>12.16</v>
       </c>
       <c r="M17" s="33" t="n">
-        <v>13.8</v>
+        <v>14.24</v>
       </c>
       <c r="N17" s="33" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="O17" s="33" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="P17" s="63" t="n">
-        <v>-21.07</v>
+        <v>-21.73</v>
       </c>
       <c r="Q17" s="63" t="n">
-        <v>-1.39</v>
+        <v>-1.45</v>
       </c>
       <c r="R17" s="63" t="n">
-        <v>-2.13</v>
+        <v>-2.19</v>
       </c>
       <c r="S17" s="33" t="n">
-        <v>5.9</v>
+        <v>6.35</v>
       </c>
       <c r="T17" s="33" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="U17" s="31" t="inlineStr">
         <is>
@@ -4057,34 +4057,34 @@
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="E18" s="29" t="n">
-        <v>12.54</v>
+        <v>12.6</v>
       </c>
       <c r="F18" s="29" t="n">
-        <v>8.84</v>
+        <v>8.9</v>
       </c>
       <c r="G18" s="29" t="n">
-        <v>16.45</v>
+        <v>16.52</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>16.06</v>
+        <v>16.12</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>40.65</v>
+        <v>40.72</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>68.56</v>
+        <v>68.66</v>
       </c>
       <c r="K18" s="29" t="n">
-        <v>42.04</v>
+        <v>42.12</v>
       </c>
       <c r="L18" s="29" t="n">
-        <v>7.55</v>
+        <v>7.56</v>
       </c>
       <c r="M18" s="29" t="n">
         <v>18.82</v>
@@ -4105,7 +4105,7 @@
         <v>-2.59</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="T18" s="29" t="n">
         <v>0.1</v>
@@ -4412,43 +4412,43 @@
         </is>
       </c>
       <c r="C23" s="63" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="D23" s="33" t="n">
-        <v>0.15</v>
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="D23" s="63" t="n">
+        <v>-0.11</v>
       </c>
       <c r="E23" s="33" t="n">
-        <v>4.35</v>
+        <v>4.09</v>
       </c>
       <c r="F23" s="63" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.19</v>
       </c>
       <c r="G23" s="33" t="n">
-        <v>7.24</v>
+        <v>6.97</v>
       </c>
       <c r="H23" s="33" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="I23" s="33" t="n">
-        <v>14.57</v>
+        <v>14.28</v>
       </c>
       <c r="J23" s="33" t="n">
-        <v>40.38</v>
+        <v>40.02</v>
       </c>
       <c r="K23" s="33" t="n">
-        <v>54.73</v>
+        <v>54.34</v>
       </c>
       <c r="L23" s="33" t="n">
-        <v>9.539999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="M23" s="33" t="n">
-        <v>14.94</v>
+        <v>14.95</v>
       </c>
       <c r="N23" s="33" t="n">
         <v>0.37</v>
       </c>
       <c r="O23" s="33" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="P23" s="63" t="n">
         <v>-22.86</v>
@@ -4460,7 +4460,7 @@
         <v>-2.22</v>
       </c>
       <c r="S23" s="33" t="n">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="T23" s="33" t="n">
         <v>0.17</v>
@@ -4801,7 +4801,7 @@
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:21 v2.0</t>
+          <t>Generated 2026-05-04 13:28 v2.0</t>
         </is>
       </c>
     </row>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="D5" s="29" t="n">
-        <v>14.28832454285263</v>
+        <v>14.2879303956883</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>415.5184553004801</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>59.37062542878062</v>
+        <v>59.36898767457182</v>
       </c>
     </row>
     <row r="6">
@@ -4922,13 +4922,13 @@
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>13.25809882704585</v>
+        <v>13.25773309892698</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>91.33928843906948</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>12.1098531291723</v>
+        <v>12.10951907571089</v>
       </c>
     </row>
     <row r="7">
@@ -4948,13 +4948,13 @@
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>8.47297670545335</v>
+        <v>8.472742976177967</v>
       </c>
       <c r="E7" s="29" t="n">
         <v>55.27743647935755</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>4.683644316267737</v>
+        <v>4.683515116716004</v>
       </c>
     </row>
     <row r="8">
@@ -4974,65 +4974,65 @@
         </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>15.33905779931094</v>
+        <v>15.35051232088437</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>21.06250524520874</v>
+        <v>21.15625143051147</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.230789853545467</v>
+        <v>3.24759298247794</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>IE00B1FZS798</t>
+          <t>LU0292107645</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>IBTM.L</t>
+          <t>XMME.DE</t>
         </is>
       </c>
       <c r="D9" s="29" t="n">
-        <v>7.354881840623588</v>
+        <v>8.481880462245561</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>41.5263607345748</v>
+        <v>36.01428440638951</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>3.054214764739086</v>
+        <v>3.054688552683102</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>LU0292107645</t>
+          <t>IE00B1FZS798</t>
         </is>
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>XMME.DE</t>
+          <t>IBTM.L</t>
         </is>
       </c>
       <c r="D10" s="33" t="n">
-        <v>8.477437318588693</v>
+        <v>7.354678954287075</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>35.93928473336356</v>
+        <v>41.5263607345748</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>3.046730336020011</v>
+        <v>3.054130513427105</v>
       </c>
     </row>
     <row r="11">
@@ -5052,13 +5052,13 @@
         </is>
       </c>
       <c r="D11" s="29" t="n">
-        <v>7.015718084819072</v>
+        <v>6.997707507776049</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>43.18181818181818</v>
+        <v>42.81818505489465</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>3.029514627535509</v>
+        <v>2.996291350279805</v>
       </c>
     </row>
     <row r="12">
@@ -5078,13 +5078,13 @@
         </is>
       </c>
       <c r="D12" s="33" t="n">
-        <v>12.3256769535062</v>
+        <v>12.32533694648823</v>
       </c>
       <c r="E12" s="33" t="n">
         <v>16.50795942585797</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>2.03471775044713</v>
+        <v>2.034661622226559</v>
       </c>
     </row>
     <row r="13">
@@ -5104,13 +5104,13 @@
         </is>
       </c>
       <c r="D13" s="29" t="n">
-        <v>7.28112767663646</v>
+        <v>7.284947748104517</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>20.09183922592474</v>
+        <v>20.1581604626714</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>1.462912466624107</v>
+        <v>1.468511456684675</v>
       </c>
     </row>
     <row r="14">
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="D14" s="33" t="n">
-        <v>6.186700251163203</v>
+        <v>6.18652958942094</v>
       </c>
       <c r="E14" s="33" t="n">
         <v>0</v>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="B18" s="28" t="n">
-        <v>52311.68453938283</v>
+        <v>52313.91400105275</v>
       </c>
       <c r="C18" s="29" t="n">
-        <v>92.05031035210889</v>
+        <v>92.02888268013419</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>6</v>
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>41.78221986945917</v>
+        <v>41.79626795598796</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>19.22076796566382</v>
+        <v>19.27412377301361</v>
       </c>
     </row>
     <row r="26">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="B26" s="33" t="n">
-        <v>15.49538355778712</v>
+        <v>15.50380579197923</v>
       </c>
       <c r="C26" s="33" t="n">
-        <v>28.50089498928615</v>
+        <v>28.58526791845049</v>
       </c>
     </row>
     <row r="27">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>9.78236697442971</v>
+        <v>9.766116970263369</v>
       </c>
       <c r="C27" s="29" t="n">
-        <v>28.11205421765055</v>
+        <v>28.04419898269251</v>
       </c>
     </row>
     <row r="28">
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>24.19739538174008</v>
+        <v>24.19785747467557</v>
       </c>
       <c r="C28" s="33" t="n">
-        <v>152.2242665905379</v>
+        <v>152.2776223978877</v>
       </c>
     </row>
     <row r="29">
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>8.742634216583923</v>
+        <v>8.735951807093869</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>28.11205421765055</v>
+        <v>28.04419898269251</v>
       </c>
     </row>
   </sheetData>

--- a/output/sample/portfolio_dashboard_sample.xlsx
+++ b/output/sample/portfolio_dashboard_sample.xlsx
@@ -20,11 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="&quot;€&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="&quot;€&quot;+#,##0.00;&quot;€&quot;-#,##0.00;&quot;€&quot;0.00"/>
-    <numFmt numFmtId="166" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;;0.00&quot;%&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot;%&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="+#,##0.00;-#,##0.00;0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00;0.00"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -254,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -268,16 +266,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -363,43 +361,37 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -860,33 +852,33 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total Value (AuM)</t>
+          <t>Total Value (EUR)</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>80820.75625323245</v>
+        <v>80831.37868844786</v>
       </c>
       <c r="D5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Total Gain</t>
+          <t>Total Gain (EUR)</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>26680.75625323245</v>
+        <v>26691.37868844786</v>
       </c>
       <c r="D6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>RTD (Return to Date)</t>
+          <t>RTD (%)</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>49.28104221136397</v>
+        <v>49.30066252022139</v>
       </c>
       <c r="D7" s="2" t="n"/>
     </row>
@@ -950,7 +942,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>64.72831538118703</v>
+        <v>64.73295060071293</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>65</v>
@@ -962,7 +954,7 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>41.79626795598796</v>
+        <v>41.79516167143485</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>55</v>
@@ -975,7 +967,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>20.61241205321405</v>
+        <v>20.60970327828998</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>25</v>
@@ -987,7 +979,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>24.19785747467557</v>
+        <v>24.19321790615446</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>8</v>
@@ -1000,7 +992,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>8.472742976177967</v>
+        <v>8.471629532799646</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>5</v>
@@ -1012,7 +1004,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>15.50380579197923</v>
+        <v>15.50544013183685</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>11</v>
@@ -1025,7 +1017,7 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>6.18652958942094</v>
+        <v>6.185716588197428</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>5</v>
@@ -1037,7 +1029,7 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>9.766116970263369</v>
+        <v>9.768936068831742</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>14</v>
@@ -1051,7 +1043,7 @@
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>8.735951807093869</v>
+        <v>8.737244221742097</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>12</v>
@@ -1107,10 +1099,10 @@
         </is>
       </c>
       <c r="B21" s="28" t="n">
-        <v>12406.40014648438</v>
+        <v>12408.00048828125</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>15.35051232088437</v>
+        <v>15.35047488934462</v>
       </c>
       <c r="D21" s="30" t="n"/>
       <c r="E21" s="12" t="inlineStr">
@@ -1129,7 +1121,7 @@
         <v>11547.61339873075</v>
       </c>
       <c r="C22" s="33" t="n">
-        <v>14.2879303956883</v>
+        <v>14.28605275092394</v>
       </c>
       <c r="D22" s="30" t="n"/>
       <c r="E22" s="34" t="inlineStr">
@@ -1148,7 +1140,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>13.25773309892698</v>
+        <v>13.25599083728018</v>
       </c>
       <c r="D23" s="30" t="n"/>
       <c r="E23" s="35" t="inlineStr">
@@ -1164,10 +1156,10 @@
         </is>
       </c>
       <c r="B24" s="32" t="n">
-        <v>9961.430530910857</v>
+        <v>9963.762713440719</v>
       </c>
       <c r="C24" s="33" t="n">
-        <v>12.32533694648823</v>
+        <v>12.32660245947866</v>
       </c>
       <c r="D24" s="30" t="n"/>
       <c r="E24" s="34" t="inlineStr">
@@ -1183,10 +1175,10 @@
         </is>
       </c>
       <c r="B25" s="28" t="n">
-        <v>6855.119934082031</v>
+        <v>6857.460021972656</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>8.481880462245561</v>
+        <v>8.483660842163392</v>
       </c>
       <c r="D25" s="30" t="n"/>
       <c r="E25" s="12" t="inlineStr">
@@ -1201,7 +1193,7 @@
     <row r="27">
       <c r="A27" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:28 v2.0</t>
+          <t>Generated 2026-05-04 13:36 v2.0</t>
         </is>
       </c>
     </row>
@@ -1333,19 +1325,19 @@
           <t>Fixed Income</t>
         </is>
       </c>
-      <c r="B14" s="40" t="n">
-        <v>20.61241205321405</v>
-      </c>
-      <c r="C14" s="40" t="n">
+      <c r="B14" s="14" t="n">
+        <v>20.60970327828998</v>
+      </c>
+      <c r="C14" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="D14" s="40" t="n">
-        <v>20.61241205321405</v>
-      </c>
-      <c r="E14" s="41" t="n">
-        <v>-4.387587946785949</v>
-      </c>
-      <c r="F14" s="42" t="inlineStr">
+      <c r="D14" s="14" t="n">
+        <v>20.60970327828998</v>
+      </c>
+      <c r="E14" s="40" t="n">
+        <v>-4.390296721710016</v>
+      </c>
+      <c r="F14" s="41" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
@@ -1357,19 +1349,19 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="B15" s="43" t="n">
-        <v>8.472742976177967</v>
-      </c>
-      <c r="C15" s="43" t="n">
+      <c r="B15" s="18" t="n">
+        <v>8.471629532799646</v>
+      </c>
+      <c r="C15" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="43" t="n">
-        <v>8.472742976177967</v>
-      </c>
-      <c r="E15" s="44" t="n">
-        <v>3.472742976177967</v>
-      </c>
-      <c r="F15" s="45" t="inlineStr">
+      <c r="D15" s="18" t="n">
+        <v>8.471629532799646</v>
+      </c>
+      <c r="E15" s="42" t="n">
+        <v>3.471629532799646</v>
+      </c>
+      <c r="F15" s="43" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
@@ -1381,19 +1373,19 @@
           <t>Cash &amp; Cash Equivalents</t>
         </is>
       </c>
-      <c r="B16" s="40" t="n">
-        <v>6.18652958942094</v>
-      </c>
-      <c r="C16" s="40" t="n">
+      <c r="B16" s="14" t="n">
+        <v>6.185716588197428</v>
+      </c>
+      <c r="C16" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="40" t="n">
-        <v>6.18652958942094</v>
-      </c>
-      <c r="E16" s="46" t="n">
-        <v>1.18652958942094</v>
-      </c>
-      <c r="F16" s="47" t="inlineStr">
+      <c r="D16" s="14" t="n">
+        <v>6.185716588197428</v>
+      </c>
+      <c r="E16" s="44" t="n">
+        <v>1.185716588197428</v>
+      </c>
+      <c r="F16" s="45" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
@@ -1405,19 +1397,19 @@
           <t>Equities</t>
         </is>
       </c>
-      <c r="B17" s="43" t="n">
-        <v>64.72831538118703</v>
-      </c>
-      <c r="C17" s="43" t="n">
+      <c r="B17" s="18" t="n">
+        <v>64.73295060071293</v>
+      </c>
+      <c r="C17" s="18" t="n">
         <v>65</v>
       </c>
-      <c r="D17" s="43" t="n">
-        <v>64.72831538118703</v>
-      </c>
-      <c r="E17" s="48" t="n">
-        <v>-0.2716846188129693</v>
-      </c>
-      <c r="F17" s="49" t="inlineStr">
+      <c r="D17" s="18" t="n">
+        <v>64.73295060071294</v>
+      </c>
+      <c r="E17" s="46" t="n">
+        <v>-0.2670493992870604</v>
+      </c>
+      <c r="F17" s="47" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
@@ -1429,19 +1421,19 @@
           <t>Alternative</t>
         </is>
       </c>
-      <c r="B18" s="40" t="n">
+      <c r="B18" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="40" t="n">
+      <c r="C18" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="40" t="n">
+      <c r="D18" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="E18" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="47" t="inlineStr">
+      <c r="F18" s="45" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
@@ -1492,19 +1484,19 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="B22" s="40" t="n">
-        <v>24.19785747467557</v>
-      </c>
-      <c r="C22" s="40" t="n">
+      <c r="B22" s="14" t="n">
+        <v>24.19321790615446</v>
+      </c>
+      <c r="C22" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="D22" s="40" t="n">
-        <v>24.19785747467557</v>
-      </c>
-      <c r="E22" s="50" t="n">
-        <v>16.19785747467557</v>
-      </c>
-      <c r="F22" s="51" t="inlineStr">
+      <c r="D22" s="14" t="n">
+        <v>24.19321790615446</v>
+      </c>
+      <c r="E22" s="48" t="n">
+        <v>16.19321790615446</v>
+      </c>
+      <c r="F22" s="49" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
@@ -1516,19 +1508,19 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="B23" s="43" t="n">
-        <v>41.79626795598796</v>
-      </c>
-      <c r="C23" s="43" t="n">
+      <c r="B23" s="18" t="n">
+        <v>41.79516167143485</v>
+      </c>
+      <c r="C23" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="D23" s="43" t="n">
-        <v>41.79626795598796</v>
-      </c>
-      <c r="E23" s="52" t="n">
-        <v>-13.20373204401204</v>
-      </c>
-      <c r="F23" s="53" t="inlineStr">
+      <c r="D23" s="18" t="n">
+        <v>41.79516167143485</v>
+      </c>
+      <c r="E23" s="50" t="n">
+        <v>-13.20483832856515</v>
+      </c>
+      <c r="F23" s="51" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
@@ -1540,19 +1532,19 @@
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="B24" s="40" t="n">
-        <v>15.50380579197923</v>
-      </c>
-      <c r="C24" s="40" t="n">
+      <c r="B24" s="14" t="n">
+        <v>15.50544013183685</v>
+      </c>
+      <c r="C24" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="D24" s="40" t="n">
-        <v>15.50380579197923</v>
-      </c>
-      <c r="E24" s="41" t="n">
-        <v>4.50380579197923</v>
-      </c>
-      <c r="F24" s="42" t="inlineStr">
+      <c r="D24" s="14" t="n">
+        <v>15.50544013183685</v>
+      </c>
+      <c r="E24" s="40" t="n">
+        <v>4.505440131836851</v>
+      </c>
+      <c r="F24" s="41" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
@@ -1564,19 +1556,19 @@
           <t>Eurozone EMU</t>
         </is>
       </c>
-      <c r="B25" s="43" t="n">
-        <v>9.766116970263369</v>
-      </c>
-      <c r="C25" s="43" t="n">
+      <c r="B25" s="18" t="n">
+        <v>9.768936068831742</v>
+      </c>
+      <c r="C25" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="D25" s="43" t="n">
-        <v>9.766116970263365</v>
-      </c>
-      <c r="E25" s="44" t="n">
-        <v>-4.233883029736635</v>
-      </c>
-      <c r="F25" s="45" t="inlineStr">
+      <c r="D25" s="18" t="n">
+        <v>9.76893606883174</v>
+      </c>
+      <c r="E25" s="42" t="n">
+        <v>-4.23106393116826</v>
+      </c>
+      <c r="F25" s="43" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
@@ -1588,19 +1580,19 @@
           <t>Dev ex-USA ex-EMU ex-JP</t>
         </is>
       </c>
-      <c r="B26" s="40" t="n">
-        <v>8.735951807093869</v>
-      </c>
-      <c r="C26" s="40" t="n">
+      <c r="B26" s="14" t="n">
+        <v>8.737244221742097</v>
+      </c>
+      <c r="C26" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="D26" s="40" t="n">
-        <v>8.735951807093867</v>
-      </c>
-      <c r="E26" s="41" t="n">
-        <v>-3.264048192906133</v>
-      </c>
-      <c r="F26" s="42" t="inlineStr">
+      <c r="D26" s="14" t="n">
+        <v>8.737244221742097</v>
+      </c>
+      <c r="E26" s="40" t="n">
+        <v>-3.262755778257903</v>
+      </c>
+      <c r="F26" s="41" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
@@ -1651,19 +1643,19 @@
           <t>CNKY.L</t>
         </is>
       </c>
-      <c r="B30" s="40" t="n">
-        <v>22.07369419634397</v>
-      </c>
-      <c r="C30" s="40" t="n">
+      <c r="B30" s="14" t="n">
+        <v>22.06921300257647</v>
+      </c>
+      <c r="C30" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="40" t="n">
-        <v>22.07369419634397</v>
-      </c>
-      <c r="E30" s="50" t="n">
-        <v>12.07369419634397</v>
-      </c>
-      <c r="F30" s="51" t="inlineStr">
+      <c r="D30" s="14" t="n">
+        <v>22.06921300257647</v>
+      </c>
+      <c r="E30" s="48" t="n">
+        <v>12.06921300257647</v>
+      </c>
+      <c r="F30" s="49" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
@@ -1675,19 +1667,19 @@
           <t>VERX.DE</t>
         </is>
       </c>
-      <c r="B31" s="43" t="n">
-        <v>10.81089082353887</v>
-      </c>
-      <c r="C31" s="43" t="n">
+      <c r="B31" s="18" t="n">
+        <v>10.81557595561772</v>
+      </c>
+      <c r="C31" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="D31" s="43" t="n">
-        <v>10.81089082353887</v>
-      </c>
-      <c r="E31" s="44" t="n">
-        <v>-4.189109176461129</v>
-      </c>
-      <c r="F31" s="45" t="inlineStr">
+      <c r="D31" s="18" t="n">
+        <v>10.81557595561772</v>
+      </c>
+      <c r="E31" s="42" t="n">
+        <v>-4.184424044382277</v>
+      </c>
+      <c r="F31" s="43" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
@@ -1699,19 +1691,19 @@
           <t>EUNL.DE</t>
         </is>
       </c>
-      <c r="B32" s="40" t="n">
-        <v>11.25465370943649</v>
-      </c>
-      <c r="C32" s="40" t="n">
+      <c r="B32" s="14" t="n">
+        <v>11.25380219913764</v>
+      </c>
+      <c r="C32" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="D32" s="40" t="n">
-        <v>11.25465370943649</v>
-      </c>
-      <c r="E32" s="41" t="n">
-        <v>-3.745346290563509</v>
-      </c>
-      <c r="F32" s="42" t="inlineStr">
+      <c r="D32" s="14" t="n">
+        <v>11.25380219913764</v>
+      </c>
+      <c r="E32" s="40" t="n">
+        <v>-3.746197800862364</v>
+      </c>
+      <c r="F32" s="41" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
@@ -1723,19 +1715,19 @@
           <t>XMME.DE</t>
         </is>
       </c>
-      <c r="B33" s="43" t="n">
-        <v>13.10381772226808</v>
-      </c>
-      <c r="C33" s="43" t="n">
+      <c r="B33" s="18" t="n">
+        <v>13.10562976573164</v>
+      </c>
+      <c r="C33" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="D33" s="43" t="n">
-        <v>13.10381772226808</v>
-      </c>
-      <c r="E33" s="48" t="n">
-        <v>-1.896182277731922</v>
-      </c>
-      <c r="F33" s="49" t="inlineStr">
+      <c r="D33" s="18" t="n">
+        <v>13.10562976573164</v>
+      </c>
+      <c r="E33" s="46" t="n">
+        <v>-1.894370234268361</v>
+      </c>
+      <c r="F33" s="47" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
@@ -1747,19 +1739,19 @@
           <t>VWCE.DE</t>
         </is>
       </c>
-      <c r="B34" s="40" t="n">
-        <v>23.71529713153314</v>
-      </c>
-      <c r="C34" s="40" t="n">
+      <c r="B34" s="14" t="n">
+        <v>23.71354116704756</v>
+      </c>
+      <c r="C34" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="D34" s="40" t="n">
-        <v>23.71529713153314</v>
-      </c>
-      <c r="E34" s="46" t="n">
-        <v>-1.284702868466862</v>
-      </c>
-      <c r="F34" s="47" t="inlineStr">
+      <c r="D34" s="14" t="n">
+        <v>23.71354116704756</v>
+      </c>
+      <c r="E34" s="44" t="n">
+        <v>-1.286458832952437</v>
+      </c>
+      <c r="F34" s="45" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
@@ -1771,19 +1763,19 @@
           <t>CSPX.L</t>
         </is>
       </c>
-      <c r="B35" s="43" t="n">
-        <v>19.04164641687945</v>
-      </c>
-      <c r="C35" s="43" t="n">
+      <c r="B35" s="18" t="n">
+        <v>19.04223790988896</v>
+      </c>
+      <c r="C35" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="D35" s="43" t="n">
-        <v>19.04164641687945</v>
-      </c>
-      <c r="E35" s="48" t="n">
-        <v>-0.9583535831205516</v>
-      </c>
-      <c r="F35" s="49" t="inlineStr">
+      <c r="D35" s="18" t="n">
+        <v>19.04223790988896</v>
+      </c>
+      <c r="E35" s="46" t="n">
+        <v>-0.9577620901110357</v>
+      </c>
+      <c r="F35" s="47" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
@@ -1834,19 +1826,19 @@
           <t>IBTM.L</t>
         </is>
       </c>
-      <c r="B39" s="40" t="n">
+      <c r="B39" s="14" t="n">
         <v>35.68082636471589</v>
       </c>
-      <c r="C39" s="40" t="n">
+      <c r="C39" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="D39" s="40" t="n">
+      <c r="D39" s="14" t="n">
         <v>35.68082636471589</v>
       </c>
-      <c r="E39" s="50" t="n">
+      <c r="E39" s="48" t="n">
         <v>5.680826364715891</v>
       </c>
-      <c r="F39" s="51" t="inlineStr">
+      <c r="F39" s="49" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
@@ -1858,19 +1850,19 @@
           <t>IEAG.L</t>
         </is>
       </c>
-      <c r="B40" s="43" t="n">
+      <c r="B40" s="18" t="n">
         <v>64.31917363528412</v>
       </c>
-      <c r="C40" s="43" t="n">
+      <c r="C40" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="D40" s="43" t="n">
+      <c r="D40" s="18" t="n">
         <v>64.31917363528412</v>
       </c>
-      <c r="E40" s="52" t="n">
+      <c r="E40" s="50" t="n">
         <v>-5.680826364715884</v>
       </c>
-      <c r="F40" s="53" t="inlineStr">
+      <c r="F40" s="51" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
@@ -1907,7 +1899,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="54" t="inlineStr">
+      <c r="A46" s="52" t="inlineStr">
         <is>
           <t>Alert threshold</t>
         </is>
@@ -1924,7 +1916,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="55" t="inlineStr">
+      <c r="A47" s="53" t="inlineStr">
         <is>
           <t>Solver tolerance</t>
         </is>
@@ -1941,7 +1933,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="54" t="inlineStr">
+      <c r="A48" s="52" t="inlineStr">
         <is>
           <t>Max tolerance</t>
         </is>
@@ -1958,7 +1950,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="55" t="inlineStr">
+      <c r="A49" s="53" t="inlineStr">
         <is>
           <t>Min transaction</t>
         </is>
@@ -1975,7 +1967,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="54" t="inlineStr">
+      <c r="A50" s="52" t="inlineStr">
         <is>
           <t>Lump sum</t>
         </is>
@@ -1992,7 +1984,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="55" t="inlineStr">
+      <c r="A51" s="53" t="inlineStr">
         <is>
           <t>No-sell mode</t>
         </is>
@@ -2011,7 +2003,7 @@
     <row r="53">
       <c r="A53" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:28 v2.0</t>
+          <t>Generated 2026-05-04 13:36 v2.0</t>
         </is>
       </c>
     </row>
@@ -2204,25 +2196,25 @@
         <v>128</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>155.0800018310547</v>
+        <v>155.1000061035156</v>
       </c>
       <c r="J4" s="28" t="n">
         <v>10240</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>12406.40014648438</v>
+        <v>12408.00048828125</v>
       </c>
       <c r="L4" s="29" t="n">
-        <v>15.35051232088437</v>
+        <v>15.35047488934462</v>
       </c>
       <c r="M4" s="29" t="n">
-        <v>23.71529713153314</v>
+        <v>23.71354116704756</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>2166.400146484375</v>
+        <v>2168.00048828125</v>
       </c>
       <c r="O4" s="29" t="n">
-        <v>21.15625143051147</v>
+        <v>21.17187976837158</v>
       </c>
       <c r="P4" s="27" t="inlineStr">
         <is>
@@ -2241,7 +2233,7 @@
       </c>
       <c r="S4" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:28</t>
+          <t>2026-05-04 13:36</t>
         </is>
       </c>
     </row>
@@ -2292,10 +2284,10 @@
         <v>11547.61339873075</v>
       </c>
       <c r="L5" s="33" t="n">
-        <v>14.2879303956883</v>
+        <v>14.28605275092394</v>
       </c>
       <c r="M5" s="33" t="n">
-        <v>22.07369419634397</v>
+        <v>22.06921300257647</v>
       </c>
       <c r="N5" s="32" t="n">
         <v>9307.613398730755</v>
@@ -2320,7 +2312,7 @@
       </c>
       <c r="S5" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:28</t>
+          <t>2026-05-04 13:36</t>
         </is>
       </c>
     </row>
@@ -2362,25 +2354,25 @@
         <v>570</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>664.0953687273905</v>
+        <v>664.2508475627146</v>
       </c>
       <c r="J6" s="28" t="n">
         <v>8550</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>9961.430530910857</v>
+        <v>9963.762713440719</v>
       </c>
       <c r="L6" s="29" t="n">
-        <v>12.32533694648823</v>
+        <v>12.32660245947866</v>
       </c>
       <c r="M6" s="29" t="n">
-        <v>19.04164641687945</v>
+        <v>19.04223790988896</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>1411.430530910857</v>
+        <v>1413.762713440719</v>
       </c>
       <c r="O6" s="29" t="n">
-        <v>16.50795942585797</v>
+        <v>16.53523641451134</v>
       </c>
       <c r="P6" s="27" t="inlineStr">
         <is>
@@ -2399,7 +2391,7 @@
       </c>
       <c r="S6" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:28</t>
+          <t>2026-05-04 13:36</t>
         </is>
       </c>
     </row>
@@ -2441,25 +2433,25 @@
         <v>56</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>76.16799926757812</v>
+        <v>76.19400024414062</v>
       </c>
       <c r="J7" s="32" t="n">
         <v>5040</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>6855.119934082031</v>
+        <v>6857.460021972656</v>
       </c>
       <c r="L7" s="33" t="n">
-        <v>8.481880462245561</v>
+        <v>8.483660842163392</v>
       </c>
       <c r="M7" s="33" t="n">
-        <v>13.10381772226808</v>
+        <v>13.10562976573164</v>
       </c>
       <c r="N7" s="32" t="n">
-        <v>1815.119934082031</v>
+        <v>1817.460021972656</v>
       </c>
       <c r="O7" s="33" t="n">
-        <v>36.01428440638951</v>
+        <v>36.06071472167969</v>
       </c>
       <c r="P7" s="31" t="inlineStr">
         <is>
@@ -2478,7 +2470,7 @@
       </c>
       <c r="S7" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:28</t>
+          <t>2026-05-04 13:36</t>
         </is>
       </c>
     </row>
@@ -2520,25 +2512,25 @@
         <v>98</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>117.754997253418</v>
+        <v>117.7699966430664</v>
       </c>
       <c r="J8" s="28" t="n">
         <v>4900</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>5887.749862670898</v>
+        <v>5888.49983215332</v>
       </c>
       <c r="L8" s="29" t="n">
-        <v>7.284947748104517</v>
+        <v>7.284918218269714</v>
       </c>
       <c r="M8" s="29" t="n">
-        <v>11.25465370943649</v>
+        <v>11.25380219913764</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>987.7498626708984</v>
+        <v>988.4998321533203</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>20.1581604626714</v>
+        <v>20.17346596231266</v>
       </c>
       <c r="P8" s="27" t="inlineStr">
         <is>
@@ -2557,7 +2549,7 @@
       </c>
       <c r="S8" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:28</t>
+          <t>2026-05-04 13:36</t>
         </is>
       </c>
     </row>
@@ -2599,25 +2591,25 @@
         <v>33</v>
       </c>
       <c r="I9" s="32" t="n">
-        <v>47.13000106811523</v>
+        <v>47.15999984741211</v>
       </c>
       <c r="J9" s="32" t="n">
         <v>3960</v>
       </c>
       <c r="K9" s="32" t="n">
-        <v>5655.600128173828</v>
+        <v>5659.199981689453</v>
       </c>
       <c r="L9" s="33" t="n">
-        <v>6.997707507776049</v>
+        <v>7.001241440532606</v>
       </c>
       <c r="M9" s="33" t="n">
-        <v>10.81089082353887</v>
+        <v>10.81557595561772</v>
       </c>
       <c r="N9" s="32" t="n">
-        <v>1695.600128173828</v>
+        <v>1699.199981689453</v>
       </c>
       <c r="O9" s="33" t="n">
-        <v>42.81818505489465</v>
+        <v>42.90909044670336</v>
       </c>
       <c r="P9" s="31" t="inlineStr">
         <is>
@@ -2636,7 +2628,7 @@
       </c>
       <c r="S9" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:28</t>
+          <t>2026-05-04 13:36</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2679,7 @@
         <v>10715.00015258789</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>13.25773309892698</v>
+        <v>13.25599083728018</v>
       </c>
       <c r="M10" s="29" t="n">
         <v>64.31917363528412</v>
@@ -2715,7 +2707,7 @@
       </c>
       <c r="S10" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:28</t>
+          <t>2026-05-04 13:36</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2758,7 @@
         <v>5944.107150852142</v>
       </c>
       <c r="L11" s="33" t="n">
-        <v>7.354678954287075</v>
+        <v>7.353712441009809</v>
       </c>
       <c r="M11" s="33" t="n">
         <v>35.68082636471589</v>
@@ -2794,7 +2786,7 @@
       </c>
       <c r="S11" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:28</t>
+          <t>2026-05-04 13:36</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2837,7 @@
         <v>5000</v>
       </c>
       <c r="L12" s="29" t="n">
-        <v>6.18652958942094</v>
+        <v>6.185716588197428</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>100</v>
@@ -2873,7 +2865,7 @@
       </c>
       <c r="S12" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:28</t>
+          <t>2026-05-04 13:36</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2885,7 @@
           <t>IE00B579F325</t>
         </is>
       </c>
-      <c r="D13" s="56" t="inlineStr">
+      <c r="D13" s="54" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
@@ -2924,7 +2916,7 @@
         <v>6847.734948739668</v>
       </c>
       <c r="L13" s="33" t="n">
-        <v>8.472742976177967</v>
+        <v>8.471629532799646</v>
       </c>
       <c r="M13" s="33" t="n">
         <v>100</v>
@@ -2952,14 +2944,14 @@
       </c>
       <c r="S13" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:28</t>
+          <t>2026-05-04 13:36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:28 v2.0</t>
+          <t>Generated 2026-05-04 13:36 v2.0</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3001,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="57" t="inlineStr">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>Period returns (1D–5Y) and risk metrics calculated on available history per instrument (max 5 years). α/β computed vs S&amp;P 500.</t>
         </is>
@@ -3123,71 +3115,71 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="58" t="inlineStr">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>** TOTAL PORTFOLIO **</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
         <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="C5" s="60" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="D5" s="60" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E5" s="60" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="F5" s="60" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="G5" s="60" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="H5" s="60" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="I5" s="60" t="n">
-        <v>22</v>
-      </c>
-      <c r="J5" s="60" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="K5" s="60" t="n">
-        <v>45.09</v>
-      </c>
-      <c r="L5" s="60" t="n">
+      <c r="C5" s="58" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D5" s="58" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E5" s="58" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="F5" s="58" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="G5" s="58" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H5" s="58" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="58" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="J5" s="58" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="K5" s="58" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="L5" s="58" t="n">
         <v>7.92</v>
       </c>
-      <c r="M5" s="60" t="n">
+      <c r="M5" s="58" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="N5" s="60" t="n">
+      <c r="N5" s="58" t="n">
         <v>0.48</v>
       </c>
-      <c r="O5" s="60" t="n">
+      <c r="O5" s="58" t="n">
         <v>0.63</v>
       </c>
-      <c r="P5" s="61" t="n">
+      <c r="P5" s="59" t="n">
         <v>-13.91</v>
       </c>
-      <c r="Q5" s="61" t="n">
+      <c r="Q5" s="59" t="n">
         <v>-0.77</v>
       </c>
-      <c r="R5" s="61" t="n">
+      <c r="R5" s="59" t="n">
         <v>-1.22</v>
       </c>
-      <c r="S5" s="60" t="n">
+      <c r="S5" s="58" t="n">
         <v>2.68</v>
       </c>
-      <c r="T5" s="60" t="n">
+      <c r="T5" s="58" t="n">
         <v>0.15</v>
       </c>
-      <c r="U5" s="59" t="inlineStr">
+      <c r="U5" s="57" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
@@ -3243,13 +3235,13 @@
       <c r="O6" s="29" t="n">
         <v>0.73</v>
       </c>
-      <c r="P6" s="62" t="n">
+      <c r="P6" s="60" t="n">
         <v>-20.22</v>
       </c>
-      <c r="Q6" s="62" t="n">
+      <c r="Q6" s="60" t="n">
         <v>-1.4</v>
       </c>
-      <c r="R6" s="62" t="n">
+      <c r="R6" s="60" t="n">
         <v>-2.13</v>
       </c>
       <c r="S6" s="29" t="n">
@@ -3276,10 +3268,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>6.64</v>
@@ -3288,19 +3280,19 @@
         <v>4.46</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>6.38</v>
+        <v>6.39</v>
       </c>
       <c r="H7" s="33" t="n">
         <v>6.52</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>23.68</v>
+        <v>23.69</v>
       </c>
       <c r="J7" s="33" t="n">
         <v>56.16</v>
       </c>
       <c r="K7" s="33" t="n">
-        <v>58.73</v>
+        <v>58.74</v>
       </c>
       <c r="L7" s="33" t="n">
         <v>9.83</v>
@@ -3314,16 +3306,16 @@
       <c r="O7" s="33" t="n">
         <v>0.55</v>
       </c>
-      <c r="P7" s="63" t="n">
+      <c r="P7" s="61" t="n">
         <v>-20.07</v>
       </c>
-      <c r="Q7" s="63" t="n">
+      <c r="Q7" s="61" t="n">
         <v>-1.44</v>
       </c>
-      <c r="R7" s="63" t="n">
+      <c r="R7" s="61" t="n">
         <v>-2.13</v>
       </c>
-      <c r="S7" s="63" t="n">
+      <c r="S7" s="61" t="n">
         <v>-0.49</v>
       </c>
       <c r="T7" s="33" t="n">
@@ -3346,10 +3338,10 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C8" s="62" t="n">
+      <c r="C8" s="60" t="n">
         <v>-0.59</v>
       </c>
-      <c r="D8" s="62" t="n">
+      <c r="D8" s="60" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" s="29" t="n">
@@ -3385,16 +3377,16 @@
       <c r="O8" s="29" t="n">
         <v>0.44</v>
       </c>
-      <c r="P8" s="62" t="n">
+      <c r="P8" s="60" t="n">
         <v>-17.35</v>
       </c>
-      <c r="Q8" s="62" t="n">
+      <c r="Q8" s="60" t="n">
         <v>-1.63</v>
       </c>
-      <c r="R8" s="62" t="n">
+      <c r="R8" s="60" t="n">
         <v>-2.43</v>
       </c>
-      <c r="S8" s="62" t="n">
+      <c r="S8" s="60" t="n">
         <v>-1.39</v>
       </c>
       <c r="T8" s="29" t="n">
@@ -3417,7 +3409,7 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C9" s="63" t="n">
+      <c r="C9" s="61" t="n">
         <v>-0.16</v>
       </c>
       <c r="D9" s="33" t="n">
@@ -3456,16 +3448,16 @@
       <c r="O9" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="P9" s="63" t="n">
+      <c r="P9" s="61" t="n">
         <v>-24.81</v>
       </c>
-      <c r="Q9" s="63" t="n">
+      <c r="Q9" s="61" t="n">
         <v>-1.93</v>
       </c>
-      <c r="R9" s="63" t="n">
+      <c r="R9" s="61" t="n">
         <v>-2.72</v>
       </c>
-      <c r="S9" s="63" t="n">
+      <c r="S9" s="61" t="n">
         <v>-3.89</v>
       </c>
       <c r="T9" s="33" t="n">
@@ -3495,7 +3487,7 @@
         <v>0.59</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>5.96</v>
+        <v>5.97</v>
       </c>
       <c r="F10" s="29" t="n">
         <v>3.97</v>
@@ -3513,7 +3505,7 @@
         <v>55.69</v>
       </c>
       <c r="K10" s="29" t="n">
-        <v>63.29</v>
+        <v>63.3</v>
       </c>
       <c r="L10" s="29" t="n">
         <v>10.47</v>
@@ -3527,16 +3519,16 @@
       <c r="O10" s="29" t="n">
         <v>0.52</v>
       </c>
-      <c r="P10" s="62" t="n">
+      <c r="P10" s="60" t="n">
         <v>-20.63</v>
       </c>
-      <c r="Q10" s="62" t="n">
+      <c r="Q10" s="60" t="n">
         <v>-1.56</v>
       </c>
-      <c r="R10" s="62" t="n">
+      <c r="R10" s="60" t="n">
         <v>-2.29</v>
       </c>
-      <c r="S10" s="62" t="n">
+      <c r="S10" s="60" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="T10" s="29" t="n">
@@ -3598,13 +3590,13 @@
       <c r="O11" s="33" t="n">
         <v>0.55</v>
       </c>
-      <c r="P11" s="63" t="n">
+      <c r="P11" s="61" t="n">
         <v>-25.91</v>
       </c>
-      <c r="Q11" s="63" t="n">
+      <c r="Q11" s="61" t="n">
         <v>-2.26</v>
       </c>
-      <c r="R11" s="63" t="n">
+      <c r="R11" s="61" t="n">
         <v>-3.15</v>
       </c>
       <c r="S11" s="33" t="n">
@@ -3630,10 +3622,10 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C12" s="62" t="n">
+      <c r="C12" s="60" t="n">
         <v>-0.42</v>
       </c>
-      <c r="D12" s="62" t="n">
+      <c r="D12" s="60" t="n">
         <v>-0.5</v>
       </c>
       <c r="E12" s="29" t="n">
@@ -3669,16 +3661,16 @@
       <c r="O12" s="29" t="n">
         <v>0.61</v>
       </c>
-      <c r="P12" s="62" t="n">
+      <c r="P12" s="60" t="n">
         <v>-22.45</v>
       </c>
-      <c r="Q12" s="62" t="n">
+      <c r="Q12" s="60" t="n">
         <v>-1.79</v>
       </c>
-      <c r="R12" s="62" t="n">
+      <c r="R12" s="60" t="n">
         <v>-2.66</v>
       </c>
-      <c r="S12" s="62" t="n">
+      <c r="S12" s="60" t="n">
         <v>-0.13</v>
       </c>
       <c r="T12" s="29" t="n">
@@ -3740,13 +3732,13 @@
       <c r="O13" s="33" t="n">
         <v>0.7</v>
       </c>
-      <c r="P13" s="63" t="n">
+      <c r="P13" s="61" t="n">
         <v>-31.38</v>
       </c>
-      <c r="Q13" s="63" t="n">
+      <c r="Q13" s="61" t="n">
         <v>-2.45</v>
       </c>
-      <c r="R13" s="63" t="n">
+      <c r="R13" s="61" t="n">
         <v>-3.4</v>
       </c>
       <c r="S13" s="33" t="n">
@@ -3772,7 +3764,7 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C14" s="62" t="n">
+      <c r="C14" s="60" t="n">
         <v>-0.09</v>
       </c>
       <c r="D14" s="29" t="n">
@@ -3811,13 +3803,13 @@
       <c r="O14" s="29" t="n">
         <v>0.62</v>
       </c>
-      <c r="P14" s="62" t="n">
+      <c r="P14" s="60" t="n">
         <v>-23.17</v>
       </c>
-      <c r="Q14" s="62" t="n">
+      <c r="Q14" s="60" t="n">
         <v>-1.87</v>
       </c>
-      <c r="R14" s="62" t="n">
+      <c r="R14" s="60" t="n">
         <v>-2.64</v>
       </c>
       <c r="S14" s="29" t="n">
@@ -3846,16 +3838,16 @@
       <c r="C15" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="63" t="n">
+      <c r="D15" s="61" t="n">
         <v>-0.11</v>
       </c>
       <c r="E15" s="33" t="n">
         <v>0.38</v>
       </c>
-      <c r="F15" s="63" t="n">
+      <c r="F15" s="61" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G15" s="63" t="n">
+      <c r="G15" s="61" t="n">
         <v>-0.64</v>
       </c>
       <c r="H15" s="33" t="n">
@@ -3867,31 +3859,31 @@
       <c r="J15" s="33" t="n">
         <v>7.86</v>
       </c>
-      <c r="K15" s="63" t="n">
+      <c r="K15" s="61" t="n">
         <v>-8.98</v>
       </c>
-      <c r="L15" s="63" t="n">
+      <c r="L15" s="61" t="n">
         <v>-1.87</v>
       </c>
       <c r="M15" s="33" t="n">
         <v>5.55</v>
       </c>
-      <c r="N15" s="63" t="n">
+      <c r="N15" s="61" t="n">
         <v>-1.06</v>
       </c>
-      <c r="O15" s="63" t="n">
+      <c r="O15" s="61" t="n">
         <v>-1.63</v>
       </c>
-      <c r="P15" s="63" t="n">
+      <c r="P15" s="61" t="n">
         <v>-19.81</v>
       </c>
-      <c r="Q15" s="63" t="n">
+      <c r="Q15" s="61" t="n">
         <v>-0.55</v>
       </c>
-      <c r="R15" s="63" t="n">
+      <c r="R15" s="61" t="n">
         <v>-0.77</v>
       </c>
-      <c r="S15" s="63" t="n">
+      <c r="S15" s="61" t="n">
         <v>-6</v>
       </c>
       <c r="T15" s="33" t="n">
@@ -3915,34 +3907,34 @@
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>6.61</v>
+        <v>6.63</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>6.85</v>
+        <v>6.86</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>24.62</v>
+        <v>24.64</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>62.81</v>
+        <v>62.83</v>
       </c>
       <c r="K16" s="29" t="n">
-        <v>70.29000000000001</v>
+        <v>70.31</v>
       </c>
       <c r="L16" s="29" t="n">
-        <v>11.52</v>
+        <v>11.53</v>
       </c>
       <c r="M16" s="29" t="n">
         <v>13.8</v>
@@ -3953,13 +3945,13 @@
       <c r="O16" s="29" t="n">
         <v>0.7</v>
       </c>
-      <c r="P16" s="62" t="n">
+      <c r="P16" s="60" t="n">
         <v>-21.07</v>
       </c>
-      <c r="Q16" s="62" t="n">
+      <c r="Q16" s="60" t="n">
         <v>-1.39</v>
       </c>
-      <c r="R16" s="62" t="n">
+      <c r="R16" s="60" t="n">
         <v>-2.13</v>
       </c>
       <c r="S16" s="29" t="n">
@@ -3977,7 +3969,7 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
@@ -3986,58 +3978,58 @@
         </is>
       </c>
       <c r="C17" s="33" t="n">
-        <v>0.62</v>
+        <v>1.87</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>0.96</v>
+        <v>1.45</v>
       </c>
       <c r="E17" s="33" t="n">
-        <v>7.32</v>
+        <v>12.64</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>4.24</v>
+        <v>8.94</v>
       </c>
       <c r="G17" s="33" t="n">
-        <v>5.39</v>
+        <v>16.56</v>
       </c>
       <c r="H17" s="33" t="n">
-        <v>5.78</v>
+        <v>16.16</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>22.94</v>
+        <v>40.77</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>62.65</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="K17" s="33" t="n">
-        <v>75.11</v>
+        <v>42.17</v>
       </c>
       <c r="L17" s="33" t="n">
-        <v>12.16</v>
+        <v>7.57</v>
       </c>
       <c r="M17" s="33" t="n">
-        <v>14.24</v>
+        <v>18.83</v>
       </c>
       <c r="N17" s="33" t="n">
-        <v>0.57</v>
+        <v>0.19</v>
       </c>
       <c r="O17" s="33" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="P17" s="63" t="n">
-        <v>-21.73</v>
-      </c>
-      <c r="Q17" s="63" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="R17" s="63" t="n">
-        <v>-2.19</v>
+        <v>0.26</v>
+      </c>
+      <c r="P17" s="61" t="n">
+        <v>-24.38</v>
+      </c>
+      <c r="Q17" s="61" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="R17" s="61" t="n">
+        <v>-2.59</v>
       </c>
       <c r="S17" s="33" t="n">
-        <v>6.35</v>
+        <v>2.75</v>
       </c>
       <c r="T17" s="33" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="U17" s="31" t="inlineStr">
         <is>
@@ -4048,7 +4040,7 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
@@ -4056,59 +4048,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
-        <v>1.83</v>
+      <c r="C18" s="60" t="n">
+        <v>-0.09</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="E18" s="29" t="n">
-        <v>12.6</v>
+        <v>8.83</v>
       </c>
       <c r="F18" s="29" t="n">
-        <v>8.9</v>
+        <v>5.43</v>
       </c>
       <c r="G18" s="29" t="n">
-        <v>16.52</v>
+        <v>4.81</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>16.12</v>
+        <v>6.41</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>40.72</v>
+        <v>25.3</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>68.66</v>
+        <v>70.91</v>
       </c>
       <c r="K18" s="29" t="n">
-        <v>42.12</v>
+        <v>88.41</v>
       </c>
       <c r="L18" s="29" t="n">
-        <v>7.56</v>
+        <v>13.83</v>
       </c>
       <c r="M18" s="29" t="n">
-        <v>18.82</v>
+        <v>17.29</v>
       </c>
       <c r="N18" s="29" t="n">
-        <v>0.19</v>
+        <v>0.57</v>
       </c>
       <c r="O18" s="29" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="P18" s="62" t="n">
-        <v>-24.38</v>
-      </c>
-      <c r="Q18" s="62" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="R18" s="62" t="n">
-        <v>-2.59</v>
+        <v>0.79</v>
+      </c>
+      <c r="P18" s="60" t="n">
+        <v>-22.73</v>
+      </c>
+      <c r="Q18" s="60" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="R18" s="60" t="n">
+        <v>-2.53</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>2.74</v>
+        <v>6.37</v>
       </c>
       <c r="T18" s="29" t="n">
-        <v>0.1</v>
+        <v>0.42</v>
       </c>
       <c r="U18" s="27" t="inlineStr">
         <is>
@@ -4119,7 +4111,7 @@
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
@@ -4127,59 +4119,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C19" s="63" t="n">
-        <v>-0.11</v>
+      <c r="C19" s="33" t="n">
+        <v>0.63</v>
       </c>
       <c r="D19" s="33" t="n">
-        <v>1.13</v>
+        <v>0.98</v>
       </c>
       <c r="E19" s="33" t="n">
-        <v>8.81</v>
+        <v>7.33</v>
       </c>
       <c r="F19" s="33" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G19" s="33" t="n">
         <v>5.4</v>
       </c>
-      <c r="G19" s="33" t="n">
-        <v>4.78</v>
-      </c>
       <c r="H19" s="33" t="n">
-        <v>6.38</v>
+        <v>5.79</v>
       </c>
       <c r="I19" s="33" t="n">
-        <v>25.28</v>
+        <v>22.96</v>
       </c>
       <c r="J19" s="33" t="n">
-        <v>70.87</v>
+        <v>62.67</v>
       </c>
       <c r="K19" s="33" t="n">
-        <v>88.36</v>
+        <v>75.13</v>
       </c>
       <c r="L19" s="33" t="n">
-        <v>13.82</v>
+        <v>12.17</v>
       </c>
       <c r="M19" s="33" t="n">
-        <v>17.29</v>
+        <v>14.24</v>
       </c>
       <c r="N19" s="33" t="n">
         <v>0.57</v>
       </c>
       <c r="O19" s="33" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="P19" s="63" t="n">
-        <v>-22.73</v>
-      </c>
-      <c r="Q19" s="63" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="R19" s="63" t="n">
-        <v>-2.53</v>
+        <v>0.73</v>
+      </c>
+      <c r="P19" s="61" t="n">
+        <v>-21.73</v>
+      </c>
+      <c r="Q19" s="61" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="R19" s="61" t="n">
+        <v>-2.19</v>
       </c>
       <c r="S19" s="33" t="n">
         <v>6.36</v>
       </c>
       <c r="T19" s="33" t="n">
-        <v>0.42</v>
+        <v>0.22</v>
       </c>
       <c r="U19" s="31" t="inlineStr">
         <is>
@@ -4201,55 +4193,55 @@
       <c r="C20" s="29" t="n">
         <v>0.31</v>
       </c>
-      <c r="D20" s="62" t="n">
+      <c r="D20" s="60" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E20" s="62" t="n">
+      <c r="E20" s="60" t="n">
         <v>-1.11</v>
       </c>
       <c r="F20" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="G20" s="62" t="n">
+      <c r="G20" s="60" t="n">
         <v>-1.55</v>
       </c>
       <c r="H20" s="29" t="n">
         <v>0.02</v>
       </c>
-      <c r="I20" s="62" t="n">
+      <c r="I20" s="60" t="n">
         <v>-0.52</v>
       </c>
-      <c r="J20" s="62" t="n">
+      <c r="J20" s="60" t="n">
         <v>-0.82</v>
       </c>
-      <c r="K20" s="62" t="n">
+      <c r="K20" s="60" t="n">
         <v>-1.61</v>
       </c>
-      <c r="L20" s="62" t="n">
+      <c r="L20" s="60" t="n">
         <v>-0.33</v>
       </c>
       <c r="M20" s="29" t="n">
         <v>10.65</v>
       </c>
-      <c r="N20" s="62" t="n">
+      <c r="N20" s="60" t="n">
         <v>-0.41</v>
       </c>
-      <c r="O20" s="62" t="n">
+      <c r="O20" s="60" t="n">
         <v>-0.61</v>
       </c>
-      <c r="P20" s="62" t="n">
+      <c r="P20" s="60" t="n">
         <v>-15.77</v>
       </c>
-      <c r="Q20" s="62" t="n">
+      <c r="Q20" s="60" t="n">
         <v>-1.1</v>
       </c>
-      <c r="R20" s="62" t="n">
+      <c r="R20" s="60" t="n">
         <v>-1.48</v>
       </c>
-      <c r="S20" s="62" t="n">
+      <c r="S20" s="60" t="n">
         <v>-4.14</v>
       </c>
-      <c r="T20" s="62" t="n">
+      <c r="T20" s="60" t="n">
         <v>-0.02</v>
       </c>
       <c r="U20" s="27" t="inlineStr">
@@ -4269,13 +4261,13 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C21" s="63" t="n">
+      <c r="C21" s="61" t="n">
         <v>-0.1</v>
       </c>
-      <c r="D21" s="63" t="n">
+      <c r="D21" s="61" t="n">
         <v>-2.09</v>
       </c>
-      <c r="E21" s="63" t="n">
+      <c r="E21" s="61" t="n">
         <v>-4.21</v>
       </c>
       <c r="F21" s="33" t="n">
@@ -4308,13 +4300,13 @@
       <c r="O21" s="33" t="n">
         <v>1.36</v>
       </c>
-      <c r="P21" s="63" t="n">
+      <c r="P21" s="61" t="n">
         <v>-15.94</v>
       </c>
-      <c r="Q21" s="63" t="n">
+      <c r="Q21" s="61" t="n">
         <v>-1.75</v>
       </c>
-      <c r="R21" s="63" t="n">
+      <c r="R21" s="61" t="n">
         <v>-2.57</v>
       </c>
       <c r="S21" s="33" t="n">
@@ -4379,13 +4371,13 @@
       <c r="O22" s="29" t="n">
         <v>0.46</v>
       </c>
-      <c r="P22" s="62" t="n">
+      <c r="P22" s="60" t="n">
         <v>-21.24</v>
       </c>
-      <c r="Q22" s="62" t="n">
+      <c r="Q22" s="60" t="n">
         <v>-1.78</v>
       </c>
-      <c r="R22" s="62" t="n">
+      <c r="R22" s="60" t="n">
         <v>-2.5</v>
       </c>
       <c r="S22" s="29" t="n">
@@ -4411,56 +4403,56 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C23" s="63" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="D23" s="63" t="n">
-        <v>-0.11</v>
+      <c r="C23" s="61" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="D23" s="61" t="n">
+        <v>-0.04</v>
       </c>
       <c r="E23" s="33" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="F23" s="63" t="n">
-        <v>-1.19</v>
+        <v>4.15</v>
+      </c>
+      <c r="F23" s="61" t="n">
+        <v>-1.13</v>
       </c>
       <c r="G23" s="33" t="n">
-        <v>6.97</v>
+        <v>7.03</v>
       </c>
       <c r="H23" s="33" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="I23" s="33" t="n">
-        <v>14.28</v>
+        <v>14.35</v>
       </c>
       <c r="J23" s="33" t="n">
-        <v>40.02</v>
+        <v>40.11</v>
       </c>
       <c r="K23" s="33" t="n">
-        <v>54.34</v>
+        <v>54.43</v>
       </c>
       <c r="L23" s="33" t="n">
-        <v>9.48</v>
+        <v>9.49</v>
       </c>
       <c r="M23" s="33" t="n">
-        <v>14.95</v>
+        <v>14.94</v>
       </c>
       <c r="N23" s="33" t="n">
         <v>0.37</v>
       </c>
       <c r="O23" s="33" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="P23" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P23" s="61" t="n">
         <v>-22.86</v>
       </c>
-      <c r="Q23" s="63" t="n">
+      <c r="Q23" s="61" t="n">
         <v>-1.53</v>
       </c>
-      <c r="R23" s="63" t="n">
+      <c r="R23" s="61" t="n">
         <v>-2.22</v>
       </c>
       <c r="S23" s="33" t="n">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="T23" s="33" t="n">
         <v>0.17</v>
@@ -4472,7 +4464,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="62" t="inlineStr">
         <is>
           <t>Legend — Rating Thresholds</t>
         </is>
@@ -4516,7 +4508,7 @@
           <t>CAGR</t>
         </is>
       </c>
-      <c r="B28" s="65" t="inlineStr">
+      <c r="B28" s="63" t="inlineStr">
         <is>
           <t>Compound Annual Growth Rate. The single yearly return that, if repeated every year, would grow your portfolio from start to end value. Accounts for compounding. ~7% is the long-term global equity average.</t>
         </is>
@@ -4548,7 +4540,7 @@
           <t>α (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B29" s="66" t="inlineStr">
+      <c r="B29" s="64" t="inlineStr">
         <is>
           <t>Extra annual return vs the benchmark, after adjusting for how risky the portfolio is (CAPM). Positive = you beat the market beyond what your risk alone justified. Negative = you underperformed after fees and noise.</t>
         </is>
@@ -4580,7 +4572,7 @@
           <t>β (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B30" s="65" t="inlineStr">
+      <c r="B30" s="63" t="inlineStr">
         <is>
           <t>How much your portfolio moves when the benchmark moves 1%. β=1 in line, β=0.5 half as reactive, β=1.5 amplifies by 50%, β≈0 uncorrelated. Tells you how much systematic market risk you're running.</t>
         </is>
@@ -4612,7 +4604,7 @@
           <t>Max DD</t>
         </is>
       </c>
-      <c r="B31" s="66" t="inlineStr">
+      <c r="B31" s="64" t="inlineStr">
         <is>
           <t>Maximum Drawdown. Worst peak-to-trough loss over the period — the most painful scenario an investor lived through. -20% is typical for diversified equity; deeper drops signal concentration or high volatility.</t>
         </is>
@@ -4644,7 +4636,7 @@
           <t>Volatility</t>
         </is>
       </c>
-      <c r="B32" s="65" t="inlineStr">
+      <c r="B32" s="63" t="inlineStr">
         <is>
           <t>How bumpy the ride is. Annualized standard deviation of daily returns. A 15% vol means ~±15% year-to-year noise around the average return. Equity indexes ~15–20%, bonds ~3–7%.</t>
         </is>
@@ -4676,7 +4668,7 @@
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="B33" s="66" t="inlineStr">
+      <c r="B33" s="64" t="inlineStr">
         <is>
           <t>Return per unit of risk taken: (CAGR − risk-free rate) / Volatility. Above 1 is good, above 2 is excellent, negative means you were paid less than a safe bond for the risk you ran.</t>
         </is>
@@ -4708,7 +4700,7 @@
           <t>Sortino</t>
         </is>
       </c>
-      <c r="B34" s="65" t="inlineStr">
+      <c r="B34" s="63" t="inlineStr">
         <is>
           <t>Like Sharpe but only penalizes downside volatility (ignores upside swings). More honest when returns are asymmetric. Usually higher than Sharpe — the gap shows how much of your volatility is actually good volatility.</t>
         </is>
@@ -4740,7 +4732,7 @@
           <t>VaR 95%</t>
         </is>
       </c>
-      <c r="B35" s="66" t="inlineStr">
+      <c r="B35" s="64" t="inlineStr">
         <is>
           <t>Value at Risk. The daily loss exceeded only 5% of the time (historical simulation). A VaR of -1.2% means on an average month you should expect about one day worse than -1.2%. Non-parametric: no normal-distribution assumption.</t>
         </is>
@@ -4772,7 +4764,7 @@
           <t>CVaR 95%</t>
         </is>
       </c>
-      <c r="B36" s="65" t="inlineStr">
+      <c r="B36" s="63" t="inlineStr">
         <is>
           <t>Conditional VaR, a.k.a. Expected Shortfall. The average loss on the worst 5% of days. Always more negative than VaR. Captures tail risk VaR misses — how bad it really gets when it goes bad.</t>
         </is>
@@ -4801,7 +4793,7 @@
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:28 v2.0</t>
+          <t>Generated 2026-05-04 13:36 v2.0</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4833,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" s="62" t="inlineStr">
         <is>
           <t>Return Contribution by Holding</t>
         </is>
@@ -4896,13 +4888,13 @@
         </is>
       </c>
       <c r="D5" s="29" t="n">
-        <v>14.2879303956883</v>
+        <v>14.28605275092394</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>415.5184553004801</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>59.36898767457182</v>
+        <v>59.3611857140509</v>
       </c>
     </row>
     <row r="6">
@@ -4922,13 +4914,13 @@
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>13.25773309892698</v>
+        <v>13.25599083728018</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>91.33928843906948</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>12.10951907571089</v>
+        <v>12.10792770631996</v>
       </c>
     </row>
     <row r="7">
@@ -4948,13 +4940,13 @@
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>8.472742976177967</v>
+        <v>8.471629532799646</v>
       </c>
       <c r="E7" s="29" t="n">
         <v>55.27743647935755</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>4.683515116716004</v>
+        <v>4.68289963375982</v>
       </c>
     </row>
     <row r="8">
@@ -4974,13 +4966,13 @@
         </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>15.35051232088437</v>
+        <v>15.35047488934462</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>21.15625143051147</v>
+        <v>21.17187976837158</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.24759298247794</v>
+        <v>3.249984087446114</v>
       </c>
     </row>
     <row r="9">
@@ -5000,13 +4992,13 @@
         </is>
       </c>
       <c r="D9" s="29" t="n">
-        <v>8.481880462245561</v>
+        <v>8.483660842163392</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>36.01428440638951</v>
+        <v>36.06071472167969</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>3.054688552683102</v>
+        <v>3.059268734247389</v>
       </c>
     </row>
     <row r="10">
@@ -5026,13 +5018,13 @@
         </is>
       </c>
       <c r="D10" s="33" t="n">
-        <v>7.354678954287075</v>
+        <v>7.353712441009809</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>41.5263607345748</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>3.054130513427105</v>
+        <v>3.053729155637039</v>
       </c>
     </row>
     <row r="11">
@@ -5052,13 +5044,13 @@
         </is>
       </c>
       <c r="D11" s="29" t="n">
-        <v>6.997707507776049</v>
+        <v>7.001241440532606</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>42.81818505489465</v>
+        <v>42.90909044670336</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>2.996291350279805</v>
+        <v>3.004169022110213</v>
       </c>
     </row>
     <row r="12">
@@ -5078,13 +5070,13 @@
         </is>
       </c>
       <c r="D12" s="33" t="n">
-        <v>12.32533694648823</v>
+        <v>12.32660245947866</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.50795942585797</v>
+        <v>16.53523641451134</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>2.034661622226559</v>
+        <v>2.038232858551765</v>
       </c>
     </row>
     <row r="13">
@@ -5104,13 +5096,13 @@
         </is>
       </c>
       <c r="D13" s="29" t="n">
-        <v>7.284947748104517</v>
+        <v>7.284918218269714</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>20.1581604626714</v>
+        <v>20.17346596231266</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>1.468511456684675</v>
+        <v>1.469620497144954</v>
       </c>
     </row>
     <row r="14">
@@ -5130,7 +5122,7 @@
         </is>
       </c>
       <c r="D14" s="33" t="n">
-        <v>6.18652958942094</v>
+        <v>6.185716588197428</v>
       </c>
       <c r="E14" s="33" t="n">
         <v>0</v>
@@ -5140,7 +5132,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="64" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr">
         <is>
           <t>Breakdown by Asset Class</t>
         </is>
@@ -5175,10 +5167,10 @@
         </is>
       </c>
       <c r="B18" s="28" t="n">
-        <v>52313.91400105275</v>
+        <v>52324.53643626816</v>
       </c>
       <c r="C18" s="29" t="n">
-        <v>92.02888268013419</v>
+        <v>92.06147376900979</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>6</v>
@@ -5233,7 +5225,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="64" t="inlineStr">
+      <c r="A23" s="62" t="inlineStr">
         <is>
           <t>Breakdown by Geography (Equity Only)</t>
         </is>
@@ -5263,23 +5255,23 @@
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>41.79626795598796</v>
+        <v>41.79516167143485</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>19.27412377301361</v>
+        <v>19.29352738173186</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="56" t="inlineStr">
+      <c r="A26" s="54" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
       <c r="B26" s="33" t="n">
-        <v>15.50380579197923</v>
+        <v>15.50544013183685</v>
       </c>
       <c r="C26" s="33" t="n">
-        <v>28.58526791845049</v>
+        <v>28.61629724502563</v>
       </c>
     </row>
     <row r="27">
@@ -5289,10 +5281,10 @@
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>9.766116970263369</v>
+        <v>9.768936068831742</v>
       </c>
       <c r="C27" s="29" t="n">
-        <v>28.04419898269251</v>
+        <v>28.0848120591292</v>
       </c>
     </row>
     <row r="28">
@@ -5302,10 +5294,10 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>24.19785747467557</v>
+        <v>24.19321790615446</v>
       </c>
       <c r="C28" s="33" t="n">
-        <v>152.2776223978877</v>
+        <v>152.2879336770548</v>
       </c>
     </row>
     <row r="29">
@@ -5315,10 +5307,10 @@
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>8.735951807093869</v>
+        <v>8.737244221742097</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>28.04419898269251</v>
+        <v>28.0848120591292</v>
       </c>
     </row>
   </sheetData>

--- a/output/sample/portfolio_dashboard_sample.xlsx
+++ b/output/sample/portfolio_dashboard_sample.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="+#,##0.00;-#,##0.00;0.00"/>
     <numFmt numFmtId="165" formatCode="+0.00;-0.00;0.00"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,7 +106,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00C2410C"/>
+      <color rgb="00CA8A04"/>
       <sz val="10"/>
     </font>
     <font>
@@ -125,6 +125,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="007C3AED"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C2410C"/>
       <sz val="10"/>
     </font>
     <font>
@@ -252,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -314,125 +320,128 @@
     <xf numFmtId="2" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="23" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="23" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -827,7 +836,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of: 04 May 2026</t>
+          <t>As of: 10 May 2026</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -856,7 +865,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>80831.37868844786</v>
+        <v>82528.07497265239</v>
       </c>
       <c r="D5" s="2" t="n"/>
     </row>
@@ -867,7 +876,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>26691.37868844786</v>
+        <v>28388.07497265239</v>
       </c>
       <c r="D6" s="2" t="n"/>
     </row>
@@ -878,7 +887,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>49.30066252022139</v>
+        <v>52.43456773670556</v>
       </c>
       <c r="D7" s="2" t="n"/>
     </row>
@@ -942,7 +951,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>64.73295060071293</v>
+        <v>65.32892612382153</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>65</v>
@@ -954,7 +963,7 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>41.79516167143485</v>
+        <v>41.22858361399044</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>55</v>
@@ -967,7 +976,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>20.60970327828998</v>
+        <v>20.22486562435265</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>25</v>
@@ -979,7 +988,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>24.19321790615446</v>
+        <v>24.84297679518155</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>8</v>
@@ -988,39 +997,39 @@
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>8.471629532799646</v>
+        <v>8.387663930203299</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>5</v>
       </c>
       <c r="D14" s="2" t="n"/>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>15.50544013183685</v>
+        <v>15.67502157315777</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Equivalents</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
-        <v>6.185716588197428</v>
+      <c r="B15" s="17" t="n">
+        <v>6.058544321622511</v>
       </c>
       <c r="C15" s="18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="16" t="inlineStr">
@@ -1029,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>9.768936068831742</v>
+        <v>9.631770299638772</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>14</v>
@@ -1043,7 +1052,7 @@
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>8.737244221742097</v>
+        <v>8.621647718031447</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>12</v>
@@ -1099,10 +1108,10 @@
         </is>
       </c>
       <c r="B21" s="28" t="n">
-        <v>12408.00048828125</v>
+        <v>12651.19995117188</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>15.35047488934462</v>
+        <v>15.32957112517667</v>
       </c>
       <c r="D21" s="30" t="n"/>
       <c r="E21" s="12" t="inlineStr">
@@ -1118,10 +1127,10 @@
         </is>
       </c>
       <c r="B22" s="32" t="n">
-        <v>11547.61339873075</v>
+        <v>12262.46404320002</v>
       </c>
       <c r="C22" s="33" t="n">
-        <v>14.28605275092394</v>
+        <v>14.85853637960594</v>
       </c>
       <c r="D22" s="30" t="n"/>
       <c r="E22" s="34" t="inlineStr">
@@ -1137,10 +1146,10 @@
         </is>
       </c>
       <c r="B23" s="28" t="n">
-        <v>10715.00015258789</v>
+        <v>10752.99987792969</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>13.25599083728018</v>
+        <v>13.02950527016769</v>
       </c>
       <c r="D23" s="30" t="n"/>
       <c r="E23" s="35" t="inlineStr">
@@ -1156,10 +1165,10 @@
         </is>
       </c>
       <c r="B24" s="32" t="n">
-        <v>9963.762713440719</v>
+        <v>10108.55113043108</v>
       </c>
       <c r="C24" s="33" t="n">
-        <v>12.32660245947866</v>
+        <v>12.2486210102208</v>
       </c>
       <c r="D24" s="30" t="n"/>
       <c r="E24" s="34" t="inlineStr">
@@ -1175,10 +1184,10 @@
         </is>
       </c>
       <c r="B25" s="28" t="n">
-        <v>6857.460021972656</v>
+        <v>7170.840225219727</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>8.483660842163392</v>
+        <v>8.688970665553452</v>
       </c>
       <c r="D25" s="30" t="n"/>
       <c r="E25" s="12" t="inlineStr">
@@ -1193,7 +1202,7 @@
     <row r="27">
       <c r="A27" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:36 v2.0</t>
+          <t>Generated 2026-05-10 16:07 v2.0</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1236,7 +1245,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="37" t="inlineStr">
         <is>
-          <t>●  Action needed — largest deviation 16.2% (&gt;5.0%). Rebalancing recommended.</t>
+          <t>●  Action needed — largest deviation 16.8% (&gt;5.0%). Rebalancing recommended.</t>
         </is>
       </c>
     </row>
@@ -1326,16 +1335,16 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>20.60970327828998</v>
+        <v>20.22486562435265</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>25</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>20.60970327828998</v>
+        <v>20.22486562435265</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>-4.390296721710016</v>
+        <v>-4.775134375647347</v>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
@@ -1346,20 +1355,20 @@
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>8.471629532799646</v>
+        <v>8.387663930203299</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>5</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>8.471629532799646</v>
+        <v>8.387663930203299</v>
       </c>
       <c r="E15" s="42" t="n">
-        <v>3.471629532799646</v>
+        <v>3.387663930203299</v>
       </c>
       <c r="F15" s="43" t="inlineStr">
         <is>
@@ -1374,42 +1383,42 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>6.185716588197428</v>
+        <v>6.058544321622511</v>
       </c>
       <c r="C16" s="14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>6.185716588197428</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>1.185716588197428</v>
-      </c>
-      <c r="F16" s="45" t="inlineStr">
-        <is>
-          <t>● Aligned</t>
+        <v>6.058544321622511</v>
+      </c>
+      <c r="E16" s="40" t="n">
+        <v>3.058544321622511</v>
+      </c>
+      <c r="F16" s="41" t="inlineStr">
+        <is>
+          <t>● Drift</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Equities</t>
+          <t>Alternative</t>
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>64.73295060071293</v>
+        <v>0</v>
       </c>
       <c r="C17" s="18" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>64.73295060071294</v>
-      </c>
-      <c r="E17" s="46" t="n">
-        <v>-0.2670493992870604</v>
-      </c>
-      <c r="F17" s="47" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="E17" s="44" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F17" s="45" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
@@ -1418,607 +1427,631 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>Alternative</t>
+          <t>Equities</t>
         </is>
       </c>
       <c r="B18" s="14" t="n">
+        <v>65.32892612382153</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>65.32892612382153</v>
+      </c>
+      <c r="E18" s="46" t="n">
+        <v>0.3289261238215317</v>
+      </c>
+      <c r="F18" s="47" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="44" t="n">
+      <c r="E19" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="45" t="inlineStr">
+      <c r="F19" s="45" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="39" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>Geography (equity only)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Current %</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Target %</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Post-rebal %</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Delta after rebal (pp)</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
-        <v>24.19321790615446</v>
-      </c>
-      <c r="C22" s="14" t="n">
+      <c r="B23" s="14" t="n">
+        <v>24.84297679518155</v>
+      </c>
+      <c r="C23" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="D22" s="14" t="n">
-        <v>24.19321790615446</v>
-      </c>
-      <c r="E22" s="48" t="n">
-        <v>16.19321790615446</v>
-      </c>
-      <c r="F22" s="49" t="inlineStr">
+      <c r="D23" s="14" t="n">
+        <v>24.84297679518155</v>
+      </c>
+      <c r="E23" s="48" t="n">
+        <v>16.84297679518155</v>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
-        <v>41.79516167143485</v>
-      </c>
-      <c r="C23" s="18" t="n">
+      <c r="B24" s="18" t="n">
+        <v>41.22858361399044</v>
+      </c>
+      <c r="C24" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="D23" s="18" t="n">
-        <v>41.79516167143485</v>
-      </c>
-      <c r="E23" s="50" t="n">
-        <v>-13.20483832856515</v>
-      </c>
-      <c r="F23" s="51" t="inlineStr">
+      <c r="D24" s="18" t="n">
+        <v>41.22858361399044</v>
+      </c>
+      <c r="E24" s="50" t="n">
+        <v>-13.77141638600956</v>
+      </c>
+      <c r="F24" s="51" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
-        <v>15.50544013183685</v>
-      </c>
-      <c r="C24" s="14" t="n">
+      <c r="B25" s="14" t="n">
+        <v>15.67502157315777</v>
+      </c>
+      <c r="C25" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="D24" s="14" t="n">
-        <v>15.50544013183685</v>
-      </c>
-      <c r="E24" s="40" t="n">
-        <v>4.505440131836851</v>
-      </c>
-      <c r="F24" s="41" t="inlineStr">
+      <c r="D25" s="14" t="n">
+        <v>15.67502157315778</v>
+      </c>
+      <c r="E25" s="40" t="n">
+        <v>4.675021573157776</v>
+      </c>
+      <c r="F25" s="41" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>Eurozone EMU</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
-        <v>9.768936068831742</v>
-      </c>
-      <c r="C25" s="18" t="n">
+      <c r="B26" s="18" t="n">
+        <v>9.631770299638772</v>
+      </c>
+      <c r="C26" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="D25" s="18" t="n">
-        <v>9.76893606883174</v>
-      </c>
-      <c r="E25" s="42" t="n">
-        <v>-4.23106393116826</v>
-      </c>
-      <c r="F25" s="43" t="inlineStr">
+      <c r="D26" s="18" t="n">
+        <v>9.631770299638774</v>
+      </c>
+      <c r="E26" s="42" t="n">
+        <v>-4.368229700361226</v>
+      </c>
+      <c r="F26" s="43" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>Dev ex-USA ex-EMU ex-JP</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v>8.737244221742097</v>
-      </c>
-      <c r="C26" s="14" t="n">
+      <c r="B27" s="14" t="n">
+        <v>8.621647718031447</v>
+      </c>
+      <c r="C27" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="D26" s="14" t="n">
-        <v>8.737244221742097</v>
-      </c>
-      <c r="E26" s="40" t="n">
-        <v>-3.262755778257903</v>
-      </c>
-      <c r="F26" s="41" t="inlineStr">
+      <c r="D27" s="14" t="n">
+        <v>8.621647718031449</v>
+      </c>
+      <c r="E27" s="40" t="n">
+        <v>-3.378352281968551</v>
+      </c>
+      <c r="F27" s="41" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
         <is>
           <t>Per-Holding Equity Targets</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Current %</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Target %</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Post-rebal %</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Delta after rebal (pp)</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>CNKY.L</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
-        <v>22.06921300257647</v>
-      </c>
-      <c r="C30" s="14" t="n">
+      <c r="B31" s="14" t="n">
+        <v>22.74419198540586</v>
+      </c>
+      <c r="C31" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="14" t="n">
-        <v>22.06921300257647</v>
-      </c>
-      <c r="E30" s="48" t="n">
-        <v>12.06921300257647</v>
-      </c>
-      <c r="F30" s="49" t="inlineStr">
+      <c r="D31" s="14" t="n">
+        <v>22.74419198540586</v>
+      </c>
+      <c r="E31" s="48" t="n">
+        <v>12.74419198540586</v>
+      </c>
+      <c r="F31" s="49" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="31" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>VERX.DE</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
-        <v>10.81557595561772</v>
-      </c>
-      <c r="C31" s="18" t="n">
+      <c r="B32" s="18" t="n">
+        <v>10.65460686086223</v>
+      </c>
+      <c r="C32" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="D31" s="18" t="n">
-        <v>10.81557595561772</v>
-      </c>
-      <c r="E31" s="42" t="n">
-        <v>-4.184424044382277</v>
-      </c>
-      <c r="F31" s="43" t="inlineStr">
+      <c r="D32" s="18" t="n">
+        <v>10.65460686086223</v>
+      </c>
+      <c r="E32" s="42" t="n">
+        <v>-4.345393139137771</v>
+      </c>
+      <c r="F32" s="43" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="27" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>EUNL.DE</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
-        <v>11.25380219913764</v>
-      </c>
-      <c r="C32" s="14" t="n">
+      <c r="B33" s="14" t="n">
+        <v>11.086492811195</v>
+      </c>
+      <c r="C33" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="D32" s="14" t="n">
-        <v>11.25380219913764</v>
-      </c>
-      <c r="E32" s="40" t="n">
-        <v>-3.746197800862364</v>
-      </c>
-      <c r="F32" s="41" t="inlineStr">
+      <c r="D33" s="14" t="n">
+        <v>11.086492811195</v>
+      </c>
+      <c r="E33" s="40" t="n">
+        <v>-3.913507188804996</v>
+      </c>
+      <c r="F33" s="41" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="31" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>XMME.DE</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
-        <v>13.10562976573164</v>
-      </c>
-      <c r="C33" s="18" t="n">
+      <c r="B34" s="18" t="n">
+        <v>13.30034210126884</v>
+      </c>
+      <c r="C34" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="D33" s="18" t="n">
-        <v>13.10562976573164</v>
-      </c>
-      <c r="E33" s="46" t="n">
-        <v>-1.894370234268361</v>
-      </c>
-      <c r="F33" s="47" t="inlineStr">
+      <c r="D34" s="18" t="n">
+        <v>13.30034210126884</v>
+      </c>
+      <c r="E34" s="44" t="n">
+        <v>-1.699657898731161</v>
+      </c>
+      <c r="F34" s="45" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="27" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="27" t="inlineStr">
         <is>
           <t>VWCE.DE</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
-        <v>23.71354116704756</v>
-      </c>
-      <c r="C34" s="14" t="n">
+      <c r="B35" s="14" t="n">
+        <v>23.46521217281558</v>
+      </c>
+      <c r="C35" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="D34" s="14" t="n">
-        <v>23.71354116704756</v>
-      </c>
-      <c r="E34" s="44" t="n">
-        <v>-1.286458832952437</v>
-      </c>
-      <c r="F34" s="45" t="inlineStr">
+      <c r="D35" s="14" t="n">
+        <v>23.46521217281558</v>
+      </c>
+      <c r="E35" s="46" t="n">
+        <v>-1.53478782718442</v>
+      </c>
+      <c r="F35" s="47" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="31" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
         <is>
           <t>CSPX.L</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
-        <v>19.04223790988896</v>
-      </c>
-      <c r="C35" s="18" t="n">
+      <c r="B36" s="18" t="n">
+        <v>18.74915406845249</v>
+      </c>
+      <c r="C36" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="D35" s="18" t="n">
-        <v>19.04223790988896</v>
-      </c>
-      <c r="E35" s="46" t="n">
-        <v>-0.9577620901110357</v>
-      </c>
-      <c r="F35" s="47" t="inlineStr">
+      <c r="D36" s="18" t="n">
+        <v>18.74915406845249</v>
+      </c>
+      <c r="E36" s="44" t="n">
+        <v>-1.250845931547513</v>
+      </c>
+      <c r="F36" s="45" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="39" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="39" t="inlineStr">
         <is>
           <t>Per-Holding Fixed Income Targets</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Current %</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Target %</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Post-rebal %</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Delta after rebal (pp)</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="27" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>IEAG.L</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>64.42319821635272</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>64.42319821635272</v>
+      </c>
+      <c r="E40" s="48" t="n">
+        <v>-5.576801783647284</v>
+      </c>
+      <c r="F40" s="49" t="inlineStr">
+        <is>
+          <t>● Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>IBTM.L</t>
         </is>
       </c>
-      <c r="B39" s="14" t="n">
-        <v>35.68082636471589</v>
-      </c>
-      <c r="C39" s="14" t="n">
+      <c r="B41" s="18" t="n">
+        <v>35.57680178364728</v>
+      </c>
+      <c r="C41" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="D39" s="14" t="n">
-        <v>35.68082636471589</v>
-      </c>
-      <c r="E39" s="48" t="n">
-        <v>5.680826364715891</v>
-      </c>
-      <c r="F39" s="49" t="inlineStr">
+      <c r="D41" s="18" t="n">
+        <v>35.57680178364728</v>
+      </c>
+      <c r="E41" s="50" t="n">
+        <v>5.576801783647284</v>
+      </c>
+      <c r="F41" s="51" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="31" t="inlineStr">
-        <is>
-          <t>IEAG.L</t>
-        </is>
-      </c>
-      <c r="B40" s="18" t="n">
-        <v>64.31917363528412</v>
-      </c>
-      <c r="C40" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>64.31917363528412</v>
-      </c>
-      <c r="E40" s="50" t="n">
-        <v>-5.680826364715884</v>
-      </c>
-      <c r="F40" s="51" t="inlineStr">
-        <is>
-          <t>● Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>SOLVER PARAMETERS</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="G46" s="11" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="52" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="52" t="inlineStr">
         <is>
           <t>Alert threshold</t>
         </is>
       </c>
-      <c r="B46" s="27" t="inlineStr">
+      <c r="B47" s="27" t="inlineStr">
         <is>
           <t>±2.5%</t>
         </is>
       </c>
-      <c r="G46" s="27" t="inlineStr">
+      <c r="G47" s="27" t="inlineStr">
         <is>
           <t>Deviation at which a category turns amber (green below, red beyond 2×)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="53" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="53" t="inlineStr">
         <is>
           <t>Solver tolerance</t>
         </is>
       </c>
-      <c r="B47" s="31" t="inlineStr">
+      <c r="B48" s="31" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G47" s="31" t="inlineStr">
+      <c r="G48" s="31" t="inlineStr">
         <is>
           <t>Actual tolerance the optimizer converged at (progressive up to max)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="52" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="52" t="inlineStr">
         <is>
           <t>Max tolerance</t>
         </is>
       </c>
-      <c r="B48" s="27" t="inlineStr">
+      <c r="B49" s="27" t="inlineStr">
         <is>
           <t>±2.0%</t>
         </is>
       </c>
-      <c r="G48" s="27" t="inlineStr">
+      <c r="G49" s="27" t="inlineStr">
         <is>
           <t>Cap on solver tolerance (from config.rebalancing_max_tolerance)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="53" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="53" t="inlineStr">
         <is>
           <t>Min transaction</t>
         </is>
       </c>
-      <c r="B49" s="31" t="inlineStr">
+      <c r="B50" s="31" t="inlineStr">
         <is>
           <t>0.0 EUR</t>
         </is>
       </c>
-      <c r="G49" s="31" t="inlineStr">
+      <c r="G50" s="31" t="inlineStr">
         <is>
           <t>Trades below this amount are skipped</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="52" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="52" t="inlineStr">
         <is>
           <t>Lump sum</t>
         </is>
       </c>
-      <c r="B50" s="27" t="inlineStr">
+      <c r="B51" s="27" t="inlineStr">
         <is>
           <t>1000.0 EUR</t>
         </is>
       </c>
-      <c r="G50" s="27" t="inlineStr">
+      <c r="G51" s="27" t="inlineStr">
         <is>
           <t>Additional cash to deploy in the rebalance</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="53" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="53" t="inlineStr">
         <is>
           <t>No-sell mode</t>
         </is>
       </c>
-      <c r="B51" s="31" t="inlineStr">
+      <c r="B52" s="31" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="G51" s="31" t="inlineStr">
+      <c r="G52" s="31" t="inlineStr">
         <is>
           <t>If enabled, the solver can only buy, never sell</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="36" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-04 13:36 v2.0</t>
+    <row r="54">
+      <c r="A54" s="36" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-10 16:07 v2.0</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A44:G44"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A45:G45"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2196,25 +2229,25 @@
         <v>128</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>155.1000061035156</v>
+        <v>158.1399993896484</v>
       </c>
       <c r="J4" s="28" t="n">
         <v>10240</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>12408.00048828125</v>
+        <v>12651.19995117188</v>
       </c>
       <c r="L4" s="29" t="n">
-        <v>15.35047488934462</v>
+        <v>15.32957112517667</v>
       </c>
       <c r="M4" s="29" t="n">
-        <v>23.71354116704756</v>
+        <v>23.46521217281558</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>2168.00048828125</v>
+        <v>2411.199951171875</v>
       </c>
       <c r="O4" s="29" t="n">
-        <v>21.17187976837158</v>
+        <v>23.54687452316284</v>
       </c>
       <c r="P4" s="27" t="inlineStr">
         <is>
@@ -2233,7 +2266,7 @@
       </c>
       <c r="S4" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:36</t>
+          <t>2026-05-10 16:07</t>
         </is>
       </c>
     </row>
@@ -2275,25 +2308,25 @@
         <v>64</v>
       </c>
       <c r="I5" s="32" t="n">
-        <v>329.9318113923073</v>
+        <v>350.3561155200005</v>
       </c>
       <c r="J5" s="32" t="n">
         <v>2240</v>
       </c>
       <c r="K5" s="32" t="n">
-        <v>11547.61339873075</v>
+        <v>12262.46404320002</v>
       </c>
       <c r="L5" s="33" t="n">
-        <v>14.28605275092394</v>
+        <v>14.85853637960594</v>
       </c>
       <c r="M5" s="33" t="n">
-        <v>22.06921300257647</v>
+        <v>22.74419198540586</v>
       </c>
       <c r="N5" s="32" t="n">
-        <v>9307.613398730755</v>
+        <v>10022.46404320002</v>
       </c>
       <c r="O5" s="33" t="n">
-        <v>415.5184553004801</v>
+        <v>447.4314305000007</v>
       </c>
       <c r="P5" s="31" t="inlineStr">
         <is>
@@ -2312,7 +2345,7 @@
       </c>
       <c r="S5" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:36</t>
+          <t>2026-05-10 16:07</t>
         </is>
       </c>
     </row>
@@ -2354,25 +2387,25 @@
         <v>570</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>664.2508475627146</v>
+        <v>673.9034086954052</v>
       </c>
       <c r="J6" s="28" t="n">
         <v>8550</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>9963.762713440719</v>
+        <v>10108.55113043108</v>
       </c>
       <c r="L6" s="29" t="n">
-        <v>12.32660245947866</v>
+        <v>12.2486210102208</v>
       </c>
       <c r="M6" s="29" t="n">
-        <v>19.04223790988896</v>
+        <v>18.74915406845249</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>1413.762713440719</v>
+        <v>1558.551130431078</v>
       </c>
       <c r="O6" s="29" t="n">
-        <v>16.53523641451134</v>
+        <v>18.22866819217636</v>
       </c>
       <c r="P6" s="27" t="inlineStr">
         <is>
@@ -2391,7 +2424,7 @@
       </c>
       <c r="S6" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:36</t>
+          <t>2026-05-10 16:07</t>
         </is>
       </c>
     </row>
@@ -2433,25 +2466,25 @@
         <v>56</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>76.19400024414062</v>
+        <v>79.67600250244141</v>
       </c>
       <c r="J7" s="32" t="n">
         <v>5040</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>6857.460021972656</v>
+        <v>7170.840225219727</v>
       </c>
       <c r="L7" s="33" t="n">
-        <v>8.483660842163392</v>
+        <v>8.688970665553452</v>
       </c>
       <c r="M7" s="33" t="n">
-        <v>13.10562976573164</v>
+        <v>13.30034210126884</v>
       </c>
       <c r="N7" s="32" t="n">
-        <v>1817.460021972656</v>
+        <v>2130.840225219727</v>
       </c>
       <c r="O7" s="33" t="n">
-        <v>36.06071472167969</v>
+        <v>42.2785758972168</v>
       </c>
       <c r="P7" s="31" t="inlineStr">
         <is>
@@ -2470,7 +2503,7 @@
       </c>
       <c r="S7" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:36</t>
+          <t>2026-05-10 16:07</t>
         </is>
       </c>
     </row>
@@ -2512,25 +2545,25 @@
         <v>98</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>117.7699966430664</v>
+        <v>119.5449981689453</v>
       </c>
       <c r="J8" s="28" t="n">
         <v>4900</v>
       </c>
       <c r="K8" s="28" t="n">
-        <v>5888.49983215332</v>
+        <v>5977.249908447266</v>
       </c>
       <c r="L8" s="29" t="n">
-        <v>7.284918218269714</v>
+        <v>7.24268669834837</v>
       </c>
       <c r="M8" s="29" t="n">
-        <v>11.25380219913764</v>
+        <v>11.086492811195</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>988.4998321533203</v>
+        <v>1077.249908447266</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>20.17346596231266</v>
+        <v>21.98469200912787</v>
       </c>
       <c r="P8" s="27" t="inlineStr">
         <is>
@@ -2549,7 +2582,7 @@
       </c>
       <c r="S8" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:36</t>
+          <t>2026-05-10 16:07</t>
         </is>
       </c>
     </row>
@@ -2591,25 +2624,25 @@
         <v>33</v>
       </c>
       <c r="I9" s="32" t="n">
-        <v>47.15999984741211</v>
+        <v>47.86999893188477</v>
       </c>
       <c r="J9" s="32" t="n">
         <v>3960</v>
       </c>
       <c r="K9" s="32" t="n">
-        <v>5659.199981689453</v>
+        <v>5744.399871826172</v>
       </c>
       <c r="L9" s="33" t="n">
-        <v>7.001241440532606</v>
+        <v>6.960540244916307</v>
       </c>
       <c r="M9" s="33" t="n">
-        <v>10.81557595561772</v>
+        <v>10.65460686086223</v>
       </c>
       <c r="N9" s="32" t="n">
-        <v>1699.199981689453</v>
+        <v>1784.399871826172</v>
       </c>
       <c r="O9" s="33" t="n">
-        <v>42.90909044670336</v>
+        <v>45.06060282389323</v>
       </c>
       <c r="P9" s="31" t="inlineStr">
         <is>
@@ -2628,7 +2661,7 @@
       </c>
       <c r="S9" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:36</t>
+          <t>2026-05-10 16:07</t>
         </is>
       </c>
     </row>
@@ -2670,25 +2703,25 @@
         <v>56</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>107.1500015258789</v>
+        <v>107.5299987792969</v>
       </c>
       <c r="J10" s="28" t="n">
         <v>5600</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>10715.00015258789</v>
+        <v>10752.99987792969</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>13.25599083728018</v>
+        <v>13.02950527016769</v>
       </c>
       <c r="M10" s="29" t="n">
-        <v>64.31917363528412</v>
+        <v>64.42319821635272</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>5115.000152587891</v>
+        <v>5152.999877929688</v>
       </c>
       <c r="O10" s="29" t="n">
-        <v>91.33928843906948</v>
+        <v>92.01785496303013</v>
       </c>
       <c r="P10" s="27" t="inlineStr">
         <is>
@@ -2707,7 +2740,7 @@
       </c>
       <c r="S10" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:36</t>
+          <t>2026-05-10 16:07</t>
         </is>
       </c>
     </row>
@@ -2749,25 +2782,25 @@
         <v>105</v>
       </c>
       <c r="I11" s="32" t="n">
-        <v>148.6026787713035</v>
+        <v>148.4548096913568</v>
       </c>
       <c r="J11" s="32" t="n">
         <v>4200</v>
       </c>
       <c r="K11" s="32" t="n">
-        <v>5944.107150852142</v>
+        <v>5938.192387654271</v>
       </c>
       <c r="L11" s="33" t="n">
-        <v>7.353712441009809</v>
+        <v>7.195360354184961</v>
       </c>
       <c r="M11" s="33" t="n">
-        <v>35.68082636471589</v>
+        <v>35.57680178364728</v>
       </c>
       <c r="N11" s="32" t="n">
-        <v>1744.107150852142</v>
+        <v>1738.192387654271</v>
       </c>
       <c r="O11" s="33" t="n">
-        <v>41.5263607345748</v>
+        <v>41.38553303938742</v>
       </c>
       <c r="P11" s="31" t="inlineStr">
         <is>
@@ -2786,7 +2819,7 @@
       </c>
       <c r="S11" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:36</t>
+          <t>2026-05-10 16:07</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2870,7 @@
         <v>5000</v>
       </c>
       <c r="L12" s="29" t="n">
-        <v>6.185716588197428</v>
+        <v>6.058544321622511</v>
       </c>
       <c r="M12" s="29" t="n">
         <v>100</v>
@@ -2865,7 +2898,7 @@
       </c>
       <c r="S12" s="27" t="inlineStr">
         <is>
-          <t>2026-05-04 13:36</t>
+          <t>2026-05-10 16:07</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2920,12 @@
       </c>
       <c r="D13" s="54" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E13" s="31" t="inlineStr">
         <is>
-          <t>Commodity</t>
+          <t>Gold ETC</t>
         </is>
       </c>
       <c r="F13" s="31" t="inlineStr">
@@ -2907,25 +2940,25 @@
         <v>245</v>
       </c>
       <c r="I13" s="32" t="n">
-        <v>380.429719374426</v>
+        <v>384.5654209317945</v>
       </c>
       <c r="J13" s="32" t="n">
         <v>4410</v>
       </c>
       <c r="K13" s="32" t="n">
-        <v>6847.734948739668</v>
+        <v>6922.177576772301</v>
       </c>
       <c r="L13" s="33" t="n">
-        <v>8.471629532799646</v>
+        <v>8.387663930203299</v>
       </c>
       <c r="M13" s="33" t="n">
         <v>100</v>
       </c>
       <c r="N13" s="32" t="n">
-        <v>2437.734948739668</v>
+        <v>2512.177576772301</v>
       </c>
       <c r="O13" s="33" t="n">
-        <v>55.27743647935755</v>
+        <v>56.9654779313447</v>
       </c>
       <c r="P13" s="31" t="inlineStr">
         <is>
@@ -2944,14 +2977,14 @@
       </c>
       <c r="S13" s="31" t="inlineStr">
         <is>
-          <t>2026-05-04 13:36</t>
+          <t>2026-05-10 16:07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:36 v2.0</t>
+          <t>Generated 2026-05-10 16:07 v2.0</t>
         </is>
       </c>
     </row>
@@ -3126,43 +3159,43 @@
         </is>
       </c>
       <c r="C5" s="58" t="n">
-        <v>0.29</v>
+        <v>0.04</v>
       </c>
       <c r="D5" s="58" t="n">
-        <v>0.48</v>
+        <v>2.53</v>
       </c>
       <c r="E5" s="58" t="n">
-        <v>5.93</v>
+        <v>5.32</v>
       </c>
       <c r="F5" s="58" t="n">
-        <v>4.02</v>
+        <v>5.36</v>
       </c>
       <c r="G5" s="58" t="n">
-        <v>6.6</v>
+        <v>10.25</v>
       </c>
       <c r="H5" s="58" t="n">
-        <v>7</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I5" s="58" t="n">
-        <v>22.02</v>
+        <v>24.25</v>
       </c>
       <c r="J5" s="58" t="n">
-        <v>48.94</v>
+        <v>51.75</v>
       </c>
       <c r="K5" s="58" t="n">
-        <v>45.12</v>
+        <v>48.59</v>
       </c>
       <c r="L5" s="58" t="n">
-        <v>7.92</v>
+        <v>8.25</v>
       </c>
       <c r="M5" s="58" t="n">
-        <v>8.109999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="N5" s="58" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="O5" s="58" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="P5" s="59" t="n">
         <v>-13.91</v>
@@ -3174,7 +3207,7 @@
         <v>-1.22</v>
       </c>
       <c r="S5" s="58" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="T5" s="58" t="n">
         <v>0.15</v>
@@ -3196,44 +3229,44 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
-        <v>1.26</v>
+      <c r="C6" s="60" t="n">
+        <v>-0.02</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>1.21</v>
+        <v>1.69</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>7.53</v>
+        <v>7.02</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>4.84</v>
+        <v>6.17</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>6.67</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H6" s="29" t="n">
-        <v>7.18</v>
+        <v>9</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>25.71</v>
+        <v>26.86</v>
       </c>
       <c r="J6" s="29" t="n">
-        <v>63.96</v>
+        <v>65.69</v>
       </c>
       <c r="K6" s="29" t="n">
-        <v>73.13</v>
+        <v>74.83</v>
       </c>
       <c r="L6" s="29" t="n">
-        <v>11.62</v>
+        <v>11.84</v>
       </c>
       <c r="M6" s="29" t="n">
         <v>14.13</v>
       </c>
       <c r="N6" s="29" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="O6" s="29" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="P6" s="60" t="n">
         <v>-20.22</v>
@@ -3245,7 +3278,7 @@
         <v>-2.13</v>
       </c>
       <c r="S6" s="29" t="n">
-        <v>5.17</v>
+        <v>5.19</v>
       </c>
       <c r="T6" s="29" t="n">
         <v>0.3</v>
@@ -3267,44 +3300,44 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n">
-        <v>0.39</v>
+      <c r="C7" s="61" t="n">
+        <v>-0.15</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.66</v>
+        <v>2</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6.64</v>
+        <v>5.95</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>4.46</v>
+        <v>5.22</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>6.39</v>
+        <v>7.4</v>
       </c>
       <c r="H7" s="33" t="n">
-        <v>6.52</v>
+        <v>8.07</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>23.69</v>
+        <v>21.67</v>
       </c>
       <c r="J7" s="33" t="n">
-        <v>56.16</v>
+        <v>58.3</v>
       </c>
       <c r="K7" s="33" t="n">
-        <v>58.74</v>
+        <v>63.02</v>
       </c>
       <c r="L7" s="33" t="n">
-        <v>9.83</v>
+        <v>10.07</v>
       </c>
       <c r="M7" s="33" t="n">
         <v>15.1</v>
       </c>
       <c r="N7" s="33" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="O7" s="33" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="P7" s="61" t="n">
         <v>-20.07</v>
@@ -3316,7 +3349,7 @@
         <v>-2.13</v>
       </c>
       <c r="S7" s="61" t="n">
-        <v>-0.49</v>
+        <v>-0.74</v>
       </c>
       <c r="T7" s="33" t="n">
         <v>0.78</v>
@@ -3338,44 +3371,44 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C8" s="60" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="D8" s="60" t="n">
-        <v>-0.06</v>
+      <c r="C8" s="29" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>1.3</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>2.17</v>
+        <v>0.84</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>1.72</v>
+        <v>0.28</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>8.08</v>
+        <v>8.76</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>5.41</v>
+        <v>6.77</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>20.86</v>
+        <v>20.7</v>
       </c>
       <c r="J8" s="29" t="n">
-        <v>44.52</v>
+        <v>45.1</v>
       </c>
       <c r="K8" s="29" t="n">
-        <v>55.3</v>
+        <v>56.74</v>
       </c>
       <c r="L8" s="29" t="n">
-        <v>9.210000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="M8" s="29" t="n">
-        <v>17.99</v>
+        <v>18.03</v>
       </c>
       <c r="N8" s="29" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="P8" s="60" t="n">
         <v>-17.35</v>
@@ -3384,10 +3417,10 @@
         <v>-1.63</v>
       </c>
       <c r="R8" s="60" t="n">
-        <v>-2.43</v>
+        <v>-2.44</v>
       </c>
       <c r="S8" s="60" t="n">
-        <v>-1.39</v>
+        <v>-1.72</v>
       </c>
       <c r="T8" s="29" t="n">
         <v>0.8100000000000001</v>
@@ -3409,56 +3442,56 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C9" s="61" t="n">
-        <v>-0.16</v>
+      <c r="C9" s="33" t="n">
+        <v>1.66</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>0.22</v>
+        <v>5.4</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>10.58</v>
+        <v>11.43</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>9.289999999999999</v>
+        <v>12.62</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>14.88</v>
+        <v>21.56</v>
       </c>
       <c r="H9" s="33" t="n">
-        <v>14.24</v>
+        <v>20.4</v>
       </c>
       <c r="I9" s="33" t="n">
-        <v>44.95</v>
+        <v>49.58</v>
       </c>
       <c r="J9" s="33" t="n">
-        <v>67.23</v>
+        <v>74.2</v>
       </c>
       <c r="K9" s="33" t="n">
-        <v>37.29</v>
+        <v>46.75</v>
       </c>
       <c r="L9" s="33" t="n">
-        <v>6.55</v>
+        <v>7.98</v>
       </c>
       <c r="M9" s="33" t="n">
-        <v>20.13</v>
+        <v>20.18</v>
       </c>
       <c r="N9" s="33" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="O9" s="33" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="P9" s="61" t="n">
         <v>-24.81</v>
       </c>
       <c r="Q9" s="61" t="n">
-        <v>-1.93</v>
+        <v>-1.92</v>
       </c>
       <c r="R9" s="61" t="n">
-        <v>-2.72</v>
+        <v>-2.71</v>
       </c>
       <c r="S9" s="61" t="n">
-        <v>-3.89</v>
+        <v>-2.96</v>
       </c>
       <c r="T9" s="33" t="n">
         <v>0.79</v>
@@ -3480,44 +3513,44 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
-        <v>0.02</v>
+      <c r="C10" s="60" t="n">
+        <v>-0.01</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>0.59</v>
+        <v>1.82</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>5.97</v>
+        <v>5.44</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>3.97</v>
+        <v>4.4</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>5.08</v>
+        <v>5.88</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>5.36</v>
+        <v>6.67</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>21.74</v>
+        <v>19.44</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>55.69</v>
+        <v>57.46</v>
       </c>
       <c r="K10" s="29" t="n">
-        <v>63.3</v>
+        <v>67.3</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>10.47</v>
+        <v>10.65</v>
       </c>
       <c r="M10" s="29" t="n">
         <v>16.47</v>
       </c>
       <c r="N10" s="29" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="O10" s="29" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="P10" s="60" t="n">
         <v>-20.63</v>
@@ -3529,7 +3562,7 @@
         <v>-2.29</v>
       </c>
       <c r="S10" s="60" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.93</v>
       </c>
       <c r="T10" s="29" t="n">
         <v>0.86</v>
@@ -3552,55 +3585,55 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>0.01</v>
+        <v>2.32</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>1.1</v>
+        <v>5.32</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>14.71</v>
+        <v>15.22</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>11.58</v>
+        <v>17.7</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>10.92</v>
+        <v>17.4</v>
       </c>
       <c r="H11" s="33" t="n">
-        <v>13.11</v>
+        <v>19.13</v>
       </c>
       <c r="I11" s="33" t="n">
-        <v>31.19</v>
+        <v>34.05</v>
       </c>
       <c r="J11" s="33" t="n">
-        <v>95.37</v>
+        <v>106.05</v>
       </c>
       <c r="K11" s="33" t="n">
-        <v>81.36</v>
+        <v>100.48</v>
       </c>
       <c r="L11" s="33" t="n">
-        <v>12.66</v>
+        <v>14.94</v>
       </c>
       <c r="M11" s="33" t="n">
-        <v>21.97</v>
+        <v>22</v>
       </c>
       <c r="N11" s="33" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="O11" s="33" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="P11" s="61" t="n">
         <v>-25.91</v>
       </c>
       <c r="Q11" s="61" t="n">
-        <v>-2.26</v>
+        <v>-2.25</v>
       </c>
       <c r="R11" s="61" t="n">
-        <v>-3.15</v>
+        <v>-3.13</v>
       </c>
       <c r="S11" s="33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T11" s="33" t="n">
         <v>1.06</v>
@@ -3622,44 +3655,44 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C12" s="60" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="D12" s="60" t="n">
-        <v>-0.5</v>
+      <c r="C12" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>1.06</v>
       </c>
       <c r="E12" s="29" t="n">
-        <v>6.05</v>
+        <v>4.81</v>
       </c>
       <c r="F12" s="29" t="n">
-        <v>2.94</v>
+        <v>3.67</v>
       </c>
       <c r="G12" s="29" t="n">
-        <v>4.41</v>
+        <v>5.72</v>
       </c>
       <c r="H12" s="29" t="n">
-        <v>4.41</v>
+        <v>5.52</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>19.24</v>
+        <v>18.85</v>
       </c>
       <c r="J12" s="29" t="n">
-        <v>60.57</v>
+        <v>63.51</v>
       </c>
       <c r="K12" s="29" t="n">
-        <v>76.41</v>
+        <v>79.73</v>
       </c>
       <c r="L12" s="29" t="n">
-        <v>12.04</v>
+        <v>12.46</v>
       </c>
       <c r="M12" s="29" t="n">
-        <v>18.91</v>
+        <v>18.9</v>
       </c>
       <c r="N12" s="29" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="O12" s="29" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="P12" s="60" t="n">
         <v>-22.45</v>
@@ -3671,7 +3704,7 @@
         <v>-2.66</v>
       </c>
       <c r="S12" s="60" t="n">
-        <v>-0.13</v>
+        <v>-0.34</v>
       </c>
       <c r="T12" s="29" t="n">
         <v>1</v>
@@ -3694,55 +3727,55 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.98</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>1.1</v>
+        <v>4.96</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>13.84</v>
+        <v>16.37</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>8.76</v>
+        <v>16.05</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>4.86</v>
+        <v>11.77</v>
       </c>
       <c r="H13" s="33" t="n">
-        <v>10.14</v>
+        <v>15.6</v>
       </c>
       <c r="I13" s="33" t="n">
-        <v>35.22</v>
+        <v>39.74</v>
       </c>
       <c r="J13" s="33" t="n">
-        <v>97.62</v>
+        <v>106.55</v>
       </c>
       <c r="K13" s="33" t="n">
-        <v>106.49</v>
+        <v>125.92</v>
       </c>
       <c r="L13" s="33" t="n">
-        <v>15.63</v>
+        <v>17.73</v>
       </c>
       <c r="M13" s="33" t="n">
-        <v>23.9</v>
+        <v>23.87</v>
       </c>
       <c r="N13" s="33" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="O13" s="33" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="P13" s="61" t="n">
         <v>-31.38</v>
       </c>
       <c r="Q13" s="61" t="n">
-        <v>-2.45</v>
+        <v>-2.43</v>
       </c>
       <c r="R13" s="61" t="n">
-        <v>-3.4</v>
+        <v>-3.39</v>
       </c>
       <c r="S13" s="33" t="n">
-        <v>1.59</v>
+        <v>2.93</v>
       </c>
       <c r="T13" s="33" t="n">
         <v>1.23</v>
@@ -3764,56 +3797,56 @@
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C14" s="60" t="n">
-        <v>-0.09</v>
+      <c r="C14" s="29" t="n">
+        <v>0.48</v>
       </c>
       <c r="D14" s="29" t="n">
-        <v>0.52</v>
+        <v>1.81</v>
       </c>
       <c r="E14" s="29" t="n">
-        <v>8.51</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="F14" s="29" t="n">
-        <v>4.7</v>
+        <v>6.56</v>
       </c>
       <c r="G14" s="29" t="n">
-        <v>3.71</v>
+        <v>6.03</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>5.61</v>
+        <v>7.52</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>24.57</v>
+        <v>25.28</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>64.14</v>
+        <v>67.53</v>
       </c>
       <c r="K14" s="29" t="n">
-        <v>77.33</v>
+        <v>82.37</v>
       </c>
       <c r="L14" s="29" t="n">
-        <v>12.15</v>
+        <v>12.79</v>
       </c>
       <c r="M14" s="29" t="n">
-        <v>18.56</v>
+        <v>18.55</v>
       </c>
       <c r="N14" s="29" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="O14" s="29" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="P14" s="60" t="n">
         <v>-23.17</v>
       </c>
       <c r="Q14" s="60" t="n">
-        <v>-1.87</v>
+        <v>-1.86</v>
       </c>
       <c r="R14" s="60" t="n">
         <v>-2.64</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" s="29" t="n">
         <v>1</v>
@@ -3835,44 +3868,44 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="61" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="E15" s="33" t="n">
-        <v>0.38</v>
+      <c r="C15" s="61" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E15" s="61" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F15" s="61" t="n">
-        <v>-0.8</v>
+        <v>-0.58</v>
       </c>
       <c r="G15" s="61" t="n">
-        <v>-0.64</v>
+        <v>-0.31</v>
       </c>
       <c r="H15" s="33" t="n">
-        <v>0.09</v>
+        <v>0.44</v>
       </c>
       <c r="I15" s="33" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="J15" s="33" t="n">
-        <v>7.86</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="K15" s="61" t="n">
-        <v>-8.98</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L15" s="61" t="n">
-        <v>-1.87</v>
+        <v>-1.73</v>
       </c>
       <c r="M15" s="33" t="n">
         <v>5.55</v>
       </c>
       <c r="N15" s="61" t="n">
-        <v>-1.06</v>
+        <v>-1.03</v>
       </c>
       <c r="O15" s="61" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="P15" s="61" t="n">
         <v>-19.81</v>
@@ -3884,7 +3917,7 @@
         <v>-0.77</v>
       </c>
       <c r="S15" s="61" t="n">
-        <v>-6</v>
+        <v>-5.88</v>
       </c>
       <c r="T15" s="33" t="n">
         <v>0.02</v>
@@ -3898,7 +3931,7 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
@@ -3906,59 +3939,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="60" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E16" s="29" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="F16" s="29" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="G16" s="29" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="H16" s="29" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="J16" s="29" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="K16" s="29" t="n">
+        <v>77.81</v>
+      </c>
+      <c r="L16" s="29" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="M16" s="29" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="N16" s="29" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="O16" s="29" t="n">
         <v>0.74</v>
       </c>
-      <c r="D16" s="29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E16" s="29" t="n">
-        <v>7.77</v>
-      </c>
-      <c r="F16" s="29" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="G16" s="29" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="H16" s="29" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="I16" s="29" t="n">
-        <v>24.64</v>
-      </c>
-      <c r="J16" s="29" t="n">
-        <v>62.83</v>
-      </c>
-      <c r="K16" s="29" t="n">
-        <v>70.31</v>
-      </c>
-      <c r="L16" s="29" t="n">
-        <v>11.53</v>
-      </c>
-      <c r="M16" s="29" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="N16" s="29" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O16" s="29" t="n">
-        <v>0.7</v>
-      </c>
       <c r="P16" s="60" t="n">
-        <v>-21.07</v>
+        <v>-21.73</v>
       </c>
       <c r="Q16" s="60" t="n">
-        <v>-1.39</v>
+        <v>-1.45</v>
       </c>
       <c r="R16" s="60" t="n">
-        <v>-2.13</v>
+        <v>-2.19</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>5.92</v>
+        <v>6.28</v>
       </c>
       <c r="T16" s="29" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="U16" s="27" t="inlineStr">
         <is>
@@ -3969,7 +4002,7 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
@@ -3978,58 +4011,58 @@
         </is>
       </c>
       <c r="C17" s="33" t="n">
-        <v>1.87</v>
+        <v>0.1</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>1.45</v>
+        <v>2.32</v>
       </c>
       <c r="E17" s="33" t="n">
-        <v>12.64</v>
+        <v>6.79</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>8.94</v>
+        <v>6.46</v>
       </c>
       <c r="G17" s="33" t="n">
-        <v>16.56</v>
+        <v>9.41</v>
       </c>
       <c r="H17" s="33" t="n">
-        <v>16.16</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>40.77</v>
+        <v>26.51</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>68.70999999999999</v>
+        <v>65</v>
       </c>
       <c r="K17" s="33" t="n">
-        <v>42.17</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="L17" s="33" t="n">
-        <v>7.57</v>
+        <v>11.7</v>
       </c>
       <c r="M17" s="33" t="n">
-        <v>18.83</v>
+        <v>13.8</v>
       </c>
       <c r="N17" s="33" t="n">
-        <v>0.19</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O17" s="33" t="n">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
       <c r="P17" s="61" t="n">
-        <v>-24.38</v>
+        <v>-21.07</v>
       </c>
       <c r="Q17" s="61" t="n">
-        <v>-1.59</v>
+        <v>-1.39</v>
       </c>
       <c r="R17" s="61" t="n">
-        <v>-2.59</v>
+        <v>-2.13</v>
       </c>
       <c r="S17" s="33" t="n">
-        <v>2.75</v>
+        <v>5.98</v>
       </c>
       <c r="T17" s="33" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="U17" s="31" t="inlineStr">
         <is>
@@ -4040,7 +4073,7 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
@@ -4048,59 +4081,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C18" s="60" t="n">
-        <v>-0.09</v>
+      <c r="C18" s="29" t="n">
+        <v>0.68</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>1.16</v>
+        <v>4.83</v>
       </c>
       <c r="E18" s="29" t="n">
-        <v>8.83</v>
+        <v>11.75</v>
       </c>
       <c r="F18" s="29" t="n">
-        <v>5.43</v>
+        <v>13.25</v>
       </c>
       <c r="G18" s="29" t="n">
-        <v>4.81</v>
+        <v>22.39</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>6.41</v>
+        <v>21.47</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>25.3</v>
+        <v>48.97</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>70.91</v>
+        <v>75.97</v>
       </c>
       <c r="K18" s="29" t="n">
-        <v>88.41</v>
+        <v>50.05</v>
       </c>
       <c r="L18" s="29" t="n">
-        <v>13.83</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M18" s="29" t="n">
-        <v>17.29</v>
+        <v>18.84</v>
       </c>
       <c r="N18" s="29" t="n">
-        <v>0.57</v>
+        <v>0.24</v>
       </c>
       <c r="O18" s="29" t="n">
-        <v>0.79</v>
+        <v>0.32</v>
       </c>
       <c r="P18" s="60" t="n">
-        <v>-22.73</v>
+        <v>-24.38</v>
       </c>
       <c r="Q18" s="60" t="n">
-        <v>-1.73</v>
+        <v>-1.58</v>
       </c>
       <c r="R18" s="60" t="n">
-        <v>-2.53</v>
+        <v>-2.58</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>6.37</v>
+        <v>3.59</v>
       </c>
       <c r="T18" s="29" t="n">
-        <v>0.42</v>
+        <v>0.1</v>
       </c>
       <c r="U18" s="27" t="inlineStr">
         <is>
@@ -4111,7 +4144,7 @@
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
@@ -4119,59 +4152,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C19" s="33" t="n">
-        <v>0.63</v>
+      <c r="C19" s="61" t="n">
+        <v>-0.17</v>
       </c>
       <c r="D19" s="33" t="n">
-        <v>0.98</v>
+        <v>1.36</v>
       </c>
       <c r="E19" s="33" t="n">
-        <v>7.33</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F19" s="33" t="n">
-        <v>4.25</v>
+        <v>6.68</v>
       </c>
       <c r="G19" s="33" t="n">
-        <v>5.4</v>
+        <v>7.3</v>
       </c>
       <c r="H19" s="33" t="n">
-        <v>5.79</v>
+        <v>7.95</v>
       </c>
       <c r="I19" s="33" t="n">
-        <v>22.96</v>
+        <v>25.92</v>
       </c>
       <c r="J19" s="33" t="n">
-        <v>62.67</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="K19" s="33" t="n">
-        <v>75.13</v>
+        <v>91.22</v>
       </c>
       <c r="L19" s="33" t="n">
-        <v>12.17</v>
+        <v>13.86</v>
       </c>
       <c r="M19" s="33" t="n">
-        <v>14.24</v>
+        <v>17.28</v>
       </c>
       <c r="N19" s="33" t="n">
         <v>0.57</v>
       </c>
       <c r="O19" s="33" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="P19" s="61" t="n">
-        <v>-21.73</v>
+        <v>-22.73</v>
       </c>
       <c r="Q19" s="61" t="n">
-        <v>-1.45</v>
+        <v>-1.73</v>
       </c>
       <c r="R19" s="61" t="n">
-        <v>-2.19</v>
+        <v>-2.53</v>
       </c>
       <c r="S19" s="33" t="n">
-        <v>6.36</v>
+        <v>6.14</v>
       </c>
       <c r="T19" s="33" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="U19" s="31" t="inlineStr">
         <is>
@@ -4190,56 +4223,56 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
-        <v>0.31</v>
+      <c r="C20" s="60" t="n">
+        <v>-0.15</v>
       </c>
       <c r="D20" s="60" t="n">
-        <v>-0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="E20" s="60" t="n">
-        <v>-1.11</v>
+        <v>-0.83</v>
       </c>
       <c r="F20" s="29" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="G20" s="60" t="n">
         <v>-1.55</v>
       </c>
-      <c r="H20" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I20" s="60" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="J20" s="60" t="n">
-        <v>-0.82</v>
+      <c r="H20" s="60" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J20" s="29" t="n">
+        <v>0.08</v>
       </c>
       <c r="K20" s="60" t="n">
-        <v>-1.61</v>
+        <v>-0.1</v>
       </c>
       <c r="L20" s="60" t="n">
-        <v>-0.33</v>
+        <v>-0.02</v>
       </c>
       <c r="M20" s="29" t="n">
-        <v>10.65</v>
+        <v>10.62</v>
       </c>
       <c r="N20" s="60" t="n">
-        <v>-0.41</v>
+        <v>-0.38</v>
       </c>
       <c r="O20" s="60" t="n">
-        <v>-0.61</v>
+        <v>-0.57</v>
       </c>
       <c r="P20" s="60" t="n">
         <v>-15.77</v>
       </c>
       <c r="Q20" s="60" t="n">
-        <v>-1.1</v>
+        <v>-1.09</v>
       </c>
       <c r="R20" s="60" t="n">
         <v>-1.48</v>
       </c>
       <c r="S20" s="60" t="n">
-        <v>-4.14</v>
+        <v>-3.83</v>
       </c>
       <c r="T20" s="60" t="n">
         <v>-0.02</v>
@@ -4262,43 +4295,43 @@
         </is>
       </c>
       <c r="C21" s="61" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="D21" s="61" t="n">
-        <v>-2.09</v>
+        <v>-1.08</v>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>1.09</v>
       </c>
       <c r="E21" s="61" t="n">
-        <v>-4.21</v>
-      </c>
-      <c r="F21" s="33" t="n">
-        <v>0.51</v>
+        <v>-1.87</v>
+      </c>
+      <c r="F21" s="61" t="n">
+        <v>-6.82</v>
       </c>
       <c r="G21" s="33" t="n">
-        <v>13.93</v>
+        <v>12.57</v>
       </c>
       <c r="H21" s="33" t="n">
-        <v>7.54</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="I21" s="33" t="n">
-        <v>39.11</v>
+        <v>35</v>
       </c>
       <c r="J21" s="33" t="n">
-        <v>114.75</v>
+        <v>116.16</v>
       </c>
       <c r="K21" s="33" t="n">
-        <v>165.56</v>
+        <v>162.76</v>
       </c>
       <c r="L21" s="33" t="n">
-        <v>21.61</v>
+        <v>21.34</v>
       </c>
       <c r="M21" s="33" t="n">
-        <v>17.9</v>
+        <v>17.92</v>
       </c>
       <c r="N21" s="33" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="O21" s="33" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P21" s="61" t="n">
         <v>-15.94</v>
@@ -4310,7 +4343,7 @@
         <v>-2.57</v>
       </c>
       <c r="S21" s="33" t="n">
-        <v>17.05</v>
+        <v>16.71</v>
       </c>
       <c r="T21" s="33" t="n">
         <v>0.07000000000000001</v>
@@ -4324,7 +4357,7 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
+          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
@@ -4332,59 +4365,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
-        <v>0.04</v>
+      <c r="C22" s="60" t="n">
+        <v>-0.49</v>
       </c>
       <c r="D22" s="29" t="n">
-        <v>0.93</v>
+        <v>2.47</v>
       </c>
       <c r="E22" s="29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F22" s="29" t="n">
-        <v>10.93</v>
+        <v>1.42</v>
+      </c>
+      <c r="F22" s="60" t="n">
+        <v>-0.48</v>
       </c>
       <c r="G22" s="29" t="n">
-        <v>10.3</v>
+        <v>8.51</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>17.9</v>
+        <v>3.65</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>44.84</v>
+        <v>16.35</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>73.92</v>
+        <v>42.11</v>
       </c>
       <c r="K22" s="29" t="n">
-        <v>57.6</v>
+        <v>55.61</v>
       </c>
       <c r="L22" s="29" t="n">
-        <v>9.539999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="M22" s="29" t="n">
-        <v>18.27</v>
+        <v>14.99</v>
       </c>
       <c r="N22" s="29" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="O22" s="29" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="P22" s="60" t="n">
-        <v>-21.24</v>
+        <v>-22.86</v>
       </c>
       <c r="Q22" s="60" t="n">
-        <v>-1.78</v>
+        <v>-1.53</v>
       </c>
       <c r="R22" s="60" t="n">
-        <v>-2.5</v>
+        <v>-2.22</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="T22" s="29" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="U22" s="27" t="inlineStr">
         <is>
@@ -4395,7 +4428,7 @@
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
+          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
       <c r="B23" s="31" t="inlineStr">
@@ -4403,59 +4436,59 @@
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C23" s="61" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="D23" s="61" t="n">
-        <v>-0.04</v>
+      <c r="C23" s="33" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>6.19</v>
       </c>
       <c r="E23" s="33" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="F23" s="61" t="n">
-        <v>-1.13</v>
+        <v>12.14</v>
+      </c>
+      <c r="F23" s="33" t="n">
+        <v>12.06</v>
       </c>
       <c r="G23" s="33" t="n">
-        <v>7.03</v>
+        <v>20.84</v>
       </c>
       <c r="H23" s="33" t="n">
-        <v>2.11</v>
+        <v>25.2</v>
       </c>
       <c r="I23" s="33" t="n">
-        <v>14.35</v>
+        <v>51.96</v>
       </c>
       <c r="J23" s="33" t="n">
-        <v>40.11</v>
+        <v>80.48</v>
       </c>
       <c r="K23" s="33" t="n">
-        <v>54.43</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="L23" s="33" t="n">
-        <v>9.49</v>
+        <v>10.46</v>
       </c>
       <c r="M23" s="33" t="n">
-        <v>14.94</v>
+        <v>18.31</v>
       </c>
       <c r="N23" s="33" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="O23" s="33" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="P23" s="61" t="n">
-        <v>-22.86</v>
+        <v>-21.24</v>
       </c>
       <c r="Q23" s="61" t="n">
-        <v>-1.53</v>
+        <v>-1.78</v>
       </c>
       <c r="R23" s="61" t="n">
-        <v>-2.22</v>
+        <v>-2.5</v>
       </c>
       <c r="S23" s="33" t="n">
-        <v>4.07</v>
+        <v>4.17</v>
       </c>
       <c r="T23" s="33" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="U23" s="31" t="inlineStr">
         <is>
@@ -4793,7 +4826,7 @@
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
         <is>
-          <t>Generated 2026-05-04 13:36 v2.0</t>
+          <t>Generated 2026-05-10 16:07 v2.0</t>
         </is>
       </c>
     </row>
@@ -4888,13 +4921,13 @@
         </is>
       </c>
       <c r="D5" s="29" t="n">
-        <v>14.28605275092394</v>
+        <v>14.85853637960594</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>415.5184553004801</v>
+        <v>447.4314305000007</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>59.3611857140509</v>
+        <v>66.48176187463385</v>
       </c>
     </row>
     <row r="6">
@@ -4914,13 +4947,13 @@
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>13.25599083728018</v>
+        <v>13.02950527016769</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>91.33928843906948</v>
+        <v>92.01785496303013</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>12.10792770631996</v>
+        <v>11.98947126190327</v>
       </c>
     </row>
     <row r="7">
@@ -4940,117 +4973,117 @@
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>8.471629532799646</v>
+        <v>8.387663930203299</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>55.27743647935755</v>
+        <v>56.9654779313447</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>4.68289963375982</v>
+        <v>4.77807284511532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>IE00B3RBWM25</t>
+          <t>LU0292107645</t>
         </is>
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>XMME.DE</t>
         </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>15.35047488934462</v>
+        <v>8.688970665553452</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>21.17187976837158</v>
+        <v>42.2785758972168</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.249984087446114</v>
+        <v>3.67357305752292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>LU0292107645</t>
+          <t>IE00B3RBWM25</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>XMME.DE</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="D9" s="29" t="n">
-        <v>8.483660842163392</v>
+        <v>15.32957112517667</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>36.06071472167969</v>
+        <v>23.54687452316284</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>3.059268734247389</v>
+        <v>3.609634877784353</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
+          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>IE00B1FZS798</t>
+          <t>IE00B945VV12</t>
         </is>
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>IBTM.L</t>
+          <t>VERX.DE</t>
         </is>
       </c>
       <c r="D10" s="33" t="n">
-        <v>7.353712441009809</v>
+        <v>6.960540244916307</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>41.5263607345748</v>
+        <v>45.06060282389323</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>3.053729155637039</v>
+        <v>3.136461394158983</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
+          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>IE00B945VV12</t>
+          <t>IE00B1FZS798</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>VERX.DE</t>
+          <t>IBTM.L</t>
         </is>
       </c>
       <c r="D11" s="29" t="n">
-        <v>7.001241440532606</v>
+        <v>7.195360354184961</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>42.90909044670336</v>
+        <v>41.38553303938742</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>3.004169022110213</v>
+        <v>2.977838236684201</v>
       </c>
     </row>
     <row r="12">
@@ -5070,13 +5103,13 @@
         </is>
       </c>
       <c r="D12" s="33" t="n">
-        <v>12.32660245947866</v>
+        <v>12.2486210102208</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.53523641451134</v>
+        <v>18.22866819217636</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>2.038232858551765</v>
+        <v>2.23276048207035</v>
       </c>
     </row>
     <row r="13">
@@ -5096,13 +5129,13 @@
         </is>
       </c>
       <c r="D13" s="29" t="n">
-        <v>7.284918218269714</v>
+        <v>7.24268669834837</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>20.17346596231266</v>
+        <v>21.98469200912787</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>1.469620497144954</v>
+        <v>1.592282363817961</v>
       </c>
     </row>
     <row r="14">
@@ -5122,7 +5155,7 @@
         </is>
       </c>
       <c r="D14" s="33" t="n">
-        <v>6.185716588197428</v>
+        <v>6.058544321622511</v>
       </c>
       <c r="E14" s="33" t="n">
         <v>0</v>
@@ -5167,10 +5200,10 @@
         </is>
       </c>
       <c r="B18" s="28" t="n">
-        <v>52324.53643626816</v>
+        <v>53914.70513029613</v>
       </c>
       <c r="C18" s="29" t="n">
-        <v>92.06147376900979</v>
+        <v>99.7551406575963</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>6</v>
@@ -5183,10 +5216,10 @@
         </is>
       </c>
       <c r="B19" s="32" t="n">
-        <v>16659.10730344003</v>
+        <v>16691.19226558396</v>
       </c>
       <c r="C19" s="33" t="n">
-        <v>66.43282458682214</v>
+        <v>66.70169400120878</v>
       </c>
       <c r="D19" s="31" t="n">
         <v>2</v>
@@ -5195,21 +5228,21 @@
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="B20" s="28" t="n">
-        <v>6847.734948739668</v>
+        <v>6922.177576772301</v>
       </c>
       <c r="C20" s="29" t="n">
-        <v>55.27743647935755</v>
+        <v>56.9654779313447</v>
       </c>
       <c r="D20" s="27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Equivalents</t>
         </is>
@@ -5255,23 +5288,23 @@
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>41.79516167143485</v>
+        <v>41.22858361399044</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>19.29352738173186</v>
+        <v>21.25341157482235</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="54" t="inlineStr">
+      <c r="A26" s="65" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
       <c r="B26" s="33" t="n">
-        <v>15.50544013183685</v>
+        <v>15.67502157315777</v>
       </c>
       <c r="C26" s="33" t="n">
-        <v>28.61629724502563</v>
+        <v>32.91272521018982</v>
       </c>
     </row>
     <row r="27">
@@ -5281,10 +5314,10 @@
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>9.768936068831742</v>
+        <v>9.631770299638772</v>
       </c>
       <c r="C27" s="29" t="n">
-        <v>28.0848120591292</v>
+        <v>30.19738978539465</v>
       </c>
     </row>
     <row r="28">
@@ -5294,10 +5327,10 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>24.19321790615446</v>
+        <v>24.84297679518155</v>
       </c>
       <c r="C28" s="33" t="n">
-        <v>152.2879336770548</v>
+        <v>164.3209990107638</v>
       </c>
     </row>
     <row r="29">
@@ -5307,10 +5340,10 @@
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>8.737244221742097</v>
+        <v>8.621647718031447</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>28.0848120591292</v>
+        <v>30.19738978539465</v>
       </c>
     </row>
   </sheetData>

--- a/output/sample/portfolio_dashboard_sample.xlsx
+++ b/output/sample/portfolio_dashboard_sample.xlsx
@@ -82,7 +82,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0016A34A"/>
+      <color rgb="00D97706"/>
       <sz val="10"/>
     </font>
     <font>
@@ -100,7 +100,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00D97706"/>
+      <color rgb="00DC2626"/>
       <sz val="10"/>
     </font>
     <font>
@@ -113,12 +113,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0015803D"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00DC2626"/>
       <sz val="10"/>
     </font>
     <font>
@@ -160,6 +154,12 @@
       <i val="1"/>
       <color rgb="0064748B"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0016A34A"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -258,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -296,7 +296,7 @@
     <xf numFmtId="2" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -308,49 +308,46 @@
     <xf numFmtId="2" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -359,11 +356,11 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -379,28 +376,28 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -412,17 +409,17 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="22" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="24" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -434,13 +431,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -954,7 +951,7 @@
         <v>65.32892612382153</v>
       </c>
       <c r="C12" s="14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="12" t="inlineStr">
@@ -979,7 +976,7 @@
         <v>20.22486562435265</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="19" t="inlineStr">
@@ -987,7 +984,7 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="17" t="n">
         <v>24.84297679518155</v>
       </c>
       <c r="G13" s="18" t="n">
@@ -995,24 +992,24 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="13" t="n">
         <v>8.387663930203299</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>5</v>
       </c>
       <c r="D14" s="2" t="n"/>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="13" t="n">
         <v>15.67502157315777</v>
       </c>
       <c r="G14" s="14" t="n">
@@ -1020,7 +1017,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Equivalents</t>
         </is>
@@ -1029,7 +1026,7 @@
         <v>6.058544321622511</v>
       </c>
       <c r="C15" s="18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="16" t="inlineStr">
@@ -1037,7 +1034,7 @@
           <t>Eurozone EMU</t>
         </is>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="23" t="n">
         <v>9.631770299638772</v>
       </c>
       <c r="G15" s="18" t="n">
@@ -1046,12 +1043,12 @@
     </row>
     <row r="16">
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>Dev ex-USA ex-EMU ex-JP</t>
         </is>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="13" t="n">
         <v>8.621647718031447</v>
       </c>
       <c r="G16" s="14" t="n">
@@ -1094,7 +1091,7 @@
           <t>Weight %</t>
         </is>
       </c>
-      <c r="D20" s="26" t="n"/>
+      <c r="D20" s="25" t="n"/>
       <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Class</t>
@@ -1102,18 +1099,18 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
-      <c r="B21" s="28" t="n">
+      <c r="B21" s="27" t="n">
         <v>12651.19995117188</v>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="28" t="n">
         <v>15.32957112517667</v>
       </c>
-      <c r="D21" s="30" t="n"/>
+      <c r="D21" s="29" t="n"/>
       <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Equities</t>
@@ -1121,75 +1118,75 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
-      <c r="B22" s="32" t="n">
+      <c r="B22" s="31" t="n">
         <v>12262.46404320002</v>
       </c>
-      <c r="C22" s="33" t="n">
+      <c r="C22" s="32" t="n">
         <v>14.85853637960594</v>
       </c>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="34" t="inlineStr">
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
         </is>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="27" t="n">
         <v>10752.99987792969</v>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="28" t="n">
         <v>13.02950527016769</v>
       </c>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="35" t="inlineStr">
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="34" t="inlineStr">
         <is>
           <t>Fixed Income</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
-      <c r="B24" s="32" t="n">
+      <c r="B24" s="31" t="n">
         <v>10108.55113043108</v>
       </c>
-      <c r="C24" s="33" t="n">
+      <c r="C24" s="32" t="n">
         <v>12.2486210102208</v>
       </c>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="34" t="inlineStr">
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="27" t="n">
         <v>7170.840225219727</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="28" t="n">
         <v>8.688970665553452</v>
       </c>
-      <c r="D25" s="30" t="n"/>
+      <c r="D25" s="29" t="n"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Equities</t>
@@ -1200,9 +1197,9 @@
       <c r="D26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="36" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-10 16:07 v2.0</t>
+      <c r="A27" s="35" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-10 16:30 v2.0</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1240,7 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>●  Action needed — largest deviation 16.8% (&gt;5.0%). Rebalancing recommended.</t>
         </is>
@@ -1283,14 +1280,14 @@
       <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>Status color based on delta after rebalancing vs target. Threshold ±2.5% (green), ±5.0% (amber), beyond (red).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>Asset Allocation</t>
         </is>
@@ -1329,127 +1326,125 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>Cash &amp; Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>6.058544321622511</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="26" t="inlineStr"/>
+      <c r="E14" s="39" t="n">
+        <v>6.058544321622511</v>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>● Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>Fixed Income</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B15" s="18" t="n">
         <v>20.22486562435265</v>
       </c>
-      <c r="C14" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="D14" s="14" t="n">
+      <c r="C15" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="D15" s="18" t="n">
         <v>20.22486562435265</v>
       </c>
-      <c r="E14" s="40" t="n">
-        <v>-4.775134375647347</v>
-      </c>
-      <c r="F14" s="41" t="inlineStr">
+      <c r="E15" s="41" t="n">
+        <v>-5.775134375647347</v>
+      </c>
+      <c r="F15" s="42" t="inlineStr">
+        <is>
+          <t>● Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>8.387663930203299</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>8.387663930203299</v>
+      </c>
+      <c r="E16" s="43" t="n">
+        <v>3.387663930203299</v>
+      </c>
+      <c r="F16" s="44" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="n">
-        <v>8.387663930203299</v>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>8.387663930203299</v>
-      </c>
-      <c r="E15" s="42" t="n">
-        <v>3.387663930203299</v>
-      </c>
-      <c r="F15" s="43" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>Equities</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>65.32892612382153</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>68</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>65.32892612382153</v>
+      </c>
+      <c r="E17" s="45" t="n">
+        <v>-2.671073876178468</v>
+      </c>
+      <c r="F17" s="46" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>Cash &amp; Cash Equivalents</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>6.058544321622511</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>6.058544321622511</v>
-      </c>
-      <c r="E16" s="40" t="n">
-        <v>3.058544321622511</v>
-      </c>
-      <c r="F16" s="41" t="inlineStr">
-        <is>
-          <t>● Drift</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B18" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="18" t="n">
+      <c r="C18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="44" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F17" s="45" t="inlineStr">
+      <c r="E18" s="47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F18" s="48" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>Equities</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>65.32892612382153</v>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>65</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>65.32892612382153</v>
-      </c>
-      <c r="E18" s="46" t="n">
-        <v>0.3289261238215317</v>
-      </c>
-      <c r="F18" s="47" t="inlineStr">
-        <is>
-          <t>● Aligned</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
@@ -1463,17 +1458,17 @@
       <c r="D19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="44" t="n">
+      <c r="E19" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="45" t="inlineStr">
+      <c r="F19" s="50" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="38" t="inlineStr">
         <is>
           <t>Geography (equity only)</t>
         </is>
@@ -1512,7 +1507,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
@@ -1526,17 +1521,17 @@
       <c r="D23" s="14" t="n">
         <v>24.84297679518155</v>
       </c>
-      <c r="E23" s="48" t="n">
+      <c r="E23" s="39" t="n">
         <v>16.84297679518155</v>
       </c>
-      <c r="F23" s="49" t="inlineStr">
+      <c r="F23" s="40" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
@@ -1550,17 +1545,17 @@
       <c r="D24" s="18" t="n">
         <v>41.22858361399044</v>
       </c>
-      <c r="E24" s="50" t="n">
+      <c r="E24" s="41" t="n">
         <v>-13.77141638600956</v>
       </c>
-      <c r="F24" s="51" t="inlineStr">
+      <c r="F24" s="42" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
@@ -1574,17 +1569,17 @@
       <c r="D25" s="14" t="n">
         <v>15.67502157315778</v>
       </c>
-      <c r="E25" s="40" t="n">
+      <c r="E25" s="43" t="n">
         <v>4.675021573157776</v>
       </c>
-      <c r="F25" s="41" t="inlineStr">
+      <c r="F25" s="44" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>Eurozone EMU</t>
         </is>
@@ -1598,17 +1593,17 @@
       <c r="D26" s="18" t="n">
         <v>9.631770299638774</v>
       </c>
-      <c r="E26" s="42" t="n">
+      <c r="E26" s="45" t="n">
         <v>-4.368229700361226</v>
       </c>
-      <c r="F26" s="43" t="inlineStr">
+      <c r="F26" s="46" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>Dev ex-USA ex-EMU ex-JP</t>
         </is>
@@ -1622,17 +1617,17 @@
       <c r="D27" s="14" t="n">
         <v>8.621647718031449</v>
       </c>
-      <c r="E27" s="40" t="n">
+      <c r="E27" s="43" t="n">
         <v>-3.378352281968551</v>
       </c>
-      <c r="F27" s="41" t="inlineStr">
+      <c r="F27" s="44" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>Per-Holding Equity Targets</t>
         </is>
@@ -1671,7 +1666,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>CNKY.L</t>
         </is>
@@ -1685,17 +1680,17 @@
       <c r="D31" s="14" t="n">
         <v>22.74419198540586</v>
       </c>
-      <c r="E31" s="48" t="n">
+      <c r="E31" s="39" t="n">
         <v>12.74419198540586</v>
       </c>
-      <c r="F31" s="49" t="inlineStr">
+      <c r="F31" s="40" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>VERX.DE</t>
         </is>
@@ -1709,17 +1704,17 @@
       <c r="D32" s="18" t="n">
         <v>10.65460686086223</v>
       </c>
-      <c r="E32" s="42" t="n">
+      <c r="E32" s="45" t="n">
         <v>-4.345393139137771</v>
       </c>
-      <c r="F32" s="43" t="inlineStr">
+      <c r="F32" s="46" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>EUNL.DE</t>
         </is>
@@ -1733,17 +1728,17 @@
       <c r="D33" s="14" t="n">
         <v>11.086492811195</v>
       </c>
-      <c r="E33" s="40" t="n">
+      <c r="E33" s="43" t="n">
         <v>-3.913507188804996</v>
       </c>
-      <c r="F33" s="41" t="inlineStr">
+      <c r="F33" s="44" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="31" t="inlineStr">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>XMME.DE</t>
         </is>
@@ -1757,17 +1752,17 @@
       <c r="D34" s="18" t="n">
         <v>13.30034210126884</v>
       </c>
-      <c r="E34" s="44" t="n">
+      <c r="E34" s="49" t="n">
         <v>-1.699657898731161</v>
       </c>
-      <c r="F34" s="45" t="inlineStr">
+      <c r="F34" s="50" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>VWCE.DE</t>
         </is>
@@ -1781,17 +1776,17 @@
       <c r="D35" s="14" t="n">
         <v>23.46521217281558</v>
       </c>
-      <c r="E35" s="46" t="n">
+      <c r="E35" s="47" t="n">
         <v>-1.53478782718442</v>
       </c>
-      <c r="F35" s="47" t="inlineStr">
+      <c r="F35" s="48" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="31" t="inlineStr">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>CSPX.L</t>
         </is>
@@ -1805,17 +1800,17 @@
       <c r="D36" s="18" t="n">
         <v>18.74915406845249</v>
       </c>
-      <c r="E36" s="44" t="n">
+      <c r="E36" s="49" t="n">
         <v>-1.250845931547513</v>
       </c>
-      <c r="F36" s="45" t="inlineStr">
+      <c r="F36" s="50" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="38" t="inlineStr">
         <is>
           <t>Per-Holding Fixed Income Targets</t>
         </is>
@@ -1854,7 +1849,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="27" t="inlineStr">
+      <c r="A40" s="26" t="inlineStr">
         <is>
           <t>IEAG.L</t>
         </is>
@@ -1868,17 +1863,17 @@
       <c r="D40" s="14" t="n">
         <v>64.42319821635272</v>
       </c>
-      <c r="E40" s="48" t="n">
+      <c r="E40" s="39" t="n">
         <v>-5.576801783647284</v>
       </c>
-      <c r="F40" s="49" t="inlineStr">
+      <c r="F40" s="40" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="inlineStr">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t>IBTM.L</t>
         </is>
@@ -1892,10 +1887,10 @@
       <c r="D41" s="18" t="n">
         <v>35.57680178364728</v>
       </c>
-      <c r="E41" s="50" t="n">
+      <c r="E41" s="41" t="n">
         <v>5.576801783647284</v>
       </c>
-      <c r="F41" s="51" t="inlineStr">
+      <c r="F41" s="42" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
@@ -1932,111 +1927,111 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="52" t="inlineStr">
+      <c r="A47" s="51" t="inlineStr">
         <is>
           <t>Alert threshold</t>
         </is>
       </c>
-      <c r="B47" s="27" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>±2.5%</t>
         </is>
       </c>
-      <c r="G47" s="27" t="inlineStr">
+      <c r="G47" s="26" t="inlineStr">
         <is>
           <t>Deviation at which a category turns amber (green below, red beyond 2×)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="53" t="inlineStr">
+      <c r="A48" s="52" t="inlineStr">
         <is>
           <t>Solver tolerance</t>
         </is>
       </c>
-      <c r="B48" s="31" t="inlineStr">
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G48" s="31" t="inlineStr">
+      <c r="G48" s="30" t="inlineStr">
         <is>
           <t>Actual tolerance the optimizer converged at (progressive up to max)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="52" t="inlineStr">
+      <c r="A49" s="51" t="inlineStr">
         <is>
           <t>Max tolerance</t>
         </is>
       </c>
-      <c r="B49" s="27" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>±2.0%</t>
         </is>
       </c>
-      <c r="G49" s="27" t="inlineStr">
-        <is>
-          <t>Cap on solver tolerance (from config.rebalancing_max_tolerance)</t>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t>Cap on solver tolerance (from config.rebalancing_max_tolerance_pctg)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="53" t="inlineStr">
+      <c r="A50" s="52" t="inlineStr">
         <is>
           <t>Min transaction</t>
         </is>
       </c>
-      <c r="B50" s="31" t="inlineStr">
+      <c r="B50" s="30" t="inlineStr">
         <is>
           <t>0.0 EUR</t>
         </is>
       </c>
-      <c r="G50" s="31" t="inlineStr">
+      <c r="G50" s="30" t="inlineStr">
         <is>
           <t>Trades below this amount are skipped</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="52" t="inlineStr">
+      <c r="A51" s="51" t="inlineStr">
         <is>
           <t>Lump sum</t>
         </is>
       </c>
-      <c r="B51" s="27" t="inlineStr">
+      <c r="B51" s="26" t="inlineStr">
         <is>
           <t>1000.0 EUR</t>
         </is>
       </c>
-      <c r="G51" s="27" t="inlineStr">
+      <c r="G51" s="26" t="inlineStr">
         <is>
           <t>Additional cash to deploy in the rebalance</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="53" t="inlineStr">
+      <c r="A52" s="52" t="inlineStr">
         <is>
           <t>No-sell mode</t>
         </is>
       </c>
-      <c r="B52" s="31" t="inlineStr">
+      <c r="B52" s="30" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="G52" s="31" t="inlineStr">
+      <c r="G52" s="30" t="inlineStr">
         <is>
           <t>If enabled, the solver can only buy, never sell</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="36" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-10 16:07 v2.0</t>
+      <c r="A54" s="35" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-10 16:30 v2.0</t>
         </is>
       </c>
     </row>
@@ -2192,17 +2187,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>VWCE.DE</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>IE00B3RBWM25</t>
         </is>
@@ -2212,155 +2207,155 @@
           <t>Equities</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F4" s="27" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G4" s="28" t="n">
+      <c r="G4" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="H4" s="28" t="n">
+      <c r="H4" s="27" t="n">
         <v>128</v>
       </c>
-      <c r="I4" s="28" t="n">
+      <c r="I4" s="27" t="n">
         <v>158.1399993896484</v>
       </c>
-      <c r="J4" s="28" t="n">
+      <c r="J4" s="27" t="n">
         <v>10240</v>
       </c>
-      <c r="K4" s="28" t="n">
+      <c r="K4" s="27" t="n">
         <v>12651.19995117188</v>
       </c>
-      <c r="L4" s="29" t="n">
+      <c r="L4" s="28" t="n">
         <v>15.32957112517667</v>
       </c>
-      <c r="M4" s="29" t="n">
+      <c r="M4" s="28" t="n">
         <v>23.46521217281558</v>
       </c>
-      <c r="N4" s="28" t="n">
+      <c r="N4" s="27" t="n">
         <v>2411.199951171875</v>
       </c>
-      <c r="O4" s="29" t="n">
+      <c r="O4" s="28" t="n">
         <v>23.54687452316284</v>
       </c>
-      <c r="P4" s="27" t="inlineStr">
+      <c r="P4" s="26" t="inlineStr">
         <is>
           <t>USA: 62, Dev ex-USA ex-EMU ex-JP: 13, Emerging Markets: 10, Eurozone EMU: 7, Japan: 6</t>
         </is>
       </c>
-      <c r="Q4" s="27" t="inlineStr">
+      <c r="Q4" s="26" t="inlineStr">
         <is>
           <t>index_geo_allocation (index: FTSE All-World)</t>
         </is>
       </c>
-      <c r="R4" s="27" t="inlineStr">
+      <c r="R4" s="26" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S4" s="27" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:07</t>
+      <c r="S4" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:30</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>CNKY.L</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>IE00B52MJD48</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F5" s="31" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G5" s="32" t="n">
+      <c r="G5" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="H5" s="32" t="n">
+      <c r="H5" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="I5" s="32" t="n">
+      <c r="I5" s="31" t="n">
         <v>350.3561155200005</v>
       </c>
-      <c r="J5" s="32" t="n">
+      <c r="J5" s="31" t="n">
         <v>2240</v>
       </c>
-      <c r="K5" s="32" t="n">
+      <c r="K5" s="31" t="n">
         <v>12262.46404320002</v>
       </c>
-      <c r="L5" s="33" t="n">
+      <c r="L5" s="32" t="n">
         <v>14.85853637960594</v>
       </c>
-      <c r="M5" s="33" t="n">
+      <c r="M5" s="32" t="n">
         <v>22.74419198540586</v>
       </c>
-      <c r="N5" s="32" t="n">
+      <c r="N5" s="31" t="n">
         <v>10022.46404320002</v>
       </c>
-      <c r="O5" s="33" t="n">
+      <c r="O5" s="32" t="n">
         <v>447.4314305000007</v>
       </c>
-      <c r="P5" s="31" t="inlineStr">
+      <c r="P5" s="30" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="Q5" s="31" t="inlineStr">
+      <c r="Q5" s="30" t="inlineStr">
         <is>
           <t>yfinance_top_holdings</t>
         </is>
       </c>
-      <c r="R5" s="31" t="inlineStr">
+      <c r="R5" s="30" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S5" s="31" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:07</t>
+      <c r="S5" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:30</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>CSPX.L</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>IE00B5BMR087</t>
         </is>
@@ -2370,155 +2365,155 @@
           <t>Equities</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F6" s="27" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G6" s="28" t="n">
+      <c r="G6" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="H6" s="27" t="n">
         <v>570</v>
       </c>
-      <c r="I6" s="28" t="n">
+      <c r="I6" s="27" t="n">
         <v>673.9034086954052</v>
       </c>
-      <c r="J6" s="28" t="n">
+      <c r="J6" s="27" t="n">
         <v>8550</v>
       </c>
-      <c r="K6" s="28" t="n">
+      <c r="K6" s="27" t="n">
         <v>10108.55113043108</v>
       </c>
-      <c r="L6" s="29" t="n">
+      <c r="L6" s="28" t="n">
         <v>12.2486210102208</v>
       </c>
-      <c r="M6" s="29" t="n">
+      <c r="M6" s="28" t="n">
         <v>18.74915406845249</v>
       </c>
-      <c r="N6" s="28" t="n">
+      <c r="N6" s="27" t="n">
         <v>1558.551130431078</v>
       </c>
-      <c r="O6" s="29" t="n">
+      <c r="O6" s="28" t="n">
         <v>18.22866819217636</v>
       </c>
-      <c r="P6" s="27" t="inlineStr">
+      <c r="P6" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q6" s="27" t="inlineStr">
+      <c r="Q6" s="26" t="inlineStr">
         <is>
           <t>index_geo_allocation (index: S&amp;P 500)</t>
         </is>
       </c>
-      <c r="R6" s="27" t="inlineStr">
+      <c r="R6" s="26" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S6" s="27" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:07</t>
+      <c r="S6" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:30</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>XMME.DE</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>LU0292107645</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F7" s="31" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G7" s="32" t="n">
+      <c r="G7" s="31" t="n">
         <v>90</v>
       </c>
-      <c r="H7" s="32" t="n">
+      <c r="H7" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="I7" s="32" t="n">
+      <c r="I7" s="31" t="n">
         <v>79.67600250244141</v>
       </c>
-      <c r="J7" s="32" t="n">
+      <c r="J7" s="31" t="n">
         <v>5040</v>
       </c>
-      <c r="K7" s="32" t="n">
+      <c r="K7" s="31" t="n">
         <v>7170.840225219727</v>
       </c>
-      <c r="L7" s="33" t="n">
+      <c r="L7" s="32" t="n">
         <v>8.688970665553452</v>
       </c>
-      <c r="M7" s="33" t="n">
+      <c r="M7" s="32" t="n">
         <v>13.30034210126884</v>
       </c>
-      <c r="N7" s="32" t="n">
+      <c r="N7" s="31" t="n">
         <v>2130.840225219727</v>
       </c>
-      <c r="O7" s="33" t="n">
+      <c r="O7" s="32" t="n">
         <v>42.2785758972168</v>
       </c>
-      <c r="P7" s="31" t="inlineStr">
+      <c r="P7" s="30" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="Q7" s="31" t="inlineStr">
+      <c r="Q7" s="30" t="inlineStr">
         <is>
           <t>index_geo_allocation (index: MSCI Emerging Markets)</t>
         </is>
       </c>
-      <c r="R7" s="31" t="inlineStr">
+      <c r="R7" s="30" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S7" s="31" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:07</t>
+      <c r="S7" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:30</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>EUNL.DE</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>IE00B4L5Y983</t>
         </is>
@@ -2528,234 +2523,234 @@
           <t>Equities</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F8" s="27" t="inlineStr">
+      <c r="F8" s="26" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G8" s="28" t="n">
+      <c r="G8" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="27" t="n">
         <v>98</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="I8" s="27" t="n">
         <v>119.5449981689453</v>
       </c>
-      <c r="J8" s="28" t="n">
+      <c r="J8" s="27" t="n">
         <v>4900</v>
       </c>
-      <c r="K8" s="28" t="n">
+      <c r="K8" s="27" t="n">
         <v>5977.249908447266</v>
       </c>
-      <c r="L8" s="29" t="n">
+      <c r="L8" s="28" t="n">
         <v>7.24268669834837</v>
       </c>
-      <c r="M8" s="29" t="n">
+      <c r="M8" s="28" t="n">
         <v>11.086492811195</v>
       </c>
-      <c r="N8" s="28" t="n">
+      <c r="N8" s="27" t="n">
         <v>1077.249908447266</v>
       </c>
-      <c r="O8" s="29" t="n">
+      <c r="O8" s="28" t="n">
         <v>21.98469200912787</v>
       </c>
-      <c r="P8" s="27" t="inlineStr">
+      <c r="P8" s="26" t="inlineStr">
         <is>
           <t>USA: 71, Dev ex-USA ex-EMU ex-JP: 14, Eurozone EMU: 8, Japan: 6</t>
         </is>
       </c>
-      <c r="Q8" s="27" t="inlineStr">
+      <c r="Q8" s="26" t="inlineStr">
         <is>
           <t>index_geo_allocation (index: MSCI World)</t>
         </is>
       </c>
-      <c r="R8" s="27" t="inlineStr">
+      <c r="R8" s="26" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S8" s="27" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:07</t>
+      <c r="S8" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:30</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>VERX.DE</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>IE00B945VV12</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" s="31" t="n">
         <v>120</v>
       </c>
-      <c r="H9" s="32" t="n">
+      <c r="H9" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="I9" s="32" t="n">
+      <c r="I9" s="31" t="n">
         <v>47.86999893188477</v>
       </c>
-      <c r="J9" s="32" t="n">
+      <c r="J9" s="31" t="n">
         <v>3960</v>
       </c>
-      <c r="K9" s="32" t="n">
+      <c r="K9" s="31" t="n">
         <v>5744.399871826172</v>
       </c>
-      <c r="L9" s="33" t="n">
+      <c r="L9" s="32" t="n">
         <v>6.960540244916307</v>
       </c>
-      <c r="M9" s="33" t="n">
+      <c r="M9" s="32" t="n">
         <v>10.65460686086223</v>
       </c>
-      <c r="N9" s="32" t="n">
+      <c r="N9" s="31" t="n">
         <v>1784.399871826172</v>
       </c>
-      <c r="O9" s="33" t="n">
+      <c r="O9" s="32" t="n">
         <v>45.06060282389323</v>
       </c>
-      <c r="P9" s="31" t="inlineStr">
+      <c r="P9" s="30" t="inlineStr">
         <is>
           <t>Eurozone EMU: 64, Dev ex-USA ex-EMU ex-JP: 35</t>
         </is>
       </c>
-      <c r="Q9" s="31" t="inlineStr">
+      <c r="Q9" s="30" t="inlineStr">
         <is>
           <t>yfinance_top_holdings</t>
         </is>
       </c>
-      <c r="R9" s="31" t="inlineStr">
+      <c r="R9" s="30" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S9" s="31" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:07</t>
+      <c r="S9" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>IEAG.L</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>IE00B3F81R35</t>
         </is>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>Fixed Income</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>Bond ETF</t>
         </is>
       </c>
-      <c r="F10" s="27" t="inlineStr">
+      <c r="F10" s="26" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G10" s="28" t="n">
+      <c r="G10" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="28" t="n">
+      <c r="H10" s="27" t="n">
         <v>56</v>
       </c>
-      <c r="I10" s="28" t="n">
+      <c r="I10" s="27" t="n">
         <v>107.5299987792969</v>
       </c>
-      <c r="J10" s="28" t="n">
+      <c r="J10" s="27" t="n">
         <v>5600</v>
       </c>
-      <c r="K10" s="28" t="n">
+      <c r="K10" s="27" t="n">
         <v>10752.99987792969</v>
       </c>
-      <c r="L10" s="29" t="n">
+      <c r="L10" s="28" t="n">
         <v>13.02950527016769</v>
       </c>
-      <c r="M10" s="29" t="n">
+      <c r="M10" s="28" t="n">
         <v>64.42319821635272</v>
       </c>
-      <c r="N10" s="28" t="n">
+      <c r="N10" s="27" t="n">
         <v>5152.999877929688</v>
       </c>
-      <c r="O10" s="29" t="n">
+      <c r="O10" s="28" t="n">
         <v>92.01785496303013</v>
       </c>
-      <c r="P10" s="27" t="inlineStr">
+      <c r="P10" s="26" t="inlineStr">
         <is>
           <t>Eurozone EMU</t>
         </is>
       </c>
-      <c r="Q10" s="27" t="inlineStr">
+      <c r="Q10" s="26" t="inlineStr">
         <is>
           <t>index_geo_allocation (ticker)</t>
         </is>
       </c>
-      <c r="R10" s="27" t="inlineStr">
+      <c r="R10" s="26" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S10" s="27" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:07</t>
+      <c r="S10" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:30</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>IBTM.L</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>IE00B1FZS798</t>
         </is>
@@ -2765,226 +2760,226 @@
           <t>Fixed Income</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>Bond ETF</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="G11" s="32" t="n">
+      <c r="G11" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="H11" s="32" t="n">
+      <c r="H11" s="31" t="n">
         <v>105</v>
       </c>
-      <c r="I11" s="32" t="n">
+      <c r="I11" s="31" t="n">
         <v>148.4548096913568</v>
       </c>
-      <c r="J11" s="32" t="n">
+      <c r="J11" s="31" t="n">
         <v>4200</v>
       </c>
-      <c r="K11" s="32" t="n">
+      <c r="K11" s="31" t="n">
         <v>5938.192387654271</v>
       </c>
-      <c r="L11" s="33" t="n">
+      <c r="L11" s="32" t="n">
         <v>7.195360354184961</v>
       </c>
-      <c r="M11" s="33" t="n">
+      <c r="M11" s="32" t="n">
         <v>35.57680178364728</v>
       </c>
-      <c r="N11" s="32" t="n">
+      <c r="N11" s="31" t="n">
         <v>1738.192387654271</v>
       </c>
-      <c r="O11" s="33" t="n">
+      <c r="O11" s="32" t="n">
         <v>41.38553303938742</v>
       </c>
-      <c r="P11" s="31" t="inlineStr">
+      <c r="P11" s="30" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="Q11" s="31" t="inlineStr">
+      <c r="Q11" s="30" t="inlineStr">
         <is>
           <t>not_available</t>
         </is>
       </c>
-      <c r="R11" s="31" t="inlineStr">
+      <c r="R11" s="30" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S11" s="31" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:07</t>
+      <c r="S11" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:30</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Equivalents</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>Money Market Instrument</t>
         </is>
       </c>
-      <c r="F12" s="27" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G12" s="28" t="n">
+      <c r="G12" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="H12" s="28" t="n">
+      <c r="H12" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="28" t="n">
+      <c r="I12" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="28" t="n">
+      <c r="J12" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="K12" s="28" t="n">
+      <c r="K12" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="L12" s="29" t="n">
+      <c r="L12" s="28" t="n">
         <v>6.058544321622511</v>
       </c>
-      <c r="M12" s="29" t="n">
+      <c r="M12" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="N12" s="28" t="n">
+      <c r="N12" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="29" t="n">
+      <c r="O12" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="27" t="inlineStr">
+      <c r="P12" s="26" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="Q12" s="27" t="inlineStr">
+      <c r="Q12" s="26" t="inlineStr">
         <is>
           <t>not_available</t>
         </is>
       </c>
-      <c r="R12" s="27" t="inlineStr">
+      <c r="R12" s="26" t="inlineStr">
         <is>
           <t>input_csv (no market data)</t>
         </is>
       </c>
-      <c r="S12" s="27" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:07</t>
+      <c r="S12" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:30</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>SGLD.L</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>IE00B579F325</t>
         </is>
       </c>
-      <c r="D13" s="54" t="inlineStr">
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="E13" s="31" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>Gold ETC</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G13" s="32" t="n">
+      <c r="G13" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="H13" s="32" t="n">
+      <c r="H13" s="31" t="n">
         <v>245</v>
       </c>
-      <c r="I13" s="32" t="n">
+      <c r="I13" s="31" t="n">
         <v>384.5654209317945</v>
       </c>
-      <c r="J13" s="32" t="n">
+      <c r="J13" s="31" t="n">
         <v>4410</v>
       </c>
-      <c r="K13" s="32" t="n">
+      <c r="K13" s="31" t="n">
         <v>6922.177576772301</v>
       </c>
-      <c r="L13" s="33" t="n">
+      <c r="L13" s="32" t="n">
         <v>8.387663930203299</v>
       </c>
-      <c r="M13" s="33" t="n">
+      <c r="M13" s="32" t="n">
         <v>100</v>
       </c>
-      <c r="N13" s="32" t="n">
+      <c r="N13" s="31" t="n">
         <v>2512.177576772301</v>
       </c>
-      <c r="O13" s="33" t="n">
+      <c r="O13" s="32" t="n">
         <v>56.9654779313447</v>
       </c>
-      <c r="P13" s="31" t="inlineStr">
+      <c r="P13" s="30" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="Q13" s="31" t="inlineStr">
+      <c r="Q13" s="30" t="inlineStr">
         <is>
           <t>not_available</t>
         </is>
       </c>
-      <c r="R13" s="31" t="inlineStr">
+      <c r="R13" s="30" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S13" s="31" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:07</t>
+      <c r="S13" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:30</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-10 16:07 v2.0</t>
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-10 16:30 v2.0</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3029,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="A2" s="54" t="inlineStr">
         <is>
           <t>Period returns (1D–5Y) and risk metrics calculated on available history per instrument (max 5 years). α/β computed vs S&amp;P 500.</t>
         </is>
@@ -3148,1356 +3143,1356 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="56" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>** TOTAL PORTFOLIO **</t>
         </is>
       </c>
-      <c r="B5" s="57" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="C5" s="58" t="n">
+      <c r="C5" s="57" t="n">
         <v>0.04</v>
       </c>
-      <c r="D5" s="58" t="n">
+      <c r="D5" s="57" t="n">
         <v>2.53</v>
       </c>
-      <c r="E5" s="58" t="n">
+      <c r="E5" s="57" t="n">
         <v>5.32</v>
       </c>
-      <c r="F5" s="58" t="n">
+      <c r="F5" s="57" t="n">
         <v>5.36</v>
       </c>
-      <c r="G5" s="58" t="n">
+      <c r="G5" s="57" t="n">
         <v>10.25</v>
       </c>
-      <c r="H5" s="58" t="n">
+      <c r="H5" s="57" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="I5" s="58" t="n">
+      <c r="I5" s="57" t="n">
         <v>24.25</v>
       </c>
-      <c r="J5" s="58" t="n">
+      <c r="J5" s="57" t="n">
         <v>51.75</v>
       </c>
-      <c r="K5" s="58" t="n">
+      <c r="K5" s="57" t="n">
         <v>48.59</v>
       </c>
-      <c r="L5" s="58" t="n">
+      <c r="L5" s="57" t="n">
         <v>8.25</v>
       </c>
-      <c r="M5" s="58" t="n">
+      <c r="M5" s="57" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="N5" s="58" t="n">
+      <c r="N5" s="57" t="n">
         <v>0.52</v>
       </c>
-      <c r="O5" s="58" t="n">
+      <c r="O5" s="57" t="n">
         <v>0.68</v>
       </c>
-      <c r="P5" s="59" t="n">
+      <c r="P5" s="58" t="n">
         <v>-13.91</v>
       </c>
-      <c r="Q5" s="59" t="n">
+      <c r="Q5" s="58" t="n">
         <v>-0.77</v>
       </c>
-      <c r="R5" s="59" t="n">
+      <c r="R5" s="58" t="n">
         <v>-1.22</v>
       </c>
-      <c r="S5" s="58" t="n">
+      <c r="S5" s="57" t="n">
         <v>2.92</v>
       </c>
-      <c r="T5" s="58" t="n">
+      <c r="T5" s="57" t="n">
         <v>0.15</v>
       </c>
-      <c r="U5" s="57" t="inlineStr">
+      <c r="U5" s="56" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>FTSE All-World</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C6" s="60" t="n">
+      <c r="C6" s="59" t="n">
         <v>-0.02</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="28" t="n">
         <v>1.69</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="28" t="n">
         <v>7.02</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="28" t="n">
         <v>6.17</v>
       </c>
-      <c r="G6" s="29" t="n">
+      <c r="G6" s="28" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="I6" s="29" t="n">
+      <c r="I6" s="28" t="n">
         <v>26.86</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="28" t="n">
         <v>65.69</v>
       </c>
-      <c r="K6" s="29" t="n">
+      <c r="K6" s="28" t="n">
         <v>74.83</v>
       </c>
-      <c r="L6" s="29" t="n">
+      <c r="L6" s="28" t="n">
         <v>11.84</v>
       </c>
-      <c r="M6" s="29" t="n">
+      <c r="M6" s="28" t="n">
         <v>14.13</v>
       </c>
-      <c r="N6" s="29" t="n">
+      <c r="N6" s="28" t="n">
         <v>0.55</v>
       </c>
-      <c r="O6" s="29" t="n">
+      <c r="O6" s="28" t="n">
         <v>0.75</v>
       </c>
-      <c r="P6" s="60" t="n">
+      <c r="P6" s="59" t="n">
         <v>-20.22</v>
       </c>
-      <c r="Q6" s="60" t="n">
+      <c r="Q6" s="59" t="n">
         <v>-1.4</v>
       </c>
-      <c r="R6" s="60" t="n">
+      <c r="R6" s="59" t="n">
         <v>-2.13</v>
       </c>
-      <c r="S6" s="29" t="n">
+      <c r="S6" s="28" t="n">
         <v>5.19</v>
       </c>
-      <c r="T6" s="29" t="n">
+      <c r="T6" s="28" t="n">
         <v>0.3</v>
       </c>
-      <c r="U6" s="27" t="inlineStr">
+      <c r="U6" s="26" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>MSCI ACWI</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C7" s="61" t="n">
+      <c r="C7" s="60" t="n">
         <v>-0.15</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="32" t="n">
         <v>5.95</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="32" t="n">
         <v>5.22</v>
       </c>
-      <c r="G7" s="33" t="n">
+      <c r="G7" s="32" t="n">
         <v>7.4</v>
       </c>
-      <c r="H7" s="33" t="n">
+      <c r="H7" s="32" t="n">
         <v>8.07</v>
       </c>
-      <c r="I7" s="33" t="n">
+      <c r="I7" s="32" t="n">
         <v>21.67</v>
       </c>
-      <c r="J7" s="33" t="n">
+      <c r="J7" s="32" t="n">
         <v>58.3</v>
       </c>
-      <c r="K7" s="33" t="n">
+      <c r="K7" s="32" t="n">
         <v>63.02</v>
       </c>
-      <c r="L7" s="33" t="n">
+      <c r="L7" s="32" t="n">
         <v>10.07</v>
       </c>
-      <c r="M7" s="33" t="n">
+      <c r="M7" s="32" t="n">
         <v>15.1</v>
       </c>
-      <c r="N7" s="33" t="n">
+      <c r="N7" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O7" s="33" t="n">
+      <c r="O7" s="32" t="n">
         <v>0.57</v>
       </c>
-      <c r="P7" s="61" t="n">
+      <c r="P7" s="60" t="n">
         <v>-20.07</v>
       </c>
-      <c r="Q7" s="61" t="n">
+      <c r="Q7" s="60" t="n">
         <v>-1.44</v>
       </c>
-      <c r="R7" s="61" t="n">
+      <c r="R7" s="60" t="n">
         <v>-2.13</v>
       </c>
-      <c r="S7" s="61" t="n">
+      <c r="S7" s="60" t="n">
         <v>-0.74</v>
       </c>
-      <c r="T7" s="33" t="n">
+      <c r="T7" s="32" t="n">
         <v>0.78</v>
       </c>
-      <c r="U7" s="31" t="inlineStr">
+      <c r="U7" s="30" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>MSCI EAFE</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="28" t="n">
         <v>0.68</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="28" t="n">
         <v>1.3</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="28" t="n">
         <v>0.84</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="28" t="n">
         <v>0.28</v>
       </c>
-      <c r="G8" s="29" t="n">
+      <c r="G8" s="28" t="n">
         <v>8.76</v>
       </c>
-      <c r="H8" s="29" t="n">
+      <c r="H8" s="28" t="n">
         <v>6.77</v>
       </c>
-      <c r="I8" s="29" t="n">
+      <c r="I8" s="28" t="n">
         <v>20.7</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="J8" s="28" t="n">
         <v>45.1</v>
       </c>
-      <c r="K8" s="29" t="n">
+      <c r="K8" s="28" t="n">
         <v>56.74</v>
       </c>
-      <c r="L8" s="29" t="n">
+      <c r="L8" s="28" t="n">
         <v>9.42</v>
       </c>
-      <c r="M8" s="29" t="n">
+      <c r="M8" s="28" t="n">
         <v>18.03</v>
       </c>
-      <c r="N8" s="29" t="n">
+      <c r="N8" s="28" t="n">
         <v>0.3</v>
       </c>
-      <c r="O8" s="29" t="n">
+      <c r="O8" s="28" t="n">
         <v>0.45</v>
       </c>
-      <c r="P8" s="60" t="n">
+      <c r="P8" s="59" t="n">
         <v>-17.35</v>
       </c>
-      <c r="Q8" s="60" t="n">
+      <c r="Q8" s="59" t="n">
         <v>-1.63</v>
       </c>
-      <c r="R8" s="60" t="n">
+      <c r="R8" s="59" t="n">
         <v>-2.44</v>
       </c>
-      <c r="S8" s="60" t="n">
+      <c r="S8" s="59" t="n">
         <v>-1.72</v>
       </c>
-      <c r="T8" s="29" t="n">
+      <c r="T8" s="28" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="U8" s="27" t="inlineStr">
+      <c r="U8" s="26" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>MSCI Emerging Markets</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="32" t="n">
         <v>1.66</v>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="32" t="n">
         <v>5.4</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="32" t="n">
         <v>11.43</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="32" t="n">
         <v>12.62</v>
       </c>
-      <c r="G9" s="33" t="n">
+      <c r="G9" s="32" t="n">
         <v>21.56</v>
       </c>
-      <c r="H9" s="33" t="n">
+      <c r="H9" s="32" t="n">
         <v>20.4</v>
       </c>
-      <c r="I9" s="33" t="n">
+      <c r="I9" s="32" t="n">
         <v>49.58</v>
       </c>
-      <c r="J9" s="33" t="n">
+      <c r="J9" s="32" t="n">
         <v>74.2</v>
       </c>
-      <c r="K9" s="33" t="n">
+      <c r="K9" s="32" t="n">
         <v>46.75</v>
       </c>
-      <c r="L9" s="33" t="n">
+      <c r="L9" s="32" t="n">
         <v>7.98</v>
       </c>
-      <c r="M9" s="33" t="n">
+      <c r="M9" s="32" t="n">
         <v>20.18</v>
       </c>
-      <c r="N9" s="33" t="n">
+      <c r="N9" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="O9" s="33" t="n">
+      <c r="O9" s="32" t="n">
         <v>0.31</v>
       </c>
-      <c r="P9" s="61" t="n">
+      <c r="P9" s="60" t="n">
         <v>-24.81</v>
       </c>
-      <c r="Q9" s="61" t="n">
+      <c r="Q9" s="60" t="n">
         <v>-1.92</v>
       </c>
-      <c r="R9" s="61" t="n">
+      <c r="R9" s="60" t="n">
         <v>-2.71</v>
       </c>
-      <c r="S9" s="61" t="n">
+      <c r="S9" s="60" t="n">
         <v>-2.96</v>
       </c>
-      <c r="T9" s="33" t="n">
+      <c r="T9" s="32" t="n">
         <v>0.79</v>
       </c>
-      <c r="U9" s="31" t="inlineStr">
+      <c r="U9" s="30" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>MSCI World</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C10" s="60" t="n">
+      <c r="C10" s="59" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="28" t="n">
         <v>1.82</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="28" t="n">
         <v>5.44</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="28" t="n">
         <v>4.4</v>
       </c>
-      <c r="G10" s="29" t="n">
+      <c r="G10" s="28" t="n">
         <v>5.88</v>
       </c>
-      <c r="H10" s="29" t="n">
+      <c r="H10" s="28" t="n">
         <v>6.67</v>
       </c>
-      <c r="I10" s="29" t="n">
+      <c r="I10" s="28" t="n">
         <v>19.44</v>
       </c>
-      <c r="J10" s="29" t="n">
+      <c r="J10" s="28" t="n">
         <v>57.46</v>
       </c>
-      <c r="K10" s="29" t="n">
+      <c r="K10" s="28" t="n">
         <v>67.3</v>
       </c>
-      <c r="L10" s="29" t="n">
+      <c r="L10" s="28" t="n">
         <v>10.65</v>
       </c>
-      <c r="M10" s="29" t="n">
+      <c r="M10" s="28" t="n">
         <v>16.47</v>
       </c>
-      <c r="N10" s="29" t="n">
+      <c r="N10" s="28" t="n">
         <v>0.4</v>
       </c>
-      <c r="O10" s="29" t="n">
+      <c r="O10" s="28" t="n">
         <v>0.54</v>
       </c>
-      <c r="P10" s="60" t="n">
+      <c r="P10" s="59" t="n">
         <v>-20.63</v>
       </c>
-      <c r="Q10" s="60" t="n">
+      <c r="Q10" s="59" t="n">
         <v>-1.56</v>
       </c>
-      <c r="R10" s="60" t="n">
+      <c r="R10" s="59" t="n">
         <v>-2.29</v>
       </c>
-      <c r="S10" s="60" t="n">
+      <c r="S10" s="59" t="n">
         <v>-0.93</v>
       </c>
-      <c r="T10" s="29" t="n">
+      <c r="T10" s="28" t="n">
         <v>0.86</v>
       </c>
-      <c r="U10" s="27" t="inlineStr">
+      <c r="U10" s="26" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>MSCI World Momentum</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="32" t="n">
         <v>2.32</v>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="32" t="n">
         <v>5.32</v>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="32" t="n">
         <v>15.22</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="32" t="n">
         <v>17.7</v>
       </c>
-      <c r="G11" s="33" t="n">
+      <c r="G11" s="32" t="n">
         <v>17.4</v>
       </c>
-      <c r="H11" s="33" t="n">
+      <c r="H11" s="32" t="n">
         <v>19.13</v>
       </c>
-      <c r="I11" s="33" t="n">
+      <c r="I11" s="32" t="n">
         <v>34.05</v>
       </c>
-      <c r="J11" s="33" t="n">
+      <c r="J11" s="32" t="n">
         <v>106.05</v>
       </c>
-      <c r="K11" s="33" t="n">
+      <c r="K11" s="32" t="n">
         <v>100.48</v>
       </c>
-      <c r="L11" s="33" t="n">
+      <c r="L11" s="32" t="n">
         <v>14.94</v>
       </c>
-      <c r="M11" s="33" t="n">
+      <c r="M11" s="32" t="n">
         <v>22</v>
       </c>
-      <c r="N11" s="33" t="n">
+      <c r="N11" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="O11" s="33" t="n">
+      <c r="O11" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="P11" s="61" t="n">
+      <c r="P11" s="60" t="n">
         <v>-25.91</v>
       </c>
-      <c r="Q11" s="61" t="n">
+      <c r="Q11" s="60" t="n">
         <v>-2.25</v>
       </c>
-      <c r="R11" s="61" t="n">
+      <c r="R11" s="60" t="n">
         <v>-3.13</v>
       </c>
-      <c r="S11" s="33" t="n">
+      <c r="S11" s="32" t="n">
         <v>1.6</v>
       </c>
-      <c r="T11" s="33" t="n">
+      <c r="T11" s="32" t="n">
         <v>1.06</v>
       </c>
-      <c r="U11" s="31" t="inlineStr">
+      <c r="U11" s="30" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>MSCI World Quality</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="28" t="n">
         <v>1.06</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="28" t="n">
         <v>4.81</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="28" t="n">
         <v>3.67</v>
       </c>
-      <c r="G12" s="29" t="n">
+      <c r="G12" s="28" t="n">
         <v>5.72</v>
       </c>
-      <c r="H12" s="29" t="n">
+      <c r="H12" s="28" t="n">
         <v>5.52</v>
       </c>
-      <c r="I12" s="29" t="n">
+      <c r="I12" s="28" t="n">
         <v>18.85</v>
       </c>
-      <c r="J12" s="29" t="n">
+      <c r="J12" s="28" t="n">
         <v>63.51</v>
       </c>
-      <c r="K12" s="29" t="n">
+      <c r="K12" s="28" t="n">
         <v>79.73</v>
       </c>
-      <c r="L12" s="29" t="n">
+      <c r="L12" s="28" t="n">
         <v>12.46</v>
       </c>
-      <c r="M12" s="29" t="n">
+      <c r="M12" s="28" t="n">
         <v>18.9</v>
       </c>
-      <c r="N12" s="29" t="n">
+      <c r="N12" s="28" t="n">
         <v>0.45</v>
       </c>
-      <c r="O12" s="29" t="n">
+      <c r="O12" s="28" t="n">
         <v>0.64</v>
       </c>
-      <c r="P12" s="60" t="n">
+      <c r="P12" s="59" t="n">
         <v>-22.45</v>
       </c>
-      <c r="Q12" s="60" t="n">
+      <c r="Q12" s="59" t="n">
         <v>-1.79</v>
       </c>
-      <c r="R12" s="60" t="n">
+      <c r="R12" s="59" t="n">
         <v>-2.66</v>
       </c>
-      <c r="S12" s="60" t="n">
+      <c r="S12" s="59" t="n">
         <v>-0.34</v>
       </c>
-      <c r="T12" s="29" t="n">
+      <c r="T12" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="U12" s="27" t="inlineStr">
+      <c r="U12" s="26" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>Nasdaq 100</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C13" s="33" t="n">
+      <c r="C13" s="32" t="n">
         <v>1.98</v>
       </c>
-      <c r="D13" s="33" t="n">
+      <c r="D13" s="32" t="n">
         <v>4.96</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="32" t="n">
         <v>16.37</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="32" t="n">
         <v>16.05</v>
       </c>
-      <c r="G13" s="33" t="n">
+      <c r="G13" s="32" t="n">
         <v>11.77</v>
       </c>
-      <c r="H13" s="33" t="n">
+      <c r="H13" s="32" t="n">
         <v>15.6</v>
       </c>
-      <c r="I13" s="33" t="n">
+      <c r="I13" s="32" t="n">
         <v>39.74</v>
       </c>
-      <c r="J13" s="33" t="n">
+      <c r="J13" s="32" t="n">
         <v>106.55</v>
       </c>
-      <c r="K13" s="33" t="n">
+      <c r="K13" s="32" t="n">
         <v>125.92</v>
       </c>
-      <c r="L13" s="33" t="n">
+      <c r="L13" s="32" t="n">
         <v>17.73</v>
       </c>
-      <c r="M13" s="33" t="n">
+      <c r="M13" s="32" t="n">
         <v>23.87</v>
       </c>
-      <c r="N13" s="33" t="n">
+      <c r="N13" s="32" t="n">
         <v>0.57</v>
       </c>
-      <c r="O13" s="33" t="n">
+      <c r="O13" s="32" t="n">
         <v>0.82</v>
       </c>
-      <c r="P13" s="61" t="n">
+      <c r="P13" s="60" t="n">
         <v>-31.38</v>
       </c>
-      <c r="Q13" s="61" t="n">
+      <c r="Q13" s="60" t="n">
         <v>-2.43</v>
       </c>
-      <c r="R13" s="61" t="n">
+      <c r="R13" s="60" t="n">
         <v>-3.39</v>
       </c>
-      <c r="S13" s="33" t="n">
+      <c r="S13" s="32" t="n">
         <v>2.93</v>
       </c>
-      <c r="T13" s="33" t="n">
+      <c r="T13" s="32" t="n">
         <v>1.23</v>
       </c>
-      <c r="U13" s="31" t="inlineStr">
+      <c r="U13" s="30" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="28" t="n">
         <v>0.48</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="28" t="n">
         <v>1.81</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="28" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="28" t="n">
         <v>6.56</v>
       </c>
-      <c r="G14" s="29" t="n">
+      <c r="G14" s="28" t="n">
         <v>6.03</v>
       </c>
-      <c r="H14" s="29" t="n">
+      <c r="H14" s="28" t="n">
         <v>7.52</v>
       </c>
-      <c r="I14" s="29" t="n">
+      <c r="I14" s="28" t="n">
         <v>25.28</v>
       </c>
-      <c r="J14" s="29" t="n">
+      <c r="J14" s="28" t="n">
         <v>67.53</v>
       </c>
-      <c r="K14" s="29" t="n">
+      <c r="K14" s="28" t="n">
         <v>82.37</v>
       </c>
-      <c r="L14" s="29" t="n">
+      <c r="L14" s="28" t="n">
         <v>12.79</v>
       </c>
-      <c r="M14" s="29" t="n">
+      <c r="M14" s="28" t="n">
         <v>18.55</v>
       </c>
-      <c r="N14" s="29" t="n">
+      <c r="N14" s="28" t="n">
         <v>0.47</v>
       </c>
-      <c r="O14" s="29" t="n">
+      <c r="O14" s="28" t="n">
         <v>0.67</v>
       </c>
-      <c r="P14" s="60" t="n">
+      <c r="P14" s="59" t="n">
         <v>-23.17</v>
       </c>
-      <c r="Q14" s="60" t="n">
+      <c r="Q14" s="59" t="n">
         <v>-1.86</v>
       </c>
-      <c r="R14" s="60" t="n">
+      <c r="R14" s="59" t="n">
         <v>-2.64</v>
       </c>
-      <c r="S14" s="29" t="n">
+      <c r="S14" s="28" t="n">
         <v>-0</v>
       </c>
-      <c r="T14" s="29" t="n">
+      <c r="T14" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="U14" s="27" t="inlineStr">
+      <c r="U14" s="26" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
         </is>
       </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C15" s="61" t="n">
+      <c r="C15" s="60" t="n">
         <v>-0.05</v>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D15" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E15" s="61" t="n">
+      <c r="E15" s="60" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F15" s="61" t="n">
+      <c r="F15" s="60" t="n">
         <v>-0.58</v>
       </c>
-      <c r="G15" s="61" t="n">
+      <c r="G15" s="60" t="n">
         <v>-0.31</v>
       </c>
-      <c r="H15" s="33" t="n">
+      <c r="H15" s="32" t="n">
         <v>0.44</v>
       </c>
-      <c r="I15" s="33" t="n">
+      <c r="I15" s="32" t="n">
         <v>0.74</v>
       </c>
-      <c r="J15" s="33" t="n">
+      <c r="J15" s="32" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="K15" s="61" t="n">
+      <c r="K15" s="60" t="n">
         <v>-8.369999999999999</v>
       </c>
-      <c r="L15" s="61" t="n">
+      <c r="L15" s="60" t="n">
         <v>-1.73</v>
       </c>
-      <c r="M15" s="33" t="n">
+      <c r="M15" s="32" t="n">
         <v>5.55</v>
       </c>
-      <c r="N15" s="61" t="n">
+      <c r="N15" s="60" t="n">
         <v>-1.03</v>
       </c>
-      <c r="O15" s="61" t="n">
+      <c r="O15" s="60" t="n">
         <v>-1.59</v>
       </c>
-      <c r="P15" s="61" t="n">
+      <c r="P15" s="60" t="n">
         <v>-19.81</v>
       </c>
-      <c r="Q15" s="61" t="n">
+      <c r="Q15" s="60" t="n">
         <v>-0.55</v>
       </c>
-      <c r="R15" s="61" t="n">
+      <c r="R15" s="60" t="n">
         <v>-0.77</v>
       </c>
-      <c r="S15" s="61" t="n">
+      <c r="S15" s="60" t="n">
         <v>-5.88</v>
       </c>
-      <c r="T15" s="33" t="n">
+      <c r="T15" s="32" t="n">
         <v>0.02</v>
       </c>
-      <c r="U15" s="31" t="inlineStr">
+      <c r="U15" s="30" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D16" s="28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="E16" s="28" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="I16" s="28" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="J16" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="K16" s="28" t="n">
+        <v>73.76000000000001</v>
+      </c>
+      <c r="L16" s="28" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M16" s="28" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P16" s="59" t="n">
+        <v>-21.07</v>
+      </c>
+      <c r="Q16" s="59" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="R16" s="59" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="S16" s="28" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="T16" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U16" s="26" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C16" s="60" t="n">
+      <c r="C17" s="60" t="n">
         <v>-0.04</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D17" s="32" t="n">
         <v>1.83</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E17" s="32" t="n">
         <v>6.27</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F17" s="32" t="n">
         <v>5.59</v>
       </c>
-      <c r="G16" s="29" t="n">
+      <c r="G17" s="32" t="n">
         <v>7.78</v>
       </c>
-      <c r="H16" s="29" t="n">
+      <c r="H17" s="32" t="n">
         <v>7.39</v>
       </c>
-      <c r="I16" s="29" t="n">
+      <c r="I17" s="32" t="n">
         <v>24.05</v>
       </c>
-      <c r="J16" s="29" t="n">
+      <c r="J17" s="32" t="n">
         <v>64.01000000000001</v>
       </c>
-      <c r="K16" s="29" t="n">
+      <c r="K17" s="32" t="n">
         <v>77.81</v>
       </c>
-      <c r="L16" s="29" t="n">
+      <c r="L17" s="32" t="n">
         <v>12.22</v>
       </c>
-      <c r="M16" s="29" t="n">
+      <c r="M17" s="32" t="n">
         <v>14.23</v>
       </c>
-      <c r="N16" s="29" t="n">
+      <c r="N17" s="32" t="n">
         <v>0.58</v>
       </c>
-      <c r="O16" s="29" t="n">
+      <c r="O17" s="32" t="n">
         <v>0.74</v>
       </c>
-      <c r="P16" s="60" t="n">
+      <c r="P17" s="60" t="n">
         <v>-21.73</v>
       </c>
-      <c r="Q16" s="60" t="n">
+      <c r="Q17" s="60" t="n">
         <v>-1.45</v>
       </c>
-      <c r="R16" s="60" t="n">
+      <c r="R17" s="60" t="n">
         <v>-2.19</v>
       </c>
-      <c r="S16" s="29" t="n">
+      <c r="S17" s="32" t="n">
         <v>6.28</v>
       </c>
-      <c r="T16" s="29" t="n">
+      <c r="T17" s="32" t="n">
         <v>0.22</v>
       </c>
-      <c r="U16" s="27" t="inlineStr">
+      <c r="U17" s="30" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C17" s="33" t="n">
+      <c r="C18" s="59" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="D18" s="28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E18" s="28" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="I18" s="28" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="J18" s="28" t="n">
+        <v>72.76000000000001</v>
+      </c>
+      <c r="K18" s="28" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="L18" s="28" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="M18" s="28" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P18" s="59" t="n">
+        <v>-22.73</v>
+      </c>
+      <c r="Q18" s="59" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="R18" s="59" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="S18" s="28" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="T18" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="U18" s="26" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D19" s="32" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="E19" s="32" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F19" s="32" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="G19" s="32" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="H19" s="32" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="I19" s="32" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="J19" s="32" t="n">
+        <v>75.97</v>
+      </c>
+      <c r="K19" s="32" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="L19" s="32" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="M19" s="32" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="N19" s="32" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O19" s="32" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P19" s="60" t="n">
+        <v>-24.38</v>
+      </c>
+      <c r="Q19" s="60" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="R19" s="60" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="S19" s="32" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="T19" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="D17" s="33" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="E17" s="33" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="F17" s="33" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="G17" s="33" t="n">
-        <v>9.41</v>
-      </c>
-      <c r="H17" s="33" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="I17" s="33" t="n">
-        <v>26.51</v>
-      </c>
-      <c r="J17" s="33" t="n">
-        <v>65</v>
-      </c>
-      <c r="K17" s="33" t="n">
-        <v>73.76000000000001</v>
-      </c>
-      <c r="L17" s="33" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="M17" s="33" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="N17" s="33" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="O17" s="33" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="P17" s="61" t="n">
-        <v>-21.07</v>
-      </c>
-      <c r="Q17" s="61" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="R17" s="61" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="S17" s="33" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="T17" s="33" t="n">
+      <c r="U19" s="30" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C20" s="59" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D20" s="59" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E20" s="59" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="F20" s="28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G20" s="59" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="H20" s="59" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I20" s="28" t="n">
         <v>0.2</v>
       </c>
-      <c r="U17" s="31" t="inlineStr">
+      <c r="J20" s="28" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K20" s="59" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L20" s="59" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M20" s="28" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="N20" s="59" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="O20" s="59" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="P20" s="59" t="n">
+        <v>-15.77</v>
+      </c>
+      <c r="Q20" s="59" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="R20" s="59" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="S20" s="59" t="n">
+        <v>-3.83</v>
+      </c>
+      <c r="T20" s="59" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U20" s="26" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>Invesco Physical Gold ETC</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>22.39</v>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>21.47</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>48.97</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>75.97</v>
-      </c>
-      <c r="K18" s="29" t="n">
-        <v>50.05</v>
-      </c>
-      <c r="L18" s="29" t="n">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="M18" s="29" t="n">
-        <v>18.84</v>
-      </c>
-      <c r="N18" s="29" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="O18" s="29" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="P18" s="60" t="n">
-        <v>-24.38</v>
-      </c>
-      <c r="Q18" s="60" t="n">
-        <v>-1.58</v>
-      </c>
-      <c r="R18" s="60" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="S18" s="29" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="T18" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U18" s="27" t="inlineStr">
+      <c r="C21" s="60" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="D21" s="32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E21" s="60" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="F21" s="60" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="G21" s="32" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="H21" s="32" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="I21" s="32" t="n">
+        <v>35</v>
+      </c>
+      <c r="J21" s="32" t="n">
+        <v>116.16</v>
+      </c>
+      <c r="K21" s="32" t="n">
+        <v>162.76</v>
+      </c>
+      <c r="L21" s="32" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="M21" s="32" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="N21" s="32" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O21" s="32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P21" s="60" t="n">
+        <v>-15.94</v>
+      </c>
+      <c r="Q21" s="60" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="R21" s="60" t="n">
+        <v>-2.57</v>
+      </c>
+      <c r="S21" s="32" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="T21" s="32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U21" s="30" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C19" s="61" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="D19" s="33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E19" s="33" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="F19" s="33" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="G19" s="33" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H19" s="33" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="I19" s="33" t="n">
-        <v>25.92</v>
-      </c>
-      <c r="J19" s="33" t="n">
-        <v>72.76000000000001</v>
-      </c>
-      <c r="K19" s="33" t="n">
-        <v>91.22</v>
-      </c>
-      <c r="L19" s="33" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="M19" s="33" t="n">
-        <v>17.28</v>
-      </c>
-      <c r="N19" s="33" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="O19" s="33" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="P19" s="61" t="n">
-        <v>-22.73</v>
-      </c>
-      <c r="Q19" s="61" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="R19" s="61" t="n">
-        <v>-2.53</v>
-      </c>
-      <c r="S19" s="33" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="T19" s="33" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="U19" s="31" t="inlineStr">
+      <c r="C22" s="28" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D22" s="28" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="E22" s="28" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="F22" s="28" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="G22" s="28" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="H22" s="28" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I22" s="28" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="J22" s="28" t="n">
+        <v>80.48</v>
+      </c>
+      <c r="K22" s="28" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="L22" s="28" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="M22" s="28" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="P22" s="59" t="n">
+        <v>-21.24</v>
+      </c>
+      <c r="Q22" s="59" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="R22" s="59" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="S22" s="28" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="T22" s="28" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="U22" s="26" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="B20" s="27" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C20" s="60" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="D20" s="60" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E20" s="60" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G20" s="60" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="H20" s="60" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K20" s="60" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L20" s="60" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="M20" s="29" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="N20" s="60" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="O20" s="60" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="P20" s="60" t="n">
-        <v>-15.77</v>
-      </c>
-      <c r="Q20" s="60" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="R20" s="60" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="S20" s="60" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="T20" s="60" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="U20" s="27" t="inlineStr">
+      <c r="C23" s="60" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="D23" s="32" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E23" s="32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F23" s="60" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="G23" s="32" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="H23" s="32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I23" s="32" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="J23" s="32" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="K23" s="32" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="L23" s="32" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="M23" s="32" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="N23" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O23" s="32" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="P23" s="60" t="n">
+        <v>-22.86</v>
+      </c>
+      <c r="Q23" s="60" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="R23" s="60" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="S23" s="32" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="T23" s="32" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U23" s="30" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>Invesco Physical Gold ETC</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C21" s="61" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="D21" s="33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E21" s="61" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="F21" s="61" t="n">
-        <v>-6.82</v>
-      </c>
-      <c r="G21" s="33" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="H21" s="33" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="I21" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="J21" s="33" t="n">
-        <v>116.16</v>
-      </c>
-      <c r="K21" s="33" t="n">
-        <v>162.76</v>
-      </c>
-      <c r="L21" s="33" t="n">
-        <v>21.34</v>
-      </c>
-      <c r="M21" s="33" t="n">
-        <v>17.92</v>
-      </c>
-      <c r="N21" s="33" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="O21" s="33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P21" s="61" t="n">
-        <v>-15.94</v>
-      </c>
-      <c r="Q21" s="61" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="R21" s="61" t="n">
-        <v>-2.57</v>
-      </c>
-      <c r="S21" s="33" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="T21" s="33" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U21" s="31" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="27" t="inlineStr">
-        <is>
-          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
-        </is>
-      </c>
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C22" s="60" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="D22" s="29" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="E22" s="29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="F22" s="60" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="G22" s="29" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="H22" s="29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>16.35</v>
-      </c>
-      <c r="J22" s="29" t="n">
-        <v>42.11</v>
-      </c>
-      <c r="K22" s="29" t="n">
-        <v>55.61</v>
-      </c>
-      <c r="L22" s="29" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="M22" s="29" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="N22" s="29" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O22" s="29" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="P22" s="60" t="n">
-        <v>-22.86</v>
-      </c>
-      <c r="Q22" s="60" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="R22" s="60" t="n">
-        <v>-2.22</v>
-      </c>
-      <c r="S22" s="29" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="T22" s="29" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="U22" s="27" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
-        </is>
-      </c>
-      <c r="B23" s="31" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C23" s="33" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="D23" s="33" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="E23" s="33" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="F23" s="33" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="G23" s="33" t="n">
-        <v>20.84</v>
-      </c>
-      <c r="H23" s="33" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="I23" s="33" t="n">
-        <v>51.96</v>
-      </c>
-      <c r="J23" s="33" t="n">
-        <v>80.48</v>
-      </c>
-      <c r="K23" s="33" t="n">
-        <v>64.31999999999999</v>
-      </c>
-      <c r="L23" s="33" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="M23" s="33" t="n">
-        <v>18.31</v>
-      </c>
-      <c r="N23" s="33" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O23" s="33" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="P23" s="61" t="n">
-        <v>-21.24</v>
-      </c>
-      <c r="Q23" s="61" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="R23" s="61" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="S23" s="33" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="T23" s="33" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="U23" s="31" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="62" t="inlineStr">
+      <c r="A26" s="61" t="inlineStr">
         <is>
           <t>Legend — Rating Thresholds</t>
         </is>
@@ -4536,297 +4531,297 @@
       </c>
     </row>
     <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>CAGR</t>
         </is>
       </c>
-      <c r="B28" s="63" t="inlineStr">
+      <c r="B28" s="62" t="inlineStr">
         <is>
           <t>Compound Annual Growth Rate. The single yearly return that, if repeated every year, would grow your portfolio from start to end value. Accounts for compounding. ~7% is the long-term global equity average.</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>&gt; 7.0%</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>3.0% – 7.0%</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>&lt; 3.0%</t>
         </is>
       </c>
-      <c r="F28" s="27" t="inlineStr">
+      <c r="F28" s="26" t="inlineStr">
         <is>
           <t>Equity risk premium (Dimson et al.)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>α (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B29" s="64" t="inlineStr">
+      <c r="B29" s="63" t="inlineStr">
         <is>
           <t>Extra annual return vs the benchmark, after adjusting for how risky the portfolio is (CAPM). Positive = you beat the market beyond what your risk alone justified. Negative = you underperformed after fees and noise.</t>
         </is>
       </c>
-      <c r="C29" s="31" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>&gt; 0.0%</t>
         </is>
       </c>
-      <c r="D29" s="31" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>-1.0% – 0.0%</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>&lt; -1.0%</t>
         </is>
       </c>
-      <c r="F29" s="31" t="inlineStr">
+      <c r="F29" s="30" t="inlineStr">
         <is>
           <t>Jensen's Alpha (CAPM)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>β (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B30" s="63" t="inlineStr">
+      <c r="B30" s="62" t="inlineStr">
         <is>
           <t>How much your portfolio moves when the benchmark moves 1%. β=1 in line, β=0.5 half as reactive, β=1.5 amplifies by 50%, β≈0 uncorrelated. Tells you how much systematic market risk you're running.</t>
         </is>
       </c>
-      <c r="C30" s="27" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>&lt; 0.7</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D30" s="26" t="inlineStr">
         <is>
           <t>1.0 – 0.7</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>&gt; 1.0</t>
         </is>
       </c>
-      <c r="F30" s="27" t="inlineStr">
+      <c r="F30" s="26" t="inlineStr">
         <is>
           <t>CAPM, 1.0 = market</t>
         </is>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1">
-      <c r="A31" s="31" t="inlineStr">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>Max DD</t>
         </is>
       </c>
-      <c r="B31" s="64" t="inlineStr">
+      <c r="B31" s="63" t="inlineStr">
         <is>
           <t>Maximum Drawdown. Worst peak-to-trough loss over the period — the most painful scenario an investor lived through. -20% is typical for diversified equity; deeper drops signal concentration or high volatility.</t>
         </is>
       </c>
-      <c r="C31" s="31" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
         <is>
           <t>&lt; 15.0%</t>
         </is>
       </c>
-      <c r="D31" s="31" t="inlineStr">
+      <c r="D31" s="30" t="inlineStr">
         <is>
           <t>30.0% – 15.0%</t>
         </is>
       </c>
-      <c r="E31" s="31" t="inlineStr">
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>&gt; 30.0%</t>
         </is>
       </c>
-      <c r="F31" s="31" t="inlineStr">
+      <c r="F31" s="30" t="inlineStr">
         <is>
           <t>Retail drawdown tolerance</t>
         </is>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
-      <c r="B32" s="63" t="inlineStr">
+      <c r="B32" s="62" t="inlineStr">
         <is>
           <t>How bumpy the ride is. Annualized standard deviation of daily returns. A 15% vol means ~±15% year-to-year noise around the average return. Equity indexes ~15–20%, bonds ~3–7%.</t>
         </is>
       </c>
-      <c r="C32" s="27" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>&lt; 10.0%</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="D32" s="26" t="inlineStr">
         <is>
           <t>18.0% – 10.0%</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>&gt; 18.0%</t>
         </is>
       </c>
-      <c r="F32" s="27" t="inlineStr">
+      <c r="F32" s="26" t="inlineStr">
         <is>
           <t>Hist. equity vol ~15%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1">
-      <c r="A33" s="31" t="inlineStr">
+      <c r="A33" s="30" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="B33" s="64" t="inlineStr">
+      <c r="B33" s="63" t="inlineStr">
         <is>
           <t>Return per unit of risk taken: (CAGR − risk-free rate) / Volatility. Above 1 is good, above 2 is excellent, negative means you were paid less than a safe bond for the risk you ran.</t>
         </is>
       </c>
-      <c r="C33" s="31" t="inlineStr">
+      <c r="C33" s="30" t="inlineStr">
         <is>
           <t>&gt; 1.0</t>
         </is>
       </c>
-      <c r="D33" s="31" t="inlineStr">
+      <c r="D33" s="30" t="inlineStr">
         <is>
           <t>0.5 – 1.0</t>
         </is>
       </c>
-      <c r="E33" s="31" t="inlineStr">
+      <c r="E33" s="30" t="inlineStr">
         <is>
           <t>&lt; 0.5</t>
         </is>
       </c>
-      <c r="F33" s="31" t="inlineStr">
+      <c r="F33" s="30" t="inlineStr">
         <is>
           <t>Sharpe (1994)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1">
-      <c r="A34" s="27" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>Sortino</t>
         </is>
       </c>
-      <c r="B34" s="63" t="inlineStr">
+      <c r="B34" s="62" t="inlineStr">
         <is>
           <t>Like Sharpe but only penalizes downside volatility (ignores upside swings). More honest when returns are asymmetric. Usually higher than Sharpe — the gap shows how much of your volatility is actually good volatility.</t>
         </is>
       </c>
-      <c r="C34" s="27" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>&gt; 1.5</t>
         </is>
       </c>
-      <c r="D34" s="27" t="inlineStr">
+      <c r="D34" s="26" t="inlineStr">
         <is>
           <t>0.7 – 1.5</t>
         </is>
       </c>
-      <c r="E34" s="27" t="inlineStr">
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>&lt; 0.7</t>
         </is>
       </c>
-      <c r="F34" s="27" t="inlineStr">
+      <c r="F34" s="26" t="inlineStr">
         <is>
           <t>Sortino &amp; Price (1994)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="31" t="inlineStr">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>VaR 95%</t>
         </is>
       </c>
-      <c r="B35" s="64" t="inlineStr">
+      <c r="B35" s="63" t="inlineStr">
         <is>
           <t>Value at Risk. The daily loss exceeded only 5% of the time (historical simulation). A VaR of -1.2% means on an average month you should expect about one day worse than -1.2%. Non-parametric: no normal-distribution assumption.</t>
         </is>
       </c>
-      <c r="C35" s="31" t="inlineStr">
+      <c r="C35" s="30" t="inlineStr">
         <is>
           <t>&lt; 0.8%</t>
         </is>
       </c>
-      <c r="D35" s="31" t="inlineStr">
+      <c r="D35" s="30" t="inlineStr">
         <is>
           <t>1.5% – 0.8%</t>
         </is>
       </c>
-      <c r="E35" s="31" t="inlineStr">
+      <c r="E35" s="30" t="inlineStr">
         <is>
           <t>&gt; 1.5%</t>
         </is>
       </c>
-      <c r="F35" s="31" t="inlineStr">
+      <c r="F35" s="30" t="inlineStr">
         <is>
           <t>Basel III (retail adj.)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>CVaR 95%</t>
         </is>
       </c>
-      <c r="B36" s="63" t="inlineStr">
+      <c r="B36" s="62" t="inlineStr">
         <is>
           <t>Conditional VaR, a.k.a. Expected Shortfall. The average loss on the worst 5% of days. Always more negative than VaR. Captures tail risk VaR misses — how bad it really gets when it goes bad.</t>
         </is>
       </c>
-      <c r="C36" s="27" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>&lt; 1.2%</t>
         </is>
       </c>
-      <c r="D36" s="27" t="inlineStr">
+      <c r="D36" s="26" t="inlineStr">
         <is>
           <t>2.0% – 1.2%</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>&gt; 2.0%</t>
         </is>
       </c>
-      <c r="F36" s="27" t="inlineStr">
+      <c r="F36" s="26" t="inlineStr">
         <is>
           <t>Artzner et al. (1999)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="36" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-10 16:07 v2.0</t>
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-10 16:30 v2.0</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4861,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="62" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>Return Contribution by Holding</t>
         </is>
@@ -4905,267 +4900,267 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>IE00B52MJD48</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>CNKY.L</t>
         </is>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="28" t="n">
         <v>14.85853637960594</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="28" t="n">
         <v>447.4314305000007</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="28" t="n">
         <v>66.48176187463385</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>IE00B3F81R35</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>IEAG.L</t>
         </is>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="32" t="n">
         <v>13.02950527016769</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="32" t="n">
         <v>92.01785496303013</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="32" t="n">
         <v>11.98947126190327</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>IE00B579F325</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>SGLD.L</t>
         </is>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="28" t="n">
         <v>8.387663930203299</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="28" t="n">
         <v>56.9654779313447</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="28" t="n">
         <v>4.77807284511532</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>LU0292107645</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>XMME.DE</t>
         </is>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="32" t="n">
         <v>8.688970665553452</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="32" t="n">
         <v>42.2785758972168</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="32" t="n">
         <v>3.67357305752292</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>IE00B3RBWM25</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>VWCE.DE</t>
         </is>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="28" t="n">
         <v>15.32957112517667</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="28" t="n">
         <v>23.54687452316284</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="28" t="n">
         <v>3.609634877784353</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>IE00B945VV12</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>VERX.DE</t>
         </is>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="32" t="n">
         <v>6.960540244916307</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="32" t="n">
         <v>45.06060282389323</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="32" t="n">
         <v>3.136461394158983</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>IE00B1FZS798</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>IBTM.L</t>
         </is>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="28" t="n">
         <v>7.195360354184961</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="28" t="n">
         <v>41.38553303938742</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="28" t="n">
         <v>2.977838236684201</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>IE00B5BMR087</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>CSPX.L</t>
         </is>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D12" s="32" t="n">
         <v>12.2486210102208</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="32" t="n">
         <v>18.22866819217636</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="32" t="n">
         <v>2.23276048207035</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>IE00B4L5Y983</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>EUNL.DE</t>
         </is>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="28" t="n">
         <v>7.24268669834837</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="28" t="n">
         <v>21.98469200912787</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="28" t="n">
         <v>1.592282363817961</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="32" t="n">
         <v>6.058544321622511</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="62" t="inlineStr">
+      <c r="A16" s="61" t="inlineStr">
         <is>
           <t>Breakdown by Asset Class</t>
         </is>
@@ -5199,13 +5194,13 @@
           <t>Equities</t>
         </is>
       </c>
-      <c r="B18" s="28" t="n">
+      <c r="B18" s="27" t="n">
         <v>53914.70513029613</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="28" t="n">
         <v>99.7551406575963</v>
       </c>
-      <c r="D18" s="27" t="n">
+      <c r="D18" s="26" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5215,50 +5210,50 @@
           <t>Fixed Income</t>
         </is>
       </c>
-      <c r="B19" s="32" t="n">
+      <c r="B19" s="31" t="n">
         <v>16691.19226558396</v>
       </c>
-      <c r="C19" s="33" t="n">
+      <c r="C19" s="32" t="n">
         <v>66.70169400120878</v>
       </c>
-      <c r="D19" s="31" t="n">
+      <c r="D19" s="30" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="B20" s="28" t="n">
+      <c r="B20" s="27" t="n">
         <v>6922.177576772301</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="28" t="n">
         <v>56.9654779313447</v>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Equivalents</t>
         </is>
       </c>
-      <c r="B21" s="32" t="n">
+      <c r="B21" s="31" t="n">
         <v>5000</v>
       </c>
-      <c r="C21" s="33" t="n">
+      <c r="C21" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="31" t="n">
+      <c r="D21" s="30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="62" t="inlineStr">
+      <c r="A23" s="61" t="inlineStr">
         <is>
           <t>Breakdown by Geography (Equity Only)</t>
         </is>
@@ -5287,36 +5282,36 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="28" t="n">
         <v>41.22858361399044</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="28" t="n">
         <v>21.25341157482235</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="65" t="inlineStr">
+      <c r="A26" s="64" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="B26" s="33" t="n">
+      <c r="B26" s="32" t="n">
         <v>15.67502157315777</v>
       </c>
-      <c r="C26" s="33" t="n">
+      <c r="C26" s="32" t="n">
         <v>32.91272521018982</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>Eurozone EMU</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="28" t="n">
         <v>9.631770299638772</v>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="28" t="n">
         <v>30.19738978539465</v>
       </c>
     </row>
@@ -5326,23 +5321,23 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="B28" s="33" t="n">
+      <c r="B28" s="32" t="n">
         <v>24.84297679518155</v>
       </c>
-      <c r="C28" s="33" t="n">
+      <c r="C28" s="32" t="n">
         <v>164.3209990107638</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>Dev ex-USA ex-EMU ex-JP</t>
         </is>
       </c>
-      <c r="B29" s="29" t="n">
+      <c r="B29" s="28" t="n">
         <v>8.621647718031447</v>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="28" t="n">
         <v>30.19738978539465</v>
       </c>
     </row>

--- a/output/sample/portfolio_dashboard_sample.xlsx
+++ b/output/sample/portfolio_dashboard_sample.xlsx
@@ -82,7 +82,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00D97706"/>
+      <color rgb="0016A34A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -100,7 +100,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00DC2626"/>
+      <color rgb="00D97706"/>
       <sz val="10"/>
     </font>
     <font>
@@ -112,7 +112,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0015803D"/>
+      <color rgb="00DC2626"/>
       <sz val="10"/>
     </font>
     <font>
@@ -125,6 +125,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00C2410C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
       <sz val="10"/>
     </font>
     <font>
@@ -154,12 +160,6 @@
       <i val="1"/>
       <color rgb="0064748B"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="0016A34A"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -258,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -278,6 +278,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -296,146 +302,155 @@
     <xf numFmtId="2" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="9" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -806,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -869,345 +884,378 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Total Gain (EUR)</t>
+          <t>Invested Value (EUR)</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>28388.07497265239</v>
+        <v>77528.07497265239</v>
       </c>
       <c r="D6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>Cash (EUR)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Cash Target (EUR)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Cash Δ vs Target (EUR)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Total Gain (EUR)</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>28388.07497265239</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
           <t>RTD (%)</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B11" s="12" t="n">
         <v>52.43456773670556</v>
       </c>
-      <c r="D7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="D8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="D9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="D12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>ALLOCATION</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Asset Class</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Actual %</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Target %</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Geography (Equity)</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Actual %</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>Target %</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
-        <v>65.32892612382153</v>
-      </c>
-      <c r="C12" s="14" t="n">
+      <c r="B16" s="15" t="n">
+        <v>69.54216927134365</v>
+      </c>
+      <c r="C16" s="16" t="n">
         <v>68</v>
       </c>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="F16" s="17" t="n">
         <v>41.22858361399044</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G16" s="16" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Fixed Income</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
-        <v>20.22486562435265</v>
-      </c>
-      <c r="C13" s="18" t="n">
+      <c r="B17" s="19" t="n">
+        <v>21.52922315106068</v>
+      </c>
+      <c r="C17" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F17" s="22" t="n">
         <v>24.84297679518155</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G17" s="20" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
-        <v>8.387663930203299</v>
-      </c>
-      <c r="C14" s="14" t="n">
+      <c r="B18" s="24" t="n">
+        <v>8.928607577595679</v>
+      </c>
+      <c r="C18" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F18" s="24" t="n">
         <v>15.67502157315777</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G18" s="16" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>Cash &amp; Cash Equivalents</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="n">
-        <v>6.058544321622511</v>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
+    <row r="19">
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>Eurozone EMU</t>
         </is>
       </c>
-      <c r="F15" s="23" t="n">
+      <c r="F19" s="19" t="n">
         <v>9.631770299638772</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G19" s="20" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="16">
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="24" t="inlineStr">
+    <row r="20">
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>Dev ex-USA ex-EMU ex-JP</t>
         </is>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F20" s="24" t="n">
         <v>8.621647718031447</v>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="G20" s="16" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="17">
-      <c r="D17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="D18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21">
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>TOP 5 HOLDINGS</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Value €</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
-      <c r="B21" s="27" t="n">
+      <c r="B25" s="29" t="n">
         <v>12651.19995117188</v>
       </c>
-      <c r="C21" s="28" t="n">
+      <c r="C25" s="30" t="n">
         <v>15.32957112517667</v>
       </c>
-      <c r="D21" s="29" t="n"/>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
-      <c r="B22" s="31" t="n">
+      <c r="B26" s="33" t="n">
         <v>12262.46404320002</v>
       </c>
-      <c r="C22" s="32" t="n">
+      <c r="C26" s="34" t="n">
         <v>14.85853637960594</v>
       </c>
-      <c r="D22" s="29" t="n"/>
-      <c r="E22" s="33" t="inlineStr">
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="35" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
         </is>
       </c>
-      <c r="B23" s="27" t="n">
+      <c r="B27" s="29" t="n">
         <v>10752.99987792969</v>
       </c>
-      <c r="C23" s="28" t="n">
+      <c r="C27" s="30" t="n">
         <v>13.02950527016769</v>
       </c>
-      <c r="D23" s="29" t="n"/>
-      <c r="E23" s="34" t="inlineStr">
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="36" t="inlineStr">
         <is>
           <t>Fixed Income</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
-      <c r="B24" s="31" t="n">
+      <c r="B28" s="33" t="n">
         <v>10108.55113043108</v>
       </c>
-      <c r="C24" s="32" t="n">
+      <c r="C28" s="34" t="n">
         <v>12.2486210102208</v>
       </c>
-      <c r="D24" s="29" t="n"/>
-      <c r="E24" s="33" t="inlineStr">
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="35" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
-      <c r="B25" s="27" t="n">
+      <c r="B29" s="29" t="n">
         <v>7170.840225219727</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C29" s="30" t="n">
         <v>8.688970665553452</v>
       </c>
-      <c r="D25" s="29" t="n"/>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="D26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="35" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-10 16:30 v2.0</t>
+    <row r="30">
+      <c r="D30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="37" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-10 16:57 v2.0</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A14:H14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1220,7 +1268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1240,7 +1288,7 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>●  Action needed — largest deviation 16.8% (&gt;5.0%). Rebalancing recommended.</t>
         </is>
@@ -1280,773 +1328,846 @@
       <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>Status color based on delta after rebalancing vs target. Threshold ±2.5% (green), ±5.0% (amber), beyond (red).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>Asset Allocation</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Current %</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Target %</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Post-rebal %</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Delta after rebal (pp)</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>Cash &amp; Cash Equivalents</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>6.058544321622511</v>
-      </c>
-      <c r="C14" s="14" t="n">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>21.52922315106068</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>21.52922315106068</v>
+      </c>
+      <c r="E14" s="41" t="n">
+        <v>-4.47077684893932</v>
+      </c>
+      <c r="F14" s="42" t="inlineStr">
+        <is>
+          <t>● Drift</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n">
+        <v>8.928607577595679</v>
+      </c>
+      <c r="C15" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>8.928607577595679</v>
+      </c>
+      <c r="E15" s="43" t="n">
+        <v>3.928607577595679</v>
+      </c>
+      <c r="F15" s="44" t="inlineStr">
+        <is>
+          <t>● Drift</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Equities</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n">
+        <v>69.54216927134365</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>69.54216927134364</v>
+      </c>
+      <c r="E16" s="45" t="n">
+        <v>1.542169271343639</v>
+      </c>
+      <c r="F16" s="46" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>Alternative</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="26" t="inlineStr"/>
-      <c r="E14" s="39" t="n">
-        <v>6.058544321622511</v>
-      </c>
-      <c r="F14" s="40" t="inlineStr">
+      <c r="C17" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F17" s="48" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="46" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t>Geography (equity only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Current %</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Target %</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Post-rebal %</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Delta after rebal (pp)</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n">
+        <v>24.84297679518155</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>24.84297679518155</v>
+      </c>
+      <c r="E22" s="49" t="n">
+        <v>16.84297679518155</v>
+      </c>
+      <c r="F22" s="50" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="30" t="inlineStr">
-        <is>
-          <t>Fixed Income</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="n">
-        <v>20.22486562435265</v>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>26</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>20.22486562435265</v>
-      </c>
-      <c r="E15" s="41" t="n">
-        <v>-5.775134375647347</v>
-      </c>
-      <c r="F15" s="42" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>41.22858361399044</v>
+      </c>
+      <c r="C23" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="D23" s="20" t="n">
+        <v>41.22858361399044</v>
+      </c>
+      <c r="E23" s="51" t="n">
+        <v>-13.77141638600956</v>
+      </c>
+      <c r="F23" s="52" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>8.387663930203299</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>8.387663930203299</v>
-      </c>
-      <c r="E16" s="43" t="n">
-        <v>3.387663930203299</v>
-      </c>
-      <c r="F16" s="44" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Emerging Markets</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>15.67502157315777</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>15.67502157315778</v>
+      </c>
+      <c r="E24" s="41" t="n">
+        <v>4.675021573157776</v>
+      </c>
+      <c r="F24" s="42" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>Equities</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="n">
-        <v>65.32892612382153</v>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>68</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>65.32892612382153</v>
-      </c>
-      <c r="E17" s="45" t="n">
-        <v>-2.671073876178468</v>
-      </c>
-      <c r="F17" s="46" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>Eurozone EMU</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n">
+        <v>9.631770299638772</v>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>9.631770299638774</v>
+      </c>
+      <c r="E25" s="43" t="n">
+        <v>-4.368229700361226</v>
+      </c>
+      <c r="F25" s="44" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
-        <is>
-          <t>Alternative</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F18" s="48" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Dev ex-USA ex-EMU ex-JP</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n">
+        <v>8.621647718031447</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>8.621647718031449</v>
+      </c>
+      <c r="E26" s="41" t="n">
+        <v>-3.378352281968551</v>
+      </c>
+      <c r="F26" s="42" t="inlineStr">
+        <is>
+          <t>● Drift</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>Per-Holding Equity Targets</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Current %</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Target %</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Post-rebal %</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Delta after rebal (pp)</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>CNKY.L</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="n">
+        <v>22.74419198540586</v>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>22.74419198540586</v>
+      </c>
+      <c r="E30" s="49" t="n">
+        <v>12.74419198540586</v>
+      </c>
+      <c r="F30" s="50" t="inlineStr">
+        <is>
+          <t>● Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>VERX.DE</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n">
+        <v>10.65460686086223</v>
+      </c>
+      <c r="C31" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>10.65460686086223</v>
+      </c>
+      <c r="E31" s="43" t="n">
+        <v>-4.345393139137771</v>
+      </c>
+      <c r="F31" s="44" t="inlineStr">
+        <is>
+          <t>● Drift</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>EUNL.DE</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="n">
+        <v>11.086492811195</v>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>11.086492811195</v>
+      </c>
+      <c r="E32" s="41" t="n">
+        <v>-3.913507188804996</v>
+      </c>
+      <c r="F32" s="42" t="inlineStr">
+        <is>
+          <t>● Drift</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>XMME.DE</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n">
+        <v>13.30034210126884</v>
+      </c>
+      <c r="C33" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>13.30034210126884</v>
+      </c>
+      <c r="E33" s="47" t="n">
+        <v>-1.699657898731161</v>
+      </c>
+      <c r="F33" s="48" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="50" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>VWCE.DE</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="n">
+        <v>23.46521217281558</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>23.46521217281558</v>
+      </c>
+      <c r="E34" s="45" t="n">
+        <v>-1.53478782718442</v>
+      </c>
+      <c r="F34" s="46" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="38" t="inlineStr">
-        <is>
-          <t>Geography (equity only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>CSPX.L</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="n">
+        <v>18.74915406845249</v>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="D35" s="20" t="n">
+        <v>18.74915406845249</v>
+      </c>
+      <c r="E35" s="47" t="n">
+        <v>-1.250845931547513</v>
+      </c>
+      <c r="F35" s="48" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="inlineStr">
+        <is>
+          <t>Per-Holding Fixed Income Targets</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Current %</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Target %</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>Post-rebal %</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>Delta after rebal (pp)</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="26" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="n">
-        <v>24.84297679518155</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>24.84297679518155</v>
-      </c>
-      <c r="E23" s="39" t="n">
-        <v>16.84297679518155</v>
-      </c>
-      <c r="F23" s="40" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>IEAG.L</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="n">
+        <v>64.42319821635272</v>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>64.42319821635272</v>
+      </c>
+      <c r="E39" s="49" t="n">
+        <v>-5.576801783647284</v>
+      </c>
+      <c r="F39" s="50" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="n">
-        <v>41.22858361399044</v>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>55</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>41.22858361399044</v>
-      </c>
-      <c r="E24" s="41" t="n">
-        <v>-13.77141638600956</v>
-      </c>
-      <c r="F24" s="42" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>IBTM.L</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n">
+        <v>35.57680178364728</v>
+      </c>
+      <c r="C40" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="D40" s="20" t="n">
+        <v>35.57680178364728</v>
+      </c>
+      <c r="E40" s="51" t="n">
+        <v>5.576801783647284</v>
+      </c>
+      <c r="F40" s="52" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>Emerging Markets</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="n">
-        <v>15.67502157315777</v>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>15.67502157315778</v>
-      </c>
-      <c r="E25" s="43" t="n">
-        <v>4.675021573157776</v>
-      </c>
-      <c r="F25" s="44" t="inlineStr">
-        <is>
-          <t>● Drift</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>Eurozone EMU</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="n">
-        <v>9.631770299638772</v>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>9.631770299638774</v>
-      </c>
-      <c r="E26" s="45" t="n">
-        <v>-4.368229700361226</v>
-      </c>
-      <c r="F26" s="46" t="inlineStr">
-        <is>
-          <t>● Drift</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>Dev ex-USA ex-EMU ex-JP</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="n">
-        <v>8.621647718031447</v>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>8.621647718031449</v>
-      </c>
-      <c r="E27" s="43" t="n">
-        <v>-3.378352281968551</v>
-      </c>
-      <c r="F27" s="44" t="inlineStr">
-        <is>
-          <t>● Drift</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="38" t="inlineStr">
-        <is>
-          <t>Per-Holding Equity Targets</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>CASH BUFFER</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="inlineStr">
+        <is>
+          <t>Cash is not part of the invested allocation. The solver targets 3000.0 EUR as cash buffer; any excess or shortfall drives buy/sell suggestions above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>Current %</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Target %</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Post-rebal %</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>Delta after rebal (pp)</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>Current (EUR)</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>Target (EUR)</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>Post-rebal (EUR)</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>Delta (EUR)</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="26" t="inlineStr">
-        <is>
-          <t>CNKY.L</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="n">
-        <v>22.74419198540586</v>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>22.74419198540586</v>
-      </c>
-      <c r="E31" s="39" t="n">
-        <v>12.74419198540586</v>
-      </c>
-      <c r="F31" s="40" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>Cash Buffer</t>
+        </is>
+      </c>
+      <c r="B48" s="53" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C48" s="53" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D48" s="53" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E48" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F48" s="50" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>VERX.DE</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="n">
-        <v>10.65460686086223</v>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>10.65460686086223</v>
-      </c>
-      <c r="E32" s="45" t="n">
-        <v>-4.345393139137771</v>
-      </c>
-      <c r="F32" s="46" t="inlineStr">
-        <is>
-          <t>● Drift</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="26" t="inlineStr">
-        <is>
-          <t>EUNL.DE</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="n">
-        <v>11.086492811195</v>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>11.086492811195</v>
-      </c>
-      <c r="E33" s="43" t="n">
-        <v>-3.913507188804996</v>
-      </c>
-      <c r="F33" s="44" t="inlineStr">
-        <is>
-          <t>● Drift</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="30" t="inlineStr">
-        <is>
-          <t>XMME.DE</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="n">
-        <v>13.30034210126884</v>
-      </c>
-      <c r="C34" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>13.30034210126884</v>
-      </c>
-      <c r="E34" s="49" t="n">
-        <v>-1.699657898731161</v>
-      </c>
-      <c r="F34" s="50" t="inlineStr">
-        <is>
-          <t>● Aligned</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="26" t="inlineStr">
-        <is>
-          <t>VWCE.DE</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="n">
-        <v>23.46521217281558</v>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>23.46521217281558</v>
-      </c>
-      <c r="E35" s="47" t="n">
-        <v>-1.53478782718442</v>
-      </c>
-      <c r="F35" s="48" t="inlineStr">
-        <is>
-          <t>● Aligned</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="30" t="inlineStr">
-        <is>
-          <t>CSPX.L</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="n">
-        <v>18.74915406845249</v>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>18.74915406845249</v>
-      </c>
-      <c r="E36" s="49" t="n">
-        <v>-1.250845931547513</v>
-      </c>
-      <c r="F36" s="50" t="inlineStr">
-        <is>
-          <t>● Aligned</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="38" t="inlineStr">
-        <is>
-          <t>Per-Holding Fixed Income Targets</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>Current %</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>Target %</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>Post-rebal %</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>Delta after rebal (pp)</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="26" t="inlineStr">
-        <is>
-          <t>IEAG.L</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="n">
-        <v>64.42319821635272</v>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>64.42319821635272</v>
-      </c>
-      <c r="E40" s="39" t="n">
-        <v>-5.576801783647284</v>
-      </c>
-      <c r="F40" s="40" t="inlineStr">
-        <is>
-          <t>● Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t>IBTM.L</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="n">
-        <v>35.57680178364728</v>
-      </c>
-      <c r="C41" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>35.57680178364728</v>
-      </c>
-      <c r="E41" s="41" t="n">
-        <v>5.576801783647284</v>
-      </c>
-      <c r="F41" s="42" t="inlineStr">
-        <is>
-          <t>● Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>SOLVER PARAMETERS</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="G46" s="11" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="51" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="55" t="inlineStr">
         <is>
           <t>Alert threshold</t>
         </is>
       </c>
-      <c r="B47" s="26" t="inlineStr">
+      <c r="B53" s="28" t="inlineStr">
         <is>
           <t>±2.5%</t>
         </is>
       </c>
-      <c r="G47" s="26" t="inlineStr">
+      <c r="G53" s="28" t="inlineStr">
         <is>
           <t>Deviation at which a category turns amber (green below, red beyond 2×)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="52" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="56" t="inlineStr">
         <is>
           <t>Solver tolerance</t>
         </is>
       </c>
-      <c r="B48" s="30" t="inlineStr">
+      <c r="B54" s="32" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G48" s="30" t="inlineStr">
+      <c r="G54" s="32" t="inlineStr">
         <is>
           <t>Actual tolerance the optimizer converged at (progressive up to max)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="51" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="55" t="inlineStr">
         <is>
           <t>Max tolerance</t>
         </is>
       </c>
-      <c r="B49" s="26" t="inlineStr">
+      <c r="B55" s="28" t="inlineStr">
         <is>
           <t>±2.0%</t>
         </is>
       </c>
-      <c r="G49" s="26" t="inlineStr">
+      <c r="G55" s="28" t="inlineStr">
         <is>
           <t>Cap on solver tolerance (from config.rebalancing_max_tolerance_pctg)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="52" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="56" t="inlineStr">
         <is>
           <t>Min transaction</t>
         </is>
       </c>
-      <c r="B50" s="30" t="inlineStr">
+      <c r="B56" s="32" t="inlineStr">
         <is>
           <t>0.0 EUR</t>
         </is>
       </c>
-      <c r="G50" s="30" t="inlineStr">
+      <c r="G56" s="32" t="inlineStr">
         <is>
           <t>Trades below this amount are skipped</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="51" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="55" t="inlineStr">
         <is>
           <t>Lump sum</t>
         </is>
       </c>
-      <c r="B51" s="26" t="inlineStr">
+      <c r="B57" s="28" t="inlineStr">
         <is>
           <t>1000.0 EUR</t>
         </is>
       </c>
-      <c r="G51" s="26" t="inlineStr">
+      <c r="G57" s="28" t="inlineStr">
         <is>
           <t>Additional cash to deploy in the rebalance</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="52" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="56" t="inlineStr">
+        <is>
+          <t>Cash buffer target</t>
+        </is>
+      </c>
+      <c r="B58" s="32" t="inlineStr">
+        <is>
+          <t>3000.0 EUR</t>
+        </is>
+      </c>
+      <c r="G58" s="32" t="inlineStr">
+        <is>
+          <t>Absolute cash target used by the solver (from target_cash_buffer_eur)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="55" t="inlineStr">
         <is>
           <t>No-sell mode</t>
         </is>
       </c>
-      <c r="B52" s="30" t="inlineStr">
+      <c r="B59" s="28" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="G52" s="30" t="inlineStr">
+      <c r="G59" s="28" t="inlineStr">
         <is>
           <t>If enabled, the solver can only buy, never sell</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="35" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-10 16:30 v2.0</t>
+    <row r="61">
+      <c r="A61" s="37" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-10 16:57 v2.0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="A44:G44"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="A45:G45"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2059,7 +2180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2090,896 +2211,929 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>ISIN</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Asset Class</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Security Type</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>Avg Price</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>Cost Basis (EUR)</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t>Value (EUR)</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>% of Portfolio</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
+        <is>
+          <t>% of Invested</t>
+        </is>
+      </c>
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>% of Asset Class</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t>Gain (EUR)</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t>Gain %</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="Q3" s="13" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="R3" s="13" t="inlineStr">
         <is>
           <t>Geo Source</t>
         </is>
       </c>
-      <c r="R3" s="11" t="inlineStr">
+      <c r="S3" s="13" t="inlineStr">
         <is>
           <t>Data Source</t>
         </is>
       </c>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="T3" s="13" t="inlineStr">
         <is>
           <t>Fetch Time</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>VWCE.DE</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>IE00B3RBWM25</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F4" s="26" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G4" s="27" t="n">
+      <c r="G4" s="29" t="n">
         <v>80</v>
       </c>
-      <c r="H4" s="27" t="n">
+      <c r="H4" s="29" t="n">
         <v>128</v>
       </c>
-      <c r="I4" s="27" t="n">
+      <c r="I4" s="29" t="n">
         <v>158.1399993896484</v>
       </c>
-      <c r="J4" s="27" t="n">
+      <c r="J4" s="29" t="n">
         <v>10240</v>
       </c>
-      <c r="K4" s="27" t="n">
+      <c r="K4" s="29" t="n">
         <v>12651.19995117188</v>
       </c>
-      <c r="L4" s="28" t="n">
+      <c r="L4" s="30" t="n">
         <v>15.32957112517667</v>
       </c>
-      <c r="M4" s="28" t="n">
+      <c r="M4" s="30" t="n">
+        <v>16.31821756909934</v>
+      </c>
+      <c r="N4" s="30" t="n">
         <v>23.46521217281558</v>
       </c>
-      <c r="N4" s="27" t="n">
+      <c r="O4" s="29" t="n">
         <v>2411.199951171875</v>
       </c>
-      <c r="O4" s="28" t="n">
+      <c r="P4" s="30" t="n">
         <v>23.54687452316284</v>
       </c>
-      <c r="P4" s="26" t="inlineStr">
+      <c r="Q4" s="28" t="inlineStr">
         <is>
           <t>USA: 62, Dev ex-USA ex-EMU ex-JP: 13, Emerging Markets: 10, Eurozone EMU: 7, Japan: 6</t>
         </is>
       </c>
-      <c r="Q4" s="26" t="inlineStr">
+      <c r="R4" s="28" t="inlineStr">
         <is>
           <t>index_geo_allocation (index: FTSE All-World)</t>
         </is>
       </c>
-      <c r="R4" s="26" t="inlineStr">
+      <c r="S4" s="28" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S4" s="26" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:30</t>
+      <c r="T4" s="28" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:57</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>CNKY.L</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>IE00B52MJD48</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="E5" s="30" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="33" t="n">
         <v>35</v>
       </c>
-      <c r="H5" s="31" t="n">
+      <c r="H5" s="33" t="n">
         <v>64</v>
       </c>
-      <c r="I5" s="31" t="n">
+      <c r="I5" s="33" t="n">
         <v>350.3561155200005</v>
       </c>
-      <c r="J5" s="31" t="n">
+      <c r="J5" s="33" t="n">
         <v>2240</v>
       </c>
-      <c r="K5" s="31" t="n">
+      <c r="K5" s="33" t="n">
         <v>12262.46404320002</v>
       </c>
-      <c r="L5" s="32" t="n">
+      <c r="L5" s="34" t="n">
         <v>14.85853637960594</v>
       </c>
-      <c r="M5" s="32" t="n">
+      <c r="M5" s="34" t="n">
+        <v>15.81680448989032</v>
+      </c>
+      <c r="N5" s="34" t="n">
         <v>22.74419198540586</v>
       </c>
-      <c r="N5" s="31" t="n">
+      <c r="O5" s="33" t="n">
         <v>10022.46404320002</v>
       </c>
-      <c r="O5" s="32" t="n">
+      <c r="P5" s="34" t="n">
         <v>447.4314305000007</v>
       </c>
-      <c r="P5" s="30" t="inlineStr">
+      <c r="Q5" s="32" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="Q5" s="30" t="inlineStr">
+      <c r="R5" s="32" t="inlineStr">
         <is>
           <t>yfinance_top_holdings</t>
         </is>
       </c>
-      <c r="R5" s="30" t="inlineStr">
+      <c r="S5" s="32" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S5" s="30" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:30</t>
+      <c r="T5" s="32" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:57</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>CSPX.L</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>IE00B5BMR087</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="H6" s="27" t="n">
+      <c r="H6" s="29" t="n">
         <v>570</v>
       </c>
-      <c r="I6" s="27" t="n">
+      <c r="I6" s="29" t="n">
         <v>673.9034086954052</v>
       </c>
-      <c r="J6" s="27" t="n">
+      <c r="J6" s="29" t="n">
         <v>8550</v>
       </c>
-      <c r="K6" s="27" t="n">
+      <c r="K6" s="29" t="n">
         <v>10108.55113043108</v>
       </c>
-      <c r="L6" s="28" t="n">
+      <c r="L6" s="30" t="n">
         <v>12.2486210102208</v>
       </c>
-      <c r="M6" s="28" t="n">
+      <c r="M6" s="30" t="n">
+        <v>13.03856845922824</v>
+      </c>
+      <c r="N6" s="30" t="n">
         <v>18.74915406845249</v>
       </c>
-      <c r="N6" s="27" t="n">
+      <c r="O6" s="29" t="n">
         <v>1558.551130431078</v>
       </c>
-      <c r="O6" s="28" t="n">
+      <c r="P6" s="30" t="n">
         <v>18.22866819217636</v>
       </c>
-      <c r="P6" s="26" t="inlineStr">
+      <c r="Q6" s="28" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q6" s="26" t="inlineStr">
+      <c r="R6" s="28" t="inlineStr">
         <is>
           <t>index_geo_allocation (index: S&amp;P 500)</t>
         </is>
       </c>
-      <c r="R6" s="26" t="inlineStr">
+      <c r="S6" s="28" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S6" s="26" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:30</t>
+      <c r="T6" s="28" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:57</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>XMME.DE</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>LU0292107645</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G7" s="31" t="n">
+      <c r="G7" s="33" t="n">
         <v>90</v>
       </c>
-      <c r="H7" s="31" t="n">
+      <c r="H7" s="33" t="n">
         <v>56</v>
       </c>
-      <c r="I7" s="31" t="n">
+      <c r="I7" s="33" t="n">
         <v>79.67600250244141</v>
       </c>
-      <c r="J7" s="31" t="n">
+      <c r="J7" s="33" t="n">
         <v>5040</v>
       </c>
-      <c r="K7" s="31" t="n">
+      <c r="K7" s="33" t="n">
         <v>7170.840225219727</v>
       </c>
-      <c r="L7" s="32" t="n">
+      <c r="L7" s="34" t="n">
         <v>8.688970665553452</v>
       </c>
-      <c r="M7" s="32" t="n">
+      <c r="M7" s="34" t="n">
+        <v>9.249346417732159</v>
+      </c>
+      <c r="N7" s="34" t="n">
         <v>13.30034210126884</v>
       </c>
-      <c r="N7" s="31" t="n">
+      <c r="O7" s="33" t="n">
         <v>2130.840225219727</v>
       </c>
-      <c r="O7" s="32" t="n">
+      <c r="P7" s="34" t="n">
         <v>42.2785758972168</v>
       </c>
-      <c r="P7" s="30" t="inlineStr">
+      <c r="Q7" s="32" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="Q7" s="30" t="inlineStr">
+      <c r="R7" s="32" t="inlineStr">
         <is>
           <t>index_geo_allocation (index: MSCI Emerging Markets)</t>
         </is>
       </c>
-      <c r="R7" s="30" t="inlineStr">
+      <c r="S7" s="32" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S7" s="30" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:30</t>
+      <c r="T7" s="32" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:57</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>EUNL.DE</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>IE00B4L5Y983</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="H8" s="29" t="n">
         <v>98</v>
       </c>
-      <c r="I8" s="27" t="n">
+      <c r="I8" s="29" t="n">
         <v>119.5449981689453</v>
       </c>
-      <c r="J8" s="27" t="n">
+      <c r="J8" s="29" t="n">
         <v>4900</v>
       </c>
-      <c r="K8" s="27" t="n">
+      <c r="K8" s="29" t="n">
         <v>5977.249908447266</v>
       </c>
-      <c r="L8" s="28" t="n">
+      <c r="L8" s="30" t="n">
         <v>7.24268669834837</v>
       </c>
-      <c r="M8" s="28" t="n">
+      <c r="M8" s="30" t="n">
+        <v>7.709787597016575</v>
+      </c>
+      <c r="N8" s="30" t="n">
         <v>11.086492811195</v>
       </c>
-      <c r="N8" s="27" t="n">
+      <c r="O8" s="29" t="n">
         <v>1077.249908447266</v>
       </c>
-      <c r="O8" s="28" t="n">
+      <c r="P8" s="30" t="n">
         <v>21.98469200912787</v>
       </c>
-      <c r="P8" s="26" t="inlineStr">
+      <c r="Q8" s="28" t="inlineStr">
         <is>
           <t>USA: 71, Dev ex-USA ex-EMU ex-JP: 14, Eurozone EMU: 8, Japan: 6</t>
         </is>
       </c>
-      <c r="Q8" s="26" t="inlineStr">
+      <c r="R8" s="28" t="inlineStr">
         <is>
           <t>index_geo_allocation (index: MSCI World)</t>
         </is>
       </c>
-      <c r="R8" s="26" t="inlineStr">
+      <c r="S8" s="28" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S8" s="26" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:30</t>
+      <c r="T8" s="28" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:57</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>VERX.DE</t>
         </is>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>IE00B945VV12</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G9" s="31" t="n">
+      <c r="G9" s="33" t="n">
         <v>120</v>
       </c>
-      <c r="H9" s="31" t="n">
+      <c r="H9" s="33" t="n">
         <v>33</v>
       </c>
-      <c r="I9" s="31" t="n">
+      <c r="I9" s="33" t="n">
         <v>47.86999893188477</v>
       </c>
-      <c r="J9" s="31" t="n">
+      <c r="J9" s="33" t="n">
         <v>3960</v>
       </c>
-      <c r="K9" s="31" t="n">
+      <c r="K9" s="33" t="n">
         <v>5744.399871826172</v>
       </c>
-      <c r="L9" s="32" t="n">
+      <c r="L9" s="34" t="n">
         <v>6.960540244916307</v>
       </c>
-      <c r="M9" s="32" t="n">
+      <c r="M9" s="34" t="n">
+        <v>7.409444738377004</v>
+      </c>
+      <c r="N9" s="34" t="n">
         <v>10.65460686086223</v>
       </c>
-      <c r="N9" s="31" t="n">
+      <c r="O9" s="33" t="n">
         <v>1784.399871826172</v>
       </c>
-      <c r="O9" s="32" t="n">
+      <c r="P9" s="34" t="n">
         <v>45.06060282389323</v>
       </c>
-      <c r="P9" s="30" t="inlineStr">
+      <c r="Q9" s="32" t="inlineStr">
         <is>
           <t>Eurozone EMU: 64, Dev ex-USA ex-EMU ex-JP: 35</t>
         </is>
       </c>
-      <c r="Q9" s="30" t="inlineStr">
+      <c r="R9" s="32" t="inlineStr">
         <is>
           <t>yfinance_top_holdings</t>
         </is>
       </c>
-      <c r="R9" s="30" t="inlineStr">
+      <c r="S9" s="32" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S9" s="30" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:30</t>
+      <c r="T9" s="32" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:57</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>IEAG.L</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>IE00B3F81R35</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Fixed Income</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>Bond ETF</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="29" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H10" s="29" t="n">
         <v>56</v>
       </c>
-      <c r="I10" s="27" t="n">
+      <c r="I10" s="29" t="n">
         <v>107.5299987792969</v>
       </c>
-      <c r="J10" s="27" t="n">
+      <c r="J10" s="29" t="n">
         <v>5600</v>
       </c>
-      <c r="K10" s="27" t="n">
+      <c r="K10" s="29" t="n">
         <v>10752.99987792969</v>
       </c>
-      <c r="L10" s="28" t="n">
+      <c r="L10" s="30" t="n">
         <v>13.02950527016769</v>
       </c>
-      <c r="M10" s="28" t="n">
+      <c r="M10" s="30" t="n">
+        <v>13.86981410504872</v>
+      </c>
+      <c r="N10" s="30" t="n">
         <v>64.42319821635272</v>
       </c>
-      <c r="N10" s="27" t="n">
+      <c r="O10" s="29" t="n">
         <v>5152.999877929688</v>
       </c>
-      <c r="O10" s="28" t="n">
+      <c r="P10" s="30" t="n">
         <v>92.01785496303013</v>
       </c>
-      <c r="P10" s="26" t="inlineStr">
+      <c r="Q10" s="28" t="inlineStr">
         <is>
           <t>Eurozone EMU</t>
         </is>
       </c>
-      <c r="Q10" s="26" t="inlineStr">
+      <c r="R10" s="28" t="inlineStr">
         <is>
           <t>index_geo_allocation (ticker)</t>
         </is>
       </c>
-      <c r="R10" s="26" t="inlineStr">
+      <c r="S10" s="28" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S10" s="26" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:30</t>
+      <c r="T10" s="28" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:57</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>IBTM.L</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>IE00B1FZS798</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Fixed Income</t>
         </is>
       </c>
-      <c r="E11" s="30" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>Bond ETF</t>
         </is>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="32" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="G11" s="31" t="n">
+      <c r="G11" s="33" t="n">
         <v>40</v>
       </c>
-      <c r="H11" s="31" t="n">
+      <c r="H11" s="33" t="n">
         <v>105</v>
       </c>
-      <c r="I11" s="31" t="n">
+      <c r="I11" s="33" t="n">
         <v>148.4548096913568</v>
       </c>
-      <c r="J11" s="31" t="n">
+      <c r="J11" s="33" t="n">
         <v>4200</v>
       </c>
-      <c r="K11" s="31" t="n">
+      <c r="K11" s="33" t="n">
         <v>5938.192387654271</v>
       </c>
-      <c r="L11" s="32" t="n">
+      <c r="L11" s="34" t="n">
         <v>7.195360354184961</v>
       </c>
-      <c r="M11" s="32" t="n">
+      <c r="M11" s="34" t="n">
+        <v>7.65940904601196</v>
+      </c>
+      <c r="N11" s="34" t="n">
         <v>35.57680178364728</v>
       </c>
-      <c r="N11" s="31" t="n">
+      <c r="O11" s="33" t="n">
         <v>1738.192387654271</v>
       </c>
-      <c r="O11" s="32" t="n">
+      <c r="P11" s="34" t="n">
         <v>41.38553303938742</v>
       </c>
-      <c r="P11" s="30" t="inlineStr">
+      <c r="Q11" s="32" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="Q11" s="30" t="inlineStr">
+      <c r="R11" s="32" t="inlineStr">
         <is>
           <t>not_available</t>
         </is>
       </c>
-      <c r="R11" s="30" t="inlineStr">
+      <c r="S11" s="32" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S11" s="30" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:30</t>
+      <c r="T11" s="32" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:57</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Equivalents</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>Money Market Instrument</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="G12" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="H12" s="27" t="n">
+      <c r="H12" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="27" t="n">
+      <c r="I12" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="27" t="n">
+      <c r="J12" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="K12" s="27" t="n">
+      <c r="K12" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="L12" s="28" t="n">
+      <c r="L12" s="30" t="n">
         <v>6.058544321622511</v>
       </c>
-      <c r="M12" s="28" t="n">
+      <c r="M12" s="28" t="inlineStr"/>
+      <c r="N12" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="N12" s="27" t="n">
+      <c r="O12" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="28" t="n">
+      <c r="P12" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="26" t="inlineStr">
+      <c r="Q12" s="28" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="Q12" s="26" t="inlineStr">
+      <c r="R12" s="28" t="inlineStr">
         <is>
           <t>not_available</t>
         </is>
       </c>
-      <c r="R12" s="26" t="inlineStr">
+      <c r="S12" s="28" t="inlineStr">
         <is>
           <t>input_csv (no market data)</t>
         </is>
       </c>
-      <c r="S12" s="26" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:30</t>
+      <c r="T12" s="28" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:57</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>SGLD.L</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>IE00B579F325</t>
         </is>
       </c>
-      <c r="D13" s="53" t="inlineStr">
+      <c r="D13" s="57" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>Gold ETC</t>
         </is>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G13" s="31" t="n">
+      <c r="G13" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="H13" s="31" t="n">
+      <c r="H13" s="33" t="n">
         <v>245</v>
       </c>
-      <c r="I13" s="31" t="n">
+      <c r="I13" s="33" t="n">
         <v>384.5654209317945</v>
       </c>
-      <c r="J13" s="31" t="n">
+      <c r="J13" s="33" t="n">
         <v>4410</v>
       </c>
-      <c r="K13" s="31" t="n">
+      <c r="K13" s="33" t="n">
         <v>6922.177576772301</v>
       </c>
-      <c r="L13" s="32" t="n">
+      <c r="L13" s="34" t="n">
         <v>8.387663930203299</v>
       </c>
-      <c r="M13" s="32" t="n">
+      <c r="M13" s="34" t="n">
+        <v>8.928607577595679</v>
+      </c>
+      <c r="N13" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="N13" s="31" t="n">
+      <c r="O13" s="33" t="n">
         <v>2512.177576772301</v>
       </c>
-      <c r="O13" s="32" t="n">
+      <c r="P13" s="34" t="n">
         <v>56.9654779313447</v>
       </c>
-      <c r="P13" s="30" t="inlineStr">
+      <c r="Q13" s="32" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="Q13" s="30" t="inlineStr">
+      <c r="R13" s="32" t="inlineStr">
         <is>
           <t>not_available</t>
         </is>
       </c>
-      <c r="R13" s="30" t="inlineStr">
+      <c r="S13" s="32" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="S13" s="30" t="inlineStr">
-        <is>
-          <t>2026-05-10 16:30</t>
+      <c r="T13" s="32" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:57</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-10 16:30 v2.0</t>
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-10 16:57 v2.0</t>
         </is>
       </c>
     </row>
@@ -3029,1799 +3183,1799 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>Period returns (1D–5Y) and risk metrics calculated on available history per instrument (max 5 years). α/β computed vs S&amp;P 500.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>CAGR</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="13" t="inlineStr">
         <is>
           <t>Sortino</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t>Max DD</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="Q4" s="13" t="inlineStr">
         <is>
           <t>VaR 95%</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr">
+      <c r="R4" s="13" t="inlineStr">
         <is>
           <t>CVaR 95%</t>
         </is>
       </c>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="S4" s="13" t="inlineStr">
         <is>
           <t>α (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="T4" s="13" t="inlineStr">
         <is>
           <t>β (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr">
+      <c r="U4" s="13" t="inlineStr">
         <is>
           <t>Period Used</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="55" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>** TOTAL PORTFOLIO **</t>
         </is>
       </c>
-      <c r="B5" s="56" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="C5" s="57" t="n">
+      <c r="C5" s="61" t="n">
         <v>0.04</v>
       </c>
-      <c r="D5" s="57" t="n">
+      <c r="D5" s="61" t="n">
         <v>2.53</v>
       </c>
-      <c r="E5" s="57" t="n">
+      <c r="E5" s="61" t="n">
         <v>5.32</v>
       </c>
-      <c r="F5" s="57" t="n">
+      <c r="F5" s="61" t="n">
         <v>5.36</v>
       </c>
-      <c r="G5" s="57" t="n">
+      <c r="G5" s="61" t="n">
         <v>10.25</v>
       </c>
-      <c r="H5" s="57" t="n">
+      <c r="H5" s="61" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="I5" s="57" t="n">
+      <c r="I5" s="61" t="n">
         <v>24.25</v>
       </c>
-      <c r="J5" s="57" t="n">
+      <c r="J5" s="61" t="n">
         <v>51.75</v>
       </c>
-      <c r="K5" s="57" t="n">
+      <c r="K5" s="61" t="n">
         <v>48.59</v>
       </c>
-      <c r="L5" s="57" t="n">
+      <c r="L5" s="61" t="n">
         <v>8.25</v>
       </c>
-      <c r="M5" s="57" t="n">
+      <c r="M5" s="61" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="N5" s="57" t="n">
+      <c r="N5" s="61" t="n">
         <v>0.52</v>
       </c>
-      <c r="O5" s="57" t="n">
+      <c r="O5" s="61" t="n">
         <v>0.68</v>
       </c>
-      <c r="P5" s="58" t="n">
+      <c r="P5" s="62" t="n">
         <v>-13.91</v>
       </c>
-      <c r="Q5" s="58" t="n">
+      <c r="Q5" s="62" t="n">
         <v>-0.77</v>
       </c>
-      <c r="R5" s="58" t="n">
+      <c r="R5" s="62" t="n">
         <v>-1.22</v>
       </c>
-      <c r="S5" s="57" t="n">
+      <c r="S5" s="61" t="n">
         <v>2.92</v>
       </c>
-      <c r="T5" s="57" t="n">
+      <c r="T5" s="61" t="n">
         <v>0.15</v>
       </c>
-      <c r="U5" s="56" t="inlineStr">
+      <c r="U5" s="60" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>FTSE All-World</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C6" s="59" t="n">
+      <c r="C6" s="63" t="n">
         <v>-0.02</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="30" t="n">
         <v>1.69</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="30" t="n">
         <v>7.02</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="30" t="n">
         <v>6.17</v>
       </c>
-      <c r="G6" s="28" t="n">
+      <c r="G6" s="30" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="H6" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="I6" s="28" t="n">
+      <c r="I6" s="30" t="n">
         <v>26.86</v>
       </c>
-      <c r="J6" s="28" t="n">
+      <c r="J6" s="30" t="n">
         <v>65.69</v>
       </c>
-      <c r="K6" s="28" t="n">
+      <c r="K6" s="30" t="n">
         <v>74.83</v>
       </c>
-      <c r="L6" s="28" t="n">
+      <c r="L6" s="30" t="n">
         <v>11.84</v>
       </c>
-      <c r="M6" s="28" t="n">
+      <c r="M6" s="30" t="n">
         <v>14.13</v>
       </c>
-      <c r="N6" s="28" t="n">
+      <c r="N6" s="30" t="n">
         <v>0.55</v>
       </c>
-      <c r="O6" s="28" t="n">
+      <c r="O6" s="30" t="n">
         <v>0.75</v>
       </c>
-      <c r="P6" s="59" t="n">
+      <c r="P6" s="63" t="n">
         <v>-20.22</v>
       </c>
-      <c r="Q6" s="59" t="n">
+      <c r="Q6" s="63" t="n">
         <v>-1.4</v>
       </c>
-      <c r="R6" s="59" t="n">
+      <c r="R6" s="63" t="n">
         <v>-2.13</v>
       </c>
-      <c r="S6" s="28" t="n">
+      <c r="S6" s="30" t="n">
         <v>5.19</v>
       </c>
-      <c r="T6" s="28" t="n">
+      <c r="T6" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="U6" s="26" t="inlineStr">
+      <c r="U6" s="28" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>MSCI ACWI</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C7" s="60" t="n">
+      <c r="C7" s="64" t="n">
         <v>-0.15</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="34" t="n">
         <v>5.95</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="34" t="n">
         <v>5.22</v>
       </c>
-      <c r="G7" s="32" t="n">
+      <c r="G7" s="34" t="n">
         <v>7.4</v>
       </c>
-      <c r="H7" s="32" t="n">
+      <c r="H7" s="34" t="n">
         <v>8.07</v>
       </c>
-      <c r="I7" s="32" t="n">
+      <c r="I7" s="34" t="n">
         <v>21.67</v>
       </c>
-      <c r="J7" s="32" t="n">
+      <c r="J7" s="34" t="n">
         <v>58.3</v>
       </c>
-      <c r="K7" s="32" t="n">
+      <c r="K7" s="34" t="n">
         <v>63.02</v>
       </c>
-      <c r="L7" s="32" t="n">
+      <c r="L7" s="34" t="n">
         <v>10.07</v>
       </c>
-      <c r="M7" s="32" t="n">
+      <c r="M7" s="34" t="n">
         <v>15.1</v>
       </c>
-      <c r="N7" s="32" t="n">
+      <c r="N7" s="34" t="n">
         <v>0.4</v>
       </c>
-      <c r="O7" s="32" t="n">
+      <c r="O7" s="34" t="n">
         <v>0.57</v>
       </c>
-      <c r="P7" s="60" t="n">
+      <c r="P7" s="64" t="n">
         <v>-20.07</v>
       </c>
-      <c r="Q7" s="60" t="n">
+      <c r="Q7" s="64" t="n">
         <v>-1.44</v>
       </c>
-      <c r="R7" s="60" t="n">
+      <c r="R7" s="64" t="n">
         <v>-2.13</v>
       </c>
-      <c r="S7" s="60" t="n">
+      <c r="S7" s="64" t="n">
         <v>-0.74</v>
       </c>
-      <c r="T7" s="32" t="n">
+      <c r="T7" s="34" t="n">
         <v>0.78</v>
       </c>
-      <c r="U7" s="30" t="inlineStr">
+      <c r="U7" s="32" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>MSCI EAFE</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.68</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="30" t="n">
         <v>1.3</v>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="30" t="n">
         <v>0.84</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="30" t="n">
         <v>0.28</v>
       </c>
-      <c r="G8" s="28" t="n">
+      <c r="G8" s="30" t="n">
         <v>8.76</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="30" t="n">
         <v>6.77</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="I8" s="30" t="n">
         <v>20.7</v>
       </c>
-      <c r="J8" s="28" t="n">
+      <c r="J8" s="30" t="n">
         <v>45.1</v>
       </c>
-      <c r="K8" s="28" t="n">
+      <c r="K8" s="30" t="n">
         <v>56.74</v>
       </c>
-      <c r="L8" s="28" t="n">
+      <c r="L8" s="30" t="n">
         <v>9.42</v>
       </c>
-      <c r="M8" s="28" t="n">
+      <c r="M8" s="30" t="n">
         <v>18.03</v>
       </c>
-      <c r="N8" s="28" t="n">
+      <c r="N8" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="O8" s="28" t="n">
+      <c r="O8" s="30" t="n">
         <v>0.45</v>
       </c>
-      <c r="P8" s="59" t="n">
+      <c r="P8" s="63" t="n">
         <v>-17.35</v>
       </c>
-      <c r="Q8" s="59" t="n">
+      <c r="Q8" s="63" t="n">
         <v>-1.63</v>
       </c>
-      <c r="R8" s="59" t="n">
+      <c r="R8" s="63" t="n">
         <v>-2.44</v>
       </c>
-      <c r="S8" s="59" t="n">
+      <c r="S8" s="63" t="n">
         <v>-1.72</v>
       </c>
-      <c r="T8" s="28" t="n">
+      <c r="T8" s="30" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="U8" s="26" t="inlineStr">
+      <c r="U8" s="28" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>MSCI Emerging Markets</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="34" t="n">
         <v>1.66</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="34" t="n">
         <v>5.4</v>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="E9" s="34" t="n">
         <v>11.43</v>
       </c>
-      <c r="F9" s="32" t="n">
+      <c r="F9" s="34" t="n">
         <v>12.62</v>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" s="34" t="n">
         <v>21.56</v>
       </c>
-      <c r="H9" s="32" t="n">
+      <c r="H9" s="34" t="n">
         <v>20.4</v>
       </c>
-      <c r="I9" s="32" t="n">
+      <c r="I9" s="34" t="n">
         <v>49.58</v>
       </c>
-      <c r="J9" s="32" t="n">
+      <c r="J9" s="34" t="n">
         <v>74.2</v>
       </c>
-      <c r="K9" s="32" t="n">
+      <c r="K9" s="34" t="n">
         <v>46.75</v>
       </c>
-      <c r="L9" s="32" t="n">
+      <c r="L9" s="34" t="n">
         <v>7.98</v>
       </c>
-      <c r="M9" s="32" t="n">
+      <c r="M9" s="34" t="n">
         <v>20.18</v>
       </c>
-      <c r="N9" s="32" t="n">
+      <c r="N9" s="34" t="n">
         <v>0.2</v>
       </c>
-      <c r="O9" s="32" t="n">
+      <c r="O9" s="34" t="n">
         <v>0.31</v>
       </c>
-      <c r="P9" s="60" t="n">
+      <c r="P9" s="64" t="n">
         <v>-24.81</v>
       </c>
-      <c r="Q9" s="60" t="n">
+      <c r="Q9" s="64" t="n">
         <v>-1.92</v>
       </c>
-      <c r="R9" s="60" t="n">
+      <c r="R9" s="64" t="n">
         <v>-2.71</v>
       </c>
-      <c r="S9" s="60" t="n">
+      <c r="S9" s="64" t="n">
         <v>-2.96</v>
       </c>
-      <c r="T9" s="32" t="n">
+      <c r="T9" s="34" t="n">
         <v>0.79</v>
       </c>
-      <c r="U9" s="30" t="inlineStr">
+      <c r="U9" s="32" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>MSCI World</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C10" s="59" t="n">
+      <c r="C10" s="63" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="30" t="n">
         <v>1.82</v>
       </c>
-      <c r="E10" s="28" t="n">
+      <c r="E10" s="30" t="n">
         <v>5.44</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="30" t="n">
         <v>4.4</v>
       </c>
-      <c r="G10" s="28" t="n">
+      <c r="G10" s="30" t="n">
         <v>5.88</v>
       </c>
-      <c r="H10" s="28" t="n">
+      <c r="H10" s="30" t="n">
         <v>6.67</v>
       </c>
-      <c r="I10" s="28" t="n">
+      <c r="I10" s="30" t="n">
         <v>19.44</v>
       </c>
-      <c r="J10" s="28" t="n">
+      <c r="J10" s="30" t="n">
         <v>57.46</v>
       </c>
-      <c r="K10" s="28" t="n">
+      <c r="K10" s="30" t="n">
         <v>67.3</v>
       </c>
-      <c r="L10" s="28" t="n">
+      <c r="L10" s="30" t="n">
         <v>10.65</v>
       </c>
-      <c r="M10" s="28" t="n">
+      <c r="M10" s="30" t="n">
         <v>16.47</v>
       </c>
-      <c r="N10" s="28" t="n">
+      <c r="N10" s="30" t="n">
         <v>0.4</v>
       </c>
-      <c r="O10" s="28" t="n">
+      <c r="O10" s="30" t="n">
         <v>0.54</v>
       </c>
-      <c r="P10" s="59" t="n">
+      <c r="P10" s="63" t="n">
         <v>-20.63</v>
       </c>
-      <c r="Q10" s="59" t="n">
+      <c r="Q10" s="63" t="n">
         <v>-1.56</v>
       </c>
-      <c r="R10" s="59" t="n">
+      <c r="R10" s="63" t="n">
         <v>-2.29</v>
       </c>
-      <c r="S10" s="59" t="n">
+      <c r="S10" s="63" t="n">
         <v>-0.93</v>
       </c>
-      <c r="T10" s="28" t="n">
+      <c r="T10" s="30" t="n">
         <v>0.86</v>
       </c>
-      <c r="U10" s="26" t="inlineStr">
+      <c r="U10" s="28" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>MSCI World Momentum</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="34" t="n">
         <v>2.32</v>
       </c>
-      <c r="D11" s="32" t="n">
+      <c r="D11" s="34" t="n">
         <v>5.32</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="34" t="n">
         <v>15.22</v>
       </c>
-      <c r="F11" s="32" t="n">
+      <c r="F11" s="34" t="n">
         <v>17.7</v>
       </c>
-      <c r="G11" s="32" t="n">
+      <c r="G11" s="34" t="n">
         <v>17.4</v>
       </c>
-      <c r="H11" s="32" t="n">
+      <c r="H11" s="34" t="n">
         <v>19.13</v>
       </c>
-      <c r="I11" s="32" t="n">
+      <c r="I11" s="34" t="n">
         <v>34.05</v>
       </c>
-      <c r="J11" s="32" t="n">
+      <c r="J11" s="34" t="n">
         <v>106.05</v>
       </c>
-      <c r="K11" s="32" t="n">
+      <c r="K11" s="34" t="n">
         <v>100.48</v>
       </c>
-      <c r="L11" s="32" t="n">
+      <c r="L11" s="34" t="n">
         <v>14.94</v>
       </c>
-      <c r="M11" s="32" t="n">
+      <c r="M11" s="34" t="n">
         <v>22</v>
       </c>
-      <c r="N11" s="32" t="n">
+      <c r="N11" s="34" t="n">
         <v>0.5</v>
       </c>
-      <c r="O11" s="32" t="n">
+      <c r="O11" s="34" t="n">
         <v>0.7</v>
       </c>
-      <c r="P11" s="60" t="n">
+      <c r="P11" s="64" t="n">
         <v>-25.91</v>
       </c>
-      <c r="Q11" s="60" t="n">
+      <c r="Q11" s="64" t="n">
         <v>-2.25</v>
       </c>
-      <c r="R11" s="60" t="n">
+      <c r="R11" s="64" t="n">
         <v>-3.13</v>
       </c>
-      <c r="S11" s="32" t="n">
+      <c r="S11" s="34" t="n">
         <v>1.6</v>
       </c>
-      <c r="T11" s="32" t="n">
+      <c r="T11" s="34" t="n">
         <v>1.06</v>
       </c>
-      <c r="U11" s="30" t="inlineStr">
+      <c r="U11" s="32" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>MSCI World Quality</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="30" t="n">
         <v>0.1</v>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="30" t="n">
         <v>1.06</v>
       </c>
-      <c r="E12" s="28" t="n">
+      <c r="E12" s="30" t="n">
         <v>4.81</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="30" t="n">
         <v>3.67</v>
       </c>
-      <c r="G12" s="28" t="n">
+      <c r="G12" s="30" t="n">
         <v>5.72</v>
       </c>
-      <c r="H12" s="28" t="n">
+      <c r="H12" s="30" t="n">
         <v>5.52</v>
       </c>
-      <c r="I12" s="28" t="n">
+      <c r="I12" s="30" t="n">
         <v>18.85</v>
       </c>
-      <c r="J12" s="28" t="n">
+      <c r="J12" s="30" t="n">
         <v>63.51</v>
       </c>
-      <c r="K12" s="28" t="n">
+      <c r="K12" s="30" t="n">
         <v>79.73</v>
       </c>
-      <c r="L12" s="28" t="n">
+      <c r="L12" s="30" t="n">
         <v>12.46</v>
       </c>
-      <c r="M12" s="28" t="n">
+      <c r="M12" s="30" t="n">
         <v>18.9</v>
       </c>
-      <c r="N12" s="28" t="n">
+      <c r="N12" s="30" t="n">
         <v>0.45</v>
       </c>
-      <c r="O12" s="28" t="n">
+      <c r="O12" s="30" t="n">
         <v>0.64</v>
       </c>
-      <c r="P12" s="59" t="n">
+      <c r="P12" s="63" t="n">
         <v>-22.45</v>
       </c>
-      <c r="Q12" s="59" t="n">
+      <c r="Q12" s="63" t="n">
         <v>-1.79</v>
       </c>
-      <c r="R12" s="59" t="n">
+      <c r="R12" s="63" t="n">
         <v>-2.66</v>
       </c>
-      <c r="S12" s="59" t="n">
+      <c r="S12" s="63" t="n">
         <v>-0.34</v>
       </c>
-      <c r="T12" s="28" t="n">
+      <c r="T12" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="U12" s="26" t="inlineStr">
+      <c r="U12" s="28" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Nasdaq 100</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C13" s="32" t="n">
+      <c r="C13" s="34" t="n">
         <v>1.98</v>
       </c>
-      <c r="D13" s="32" t="n">
+      <c r="D13" s="34" t="n">
         <v>4.96</v>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="E13" s="34" t="n">
         <v>16.37</v>
       </c>
-      <c r="F13" s="32" t="n">
+      <c r="F13" s="34" t="n">
         <v>16.05</v>
       </c>
-      <c r="G13" s="32" t="n">
+      <c r="G13" s="34" t="n">
         <v>11.77</v>
       </c>
-      <c r="H13" s="32" t="n">
+      <c r="H13" s="34" t="n">
         <v>15.6</v>
       </c>
-      <c r="I13" s="32" t="n">
+      <c r="I13" s="34" t="n">
         <v>39.74</v>
       </c>
-      <c r="J13" s="32" t="n">
+      <c r="J13" s="34" t="n">
         <v>106.55</v>
       </c>
-      <c r="K13" s="32" t="n">
+      <c r="K13" s="34" t="n">
         <v>125.92</v>
       </c>
-      <c r="L13" s="32" t="n">
+      <c r="L13" s="34" t="n">
         <v>17.73</v>
       </c>
-      <c r="M13" s="32" t="n">
+      <c r="M13" s="34" t="n">
         <v>23.87</v>
       </c>
-      <c r="N13" s="32" t="n">
+      <c r="N13" s="34" t="n">
         <v>0.57</v>
       </c>
-      <c r="O13" s="32" t="n">
+      <c r="O13" s="34" t="n">
         <v>0.82</v>
       </c>
-      <c r="P13" s="60" t="n">
+      <c r="P13" s="64" t="n">
         <v>-31.38</v>
       </c>
-      <c r="Q13" s="60" t="n">
+      <c r="Q13" s="64" t="n">
         <v>-2.43</v>
       </c>
-      <c r="R13" s="60" t="n">
+      <c r="R13" s="64" t="n">
         <v>-3.39</v>
       </c>
-      <c r="S13" s="32" t="n">
+      <c r="S13" s="34" t="n">
         <v>2.93</v>
       </c>
-      <c r="T13" s="32" t="n">
+      <c r="T13" s="34" t="n">
         <v>1.23</v>
       </c>
-      <c r="U13" s="30" t="inlineStr">
+      <c r="U13" s="32" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Benchmark index</t>
         </is>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="30" t="n">
         <v>0.48</v>
       </c>
-      <c r="D14" s="28" t="n">
+      <c r="D14" s="30" t="n">
         <v>1.81</v>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="30" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="30" t="n">
         <v>6.56</v>
       </c>
-      <c r="G14" s="28" t="n">
+      <c r="G14" s="30" t="n">
         <v>6.03</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="30" t="n">
         <v>7.52</v>
       </c>
-      <c r="I14" s="28" t="n">
+      <c r="I14" s="30" t="n">
         <v>25.28</v>
       </c>
-      <c r="J14" s="28" t="n">
+      <c r="J14" s="30" t="n">
         <v>67.53</v>
       </c>
-      <c r="K14" s="28" t="n">
+      <c r="K14" s="30" t="n">
         <v>82.37</v>
       </c>
-      <c r="L14" s="28" t="n">
+      <c r="L14" s="30" t="n">
         <v>12.79</v>
       </c>
-      <c r="M14" s="28" t="n">
+      <c r="M14" s="30" t="n">
         <v>18.55</v>
       </c>
-      <c r="N14" s="28" t="n">
+      <c r="N14" s="30" t="n">
         <v>0.47</v>
       </c>
-      <c r="O14" s="28" t="n">
+      <c r="O14" s="30" t="n">
         <v>0.67</v>
       </c>
-      <c r="P14" s="59" t="n">
+      <c r="P14" s="63" t="n">
         <v>-23.17</v>
       </c>
-      <c r="Q14" s="59" t="n">
+      <c r="Q14" s="63" t="n">
         <v>-1.86</v>
       </c>
-      <c r="R14" s="59" t="n">
+      <c r="R14" s="63" t="n">
         <v>-2.64</v>
       </c>
-      <c r="S14" s="28" t="n">
+      <c r="S14" s="30" t="n">
         <v>-0</v>
       </c>
-      <c r="T14" s="28" t="n">
+      <c r="T14" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="U14" s="26" t="inlineStr">
+      <c r="U14" s="28" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C15" s="60" t="n">
+      <c r="C15" s="64" t="n">
         <v>-0.05</v>
       </c>
-      <c r="D15" s="32" t="n">
+      <c r="D15" s="34" t="n">
         <v>0.35</v>
       </c>
-      <c r="E15" s="60" t="n">
+      <c r="E15" s="64" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F15" s="60" t="n">
+      <c r="F15" s="64" t="n">
         <v>-0.58</v>
       </c>
-      <c r="G15" s="60" t="n">
+      <c r="G15" s="64" t="n">
         <v>-0.31</v>
       </c>
-      <c r="H15" s="32" t="n">
+      <c r="H15" s="34" t="n">
         <v>0.44</v>
       </c>
-      <c r="I15" s="32" t="n">
+      <c r="I15" s="34" t="n">
         <v>0.74</v>
       </c>
-      <c r="J15" s="32" t="n">
+      <c r="J15" s="34" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="K15" s="60" t="n">
+      <c r="K15" s="64" t="n">
         <v>-8.369999999999999</v>
       </c>
-      <c r="L15" s="60" t="n">
+      <c r="L15" s="64" t="n">
         <v>-1.73</v>
       </c>
-      <c r="M15" s="32" t="n">
+      <c r="M15" s="34" t="n">
         <v>5.55</v>
       </c>
-      <c r="N15" s="60" t="n">
+      <c r="N15" s="64" t="n">
         <v>-1.03</v>
       </c>
-      <c r="O15" s="60" t="n">
+      <c r="O15" s="64" t="n">
         <v>-1.59</v>
       </c>
-      <c r="P15" s="60" t="n">
+      <c r="P15" s="64" t="n">
         <v>-19.81</v>
       </c>
-      <c r="Q15" s="60" t="n">
+      <c r="Q15" s="64" t="n">
         <v>-0.55</v>
       </c>
-      <c r="R15" s="60" t="n">
+      <c r="R15" s="64" t="n">
         <v>-0.77</v>
       </c>
-      <c r="S15" s="60" t="n">
+      <c r="S15" s="64" t="n">
         <v>-5.88</v>
       </c>
-      <c r="T15" s="32" t="n">
+      <c r="T15" s="34" t="n">
         <v>0.02</v>
       </c>
-      <c r="U15" s="30" t="inlineStr">
+      <c r="U15" s="32" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="G16" s="30" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="H16" s="30" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="I16" s="30" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="J16" s="30" t="n">
+        <v>75.97</v>
+      </c>
+      <c r="K16" s="30" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="L16" s="30" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="M16" s="30" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="N16" s="30" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O16" s="30" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P16" s="63" t="n">
+        <v>-24.38</v>
+      </c>
+      <c r="Q16" s="63" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="R16" s="63" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="S16" s="30" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="T16" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U16" s="28" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C17" s="64" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="D17" s="34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E17" s="34" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="F17" s="34" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="G17" s="34" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H17" s="34" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="I17" s="34" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="J17" s="34" t="n">
+        <v>72.76000000000001</v>
+      </c>
+      <c r="K17" s="34" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="L17" s="34" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="M17" s="34" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="N17" s="34" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O17" s="34" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P17" s="64" t="n">
+        <v>-22.73</v>
+      </c>
+      <c r="Q17" s="64" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="R17" s="64" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="S17" s="34" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="T17" s="34" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="U17" s="32" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C18" s="63" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="J18" s="30" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="K18" s="30" t="n">
+        <v>77.81</v>
+      </c>
+      <c r="L18" s="30" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="M18" s="30" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="N18" s="30" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="O18" s="30" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P18" s="63" t="n">
+        <v>-21.73</v>
+      </c>
+      <c r="Q18" s="63" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="R18" s="63" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="S18" s="30" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="T18" s="30" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U18" s="28" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C19" s="34" t="n">
         <v>0.1</v>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D19" s="34" t="n">
         <v>2.32</v>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E19" s="34" t="n">
         <v>6.79</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F19" s="34" t="n">
         <v>6.46</v>
       </c>
-      <c r="G16" s="28" t="n">
+      <c r="G19" s="34" t="n">
         <v>9.41</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="H19" s="34" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="I16" s="28" t="n">
+      <c r="I19" s="34" t="n">
         <v>26.51</v>
       </c>
-      <c r="J16" s="28" t="n">
+      <c r="J19" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="K16" s="28" t="n">
+      <c r="K19" s="34" t="n">
         <v>73.76000000000001</v>
       </c>
-      <c r="L16" s="28" t="n">
+      <c r="L19" s="34" t="n">
         <v>11.7</v>
       </c>
-      <c r="M16" s="28" t="n">
+      <c r="M19" s="34" t="n">
         <v>13.8</v>
       </c>
-      <c r="N16" s="28" t="n">
+      <c r="N19" s="34" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="O16" s="28" t="n">
+      <c r="O19" s="34" t="n">
         <v>0.71</v>
       </c>
-      <c r="P16" s="59" t="n">
+      <c r="P19" s="64" t="n">
         <v>-21.07</v>
       </c>
-      <c r="Q16" s="59" t="n">
+      <c r="Q19" s="64" t="n">
         <v>-1.39</v>
       </c>
-      <c r="R16" s="59" t="n">
+      <c r="R19" s="64" t="n">
         <v>-2.13</v>
       </c>
-      <c r="S16" s="28" t="n">
+      <c r="S19" s="34" t="n">
         <v>5.98</v>
       </c>
-      <c r="T16" s="28" t="n">
+      <c r="T19" s="34" t="n">
         <v>0.2</v>
       </c>
-      <c r="U16" s="26" t="inlineStr">
+      <c r="U19" s="32" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="B17" s="30" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C17" s="60" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="D17" s="32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E17" s="32" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="F17" s="32" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="G17" s="32" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="H17" s="32" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="I17" s="32" t="n">
-        <v>24.05</v>
-      </c>
-      <c r="J17" s="32" t="n">
-        <v>64.01000000000001</v>
-      </c>
-      <c r="K17" s="32" t="n">
-        <v>77.81</v>
-      </c>
-      <c r="L17" s="32" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="M17" s="32" t="n">
-        <v>14.23</v>
-      </c>
-      <c r="N17" s="32" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="O17" s="32" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="P17" s="60" t="n">
-        <v>-21.73</v>
-      </c>
-      <c r="Q17" s="60" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="R17" s="60" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="S17" s="32" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="T17" s="32" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="U17" s="30" t="inlineStr">
+      <c r="C20" s="63" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D20" s="63" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E20" s="63" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G20" s="63" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="H20" s="63" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J20" s="30" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K20" s="63" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L20" s="63" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M20" s="30" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="N20" s="63" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="O20" s="63" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="P20" s="63" t="n">
+        <v>-15.77</v>
+      </c>
+      <c r="Q20" s="63" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="R20" s="63" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="S20" s="63" t="n">
+        <v>-3.83</v>
+      </c>
+      <c r="T20" s="63" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U20" s="28" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
-        <is>
-          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
-        </is>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>Invesco Physical Gold ETC</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C18" s="59" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="D18" s="28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E18" s="28" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="F18" s="28" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="I18" s="28" t="n">
-        <v>25.92</v>
-      </c>
-      <c r="J18" s="28" t="n">
-        <v>72.76000000000001</v>
-      </c>
-      <c r="K18" s="28" t="n">
-        <v>91.22</v>
-      </c>
-      <c r="L18" s="28" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="M18" s="28" t="n">
-        <v>17.28</v>
-      </c>
-      <c r="N18" s="28" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="O18" s="28" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="P18" s="59" t="n">
-        <v>-22.73</v>
-      </c>
-      <c r="Q18" s="59" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="R18" s="59" t="n">
-        <v>-2.53</v>
-      </c>
-      <c r="S18" s="28" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="T18" s="28" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="U18" s="26" t="inlineStr">
+      <c r="C21" s="64" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="D21" s="34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E21" s="64" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="F21" s="64" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="G21" s="34" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="H21" s="34" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="I21" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="J21" s="34" t="n">
+        <v>116.16</v>
+      </c>
+      <c r="K21" s="34" t="n">
+        <v>162.76</v>
+      </c>
+      <c r="L21" s="34" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="M21" s="34" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="N21" s="34" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O21" s="34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P21" s="64" t="n">
+        <v>-15.94</v>
+      </c>
+      <c r="Q21" s="64" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="R21" s="64" t="n">
+        <v>-2.57</v>
+      </c>
+      <c r="S21" s="34" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="T21" s="34" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U21" s="32" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="B19" s="30" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="D19" s="32" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="E19" s="32" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="F19" s="32" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="G19" s="32" t="n">
-        <v>22.39</v>
-      </c>
-      <c r="H19" s="32" t="n">
-        <v>21.47</v>
-      </c>
-      <c r="I19" s="32" t="n">
-        <v>48.97</v>
-      </c>
-      <c r="J19" s="32" t="n">
-        <v>75.97</v>
-      </c>
-      <c r="K19" s="32" t="n">
-        <v>50.05</v>
-      </c>
-      <c r="L19" s="32" t="n">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="M19" s="32" t="n">
-        <v>18.84</v>
-      </c>
-      <c r="N19" s="32" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="O19" s="32" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="P19" s="60" t="n">
-        <v>-24.38</v>
-      </c>
-      <c r="Q19" s="60" t="n">
-        <v>-1.58</v>
-      </c>
-      <c r="R19" s="60" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="S19" s="32" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="T19" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U19" s="30" t="inlineStr">
+      <c r="C22" s="63" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="D22" s="30" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E22" s="30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F22" s="63" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="G22" s="30" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="H22" s="30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I22" s="30" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="J22" s="30" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="K22" s="30" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="L22" s="30" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="M22" s="30" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="N22" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O22" s="30" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="P22" s="63" t="n">
+        <v>-22.86</v>
+      </c>
+      <c r="Q22" s="63" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="R22" s="63" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="S22" s="30" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="T22" s="30" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U22" s="28" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>In portfolio</t>
         </is>
       </c>
-      <c r="C20" s="59" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="D20" s="59" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E20" s="59" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="F20" s="28" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G20" s="59" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="H20" s="59" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I20" s="28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J20" s="28" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K20" s="59" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L20" s="59" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="M20" s="28" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="N20" s="59" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="O20" s="59" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="P20" s="59" t="n">
-        <v>-15.77</v>
-      </c>
-      <c r="Q20" s="59" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="R20" s="59" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="S20" s="59" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="T20" s="59" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="U20" s="26" t="inlineStr">
+      <c r="C23" s="34" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D23" s="34" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="E23" s="34" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="F23" s="34" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="G23" s="34" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="H23" s="34" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I23" s="34" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="J23" s="34" t="n">
+        <v>80.48</v>
+      </c>
+      <c r="K23" s="34" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="L23" s="34" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="M23" s="34" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="N23" s="34" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O23" s="34" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="P23" s="64" t="n">
+        <v>-21.24</v>
+      </c>
+      <c r="Q23" s="64" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="R23" s="64" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="S23" s="34" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="T23" s="34" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="U23" s="32" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t>Invesco Physical Gold ETC</t>
-        </is>
-      </c>
-      <c r="B21" s="30" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C21" s="60" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="D21" s="32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E21" s="60" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="F21" s="60" t="n">
-        <v>-6.82</v>
-      </c>
-      <c r="G21" s="32" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="H21" s="32" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="I21" s="32" t="n">
-        <v>35</v>
-      </c>
-      <c r="J21" s="32" t="n">
-        <v>116.16</v>
-      </c>
-      <c r="K21" s="32" t="n">
-        <v>162.76</v>
-      </c>
-      <c r="L21" s="32" t="n">
-        <v>21.34</v>
-      </c>
-      <c r="M21" s="32" t="n">
-        <v>17.92</v>
-      </c>
-      <c r="N21" s="32" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="O21" s="32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P21" s="60" t="n">
-        <v>-15.94</v>
-      </c>
-      <c r="Q21" s="60" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="R21" s="60" t="n">
-        <v>-2.57</v>
-      </c>
-      <c r="S21" s="32" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="T21" s="32" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U21" s="30" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
-        </is>
-      </c>
-      <c r="B22" s="26" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C22" s="28" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="D22" s="28" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="E22" s="28" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="F22" s="28" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="G22" s="28" t="n">
-        <v>20.84</v>
-      </c>
-      <c r="H22" s="28" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="I22" s="28" t="n">
-        <v>51.96</v>
-      </c>
-      <c r="J22" s="28" t="n">
-        <v>80.48</v>
-      </c>
-      <c r="K22" s="28" t="n">
-        <v>64.31999999999999</v>
-      </c>
-      <c r="L22" s="28" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="M22" s="28" t="n">
-        <v>18.31</v>
-      </c>
-      <c r="N22" s="28" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O22" s="28" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="P22" s="59" t="n">
-        <v>-21.24</v>
-      </c>
-      <c r="Q22" s="59" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="R22" s="59" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="S22" s="28" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="T22" s="28" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="U22" s="26" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="30" t="inlineStr">
-        <is>
-          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
-        </is>
-      </c>
-      <c r="B23" s="30" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C23" s="60" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="D23" s="32" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="E23" s="32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="F23" s="60" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="G23" s="32" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="H23" s="32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I23" s="32" t="n">
-        <v>16.35</v>
-      </c>
-      <c r="J23" s="32" t="n">
-        <v>42.11</v>
-      </c>
-      <c r="K23" s="32" t="n">
-        <v>55.61</v>
-      </c>
-      <c r="L23" s="32" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="M23" s="32" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="N23" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O23" s="32" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="P23" s="60" t="n">
-        <v>-22.86</v>
-      </c>
-      <c r="Q23" s="60" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="R23" s="60" t="n">
-        <v>-2.22</v>
-      </c>
-      <c r="S23" s="32" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="T23" s="32" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="U23" s="30" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="61" t="inlineStr">
+      <c r="A26" s="65" t="inlineStr">
         <is>
           <t>Legend — Rating Thresholds</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>● Strong</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>● Fair</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>● Weak</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>CAGR</t>
         </is>
       </c>
-      <c r="B28" s="62" t="inlineStr">
+      <c r="B28" s="66" t="inlineStr">
         <is>
           <t>Compound Annual Growth Rate. The single yearly return that, if repeated every year, would grow your portfolio from start to end value. Accounts for compounding. ~7% is the long-term global equity average.</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>&gt; 7.0%</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr">
         <is>
           <t>3.0% – 7.0%</t>
         </is>
       </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="E28" s="28" t="inlineStr">
         <is>
           <t>&lt; 3.0%</t>
         </is>
       </c>
-      <c r="F28" s="26" t="inlineStr">
+      <c r="F28" s="28" t="inlineStr">
         <is>
           <t>Equity risk premium (Dimson et al.)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>α (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B29" s="63" t="inlineStr">
+      <c r="B29" s="67" t="inlineStr">
         <is>
           <t>Extra annual return vs the benchmark, after adjusting for how risky the portfolio is (CAPM). Positive = you beat the market beyond what your risk alone justified. Negative = you underperformed after fees and noise.</t>
         </is>
       </c>
-      <c r="C29" s="30" t="inlineStr">
+      <c r="C29" s="32" t="inlineStr">
         <is>
           <t>&gt; 0.0%</t>
         </is>
       </c>
-      <c r="D29" s="30" t="inlineStr">
+      <c r="D29" s="32" t="inlineStr">
         <is>
           <t>-1.0% – 0.0%</t>
         </is>
       </c>
-      <c r="E29" s="30" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>&lt; -1.0%</t>
         </is>
       </c>
-      <c r="F29" s="30" t="inlineStr">
+      <c r="F29" s="32" t="inlineStr">
         <is>
           <t>Jensen's Alpha (CAPM)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>β (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B30" s="62" t="inlineStr">
+      <c r="B30" s="66" t="inlineStr">
         <is>
           <t>How much your portfolio moves when the benchmark moves 1%. β=1 in line, β=0.5 half as reactive, β=1.5 amplifies by 50%, β≈0 uncorrelated. Tells you how much systematic market risk you're running.</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>&lt; 0.7</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>1.0 – 0.7</t>
         </is>
       </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>&gt; 1.0</t>
         </is>
       </c>
-      <c r="F30" s="26" t="inlineStr">
+      <c r="F30" s="28" t="inlineStr">
         <is>
           <t>CAPM, 1.0 = market</t>
         </is>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>Max DD</t>
         </is>
       </c>
-      <c r="B31" s="63" t="inlineStr">
+      <c r="B31" s="67" t="inlineStr">
         <is>
           <t>Maximum Drawdown. Worst peak-to-trough loss over the period — the most painful scenario an investor lived through. -20% is typical for diversified equity; deeper drops signal concentration or high volatility.</t>
         </is>
       </c>
-      <c r="C31" s="30" t="inlineStr">
+      <c r="C31" s="32" t="inlineStr">
         <is>
           <t>&lt; 15.0%</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr">
+      <c r="D31" s="32" t="inlineStr">
         <is>
           <t>30.0% – 15.0%</t>
         </is>
       </c>
-      <c r="E31" s="30" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>&gt; 30.0%</t>
         </is>
       </c>
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="32" t="inlineStr">
         <is>
           <t>Retail drawdown tolerance</t>
         </is>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
-      <c r="B32" s="62" t="inlineStr">
+      <c r="B32" s="66" t="inlineStr">
         <is>
           <t>How bumpy the ride is. Annualized standard deviation of daily returns. A 15% vol means ~±15% year-to-year noise around the average return. Equity indexes ~15–20%, bonds ~3–7%.</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="28" t="inlineStr">
         <is>
           <t>&lt; 10.0%</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="28" t="inlineStr">
         <is>
           <t>18.0% – 10.0%</t>
         </is>
       </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="E32" s="28" t="inlineStr">
         <is>
           <t>&gt; 18.0%</t>
         </is>
       </c>
-      <c r="F32" s="26" t="inlineStr">
+      <c r="F32" s="28" t="inlineStr">
         <is>
           <t>Hist. equity vol ~15%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1">
-      <c r="A33" s="30" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="B33" s="63" t="inlineStr">
+      <c r="B33" s="67" t="inlineStr">
         <is>
           <t>Return per unit of risk taken: (CAGR − risk-free rate) / Volatility. Above 1 is good, above 2 is excellent, negative means you were paid less than a safe bond for the risk you ran.</t>
         </is>
       </c>
-      <c r="C33" s="30" t="inlineStr">
+      <c r="C33" s="32" t="inlineStr">
         <is>
           <t>&gt; 1.0</t>
         </is>
       </c>
-      <c r="D33" s="30" t="inlineStr">
+      <c r="D33" s="32" t="inlineStr">
         <is>
           <t>0.5 – 1.0</t>
         </is>
       </c>
-      <c r="E33" s="30" t="inlineStr">
+      <c r="E33" s="32" t="inlineStr">
         <is>
           <t>&lt; 0.5</t>
         </is>
       </c>
-      <c r="F33" s="30" t="inlineStr">
+      <c r="F33" s="32" t="inlineStr">
         <is>
           <t>Sharpe (1994)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>Sortino</t>
         </is>
       </c>
-      <c r="B34" s="62" t="inlineStr">
+      <c r="B34" s="66" t="inlineStr">
         <is>
           <t>Like Sharpe but only penalizes downside volatility (ignores upside swings). More honest when returns are asymmetric. Usually higher than Sharpe — the gap shows how much of your volatility is actually good volatility.</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C34" s="28" t="inlineStr">
         <is>
           <t>&gt; 1.5</t>
         </is>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D34" s="28" t="inlineStr">
         <is>
           <t>0.7 – 1.5</t>
         </is>
       </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="E34" s="28" t="inlineStr">
         <is>
           <t>&lt; 0.7</t>
         </is>
       </c>
-      <c r="F34" s="26" t="inlineStr">
+      <c r="F34" s="28" t="inlineStr">
         <is>
           <t>Sortino &amp; Price (1994)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="30" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>VaR 95%</t>
         </is>
       </c>
-      <c r="B35" s="63" t="inlineStr">
+      <c r="B35" s="67" t="inlineStr">
         <is>
           <t>Value at Risk. The daily loss exceeded only 5% of the time (historical simulation). A VaR of -1.2% means on an average month you should expect about one day worse than -1.2%. Non-parametric: no normal-distribution assumption.</t>
         </is>
       </c>
-      <c r="C35" s="30" t="inlineStr">
+      <c r="C35" s="32" t="inlineStr">
         <is>
           <t>&lt; 0.8%</t>
         </is>
       </c>
-      <c r="D35" s="30" t="inlineStr">
+      <c r="D35" s="32" t="inlineStr">
         <is>
           <t>1.5% – 0.8%</t>
         </is>
       </c>
-      <c r="E35" s="30" t="inlineStr">
+      <c r="E35" s="32" t="inlineStr">
         <is>
           <t>&gt; 1.5%</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
+      <c r="F35" s="32" t="inlineStr">
         <is>
           <t>Basel III (retail adj.)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>CVaR 95%</t>
         </is>
       </c>
-      <c r="B36" s="62" t="inlineStr">
+      <c r="B36" s="66" t="inlineStr">
         <is>
           <t>Conditional VaR, a.k.a. Expected Shortfall. The average loss on the worst 5% of days. Always more negative than VaR. Captures tail risk VaR misses — how bad it really gets when it goes bad.</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C36" s="28" t="inlineStr">
         <is>
           <t>&lt; 1.2%</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D36" s="28" t="inlineStr">
         <is>
           <t>2.0% – 1.2%</t>
         </is>
       </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="E36" s="28" t="inlineStr">
         <is>
           <t>&gt; 2.0%</t>
         </is>
       </c>
-      <c r="F36" s="26" t="inlineStr">
+      <c r="F36" s="28" t="inlineStr">
         <is>
           <t>Artzner et al. (1999)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="35" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-10 16:30 v2.0</t>
+      <c r="A39" s="37" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-10 16:57 v2.0</t>
         </is>
       </c>
     </row>
@@ -4861,483 +5015,483 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="65" t="inlineStr">
         <is>
           <t>Return Contribution by Holding</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>ISIN</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Gain %</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Contribution</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>IE00B52MJD48</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>CNKY.L</t>
         </is>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="30" t="n">
         <v>14.85853637960594</v>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="30" t="n">
         <v>447.4314305000007</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="30" t="n">
         <v>66.48176187463385</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>IE00B3F81R35</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>IEAG.L</t>
         </is>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="34" t="n">
         <v>13.02950527016769</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="34" t="n">
         <v>92.01785496303013</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="34" t="n">
         <v>11.98947126190327</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>IE00B579F325</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>SGLD.L</t>
         </is>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="30" t="n">
         <v>8.387663930203299</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="30" t="n">
         <v>56.9654779313447</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="30" t="n">
         <v>4.77807284511532</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>LU0292107645</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>XMME.DE</t>
         </is>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="34" t="n">
         <v>8.688970665553452</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="34" t="n">
         <v>42.2785758972168</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="34" t="n">
         <v>3.67357305752292</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>IE00B3RBWM25</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>VWCE.DE</t>
         </is>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="30" t="n">
         <v>15.32957112517667</v>
       </c>
-      <c r="E9" s="28" t="n">
+      <c r="E9" s="30" t="n">
         <v>23.54687452316284</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="30" t="n">
         <v>3.609634877784353</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>IE00B945VV12</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>VERX.DE</t>
         </is>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D10" s="34" t="n">
         <v>6.960540244916307</v>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E10" s="34" t="n">
         <v>45.06060282389323</v>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F10" s="34" t="n">
         <v>3.136461394158983</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>IE00B1FZS798</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>IBTM.L</t>
         </is>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="30" t="n">
         <v>7.195360354184961</v>
       </c>
-      <c r="E11" s="28" t="n">
+      <c r="E11" s="30" t="n">
         <v>41.38553303938742</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="30" t="n">
         <v>2.977838236684201</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>IE00B5BMR087</t>
         </is>
       </c>
-      <c r="C12" s="30" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>CSPX.L</t>
         </is>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D12" s="34" t="n">
         <v>12.2486210102208</v>
       </c>
-      <c r="E12" s="32" t="n">
+      <c r="E12" s="34" t="n">
         <v>18.22866819217636</v>
       </c>
-      <c r="F12" s="32" t="n">
+      <c r="F12" s="34" t="n">
         <v>2.23276048207035</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>IE00B4L5Y983</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>EUNL.DE</t>
         </is>
       </c>
-      <c r="D13" s="28" t="n">
+      <c r="D13" s="30" t="n">
         <v>7.24268669834837</v>
       </c>
-      <c r="E13" s="28" t="n">
+      <c r="E13" s="30" t="n">
         <v>21.98469200912787</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="30" t="n">
         <v>1.592282363817961</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="C14" s="30" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" s="34" t="n">
         <v>6.058544321622511</v>
       </c>
-      <c r="E14" s="32" t="n">
+      <c r="E14" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="32" t="n">
+      <c r="F14" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="61" t="inlineStr">
+      <c r="A16" s="65" t="inlineStr">
         <is>
           <t>Breakdown by Asset Class</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Asset Class</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Total Value</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Avg Gain %</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t># Holdings</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="29" t="n">
         <v>53914.70513029613</v>
       </c>
-      <c r="C18" s="28" t="n">
+      <c r="C18" s="30" t="n">
         <v>99.7551406575963</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="28" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Fixed Income</t>
         </is>
       </c>
-      <c r="B19" s="31" t="n">
+      <c r="B19" s="33" t="n">
         <v>16691.19226558396</v>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="34" t="n">
         <v>66.70169400120878</v>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D19" s="32" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n">
+      <c r="B20" s="29" t="n">
         <v>6922.177576772301</v>
       </c>
-      <c r="C20" s="28" t="n">
+      <c r="C20" s="30" t="n">
         <v>56.9654779313447</v>
       </c>
-      <c r="D20" s="26" t="n">
+      <c r="D20" s="28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="68" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Equivalents</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="33" t="n">
         <v>5000</v>
       </c>
-      <c r="C21" s="32" t="n">
+      <c r="C21" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="30" t="n">
+      <c r="D21" s="32" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="65" t="inlineStr">
         <is>
           <t>Breakdown by Geography (Equity Only)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Weight % (within Equity)</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Avg Gain %</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="30" t="n">
         <v>41.22858361399044</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C25" s="30" t="n">
         <v>21.25341157482235</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="69" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="B26" s="32" t="n">
+      <c r="B26" s="34" t="n">
         <v>15.67502157315777</v>
       </c>
-      <c r="C26" s="32" t="n">
+      <c r="C26" s="34" t="n">
         <v>32.91272521018982</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>Eurozone EMU</t>
         </is>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="30" t="n">
         <v>9.631770299638772</v>
       </c>
-      <c r="C27" s="28" t="n">
+      <c r="C27" s="30" t="n">
         <v>30.19738978539465</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B28" s="32" t="n">
+      <c r="B28" s="34" t="n">
         <v>24.84297679518155</v>
       </c>
-      <c r="C28" s="32" t="n">
+      <c r="C28" s="34" t="n">
         <v>164.3209990107638</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>Dev ex-USA ex-EMU ex-JP</t>
         </is>
       </c>
-      <c r="B29" s="28" t="n">
+      <c r="B29" s="30" t="n">
         <v>8.621647718031447</v>
       </c>
-      <c r="C29" s="28" t="n">
+      <c r="C29" s="30" t="n">
         <v>30.19738978539465</v>
       </c>
     </row>

--- a/output/sample/portfolio_dashboard_sample.xlsx
+++ b/output/sample/portfolio_dashboard_sample.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="166" formatCode="+0.00;-0.00;0.00"/>
     <numFmt numFmtId="167" formatCode="&quot;€&quot;+#,##0.00;&quot;€&quot;-#,##0.00;&quot;€&quot;0.00"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -114,6 +114,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="009333EA"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="0015803D"/>
       <sz val="10"/>
     </font>
@@ -162,6 +168,12 @@
       <i val="1"/>
       <color rgb="0064748B"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -260,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -301,181 +313,193 @@
     <xf numFmtId="2" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="16" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="9" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="24" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="16" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="24" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="26" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="26" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -871,7 +895,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>As of: 11 May 2026</t>
+          <t>As of: 14 May 2026</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -900,7 +924,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>82305.62721539702</v>
+        <v>84348.31825577587</v>
       </c>
       <c r="D5" s="2" t="n"/>
     </row>
@@ -911,7 +935,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>77305.62721539702</v>
+        <v>79348.31825577587</v>
       </c>
       <c r="D6" s="2" t="n"/>
     </row>
@@ -933,7 +957,7 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>28165.62721539702</v>
+        <v>28708.31825577587</v>
       </c>
       <c r="D8" s="2" t="n"/>
     </row>
@@ -944,7 +968,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>52.02369267712785</v>
+        <v>51.59654611030889</v>
       </c>
       <c r="D9" s="2" t="n"/>
     </row>
@@ -1008,10 +1032,10 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>69.53374477077881</v>
+        <v>68.07295830892485</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="13" t="inlineStr">
@@ -1020,7 +1044,7 @@
         </is>
       </c>
       <c r="F14" s="16" t="n">
-        <v>41.37833258340725</v>
+        <v>41.45266796122517</v>
       </c>
       <c r="G14" s="15" t="n">
         <v>55</v>
@@ -1033,10 +1057,10 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>21.58612130892514</v>
+        <v>20.92693460623516</v>
       </c>
       <c r="C15" s="19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="20" t="inlineStr">
@@ -1045,7 +1069,7 @@
         </is>
       </c>
       <c r="F15" s="21" t="n">
-        <v>24.63924044051774</v>
+        <v>24.68848211410375</v>
       </c>
       <c r="G15" s="19" t="n">
         <v>8</v>
@@ -1058,7 +1082,7 @@
         </is>
       </c>
       <c r="B16" s="23" t="n">
-        <v>8.880133920296046</v>
+        <v>8.731628004794739</v>
       </c>
       <c r="C16" s="15" t="n">
         <v>5</v>
@@ -1070,7 +1094,7 @@
         </is>
       </c>
       <c r="F16" s="23" t="n">
-        <v>15.68231659711715</v>
+        <v>15.60865831078922</v>
       </c>
       <c r="G16" s="15" t="n">
         <v>11</v>
@@ -1079,14 +1103,14 @@
     <row r="17">
       <c r="A17" s="25" t="inlineStr">
         <is>
-          <t>Cash &amp; Cash Equivalents</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="B17" s="26" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C17" s="27" t="n">
-        <v>3000</v>
+        <v>2.268479080045248</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="17" t="inlineStr">
@@ -1095,21 +1119,32 @@
         </is>
       </c>
       <c r="F17" s="18" t="n">
-        <v>9.656154540849686</v>
+        <v>9.619304346301179</v>
       </c>
       <c r="G17" s="19" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Cash &amp; Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>3000</v>
+      </c>
       <c r="D18" s="2" t="n"/>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>Dev ex-USA ex-EMU ex-JP</t>
         </is>
       </c>
       <c r="F18" s="23" t="n">
-        <v>8.64395583810817</v>
+        <v>8.630887267580697</v>
       </c>
       <c r="G18" s="15" t="n">
         <v>12</v>
@@ -1151,7 +1186,7 @@
           <t>Weight %</t>
         </is>
       </c>
-      <c r="D22" s="29" t="n"/>
+      <c r="D22" s="30" t="n"/>
       <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Class</t>
@@ -1159,18 +1194,18 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
-      <c r="B23" s="31" t="n">
-        <v>12644.7998046875</v>
-      </c>
-      <c r="C23" s="32" t="n">
-        <v>15.36322634611066</v>
-      </c>
-      <c r="D23" s="33" t="n"/>
+      <c r="B23" s="32" t="n">
+        <v>12731.19995117188</v>
+      </c>
+      <c r="C23" s="33" t="n">
+        <v>15.09360259272281</v>
+      </c>
+      <c r="D23" s="34" t="n"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Equities</t>
@@ -1178,75 +1213,75 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
-      <c r="B24" s="35" t="n">
-        <v>12113.27520221472</v>
-      </c>
-      <c r="C24" s="36" t="n">
-        <v>14.71743258879956</v>
-      </c>
-      <c r="D24" s="33" t="n"/>
-      <c r="E24" s="37" t="inlineStr">
+      <c r="B24" s="36" t="n">
+        <v>12196.33884525299</v>
+      </c>
+      <c r="C24" s="37" t="n">
+        <v>14.45949261047398</v>
+      </c>
+      <c r="D24" s="34" t="n"/>
+      <c r="E24" s="38" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
         </is>
       </c>
-      <c r="B25" s="31" t="n">
-        <v>10752.99987792969</v>
-      </c>
-      <c r="C25" s="32" t="n">
-        <v>13.06472016766079</v>
-      </c>
-      <c r="D25" s="33" t="n"/>
-      <c r="E25" s="38" t="inlineStr">
+      <c r="B25" s="32" t="n">
+        <v>10687.0002746582</v>
+      </c>
+      <c r="C25" s="33" t="n">
+        <v>12.67008103499016</v>
+      </c>
+      <c r="D25" s="34" t="n"/>
+      <c r="E25" s="39" t="inlineStr">
         <is>
           <t>Fixed Income</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n">
-        <v>10126.38229233369</v>
-      </c>
-      <c r="C26" s="36" t="n">
-        <v>12.30338998065413</v>
-      </c>
-      <c r="D26" s="33" t="n"/>
-      <c r="E26" s="37" t="inlineStr">
+      <c r="B26" s="36" t="n">
+        <v>10189.77884650425</v>
+      </c>
+      <c r="C26" s="37" t="n">
+        <v>12.08059515259688</v>
+      </c>
+      <c r="D26" s="34" t="n"/>
+      <c r="E26" s="38" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
-      <c r="B27" s="31" t="n">
-        <v>7150.139923095703</v>
-      </c>
-      <c r="C27" s="32" t="n">
-        <v>8.687303851513711</v>
-      </c>
-      <c r="D27" s="33" t="n"/>
+      <c r="B27" s="32" t="n">
+        <v>7142.579956054688</v>
+      </c>
+      <c r="C27" s="33" t="n">
+        <v>8.467957753936119</v>
+      </c>
+      <c r="D27" s="34" t="n"/>
       <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Equities</t>
@@ -1257,9 +1292,9 @@
       <c r="D28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="39" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-11 12:13 v2.0</t>
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-14 08:51 v2.0</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1300,9 +1335,9 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="40" t="inlineStr">
-        <is>
-          <t>●  Action needed — largest deviation 16.6% (&gt;5.0%). Rebalancing recommended.</t>
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>●  Action needed — largest deviation 16.7% (&gt;5.0%). Rebalancing recommended.</t>
         </is>
       </c>
     </row>
@@ -1340,14 +1375,14 @@
       <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>Status color based on delta after rebalancing vs target. Threshold ±2.5% (green), ±5.0% (amber), beyond (red).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="42" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>Invested Allocation</t>
         </is>
@@ -1386,48 +1421,48 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>Fixed Income</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>21.58612130892514</v>
+        <v>20.92693460623516</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>21.58612130892514</v>
-      </c>
-      <c r="E14" s="43" t="n">
-        <v>-4.413878691074856</v>
-      </c>
-      <c r="F14" s="44" t="inlineStr">
+        <v>20.92693460623515</v>
+      </c>
+      <c r="E14" s="44" t="n">
+        <v>-4.073065393764846</v>
+      </c>
+      <c r="F14" s="45" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="45" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
       <c r="B15" s="19" t="n">
-        <v>8.880133920296046</v>
+        <v>8.731628004794739</v>
       </c>
       <c r="C15" s="19" t="n">
         <v>5</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>8.880133920296046</v>
-      </c>
-      <c r="E15" s="46" t="n">
-        <v>3.880133920296046</v>
-      </c>
-      <c r="F15" s="47" t="inlineStr">
+        <v>8.731628004794739</v>
+      </c>
+      <c r="E15" s="47" t="n">
+        <v>3.731628004794739</v>
+      </c>
+      <c r="F15" s="48" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
@@ -1440,25 +1475,25 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>69.53374477077881</v>
+        <v>68.07295830892485</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>69.5337447707788</v>
-      </c>
-      <c r="E16" s="48" t="n">
-        <v>1.533744770778796</v>
-      </c>
-      <c r="F16" s="49" t="inlineStr">
+        <v>68.07295830892485</v>
+      </c>
+      <c r="E16" s="49" t="n">
+        <v>2.072958308924854</v>
+      </c>
+      <c r="F16" s="50" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
@@ -1472,660 +1507,684 @@
       <c r="D17" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="50" t="n">
+      <c r="E17" s="52" t="n">
         <v>-1</v>
       </c>
-      <c r="F17" s="51" t="inlineStr">
+      <c r="F17" s="53" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="54" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>2.268479080045248</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>2.268479080045248</v>
+      </c>
+      <c r="E18" s="49" t="n">
+        <v>-0.7315209199547521</v>
+      </c>
+      <c r="F18" s="50" t="inlineStr">
+        <is>
+          <t>● Aligned</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="55" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B19" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C19" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D19" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="48" t="n">
+      <c r="E19" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="49" t="inlineStr">
+      <c r="F19" s="53" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Equivalents</t>
         </is>
       </c>
-      <c r="B19" s="27" t="n">
+      <c r="B20" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="C19" s="27" t="n">
+      <c r="C20" s="29" t="n">
         <v>3000</v>
       </c>
-      <c r="D19" s="27" t="n">
+      <c r="D20" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="E19" s="52" t="n">
+      <c r="E20" s="56" t="n">
         <v>2000</v>
       </c>
-      <c r="F19" s="53" t="inlineStr">
+      <c r="F20" s="57" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="42" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
         <is>
           <t>Geography (equity only)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Current (% / EUR)</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Target (% / EUR)</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Post-rebal (% / EUR)</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Delta (pp / EUR)</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="54" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="58" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n">
-        <v>24.63924044051774</v>
-      </c>
-      <c r="C23" s="15" t="n">
+      <c r="B24" s="15" t="n">
+        <v>24.68848211410375</v>
+      </c>
+      <c r="C24" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="D23" s="15" t="n">
-        <v>24.63924044051774</v>
-      </c>
-      <c r="E23" s="55" t="n">
-        <v>16.63924044051774</v>
-      </c>
-      <c r="F23" s="56" t="inlineStr">
+      <c r="D24" s="15" t="n">
+        <v>24.68848211410374</v>
+      </c>
+      <c r="E24" s="59" t="n">
+        <v>16.68848211410374</v>
+      </c>
+      <c r="F24" s="57" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="37" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n">
-        <v>41.37833258340725</v>
-      </c>
-      <c r="C24" s="19" t="n">
+      <c r="B25" s="19" t="n">
+        <v>41.45266796122517</v>
+      </c>
+      <c r="C25" s="19" t="n">
         <v>55</v>
       </c>
-      <c r="D24" s="19" t="n">
-        <v>41.37833258340724</v>
-      </c>
-      <c r="E24" s="57" t="n">
-        <v>-13.62166741659276</v>
-      </c>
-      <c r="F24" s="53" t="inlineStr">
+      <c r="D25" s="19" t="n">
+        <v>41.45266796122516</v>
+      </c>
+      <c r="E25" s="60" t="n">
+        <v>-13.54733203877484</v>
+      </c>
+      <c r="F25" s="61" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="B25" s="15" t="n">
-        <v>15.68231659711715</v>
-      </c>
-      <c r="C25" s="15" t="n">
+      <c r="B26" s="15" t="n">
+        <v>15.60865831078922</v>
+      </c>
+      <c r="C26" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="D25" s="15" t="n">
-        <v>15.68231659711715</v>
-      </c>
-      <c r="E25" s="43" t="n">
-        <v>4.682316597117152</v>
-      </c>
-      <c r="F25" s="44" t="inlineStr">
+      <c r="D26" s="15" t="n">
+        <v>15.60865831078922</v>
+      </c>
+      <c r="E26" s="44" t="n">
+        <v>4.608658310789217</v>
+      </c>
+      <c r="F26" s="45" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Eurozone EMU</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
-        <v>9.656154540849686</v>
-      </c>
-      <c r="C26" s="19" t="n">
+      <c r="B27" s="19" t="n">
+        <v>9.619304346301179</v>
+      </c>
+      <c r="C27" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D26" s="19" t="n">
-        <v>9.656154540849688</v>
-      </c>
-      <c r="E26" s="46" t="n">
-        <v>-4.343845459150312</v>
-      </c>
-      <c r="F26" s="47" t="inlineStr">
+      <c r="D27" s="19" t="n">
+        <v>9.619304346301174</v>
+      </c>
+      <c r="E27" s="47" t="n">
+        <v>-4.380695653698826</v>
+      </c>
+      <c r="F27" s="48" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="28" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>Dev ex-USA ex-EMU ex-JP</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v>8.64395583810817</v>
-      </c>
-      <c r="C27" s="15" t="n">
+      <c r="B28" s="15" t="n">
+        <v>8.630887267580697</v>
+      </c>
+      <c r="C28" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="D27" s="15" t="n">
-        <v>8.64395583810817</v>
-      </c>
-      <c r="E27" s="43" t="n">
-        <v>-3.35604416189183</v>
-      </c>
-      <c r="F27" s="44" t="inlineStr">
+      <c r="D28" s="15" t="n">
+        <v>8.630887267580695</v>
+      </c>
+      <c r="E28" s="44" t="n">
+        <v>-3.369112732419305</v>
+      </c>
+      <c r="F28" s="45" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="42" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
         <is>
           <t>Per-Holding Equity Targets</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Current (% / EUR)</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>Target (% / EUR)</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Post-rebal (% / EUR)</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Delta (pp / EUR)</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="30" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
-      <c r="B31" s="15" t="n">
-        <v>22.53485961056094</v>
-      </c>
-      <c r="C31" s="15" t="n">
+      <c r="B32" s="15" t="n">
+        <v>22.5796460892919</v>
+      </c>
+      <c r="C32" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="15" t="n">
-        <v>22.53485961056094</v>
-      </c>
-      <c r="E31" s="55" t="n">
-        <v>12.53485961056094</v>
-      </c>
-      <c r="F31" s="56" t="inlineStr">
+      <c r="D32" s="15" t="n">
+        <v>22.5796460892919</v>
+      </c>
+      <c r="E32" s="59" t="n">
+        <v>12.5796460892919</v>
+      </c>
+      <c r="F32" s="57" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="34" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
-        <v>10.68097967801673</v>
-      </c>
-      <c r="C32" s="19" t="n">
+      <c r="B33" s="19" t="n">
+        <v>10.61487854286597</v>
+      </c>
+      <c r="C33" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="D32" s="19" t="n">
-        <v>10.68097967801673</v>
-      </c>
-      <c r="E32" s="46" t="n">
-        <v>-4.31902032198327</v>
-      </c>
-      <c r="F32" s="47" t="inlineStr">
+      <c r="D33" s="19" t="n">
+        <v>10.61487854286597</v>
+      </c>
+      <c r="E33" s="47" t="n">
+        <v>-4.38512145713403</v>
+      </c>
+      <c r="F33" s="48" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="30" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n">
-        <v>11.12020692273602</v>
-      </c>
-      <c r="C33" s="15" t="n">
+      <c r="B34" s="15" t="n">
+        <v>11.14741884311015</v>
+      </c>
+      <c r="C34" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="D33" s="15" t="n">
-        <v>11.12020692273602</v>
-      </c>
-      <c r="E33" s="43" t="n">
-        <v>-3.879793077263978</v>
-      </c>
-      <c r="F33" s="44" t="inlineStr">
+      <c r="D34" s="15" t="n">
+        <v>11.14741884311015</v>
+      </c>
+      <c r="E34" s="44" t="n">
+        <v>-3.852581156889855</v>
+      </c>
+      <c r="F34" s="45" t="inlineStr">
         <is>
           <t>● Drift</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="34" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
-      <c r="B34" s="19" t="n">
-        <v>13.30172035828668</v>
-      </c>
-      <c r="C34" s="19" t="n">
+      <c r="B35" s="19" t="n">
+        <v>13.2233885609825</v>
+      </c>
+      <c r="C35" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="D34" s="19" t="n">
-        <v>13.30172035828668</v>
-      </c>
-      <c r="E34" s="50" t="n">
-        <v>-1.698279641713324</v>
-      </c>
-      <c r="F34" s="51" t="inlineStr">
+      <c r="D35" s="19" t="n">
+        <v>13.2233885609825</v>
+      </c>
+      <c r="E35" s="52" t="n">
+        <v>-1.776611439017499</v>
+      </c>
+      <c r="F35" s="53" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="30" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
         <is>
           <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v>23.52367824931302</v>
-      </c>
-      <c r="C35" s="15" t="n">
+      <c r="B36" s="15" t="n">
+        <v>23.56985918781337</v>
+      </c>
+      <c r="C36" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="D35" s="15" t="n">
-        <v>23.52367824931302</v>
-      </c>
-      <c r="E35" s="48" t="n">
-        <v>-1.476321750686978</v>
-      </c>
-      <c r="F35" s="49" t="inlineStr">
+      <c r="D36" s="15" t="n">
+        <v>23.56985918781337</v>
+      </c>
+      <c r="E36" s="49" t="n">
+        <v>-1.430140812186632</v>
+      </c>
+      <c r="F36" s="50" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="34" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
-      <c r="B36" s="19" t="n">
-        <v>18.83855518108661</v>
-      </c>
-      <c r="C36" s="19" t="n">
+      <c r="B37" s="19" t="n">
+        <v>18.8648087759361</v>
+      </c>
+      <c r="C37" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="D36" s="19" t="n">
-        <v>18.83855518108661</v>
-      </c>
-      <c r="E36" s="50" t="n">
-        <v>-1.161444818913392</v>
-      </c>
-      <c r="F36" s="51" t="inlineStr">
+      <c r="D37" s="19" t="n">
+        <v>18.8648087759361</v>
+      </c>
+      <c r="E37" s="52" t="n">
+        <v>-1.135191224063895</v>
+      </c>
+      <c r="F37" s="53" t="inlineStr">
         <is>
           <t>● Aligned</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="42" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
         <is>
           <t>Per-Holding Fixed Income Targets</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>Current (% / EUR)</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>Target (% / EUR)</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>Post-rebal (% / EUR)</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Delta (pp / EUR)</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="30" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n">
+        <v>64.35947263303625</v>
+      </c>
+      <c r="C41" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>64.35947263303625</v>
+      </c>
+      <c r="E41" s="59" t="n">
+        <v>-5.640527366963752</v>
+      </c>
+      <c r="F41" s="57" t="inlineStr">
+        <is>
+          <t>● Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
-        <v>35.56172300579974</v>
-      </c>
-      <c r="C40" s="15" t="n">
+      <c r="B42" s="19" t="n">
+        <v>35.64052736696375</v>
+      </c>
+      <c r="C42" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="D40" s="15" t="n">
-        <v>35.56172300579974</v>
-      </c>
-      <c r="E40" s="55" t="n">
-        <v>5.561723005799742</v>
-      </c>
-      <c r="F40" s="56" t="inlineStr">
+      <c r="D42" s="19" t="n">
+        <v>35.64052736696375</v>
+      </c>
+      <c r="E42" s="60" t="n">
+        <v>5.640527366963745</v>
+      </c>
+      <c r="F42" s="61" t="inlineStr">
         <is>
           <t>● Action</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="34" t="inlineStr">
-        <is>
-          <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="n">
-        <v>64.43827699420027</v>
-      </c>
-      <c r="C41" s="19" t="n">
-        <v>70</v>
-      </c>
-      <c r="D41" s="19" t="n">
-        <v>64.43827699420027</v>
-      </c>
-      <c r="E41" s="57" t="n">
-        <v>-5.561723005799735</v>
-      </c>
-      <c r="F41" s="53" t="inlineStr">
-        <is>
-          <t>● Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>SOLVER PARAMETERS</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="58" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="62" t="inlineStr">
         <is>
           <t>Alert threshold</t>
         </is>
       </c>
-      <c r="B47" s="30" t="inlineStr">
+      <c r="B48" s="31" t="inlineStr">
         <is>
           <t>±2.5%</t>
         </is>
       </c>
-      <c r="G47" s="30" t="inlineStr">
+      <c r="G48" s="31" t="inlineStr">
         <is>
           <t>Deviation at which a category turns amber (green below, red beyond 2×)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="59" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="63" t="inlineStr">
         <is>
           <t>Solver tolerance</t>
         </is>
       </c>
-      <c r="B48" s="34" t="inlineStr">
+      <c r="B49" s="35" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G48" s="34" t="inlineStr">
+      <c r="G49" s="35" t="inlineStr">
         <is>
           <t>Actual tolerance the optimizer converged at (progressive up to max)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="58" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="62" t="inlineStr">
         <is>
           <t>Max tolerance</t>
         </is>
       </c>
-      <c r="B49" s="30" t="inlineStr">
+      <c r="B50" s="31" t="inlineStr">
         <is>
           <t>±2.0%</t>
         </is>
       </c>
-      <c r="G49" s="30" t="inlineStr">
+      <c r="G50" s="31" t="inlineStr">
         <is>
           <t>Cap on solver tolerance (from config.rebalancing_max_tolerance_pctg)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="59" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="63" t="inlineStr">
         <is>
           <t>Min transaction</t>
         </is>
       </c>
-      <c r="B50" s="34" t="inlineStr">
+      <c r="B51" s="35" t="inlineStr">
         <is>
           <t>0.0 EUR</t>
         </is>
       </c>
-      <c r="G50" s="34" t="inlineStr">
+      <c r="G51" s="35" t="inlineStr">
         <is>
           <t>Trades below this amount are skipped</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="58" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="62" t="inlineStr">
         <is>
           <t>Lump sum</t>
         </is>
       </c>
-      <c r="B51" s="30" t="inlineStr">
+      <c r="B52" s="31" t="inlineStr">
         <is>
           <t>1000.0 EUR</t>
         </is>
       </c>
-      <c r="G51" s="30" t="inlineStr">
+      <c r="G52" s="31" t="inlineStr">
         <is>
           <t>Additional cash to deploy in the rebalance</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="59" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="63" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Equivalents target</t>
         </is>
       </c>
-      <c r="B52" s="34" t="inlineStr">
+      <c r="B53" s="35" t="inlineStr">
         <is>
           <t>3000.0 EUR</t>
         </is>
       </c>
-      <c r="G52" s="34" t="inlineStr">
+      <c r="G53" s="35" t="inlineStr">
         <is>
           <t>Absolute cash target used by the solver (from target_cash_buffer_eur)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="58" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="62" t="inlineStr">
         <is>
           <t>No-sell mode</t>
         </is>
       </c>
-      <c r="B53" s="30" t="inlineStr">
+      <c r="B54" s="31" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="G53" s="30" t="inlineStr">
+      <c r="G54" s="31" t="inlineStr">
         <is>
           <t>If enabled, the solver can only buy, never sell</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="39" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-11 12:13 v2.0</t>
+    <row r="56">
+      <c r="A56" s="40" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-14 08:51 v2.0</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A45:G45"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2138,7 +2197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2271,17 +2330,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>VWCE.DE</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>IE00B3RBWM25</t>
         </is>
@@ -2291,161 +2350,161 @@
           <t>Equities</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F4" s="30" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G4" s="60" t="n">
+      <c r="G4" s="64" t="n">
         <v>80</v>
       </c>
-      <c r="H4" s="60" t="n">
+      <c r="H4" s="64" t="n">
         <v>128</v>
       </c>
-      <c r="I4" s="60" t="n">
-        <v>158.0599975585938</v>
-      </c>
-      <c r="J4" s="60" t="n">
+      <c r="I4" s="64" t="n">
+        <v>159.1399993896484</v>
+      </c>
+      <c r="J4" s="64" t="n">
         <v>10240</v>
       </c>
-      <c r="K4" s="60" t="n">
-        <v>12644.7998046875</v>
+      <c r="K4" s="64" t="n">
+        <v>12731.19995117188</v>
       </c>
       <c r="L4" s="15" t="n">
-        <v>15.36322634611066</v>
+        <v>15.09360259272281</v>
       </c>
       <c r="M4" s="15" t="n">
-        <v>16.35689439457653</v>
-      </c>
-      <c r="N4" s="61" t="n">
-        <v>23.52367824931302</v>
-      </c>
-      <c r="O4" s="31" t="n">
-        <v>2404.7998046875</v>
-      </c>
-      <c r="P4" s="32" t="n">
-        <v>23.48437309265137</v>
-      </c>
-      <c r="Q4" s="30" t="inlineStr">
+        <v>16.04470041839249</v>
+      </c>
+      <c r="N4" s="65" t="n">
+        <v>23.56985918781337</v>
+      </c>
+      <c r="O4" s="32" t="n">
+        <v>2491.199951171875</v>
+      </c>
+      <c r="P4" s="33" t="n">
+        <v>24.32812452316284</v>
+      </c>
+      <c r="Q4" s="31" t="inlineStr">
         <is>
           <t>USA: 62, Dev ex-USA ex-EMU ex-JP: 13, Emerging Markets: 10, Eurozone EMU: 7, Japan: 6</t>
         </is>
       </c>
-      <c r="R4" s="30" t="inlineStr">
+      <c r="R4" s="31" t="inlineStr">
         <is>
           <t>index_geo_allocation (index: FTSE All-World)</t>
         </is>
       </c>
-      <c r="S4" s="30" t="inlineStr">
+      <c r="S4" s="31" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="T4" s="30" t="inlineStr">
-        <is>
-          <t>2026-05-11 12:13</t>
+      <c r="T4" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:50</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>CNKY.L</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>IE00B52MJD48</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="E5" s="34" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F5" s="34" t="inlineStr">
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G5" s="62" t="n">
+      <c r="G5" s="66" t="n">
         <v>35</v>
       </c>
-      <c r="H5" s="62" t="n">
+      <c r="H5" s="66" t="n">
         <v>64</v>
       </c>
-      <c r="I5" s="62" t="n">
-        <v>346.0935772061348</v>
-      </c>
-      <c r="J5" s="62" t="n">
+      <c r="I5" s="66" t="n">
+        <v>348.4668241500854</v>
+      </c>
+      <c r="J5" s="66" t="n">
         <v>2240</v>
       </c>
-      <c r="K5" s="62" t="n">
-        <v>12113.27520221472</v>
+      <c r="K5" s="66" t="n">
+        <v>12196.33884525299</v>
       </c>
       <c r="L5" s="19" t="n">
-        <v>14.71743258879956</v>
+        <v>14.45949261047398</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>15.66933176606076</v>
-      </c>
-      <c r="N5" s="63" t="n">
-        <v>22.53485961056094</v>
-      </c>
-      <c r="O5" s="35" t="n">
-        <v>9873.275202214718</v>
-      </c>
-      <c r="P5" s="36" t="n">
-        <v>440.7712143845856</v>
-      </c>
-      <c r="Q5" s="34" t="inlineStr">
+        <v>15.37063306866646</v>
+      </c>
+      <c r="N5" s="67" t="n">
+        <v>22.5796460892919</v>
+      </c>
+      <c r="O5" s="36" t="n">
+        <v>9956.338845252989</v>
+      </c>
+      <c r="P5" s="37" t="n">
+        <v>444.4794127345085</v>
+      </c>
+      <c r="Q5" s="35" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="R5" s="34" t="inlineStr">
+      <c r="R5" s="35" t="inlineStr">
         <is>
           <t>yfinance_top_holdings</t>
         </is>
       </c>
-      <c r="S5" s="34" t="inlineStr">
+      <c r="S5" s="35" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="T5" s="34" t="inlineStr">
-        <is>
-          <t>2026-05-11 12:13</t>
+      <c r="T5" s="35" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:50</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>CSPX.L</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>IE00B5BMR087</t>
         </is>
@@ -2455,161 +2514,161 @@
           <t>Equities</t>
         </is>
       </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F6" s="30" t="inlineStr">
+      <c r="F6" s="31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G6" s="60" t="n">
+      <c r="G6" s="64" t="n">
         <v>15</v>
       </c>
-      <c r="H6" s="60" t="n">
+      <c r="H6" s="64" t="n">
         <v>570</v>
       </c>
-      <c r="I6" s="60" t="n">
-        <v>675.0921528222461</v>
-      </c>
-      <c r="J6" s="60" t="n">
+      <c r="I6" s="64" t="n">
+        <v>679.31858976695</v>
+      </c>
+      <c r="J6" s="64" t="n">
         <v>8550</v>
       </c>
-      <c r="K6" s="60" t="n">
-        <v>10126.38229233369</v>
+      <c r="K6" s="64" t="n">
+        <v>10189.77884650425</v>
       </c>
       <c r="L6" s="15" t="n">
-        <v>12.30338998065413</v>
+        <v>12.08059515259688</v>
       </c>
       <c r="M6" s="15" t="n">
-        <v>13.09915287811909</v>
-      </c>
-      <c r="N6" s="61" t="n">
-        <v>18.83855518108661</v>
-      </c>
-      <c r="O6" s="31" t="n">
-        <v>1576.382292333692</v>
-      </c>
-      <c r="P6" s="32" t="n">
-        <v>18.43721979337651</v>
-      </c>
-      <c r="Q6" s="30" t="inlineStr">
+        <v>12.84183341310138</v>
+      </c>
+      <c r="N6" s="65" t="n">
+        <v>18.86480877593611</v>
+      </c>
+      <c r="O6" s="32" t="n">
+        <v>1639.77884650425</v>
+      </c>
+      <c r="P6" s="33" t="n">
+        <v>19.17869995911404</v>
+      </c>
+      <c r="Q6" s="31" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R6" s="30" t="inlineStr">
+      <c r="R6" s="31" t="inlineStr">
         <is>
           <t>index_geo_allocation (index: S&amp;P 500)</t>
         </is>
       </c>
-      <c r="S6" s="30" t="inlineStr">
+      <c r="S6" s="31" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="T6" s="30" t="inlineStr">
-        <is>
-          <t>2026-05-11 12:13</t>
+      <c r="T6" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:50</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>XMME.DE</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>LU0292107645</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F7" s="34" t="inlineStr">
+      <c r="F7" s="35" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G7" s="62" t="n">
+      <c r="G7" s="66" t="n">
         <v>90</v>
       </c>
-      <c r="H7" s="62" t="n">
+      <c r="H7" s="66" t="n">
         <v>56</v>
       </c>
-      <c r="I7" s="62" t="n">
-        <v>79.44599914550781</v>
-      </c>
-      <c r="J7" s="62" t="n">
+      <c r="I7" s="66" t="n">
+        <v>79.36199951171875</v>
+      </c>
+      <c r="J7" s="66" t="n">
         <v>5040</v>
       </c>
-      <c r="K7" s="62" t="n">
-        <v>7150.139923095703</v>
+      <c r="K7" s="66" t="n">
+        <v>7142.579956054688</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>8.687303851513711</v>
+        <v>8.467957753936119</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>9.249184284053779</v>
-      </c>
-      <c r="N7" s="63" t="n">
-        <v>13.30172035828668</v>
-      </c>
-      <c r="O7" s="35" t="n">
-        <v>2110.139923095703</v>
-      </c>
-      <c r="P7" s="36" t="n">
-        <v>41.86785561697824</v>
-      </c>
-      <c r="Q7" s="34" t="inlineStr">
+        <v>9.001551782144759</v>
+      </c>
+      <c r="N7" s="67" t="n">
+        <v>13.2233885609825</v>
+      </c>
+      <c r="O7" s="36" t="n">
+        <v>2102.579956054688</v>
+      </c>
+      <c r="P7" s="37" t="n">
+        <v>41.71785627092634</v>
+      </c>
+      <c r="Q7" s="35" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="R7" s="34" t="inlineStr">
+      <c r="R7" s="35" t="inlineStr">
         <is>
           <t>index_geo_allocation (index: MSCI Emerging Markets)</t>
         </is>
       </c>
-      <c r="S7" s="34" t="inlineStr">
+      <c r="S7" s="35" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="T7" s="34" t="inlineStr">
-        <is>
-          <t>2026-05-11 12:13</t>
+      <c r="T7" s="35" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:50</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>EUNL.DE</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>IE00B4L5Y983</t>
         </is>
@@ -2619,243 +2678,243 @@
           <t>Equities</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="31" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G8" s="60" t="n">
+      <c r="G8" s="64" t="n">
         <v>50</v>
       </c>
-      <c r="H8" s="60" t="n">
+      <c r="H8" s="64" t="n">
         <v>98</v>
       </c>
-      <c r="I8" s="60" t="n">
-        <v>119.5500030517578</v>
-      </c>
-      <c r="J8" s="60" t="n">
+      <c r="I8" s="64" t="n">
+        <v>120.4250030517578</v>
+      </c>
+      <c r="J8" s="64" t="n">
         <v>4900</v>
       </c>
-      <c r="K8" s="60" t="n">
-        <v>5977.500152587891</v>
+      <c r="K8" s="64" t="n">
+        <v>6021.250152587891</v>
       </c>
       <c r="L8" s="15" t="n">
-        <v>7.262565580047815</v>
+        <v>7.138553888329098</v>
       </c>
       <c r="M8" s="15" t="n">
-        <v>7.732296299637742</v>
-      </c>
-      <c r="N8" s="61" t="n">
-        <v>11.12020692273602</v>
-      </c>
-      <c r="O8" s="31" t="n">
-        <v>1077.500152587891</v>
-      </c>
-      <c r="P8" s="32" t="n">
-        <v>21.98979903240593</v>
-      </c>
-      <c r="Q8" s="30" t="inlineStr">
+        <v>7.588377781591604</v>
+      </c>
+      <c r="N8" s="65" t="n">
+        <v>11.14741884311015</v>
+      </c>
+      <c r="O8" s="32" t="n">
+        <v>1121.250152587891</v>
+      </c>
+      <c r="P8" s="33" t="n">
+        <v>22.88265617526308</v>
+      </c>
+      <c r="Q8" s="31" t="inlineStr">
         <is>
           <t>USA: 71, Dev ex-USA ex-EMU ex-JP: 14, Eurozone EMU: 8, Japan: 6</t>
         </is>
       </c>
-      <c r="R8" s="30" t="inlineStr">
+      <c r="R8" s="31" t="inlineStr">
         <is>
           <t>index_geo_allocation (index: MSCI World)</t>
         </is>
       </c>
-      <c r="S8" s="30" t="inlineStr">
+      <c r="S8" s="31" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="T8" s="30" t="inlineStr">
-        <is>
-          <t>2026-05-11 12:13</t>
+      <c r="T8" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:50</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>VERX.DE</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>IE00B945VV12</t>
         </is>
       </c>
-      <c r="D9" s="37" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>Equity ETF</t>
         </is>
       </c>
-      <c r="F9" s="34" t="inlineStr">
+      <c r="F9" s="35" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G9" s="62" t="n">
+      <c r="G9" s="66" t="n">
         <v>120</v>
       </c>
-      <c r="H9" s="62" t="n">
+      <c r="H9" s="66" t="n">
         <v>33</v>
       </c>
-      <c r="I9" s="62" t="n">
-        <v>47.84500122070312</v>
-      </c>
-      <c r="J9" s="62" t="n">
+      <c r="I9" s="66" t="n">
+        <v>47.77999877929688</v>
+      </c>
+      <c r="J9" s="66" t="n">
         <v>3960</v>
       </c>
-      <c r="K9" s="62" t="n">
-        <v>5741.400146484375</v>
+      <c r="K9" s="66" t="n">
+        <v>5733.599853515625</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>6.975707908110472</v>
+        <v>6.79752717313129</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>7.426885148330904</v>
-      </c>
-      <c r="N9" s="63" t="n">
-        <v>10.68097967801673</v>
-      </c>
-      <c r="O9" s="35" t="n">
-        <v>1781.400146484375</v>
-      </c>
-      <c r="P9" s="36" t="n">
-        <v>44.98485218394887</v>
-      </c>
-      <c r="Q9" s="34" t="inlineStr">
+        <v>7.225861845028163</v>
+      </c>
+      <c r="N9" s="67" t="n">
+        <v>10.61487854286597</v>
+      </c>
+      <c r="O9" s="36" t="n">
+        <v>1773.599853515625</v>
+      </c>
+      <c r="P9" s="37" t="n">
+        <v>44.78787508877841</v>
+      </c>
+      <c r="Q9" s="35" t="inlineStr">
         <is>
           <t>Eurozone EMU: 64, Dev ex-USA ex-EMU ex-JP: 35</t>
         </is>
       </c>
-      <c r="R9" s="34" t="inlineStr">
+      <c r="R9" s="35" t="inlineStr">
         <is>
           <t>yfinance_top_holdings</t>
         </is>
       </c>
-      <c r="S9" s="34" t="inlineStr">
+      <c r="S9" s="35" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="T9" s="34" t="inlineStr">
-        <is>
-          <t>2026-05-11 12:13</t>
+      <c r="T9" s="35" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:50</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>IEAG.L</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>IE00B3F81R35</t>
         </is>
       </c>
-      <c r="D10" s="38" t="inlineStr">
+      <c r="D10" s="39" t="inlineStr">
         <is>
           <t>Fixed Income</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t>Bond ETF</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="31" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G10" s="60" t="n">
+      <c r="G10" s="64" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="60" t="n">
+      <c r="H10" s="64" t="n">
         <v>56</v>
       </c>
-      <c r="I10" s="60" t="n">
-        <v>107.5299987792969</v>
-      </c>
-      <c r="J10" s="60" t="n">
+      <c r="I10" s="64" t="n">
+        <v>106.870002746582</v>
+      </c>
+      <c r="J10" s="64" t="n">
         <v>5600</v>
       </c>
-      <c r="K10" s="60" t="n">
-        <v>10752.99987792969</v>
+      <c r="K10" s="64" t="n">
+        <v>10687.0002746582</v>
       </c>
       <c r="L10" s="15" t="n">
-        <v>13.06472016766079</v>
+        <v>12.67008103499016</v>
       </c>
       <c r="M10" s="15" t="n">
-        <v>13.90972464134927</v>
-      </c>
-      <c r="N10" s="64" t="n">
-        <v>64.43827699420027</v>
-      </c>
-      <c r="O10" s="31" t="n">
-        <v>5152.999877929688</v>
-      </c>
-      <c r="P10" s="32" t="n">
-        <v>92.01785496303013</v>
-      </c>
-      <c r="Q10" s="30" t="inlineStr">
+        <v>13.46846475083331</v>
+      </c>
+      <c r="N10" s="68" t="n">
+        <v>64.35947263303625</v>
+      </c>
+      <c r="O10" s="32" t="n">
+        <v>5087.000274658203</v>
+      </c>
+      <c r="P10" s="33" t="n">
+        <v>90.83929061889648</v>
+      </c>
+      <c r="Q10" s="31" t="inlineStr">
         <is>
           <t>Eurozone EMU</t>
         </is>
       </c>
-      <c r="R10" s="30" t="inlineStr">
+      <c r="R10" s="31" t="inlineStr">
         <is>
           <t>index_geo_allocation (ticker)</t>
         </is>
       </c>
-      <c r="S10" s="30" t="inlineStr">
+      <c r="S10" s="31" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="T10" s="30" t="inlineStr">
-        <is>
-          <t>2026-05-11 12:13</t>
+      <c r="T10" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:50</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>IBTM.L</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>IE00B1FZS798</t>
         </is>
@@ -2865,233 +2924,315 @@
           <t>Fixed Income</t>
         </is>
       </c>
-      <c r="E11" s="34" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>Bond ETF</t>
         </is>
       </c>
-      <c r="F11" s="34" t="inlineStr">
+      <c r="F11" s="35" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="G11" s="62" t="n">
+      <c r="G11" s="66" t="n">
         <v>40</v>
       </c>
-      <c r="H11" s="62" t="n">
+      <c r="H11" s="66" t="n">
         <v>105</v>
       </c>
-      <c r="I11" s="62" t="n">
-        <v>148.3571647852841</v>
-      </c>
-      <c r="J11" s="62" t="n">
+      <c r="I11" s="66" t="n">
+        <v>147.9542599468841</v>
+      </c>
+      <c r="J11" s="66" t="n">
         <v>4200</v>
       </c>
-      <c r="K11" s="62" t="n">
-        <v>5934.286591411364</v>
+      <c r="K11" s="66" t="n">
+        <v>5918.170397875365</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>7.210061805228829</v>
+        <v>7.01634664478934</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>7.676396667575873</v>
-      </c>
-      <c r="N11" s="65" t="n">
-        <v>35.56172300579974</v>
-      </c>
-      <c r="O11" s="35" t="n">
-        <v>1734.286591411364</v>
-      </c>
-      <c r="P11" s="36" t="n">
-        <v>41.29253789074677</v>
-      </c>
-      <c r="Q11" s="34" t="inlineStr">
+        <v>7.458469855401849</v>
+      </c>
+      <c r="N11" s="69" t="n">
+        <v>35.64052736696375</v>
+      </c>
+      <c r="O11" s="36" t="n">
+        <v>1718.170397875365</v>
+      </c>
+      <c r="P11" s="37" t="n">
+        <v>40.9088189970325</v>
+      </c>
+      <c r="Q11" s="35" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="R11" s="34" t="inlineStr">
+      <c r="R11" s="35" t="inlineStr">
         <is>
           <t>not_available</t>
         </is>
       </c>
-      <c r="S11" s="34" t="inlineStr">
+      <c r="S11" s="35" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="T11" s="34" t="inlineStr">
-        <is>
-          <t>2026-05-11 12:13</t>
+      <c r="T11" s="35" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:50</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="C12" s="30" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Equivalents</t>
         </is>
       </c>
-      <c r="E12" s="30" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t>Money Market Instrument</t>
         </is>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="31" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G12" s="60" t="n">
+      <c r="G12" s="64" t="n">
         <v>5000</v>
       </c>
-      <c r="H12" s="60" t="n">
+      <c r="H12" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="60" t="n">
+      <c r="I12" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="60" t="n">
+      <c r="J12" s="64" t="n">
         <v>5000</v>
       </c>
-      <c r="K12" s="60" t="n">
+      <c r="K12" s="64" t="n">
         <v>5000</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>6.074918774283568</v>
-      </c>
-      <c r="M12" s="30" t="inlineStr"/>
-      <c r="N12" s="66" t="n">
+        <v>5.927800462883109</v>
+      </c>
+      <c r="M12" s="31" t="inlineStr"/>
+      <c r="N12" s="70" t="n">
         <v>100</v>
       </c>
-      <c r="O12" s="31" t="n">
+      <c r="O12" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="32" t="n">
+      <c r="P12" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="30" t="inlineStr">
+      <c r="Q12" s="31" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="R12" s="30" t="inlineStr">
+      <c r="R12" s="31" t="inlineStr">
         <is>
           <t>not_available</t>
         </is>
       </c>
-      <c r="S12" s="30" t="inlineStr">
+      <c r="S12" s="31" t="inlineStr">
         <is>
           <t>input_csv (no market data)</t>
         </is>
       </c>
-      <c r="T12" s="30" t="inlineStr">
-        <is>
-          <t>2026-05-11 12:13</t>
+      <c r="T12" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:50</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>SGLD.L</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>IE00B579F325</t>
         </is>
       </c>
-      <c r="D13" s="45" t="inlineStr">
+      <c r="D13" s="46" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="E13" s="34" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>Gold ETC</t>
         </is>
       </c>
-      <c r="F13" s="34" t="inlineStr">
+      <c r="F13" s="35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G13" s="62" t="n">
+      <c r="G13" s="66" t="n">
         <v>18</v>
       </c>
-      <c r="H13" s="62" t="n">
+      <c r="H13" s="66" t="n">
         <v>245</v>
       </c>
-      <c r="I13" s="62" t="n">
-        <v>381.3801791473379</v>
-      </c>
-      <c r="J13" s="62" t="n">
+      <c r="I13" s="66" t="n">
+        <v>384.911109897499</v>
+      </c>
+      <c r="J13" s="66" t="n">
         <v>4410</v>
       </c>
-      <c r="K13" s="62" t="n">
-        <v>6864.843224652082</v>
+      <c r="K13" s="66" t="n">
+        <v>6928.399978154983</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>8.340672997590458</v>
+        <v>8.214034519509287</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>8.880133920296046</v>
-      </c>
-      <c r="N13" s="67" t="n">
+        <v>8.731628004794739</v>
+      </c>
+      <c r="N13" s="71" t="n">
         <v>100</v>
       </c>
-      <c r="O13" s="35" t="n">
-        <v>2454.843224652082</v>
-      </c>
-      <c r="P13" s="36" t="n">
-        <v>55.66537924381139</v>
-      </c>
-      <c r="Q13" s="34" t="inlineStr">
+      <c r="O13" s="36" t="n">
+        <v>2518.399978154983</v>
+      </c>
+      <c r="P13" s="37" t="n">
+        <v>57.10657546836696</v>
+      </c>
+      <c r="Q13" s="35" t="inlineStr">
         <is>
           <t>Not Available</t>
         </is>
       </c>
-      <c r="R13" s="34" t="inlineStr">
+      <c r="R13" s="35" t="inlineStr">
         <is>
           <t>not_available</t>
         </is>
       </c>
-      <c r="S13" s="34" t="inlineStr">
+      <c r="S13" s="35" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="T13" s="34" t="inlineStr">
-        <is>
-          <t>2026-05-11 12:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="39" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-11 12:13 v2.0</t>
+      <c r="T13" s="35" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>Bitwise Physical Bitcoin ETC</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>BTCE.DE</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>DE000A27Z304</t>
+        </is>
+      </c>
+      <c r="D14" s="54" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G14" s="64" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="64" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" s="64" t="n">
+        <v>60</v>
+      </c>
+      <c r="J14" s="64" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K14" s="64" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>2.134008166637919</v>
+      </c>
+      <c r="M14" s="15" t="n">
+        <v>2.268479080045248</v>
+      </c>
+      <c r="N14" s="72" t="n">
+        <v>100</v>
+      </c>
+      <c r="O14" s="32" t="n">
+        <v>300</v>
+      </c>
+      <c r="P14" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q14" s="31" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="R14" s="31" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="S14" s="31" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="T14" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-14 08:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-14 08:51 v2.0</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3141,7 +3282,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="68" t="inlineStr">
+      <c r="A2" s="73" t="inlineStr">
         <is>
           <t>Period returns (1D–5Y) and risk metrics calculated on available history per instrument (max 5 years). α/β computed vs S&amp;P 500.</t>
         </is>
@@ -3255,1685 +3396,1756 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="69" t="inlineStr">
+      <c r="A5" s="74" t="inlineStr">
         <is>
           <t>** TOTAL PORTFOLIO **</t>
         </is>
       </c>
-      <c r="B5" s="70" t="inlineStr">
+      <c r="B5" s="75" t="inlineStr">
         <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="C5" s="71" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="D5" s="72" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E5" s="72" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="F5" s="72" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="G5" s="72" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="H5" s="72" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="I5" s="72" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="J5" s="72" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="K5" s="72" t="n">
-        <v>50.97</v>
-      </c>
-      <c r="L5" s="72" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="M5" s="72" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="N5" s="72" t="n">
+      <c r="C5" s="76" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="D5" s="76" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E5" s="76" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="F5" s="76" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="G5" s="76" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="H5" s="76" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="I5" s="76" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="J5" s="76" t="n">
+        <v>51.79</v>
+      </c>
+      <c r="K5" s="76" t="n">
+        <v>50.14</v>
+      </c>
+      <c r="L5" s="76" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="M5" s="76" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="N5" s="76" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O5" s="76" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P5" s="77" t="n">
+        <v>-15.33</v>
+      </c>
+      <c r="Q5" s="77" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="R5" s="77" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="S5" s="76" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T5" s="76" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="U5" s="75" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>FTSE All-World</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Benchmark index</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="G6" s="33" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="H6" s="33" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="I6" s="33" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="J6" s="33" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="K6" s="33" t="n">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="L6" s="33" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="M6" s="33" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="N6" s="33" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O6" s="33" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P6" s="78" t="n">
+        <v>-20.22</v>
+      </c>
+      <c r="Q6" s="78" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="R6" s="78" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="S6" s="33" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="T6" s="33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U6" s="31" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>MSCI ACWI</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Benchmark index</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D7" s="37" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E7" s="37" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="F7" s="37" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="G7" s="37" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="H7" s="37" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="I7" s="37" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="J7" s="37" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="K7" s="37" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="L7" s="37" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="M7" s="37" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="N7" s="37" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="O7" s="37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P7" s="79" t="n">
+        <v>-20.07</v>
+      </c>
+      <c r="Q7" s="79" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="R7" s="79" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="S7" s="79" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="T7" s="37" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="U7" s="35" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>MSCI EAFE</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Benchmark index</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D8" s="78" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G8" s="33" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H8" s="33" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="I8" s="33" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="J8" s="33" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="K8" s="33" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="L8" s="33" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="M8" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="N8" s="33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O8" s="33" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P8" s="78" t="n">
+        <v>-17.35</v>
+      </c>
+      <c r="Q8" s="78" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="R8" s="78" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="S8" s="78" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="T8" s="33" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="U8" s="31" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>MSCI Emerging Markets</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Benchmark index</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" s="79" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E9" s="37" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="F9" s="37" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="G9" s="37" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="H9" s="37" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="I9" s="37" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="J9" s="37" t="n">
+        <v>70.48</v>
+      </c>
+      <c r="K9" s="37" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="L9" s="37" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="M9" s="37" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="N9" s="37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O9" s="37" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="P9" s="79" t="n">
+        <v>-24.81</v>
+      </c>
+      <c r="Q9" s="79" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="R9" s="79" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="S9" s="79" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="T9" s="37" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="U9" s="35" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>MSCI World</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Benchmark index</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="G10" s="33" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="H10" s="33" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="I10" s="33" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="J10" s="33" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="K10" s="33" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="L10" s="33" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="M10" s="33" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="N10" s="33" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="O10" s="33" t="n">
         <v>0.55</v>
       </c>
-      <c r="O5" s="72" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="P5" s="71" t="n">
-        <v>-13.91</v>
-      </c>
-      <c r="Q5" s="71" t="n">
+      <c r="P10" s="78" t="n">
+        <v>-20.63</v>
+      </c>
+      <c r="Q10" s="78" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="R10" s="78" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="S10" s="78" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="T10" s="33" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="U10" s="31" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>MSCI World Momentum</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Benchmark index</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="D11" s="37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E11" s="37" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F11" s="37" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="G11" s="37" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="H11" s="37" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="I11" s="37" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="J11" s="37" t="n">
+        <v>106.93</v>
+      </c>
+      <c r="K11" s="37" t="n">
+        <v>102.86</v>
+      </c>
+      <c r="L11" s="37" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="M11" s="37" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="N11" s="37" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="O11" s="37" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="P11" s="79" t="n">
+        <v>-25.91</v>
+      </c>
+      <c r="Q11" s="79" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="R11" s="79" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="S11" s="37" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="T11" s="37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U11" s="35" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>MSCI World Quality</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>Benchmark index</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="G12" s="33" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="H12" s="33" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="I12" s="33" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="J12" s="33" t="n">
+        <v>61.09</v>
+      </c>
+      <c r="K12" s="33" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="L12" s="33" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="M12" s="33" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="N12" s="33" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O12" s="33" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P12" s="78" t="n">
+        <v>-22.45</v>
+      </c>
+      <c r="Q12" s="78" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="R12" s="78" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="S12" s="78" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="T12" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" s="31" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>Nasdaq 100</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Benchmark index</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="D13" s="37" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="E13" s="37" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F13" s="37" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="G13" s="37" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="H13" s="37" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="I13" s="37" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="J13" s="37" t="n">
+        <v>102.47</v>
+      </c>
+      <c r="K13" s="37" t="n">
+        <v>125.66</v>
+      </c>
+      <c r="L13" s="37" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="M13" s="37" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="N13" s="37" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O13" s="37" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="P13" s="79" t="n">
+        <v>-31.38</v>
+      </c>
+      <c r="Q13" s="79" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="R13" s="79" t="n">
+        <v>-3.38</v>
+      </c>
+      <c r="S13" s="37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T13" s="37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U13" s="35" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>Benchmark index</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D14" s="33" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="F14" s="33" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="G14" s="33" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="H14" s="33" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="I14" s="33" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="J14" s="33" t="n">
+        <v>66.44</v>
+      </c>
+      <c r="K14" s="33" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="L14" s="33" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="M14" s="33" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="N14" s="33" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="O14" s="33" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P14" s="78" t="n">
+        <v>-23.17</v>
+      </c>
+      <c r="Q14" s="78" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="R14" s="78" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="S14" s="33" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T14" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" s="31" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="79" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E15" s="37" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F15" s="79" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="G15" s="79" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="H15" s="79" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="I15" s="37" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J15" s="37" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="K15" s="79" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="L15" s="79" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="M15" s="37" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="N15" s="79" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="O15" s="79" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="P15" s="79" t="n">
+        <v>-19.81</v>
+      </c>
+      <c r="Q15" s="79" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="R15" s="79" t="n">
         <v>-0.77</v>
       </c>
-      <c r="R5" s="71" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="S5" s="72" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="T5" s="72" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="U5" s="70" t="inlineStr">
+      <c r="S15" s="79" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="T15" s="37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U15" s="35" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>FTSE All-World</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>Benchmark index</t>
-        </is>
-      </c>
-      <c r="C6" s="32" t="n">
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E16" s="33" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="F16" s="33" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="G16" s="33" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="H16" s="33" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="I16" s="33" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="J16" s="33" t="n">
+        <v>64.73999999999999</v>
+      </c>
+      <c r="K16" s="33" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="L16" s="33" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="M16" s="33" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="N16" s="33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O16" s="33" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P16" s="78" t="n">
+        <v>-21.07</v>
+      </c>
+      <c r="Q16" s="78" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="R16" s="78" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="S16" s="33" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="T16" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U16" s="31" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="D17" s="37" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E17" s="37" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="F17" s="37" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="G17" s="37" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="H17" s="37" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="I17" s="37" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="J17" s="37" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="K17" s="37" t="n">
+        <v>81.43000000000001</v>
+      </c>
+      <c r="L17" s="37" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="M17" s="37" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="N17" s="37" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O17" s="37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P17" s="79" t="n">
+        <v>-21.73</v>
+      </c>
+      <c r="Q17" s="79" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="R17" s="79" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="S17" s="37" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="T17" s="37" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U17" s="35" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E18" s="33" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="F18" s="33" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="G18" s="33" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="H18" s="33" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="I18" s="33" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="J18" s="33" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="K18" s="33" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="L18" s="33" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="M18" s="33" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="N18" s="33" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="O18" s="33" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P18" s="78" t="n">
+        <v>-24.38</v>
+      </c>
+      <c r="Q18" s="78" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="R18" s="78" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="S18" s="33" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="T18" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U18" s="31" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C19" s="79" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="D19" s="79" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E19" s="79" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="F19" s="79" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G19" s="79" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="H19" s="79" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="I19" s="79" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="J19" s="79" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="K19" s="79" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="L19" s="79" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="M19" s="37" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="N19" s="79" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="O19" s="79" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="P19" s="79" t="n">
+        <v>-15.77</v>
+      </c>
+      <c r="Q19" s="79" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="R19" s="79" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="S19" s="79" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="T19" s="79" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U19" s="35" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E20" s="33" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="F20" s="33" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="G20" s="33" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="H20" s="33" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="I20" s="33" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="J20" s="33" t="n">
+        <v>71.81</v>
+      </c>
+      <c r="K20" s="33" t="n">
+        <v>94.37</v>
+      </c>
+      <c r="L20" s="33" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="M20" s="33" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="N20" s="33" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O20" s="33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P20" s="78" t="n">
+        <v>-22.73</v>
+      </c>
+      <c r="Q20" s="78" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="R20" s="78" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="S20" s="33" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="T20" s="33" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="U20" s="31" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>Invesco Physical Gold ETC</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C21" s="37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="D21" s="79" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E21" s="79" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="F21" s="79" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="G21" s="37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H21" s="37" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="I21" s="37" t="n">
+        <v>36.44</v>
+      </c>
+      <c r="J21" s="37" t="n">
+        <v>114.46</v>
+      </c>
+      <c r="K21" s="37" t="n">
+        <v>161.12</v>
+      </c>
+      <c r="L21" s="37" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="M21" s="37" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="N21" s="37" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O21" s="37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P21" s="79" t="n">
+        <v>-15.94</v>
+      </c>
+      <c r="Q21" s="79" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="R21" s="79" t="n">
+        <v>-2.57</v>
+      </c>
+      <c r="S21" s="37" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="T21" s="37" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U21" s="35" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>Bitwise Physical Bitcoin ETC</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C22" s="78" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="D22" s="78" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="E22" s="33" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F22" s="33" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="G22" s="78" t="n">
+        <v>-19.88</v>
+      </c>
+      <c r="H22" s="78" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="I22" s="78" t="n">
+        <v>-28.45</v>
+      </c>
+      <c r="J22" s="33" t="n">
+        <v>152.63</v>
+      </c>
+      <c r="K22" s="33" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="L22" s="33" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="M22" s="33" t="n">
+        <v>54</v>
+      </c>
+      <c r="N22" s="33" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O22" s="33" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="P22" s="78" t="n">
+        <v>-74.62</v>
+      </c>
+      <c r="Q22" s="78" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="R22" s="78" t="n">
+        <v>-7.53</v>
+      </c>
+      <c r="S22" s="33" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="T22" s="33" t="n">
         <v>0.04</v>
       </c>
-      <c r="D6" s="32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E6" s="32" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="F6" s="32" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="G6" s="32" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="H6" s="32" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="I6" s="32" t="n">
-        <v>22.98</v>
-      </c>
-      <c r="J6" s="32" t="n">
-        <v>64.45</v>
-      </c>
-      <c r="K6" s="32" t="n">
-        <v>78.22</v>
-      </c>
-      <c r="L6" s="32" t="n">
-        <v>12.04</v>
-      </c>
-      <c r="M6" s="32" t="n">
-        <v>14.13</v>
-      </c>
-      <c r="N6" s="32" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="O6" s="32" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="P6" s="73" t="n">
-        <v>-20.22</v>
-      </c>
-      <c r="Q6" s="73" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="R6" s="73" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="S6" s="32" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="T6" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U6" s="30" t="inlineStr">
+      <c r="U22" s="31" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t>MSCI ACWI</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>Benchmark index</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D7" s="36" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E7" s="36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F7" s="36" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="G7" s="36" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="H7" s="36" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I7" s="36" t="n">
-        <v>21.92</v>
-      </c>
-      <c r="J7" s="36" t="n">
-        <v>57.96</v>
-      </c>
-      <c r="K7" s="36" t="n">
-        <v>66.18000000000001</v>
-      </c>
-      <c r="L7" s="36" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="M7" s="36" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="N7" s="36" t="n">
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D23" s="79" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="E23" s="37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F23" s="79" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G23" s="37" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="H23" s="37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I23" s="37" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="J23" s="37" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="K23" s="37" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="L23" s="37" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="M23" s="37" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="N23" s="37" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O23" s="37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P23" s="79" t="n">
+        <v>-22.86</v>
+      </c>
+      <c r="Q23" s="79" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="R23" s="79" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="S23" s="37" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="T23" s="37" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U23" s="35" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>In portfolio</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E24" s="33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F24" s="33" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G24" s="33" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="H24" s="33" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="I24" s="33" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="J24" s="33" t="n">
+        <v>75.79000000000001</v>
+      </c>
+      <c r="K24" s="33" t="n">
+        <v>70.06999999999999</v>
+      </c>
+      <c r="L24" s="33" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="M24" s="33" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="N24" s="33" t="n">
         <v>0.42</v>
       </c>
-      <c r="O7" s="36" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="P7" s="74" t="n">
-        <v>-20.07</v>
-      </c>
-      <c r="Q7" s="74" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="R7" s="74" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="S7" s="74" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="T7" s="36" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="U7" s="34" t="inlineStr">
+      <c r="O24" s="33" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P24" s="78" t="n">
+        <v>-21.24</v>
+      </c>
+      <c r="Q24" s="78" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="R24" s="78" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="S24" s="33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T24" s="33" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="U24" s="31" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>MSCI EAFE</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>Benchmark index</t>
-        </is>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="D8" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E8" s="32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F8" s="32" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="G8" s="32" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H8" s="32" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I8" s="32" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J8" s="32" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="K8" s="32" t="n">
-        <v>57.13</v>
-      </c>
-      <c r="L8" s="32" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="M8" s="32" t="n">
-        <v>18.04</v>
-      </c>
-      <c r="N8" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O8" s="32" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P8" s="73" t="n">
-        <v>-17.35</v>
-      </c>
-      <c r="Q8" s="73" t="n">
-        <v>-1.63</v>
-      </c>
-      <c r="R8" s="73" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="S8" s="73" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="T8" s="32" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="U8" s="30" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>MSCI Emerging Markets</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>Benchmark index</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="D9" s="36" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="E9" s="36" t="n">
-        <v>11.98</v>
-      </c>
-      <c r="F9" s="36" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="G9" s="36" t="n">
-        <v>22.16</v>
-      </c>
-      <c r="H9" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="I9" s="36" t="n">
-        <v>50.32</v>
-      </c>
-      <c r="J9" s="36" t="n">
-        <v>75.06</v>
-      </c>
-      <c r="K9" s="36" t="n">
-        <v>47.12</v>
-      </c>
-      <c r="L9" s="36" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="M9" s="36" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="N9" s="36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O9" s="36" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="P9" s="74" t="n">
-        <v>-24.81</v>
-      </c>
-      <c r="Q9" s="74" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="R9" s="74" t="n">
-        <v>-2.71</v>
-      </c>
-      <c r="S9" s="74" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="T9" s="36" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="U9" s="34" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>MSCI World</t>
-        </is>
-      </c>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>Benchmark index</t>
-        </is>
-      </c>
-      <c r="C10" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D10" s="32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="E10" s="32" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="F10" s="32" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="G10" s="32" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="H10" s="32" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="I10" s="32" t="n">
-        <v>19.58</v>
-      </c>
-      <c r="J10" s="32" t="n">
-        <v>56.91</v>
-      </c>
-      <c r="K10" s="32" t="n">
-        <v>70.54000000000001</v>
-      </c>
-      <c r="L10" s="32" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="M10" s="32" t="n">
-        <v>16.47</v>
-      </c>
-      <c r="N10" s="32" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="O10" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="P10" s="73" t="n">
-        <v>-20.63</v>
-      </c>
-      <c r="Q10" s="73" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="R10" s="73" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="S10" s="73" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="T10" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="U10" s="30" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>MSCI World Momentum</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>Benchmark index</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="E11" s="36" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="F11" s="36" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="G11" s="36" t="n">
-        <v>17.98</v>
-      </c>
-      <c r="H11" s="36" t="n">
-        <v>19.72</v>
-      </c>
-      <c r="I11" s="36" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="J11" s="36" t="n">
-        <v>107.07</v>
-      </c>
-      <c r="K11" s="36" t="n">
-        <v>100.97</v>
-      </c>
-      <c r="L11" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="M11" s="36" t="n">
-        <v>22.01</v>
-      </c>
-      <c r="N11" s="36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O11" s="36" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="P11" s="74" t="n">
-        <v>-25.91</v>
-      </c>
-      <c r="Q11" s="74" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="R11" s="74" t="n">
-        <v>-3.13</v>
-      </c>
-      <c r="S11" s="36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T11" s="36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="U11" s="34" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>MSCI World Quality</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>Benchmark index</t>
-        </is>
-      </c>
-      <c r="C12" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D12" s="32" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E12" s="32" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="F12" s="32" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="G12" s="32" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="H12" s="32" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="I12" s="32" t="n">
-        <v>19.44</v>
-      </c>
-      <c r="J12" s="32" t="n">
-        <v>64.31999999999999</v>
-      </c>
-      <c r="K12" s="32" t="n">
-        <v>80.17</v>
-      </c>
-      <c r="L12" s="32" t="n">
-        <v>12.51</v>
-      </c>
-      <c r="M12" s="32" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N12" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O12" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="P12" s="73" t="n">
-        <v>-22.45</v>
-      </c>
-      <c r="Q12" s="73" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="R12" s="73" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="S12" s="73" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="T12" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" s="30" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="34" t="inlineStr">
-        <is>
-          <t>Nasdaq 100</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>Benchmark index</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="E13" s="36" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="F13" s="36" t="n">
-        <v>16.63</v>
-      </c>
-      <c r="G13" s="36" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="H13" s="36" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="I13" s="36" t="n">
-        <v>40.43</v>
-      </c>
-      <c r="J13" s="36" t="n">
-        <v>107.58</v>
-      </c>
-      <c r="K13" s="36" t="n">
-        <v>126.48</v>
-      </c>
-      <c r="L13" s="36" t="n">
-        <v>17.79</v>
-      </c>
-      <c r="M13" s="36" t="n">
-        <v>23.88</v>
-      </c>
-      <c r="N13" s="36" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="O13" s="36" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="P13" s="74" t="n">
-        <v>-31.38</v>
-      </c>
-      <c r="Q13" s="74" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="R13" s="74" t="n">
-        <v>-3.39</v>
-      </c>
-      <c r="S13" s="36" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T13" s="36" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="U13" s="34" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>Benchmark index</t>
-        </is>
-      </c>
-      <c r="C14" s="32" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="D14" s="32" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E14" s="32" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="F14" s="32" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="G14" s="32" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="H14" s="32" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="I14" s="32" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="J14" s="32" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="K14" s="32" t="n">
-        <v>82.81999999999999</v>
-      </c>
-      <c r="L14" s="32" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="M14" s="32" t="n">
-        <v>18.55</v>
-      </c>
-      <c r="N14" s="32" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="O14" s="32" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="P14" s="73" t="n">
-        <v>-23.17</v>
-      </c>
-      <c r="Q14" s="73" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="R14" s="73" t="n">
-        <v>-2.64</v>
-      </c>
-      <c r="S14" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" s="30" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C15" s="74" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="D15" s="36" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E15" s="74" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F15" s="74" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="G15" s="74" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="H15" s="36" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I15" s="36" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="J15" s="36" t="n">
-        <v>8.869999999999999</v>
-      </c>
-      <c r="K15" s="74" t="n">
-        <v>-8.17</v>
-      </c>
-      <c r="L15" s="74" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="M15" s="36" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="N15" s="74" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="O15" s="74" t="n">
-        <v>-1.58</v>
-      </c>
-      <c r="P15" s="74" t="n">
-        <v>-19.81</v>
-      </c>
-      <c r="Q15" s="74" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="R15" s="74" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="S15" s="74" t="n">
-        <v>-5.84</v>
-      </c>
-      <c r="T15" s="36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U15" s="34" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="30" t="inlineStr">
-        <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
-        </is>
-      </c>
-      <c r="B16" s="30" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C16" s="73" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="D16" s="32" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="E16" s="32" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="F16" s="32" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="G16" s="32" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="H16" s="32" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="I16" s="32" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="J16" s="32" t="n">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="K16" s="32" t="n">
-        <v>77.86</v>
-      </c>
-      <c r="L16" s="32" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="M16" s="32" t="n">
-        <v>13.77</v>
-      </c>
-      <c r="N16" s="32" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="O16" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P16" s="73" t="n">
-        <v>-21.07</v>
-      </c>
-      <c r="Q16" s="73" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="R16" s="73" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="S16" s="32" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="T16" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U16" s="30" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E17" s="36" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="F17" s="36" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="G17" s="36" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="H17" s="36" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="I17" s="36" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="J17" s="36" t="n">
-        <v>63.24</v>
-      </c>
-      <c r="K17" s="36" t="n">
-        <v>82.09</v>
-      </c>
-      <c r="L17" s="36" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="M17" s="36" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N17" s="36" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="O17" s="36" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="P17" s="74" t="n">
-        <v>-21.73</v>
-      </c>
-      <c r="Q17" s="74" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="R17" s="74" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="S17" s="36" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="T17" s="36" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="U17" s="34" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C18" s="73" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="D18" s="32" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="E18" s="32" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="F18" s="32" t="n">
-        <v>12.68</v>
-      </c>
-      <c r="G18" s="32" t="n">
-        <v>21.63</v>
-      </c>
-      <c r="H18" s="32" t="n">
-        <v>21.12</v>
-      </c>
-      <c r="I18" s="32" t="n">
-        <v>42.83</v>
-      </c>
-      <c r="J18" s="32" t="n">
-        <v>76.41</v>
-      </c>
-      <c r="K18" s="32" t="n">
-        <v>53.16</v>
-      </c>
-      <c r="L18" s="32" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="M18" s="32" t="n">
-        <v>18.84</v>
-      </c>
-      <c r="N18" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O18" s="32" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="P18" s="73" t="n">
-        <v>-24.38</v>
-      </c>
-      <c r="Q18" s="73" t="n">
-        <v>-1.58</v>
-      </c>
-      <c r="R18" s="73" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="S18" s="32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T18" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U18" s="30" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C19" s="74" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="D19" s="36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E19" s="36" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="F19" s="36" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="G19" s="36" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="H19" s="36" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="I19" s="36" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="J19" s="36" t="n">
-        <v>72.12</v>
-      </c>
-      <c r="K19" s="36" t="n">
-        <v>97.52</v>
-      </c>
-      <c r="L19" s="36" t="n">
-        <v>14.28</v>
-      </c>
-      <c r="M19" s="36" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="N19" s="36" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O19" s="36" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="P19" s="74" t="n">
-        <v>-22.73</v>
-      </c>
-      <c r="Q19" s="74" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="R19" s="74" t="n">
-        <v>-2.53</v>
-      </c>
-      <c r="S19" s="36" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="T19" s="36" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="U19" s="34" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
-        </is>
-      </c>
-      <c r="B20" s="30" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C20" s="73" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="D20" s="73" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="E20" s="73" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="F20" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G20" s="73" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="H20" s="73" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="I20" s="73" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="J20" s="73" t="n">
-        <v>-1.82</v>
-      </c>
-      <c r="K20" s="73" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="L20" s="73" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="M20" s="32" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="N20" s="73" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="O20" s="73" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="P20" s="73" t="n">
-        <v>-15.77</v>
-      </c>
-      <c r="Q20" s="73" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="R20" s="73" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="S20" s="73" t="n">
-        <v>-3.92</v>
-      </c>
-      <c r="T20" s="73" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="U20" s="30" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>Invesco Physical Gold ETC</t>
-        </is>
-      </c>
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C21" s="74" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="D21" s="36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E21" s="74" t="n">
-        <v>-1.77</v>
-      </c>
-      <c r="F21" s="74" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="G21" s="36" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="H21" s="36" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="I21" s="36" t="n">
-        <v>37.36</v>
-      </c>
-      <c r="J21" s="36" t="n">
-        <v>114.25</v>
-      </c>
-      <c r="K21" s="36" t="n">
-        <v>162.35</v>
-      </c>
-      <c r="L21" s="36" t="n">
-        <v>21.16</v>
-      </c>
-      <c r="M21" s="36" t="n">
-        <v>17.93</v>
-      </c>
-      <c r="N21" s="36" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="O21" s="36" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P21" s="74" t="n">
-        <v>-15.94</v>
-      </c>
-      <c r="Q21" s="74" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="R21" s="74" t="n">
-        <v>-2.57</v>
-      </c>
-      <c r="S21" s="36" t="n">
-        <v>16.53</v>
-      </c>
-      <c r="T21" s="36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U21" s="34" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
-        </is>
-      </c>
-      <c r="B22" s="30" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C22" s="73" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="D22" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E22" s="32" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="F22" s="32" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="G22" s="32" t="n">
-        <v>19.04</v>
-      </c>
-      <c r="H22" s="32" t="n">
-        <v>23.67</v>
-      </c>
-      <c r="I22" s="32" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="J22" s="32" t="n">
-        <v>74.78</v>
-      </c>
-      <c r="K22" s="32" t="n">
-        <v>70.06</v>
-      </c>
-      <c r="L22" s="32" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="M22" s="32" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="N22" s="32" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="O22" s="32" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="P22" s="73" t="n">
-        <v>-21.24</v>
-      </c>
-      <c r="Q22" s="73" t="n">
-        <v>-1.77</v>
-      </c>
-      <c r="R22" s="73" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="S22" s="32" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="T22" s="32" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="U22" s="30" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="34" t="inlineStr">
-        <is>
-          <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
-        </is>
-      </c>
-      <c r="B23" s="34" t="inlineStr">
-        <is>
-          <t>In portfolio</t>
-        </is>
-      </c>
-      <c r="C23" s="74" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="D23" s="36" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E23" s="36" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="F23" s="74" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="G23" s="36" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="H23" s="36" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="I23" s="36" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="J23" s="36" t="n">
-        <v>41.72</v>
-      </c>
-      <c r="K23" s="36" t="n">
-        <v>58.37</v>
-      </c>
-      <c r="L23" s="36" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="M23" s="36" t="n">
-        <v>14.97</v>
-      </c>
-      <c r="N23" s="36" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O23" s="36" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="P23" s="74" t="n">
-        <v>-22.86</v>
-      </c>
-      <c r="Q23" s="74" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="R23" s="74" t="n">
-        <v>-2.22</v>
-      </c>
-      <c r="S23" s="36" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="T23" s="36" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="U23" s="34" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="75" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="80" t="inlineStr">
         <is>
           <t>Legend — Rating Thresholds</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>● Strong</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>● Fair</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>● Weak</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="30" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>CAGR</t>
         </is>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B29" s="31" t="inlineStr">
         <is>
           <t>&gt; 7.0%</t>
         </is>
       </c>
-      <c r="C28" s="30" t="inlineStr">
+      <c r="C29" s="31" t="inlineStr">
         <is>
           <t>3.0% – 7.0%</t>
         </is>
       </c>
-      <c r="D28" s="30" t="inlineStr">
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>&lt; 3.0%</t>
         </is>
       </c>
-      <c r="E28" s="30" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>Equity risk premium (Dimson et al.)</t>
         </is>
       </c>
-      <c r="F28" s="30" t="inlineStr">
+      <c r="F29" s="31" t="inlineStr">
         <is>
           <t>Compound Annual Growth Rate. The single yearly return that, if repeated every year, would grow your portfolio from start to end value. Accounts for compounding. ~7% is the long-term global equity average.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="34" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>α (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>&gt; 0.0%</t>
         </is>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C30" s="35" t="inlineStr">
         <is>
           <t>-1.0% – 0.0%</t>
         </is>
       </c>
-      <c r="D29" s="34" t="inlineStr">
+      <c r="D30" s="35" t="inlineStr">
         <is>
           <t>&lt; -1.0%</t>
         </is>
       </c>
-      <c r="E29" s="34" t="inlineStr">
+      <c r="E30" s="35" t="inlineStr">
         <is>
           <t>Jensen's Alpha (CAPM)</t>
         </is>
       </c>
-      <c r="F29" s="34" t="inlineStr">
+      <c r="F30" s="35" t="inlineStr">
         <is>
           <t>Extra annual return vs the benchmark, after adjusting for how risky the portfolio is (CAPM). Positive = you beat the market beyond what your risk alone justified. Negative = you underperformed after fees and noise.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>β (vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>&lt; 0.7</t>
         </is>
       </c>
-      <c r="C30" s="30" t="inlineStr">
+      <c r="C31" s="31" t="inlineStr">
         <is>
           <t>1.0 – 0.7</t>
         </is>
       </c>
-      <c r="D30" s="30" t="inlineStr">
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>&gt; 1.0</t>
         </is>
       </c>
-      <c r="E30" s="30" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>CAPM, 1.0 = market</t>
         </is>
       </c>
-      <c r="F30" s="30" t="inlineStr">
+      <c r="F31" s="31" t="inlineStr">
         <is>
           <t>How much your portfolio moves when the benchmark moves 1%. β=1 in line, β=0.5 half as reactive, β=1.5 amplifies by 50%, β≈0 uncorrelated. Tells you how much systematic market risk you're running.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>Max DD</t>
         </is>
       </c>
-      <c r="B31" s="34" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>&lt; 15.0%</t>
         </is>
       </c>
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C32" s="35" t="inlineStr">
         <is>
           <t>30.0% – 15.0%</t>
         </is>
       </c>
-      <c r="D31" s="34" t="inlineStr">
+      <c r="D32" s="35" t="inlineStr">
         <is>
           <t>&gt; 30.0%</t>
         </is>
       </c>
-      <c r="E31" s="34" t="inlineStr">
+      <c r="E32" s="35" t="inlineStr">
         <is>
           <t>Retail drawdown tolerance</t>
         </is>
       </c>
-      <c r="F31" s="34" t="inlineStr">
+      <c r="F32" s="35" t="inlineStr">
         <is>
           <t>Maximum Drawdown. Worst peak-to-trough loss over the period — the most painful scenario an investor lived through. -20% is typical for diversified equity; deeper drops signal concentration or high volatility.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="30" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B33" s="31" t="inlineStr">
         <is>
           <t>&lt; 10.0%</t>
         </is>
       </c>
-      <c r="C32" s="30" t="inlineStr">
+      <c r="C33" s="31" t="inlineStr">
         <is>
           <t>18.0% – 10.0%</t>
         </is>
       </c>
-      <c r="D32" s="30" t="inlineStr">
+      <c r="D33" s="31" t="inlineStr">
         <is>
           <t>&gt; 18.0%</t>
         </is>
       </c>
-      <c r="E32" s="30" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>Hist. equity vol ~15%</t>
         </is>
       </c>
-      <c r="F32" s="30" t="inlineStr">
+      <c r="F33" s="31" t="inlineStr">
         <is>
           <t>How bumpy the ride is. Annualized standard deviation of daily returns. A 15% vol means ~±15% year-to-year noise around the average return. Equity indexes ~15–20%, bonds ~3–7%.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="34" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="B33" s="34" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>&gt; 1.0</t>
         </is>
       </c>
-      <c r="C33" s="34" t="inlineStr">
+      <c r="C34" s="35" t="inlineStr">
         <is>
           <t>0.5 – 1.0</t>
         </is>
       </c>
-      <c r="D33" s="34" t="inlineStr">
+      <c r="D34" s="35" t="inlineStr">
         <is>
           <t>&lt; 0.5</t>
         </is>
       </c>
-      <c r="E33" s="34" t="inlineStr">
+      <c r="E34" s="35" t="inlineStr">
         <is>
           <t>Sharpe (1994)</t>
         </is>
       </c>
-      <c r="F33" s="34" t="inlineStr">
+      <c r="F34" s="35" t="inlineStr">
         <is>
           <t>Return per unit of risk taken: (CAGR − risk-free rate) / Volatility. Above 1 is good, above 2 is excellent, negative means you were paid less than a safe bond for the risk you ran.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="30" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>Sortino</t>
         </is>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>&gt; 1.5</t>
         </is>
       </c>
-      <c r="C34" s="30" t="inlineStr">
+      <c r="C35" s="31" t="inlineStr">
         <is>
           <t>0.7 – 1.5</t>
         </is>
       </c>
-      <c r="D34" s="30" t="inlineStr">
+      <c r="D35" s="31" t="inlineStr">
         <is>
           <t>&lt; 0.7</t>
         </is>
       </c>
-      <c r="E34" s="30" t="inlineStr">
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>Sortino &amp; Price (1994)</t>
         </is>
       </c>
-      <c r="F34" s="30" t="inlineStr">
+      <c r="F35" s="31" t="inlineStr">
         <is>
           <t>Like Sharpe but only penalizes downside volatility (ignores upside swings). More honest when returns are asymmetric. Usually higher than Sharpe — the gap shows how much of your volatility is actually good volatility.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="34" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>VaR 95%</t>
         </is>
       </c>
-      <c r="B35" s="34" t="inlineStr">
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>&lt; 0.8%</t>
         </is>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C36" s="35" t="inlineStr">
         <is>
           <t>1.5% – 0.8%</t>
         </is>
       </c>
-      <c r="D35" s="34" t="inlineStr">
+      <c r="D36" s="35" t="inlineStr">
         <is>
           <t>&gt; 1.5%</t>
         </is>
       </c>
-      <c r="E35" s="34" t="inlineStr">
+      <c r="E36" s="35" t="inlineStr">
         <is>
           <t>Basel III (retail adj.)</t>
         </is>
       </c>
-      <c r="F35" s="34" t="inlineStr">
+      <c r="F36" s="35" t="inlineStr">
         <is>
           <t>Value at Risk. The daily loss exceeded only 5% of the time (historical simulation). A VaR of -1.2% means on an average month you should expect about one day worse than -1.2%. Non-parametric: no normal-distribution assumption.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="30" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t>CVaR 95%</t>
         </is>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>&lt; 1.2%</t>
         </is>
       </c>
-      <c r="C36" s="30" t="inlineStr">
+      <c r="C37" s="31" t="inlineStr">
         <is>
           <t>2.0% – 1.2%</t>
         </is>
       </c>
-      <c r="D36" s="30" t="inlineStr">
+      <c r="D37" s="31" t="inlineStr">
         <is>
           <t>&gt; 2.0%</t>
         </is>
       </c>
-      <c r="E36" s="30" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>Artzner et al. (1999)</t>
         </is>
       </c>
-      <c r="F36" s="30" t="inlineStr">
+      <c r="F37" s="31" t="inlineStr">
         <is>
           <t>Conditional VaR, a.k.a. Expected Shortfall. The average loss on the worst 5% of days. Always more negative than VaR. Captures tail risk VaR misses — how bad it really gets when it goes bad.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="39" t="inlineStr">
-        <is>
-          <t>Generated 2026-05-11 12:13 v2.0</t>
+    <row r="40">
+      <c r="A40" s="40" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-14 08:51 v2.0</t>
         </is>
       </c>
     </row>
@@ -4952,7 +5164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4973,7 +5185,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="75" t="inlineStr">
+      <c r="A3" s="80" t="inlineStr">
         <is>
           <t>Return Contribution by Holding</t>
         </is>
@@ -5012,445 +5224,487 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Nikkei 225 ETF JPY Acc</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>IE00B52MJD48</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>CNKY.L</t>
         </is>
       </c>
-      <c r="D5" s="32" t="n">
-        <v>14.71743258879956</v>
-      </c>
-      <c r="E5" s="32" t="n">
-        <v>440.7712143845856</v>
-      </c>
-      <c r="F5" s="32" t="n">
-        <v>64.87020634788456</v>
+      <c r="D5" s="33" t="n">
+        <v>14.45949261047398</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>444.4794127345085</v>
+      </c>
+      <c r="F5" s="33" t="n">
+        <v>64.26946783942439</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>iShares € Aggregate Bond ESG SRI UCITS ETF EUR (Dist)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>IE00B3F81R35</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>IEAG.L</t>
         </is>
       </c>
-      <c r="D6" s="36" t="n">
-        <v>13.06472016766079</v>
-      </c>
-      <c r="E6" s="36" t="n">
-        <v>92.01785496303013</v>
-      </c>
-      <c r="F6" s="36" t="n">
-        <v>12.02187525520386</v>
+      <c r="D6" s="37" t="n">
+        <v>12.67008103499016</v>
+      </c>
+      <c r="E6" s="37" t="n">
+        <v>90.83929061889648</v>
+      </c>
+      <c r="F6" s="37" t="n">
+        <v>11.5094117330244</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>IE00B579F325</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>SGLD.L</t>
         </is>
       </c>
-      <c r="D7" s="32" t="n">
-        <v>8.340672997590458</v>
-      </c>
-      <c r="E7" s="32" t="n">
-        <v>55.66537924381139</v>
-      </c>
-      <c r="F7" s="32" t="n">
-        <v>4.642867255594901</v>
+      <c r="D7" s="33" t="n">
+        <v>8.214034519509287</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>57.10657546836696</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>4.690753821881285</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>IE00B3RBWM25</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>VWCE.DE</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>15.09360259272281</v>
+      </c>
+      <c r="E8" s="37" t="n">
+        <v>24.32812452316284</v>
+      </c>
+      <c r="F8" s="37" t="n">
+        <v>3.67199043378894</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>LU0292107645</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>XMME.DE</t>
         </is>
       </c>
-      <c r="D8" s="36" t="n">
-        <v>8.687303851513711</v>
-      </c>
-      <c r="E8" s="36" t="n">
-        <v>41.86785561697824</v>
-      </c>
-      <c r="F8" s="36" t="n">
-        <v>3.63718783355995</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>IE00B3RBWM25</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>VWCE.DE</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="n">
-        <v>15.36322634611066</v>
-      </c>
-      <c r="E9" s="32" t="n">
-        <v>23.48437309265137</v>
-      </c>
-      <c r="F9" s="32" t="n">
-        <v>3.607957394189137</v>
+      <c r="D9" s="33" t="n">
+        <v>8.467957753936119</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>41.71785627092634</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>3.532650444869832</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>Vanguard FTSE Developed Europe ex UK UCITS ETF Distributing</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>IE00B945VV12</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>VERX.DE</t>
         </is>
       </c>
-      <c r="D10" s="36" t="n">
-        <v>6.975707908110472</v>
-      </c>
-      <c r="E10" s="36" t="n">
-        <v>44.98485218394887</v>
-      </c>
-      <c r="F10" s="36" t="n">
-        <v>3.138011891247527</v>
+      <c r="D10" s="37" t="n">
+        <v>6.79752717313129</v>
+      </c>
+      <c r="E10" s="37" t="n">
+        <v>44.78787508877841</v>
+      </c>
+      <c r="F10" s="37" t="n">
+        <v>3.044467979427813</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>iShares $ Treasury Bond 7-10yr UCITS ETF USD (Dist)</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>IE00B1FZS798</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>IBTM.L</t>
         </is>
       </c>
-      <c r="D11" s="32" t="n">
-        <v>7.210061805228829</v>
-      </c>
-      <c r="E11" s="32" t="n">
-        <v>41.29253789074677</v>
-      </c>
-      <c r="F11" s="32" t="n">
-        <v>2.977217502870375</v>
+      <c r="D11" s="33" t="n">
+        <v>7.01634664478934</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>40.9088189970325</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>2.870304549121234</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>iShares VII PLC - iShares Core S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>IE00B5BMR087</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>CSPX.L</t>
         </is>
       </c>
-      <c r="D12" s="36" t="n">
-        <v>12.30338998065413</v>
-      </c>
-      <c r="E12" s="36" t="n">
-        <v>18.43721979337651</v>
-      </c>
-      <c r="F12" s="36" t="n">
-        <v>2.268403052769465</v>
+      <c r="D12" s="37" t="n">
+        <v>12.08059515259688</v>
+      </c>
+      <c r="E12" s="37" t="n">
+        <v>19.17869995911404</v>
+      </c>
+      <c r="F12" s="37" t="n">
+        <v>2.316901097591831</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>IE00B4L5Y983</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>EUNL.DE</t>
         </is>
       </c>
-      <c r="D13" s="32" t="n">
-        <v>7.262565580047815</v>
-      </c>
-      <c r="E13" s="32" t="n">
-        <v>21.98979903240593</v>
-      </c>
-      <c r="F13" s="32" t="n">
-        <v>1.597023575649201</v>
+      <c r="D13" s="33" t="n">
+        <v>7.138553888329098</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>22.88265617526308</v>
+      </c>
+      <c r="F13" s="33" t="n">
+        <v>1.633490742152221</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>Bitwise Physical Bitcoin ETC</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>DE000A27Z304</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>BTCE.DE</t>
+        </is>
+      </c>
+      <c r="D14" s="37" t="n">
+        <v>2.134008166637919</v>
+      </c>
+      <c r="E14" s="37" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="37" t="n">
+        <v>0.4268016333275838</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>CASH-EUR</t>
         </is>
       </c>
-      <c r="D14" s="36" t="n">
-        <v>6.074918774283568</v>
-      </c>
-      <c r="E14" s="36" t="n">
+      <c r="D15" s="33" t="n">
+        <v>5.927800462883109</v>
+      </c>
+      <c r="E15" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="36" t="n">
+      <c r="F15" s="33" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="75" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="80" t="inlineStr">
         <is>
           <t>Breakdown by Asset Class</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Asset Class</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Total Value</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Avg Gain %</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t># Holdings</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Equities</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n">
-        <v>53753.49752140388</v>
-      </c>
-      <c r="C18" s="32" t="n">
-        <v>98.58921901732442</v>
-      </c>
-      <c r="D18" s="30" t="n">
+      <c r="B19" s="32" t="n">
+        <v>54014.74760508732</v>
+      </c>
+      <c r="C19" s="33" t="n">
+        <v>99.56243745862552</v>
+      </c>
+      <c r="D19" s="31" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Fixed Income</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>16687.28646934105</v>
-      </c>
-      <c r="C19" s="36" t="n">
-        <v>66.65519642688845</v>
-      </c>
-      <c r="D19" s="34" t="n">
+      <c r="B20" s="36" t="n">
+        <v>16605.17067253357</v>
+      </c>
+      <c r="C20" s="37" t="n">
+        <v>65.87405480796448</v>
+      </c>
+      <c r="D20" s="35" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="B20" s="31" t="n">
-        <v>6864.843224652082</v>
-      </c>
-      <c r="C20" s="32" t="n">
-        <v>55.66537924381139</v>
-      </c>
-      <c r="D20" s="30" t="n">
+      <c r="B21" s="32" t="n">
+        <v>6928.399978154983</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>57.10657546836696</v>
+      </c>
+      <c r="D21" s="31" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C22" s="37" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" s="35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Equivalents</t>
         </is>
       </c>
-      <c r="B21" s="35" t="n">
+      <c r="B23" s="32" t="n">
         <v>5000</v>
       </c>
-      <c r="C21" s="36" t="n">
+      <c r="C23" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="34" t="n">
+      <c r="D23" s="31" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="75" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="80" t="inlineStr">
         <is>
           <t>Breakdown by Geography (Equity Only)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Weight % (within Equity)</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>Avg Gain %</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B25" s="32" t="n">
-        <v>41.37833258340725</v>
-      </c>
-      <c r="C25" s="32" t="n">
-        <v>21.30379730614461</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="76" t="inlineStr">
+      <c r="B27" s="33" t="n">
+        <v>41.45266796122517</v>
+      </c>
+      <c r="C27" s="33" t="n">
+        <v>22.12982688584665</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="55" t="inlineStr">
         <is>
           <t>Emerging Markets</t>
         </is>
       </c>
-      <c r="B26" s="36" t="n">
-        <v>15.68231659711715</v>
-      </c>
-      <c r="C26" s="36" t="n">
-        <v>32.6761143548148</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="38" t="inlineStr">
+      <c r="B28" s="37" t="n">
+        <v>15.60865831078922</v>
+      </c>
+      <c r="C28" s="37" t="n">
+        <v>33.02299039704459</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
         <is>
           <t>Eurozone EMU</t>
         </is>
       </c>
-      <c r="B27" s="32" t="n">
-        <v>9.656154540849686</v>
-      </c>
-      <c r="C27" s="32" t="n">
-        <v>30.15300810300205</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="B29" s="33" t="n">
+        <v>9.619304346301179</v>
+      </c>
+      <c r="C29" s="33" t="n">
+        <v>30.66621859573478</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B28" s="36" t="n">
-        <v>24.63924044051774</v>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>162.0817955032143</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="B30" s="37" t="n">
+        <v>24.68848211410375</v>
+      </c>
+      <c r="C30" s="37" t="n">
+        <v>163.8967311443115</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>Dev ex-USA ex-EMU ex-JP</t>
         </is>
       </c>
-      <c r="B29" s="32" t="n">
-        <v>8.64395583810817</v>
-      </c>
-      <c r="C29" s="32" t="n">
-        <v>30.15300810300205</v>
+      <c r="B31" s="33" t="n">
+        <v>8.630887267580697</v>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>30.66621859573478</v>
       </c>
     </row>
   </sheetData>
